--- a/contratos.xlsx
+++ b/contratos.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7fb4d173-0b6b-461c-b96a-62443e97b31a/LaudoA01-Bemol-2026-AlicilaneBorgesPinheiroNascimento_signed.pdf?expires_on=1785434314&amp;signature=bgg1fRvWDmIEzySHtjot%2FmIfpChGvP8hmOYztnq8AQc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7fb4d173-0b6b-461c-b96a-62443e97b31a/LaudoA01-Bemol-2026-AlicilaneBorgesPinheiroNascimento_signed.pdf?expires_on=1785434474&amp;signature=Nhu6rvLgFhPC24h6lkcE9jCp0ITYMAUm6LN6EIjRReg%3D</t>
         </is>
       </c>
       <c r="V2">
@@ -832,7 +832,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/66b67508-5546-4905-acdc-5d85735deb8e/LaudoB36-2026-BEMOL-ABDIASSIMIAODESOUZAFILHO.pdf?expires_on=1785434314&amp;signature=YkvYuMASedNFJhpyPMUCLrhgh%2FDmUOpPJer%2BwRSeS3k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/66b67508-5546-4905-acdc-5d85735deb8e/LaudoB36-2026-BEMOL-ABDIASSIMIAODESOUZAFILHO.pdf?expires_on=1785434474&amp;signature=3seWHAsNoOiegZ%2FY5z6HpP7t6r7ZurLgspv6Of0g%2B9o%3D</t>
         </is>
       </c>
       <c r="V3">
@@ -961,7 +961,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c64cc402-2d06-47a7-a8d4-8d6d316b9654/Laudo72-Bemol-2026-AdamiltonSenaDosSantos-Ajustado-Assinado.pdf?expires_on=1785434314&amp;signature=3FhfVxSxFlnxbJGE382v%2BH3q10g7DhBKi4LHFdZNAn8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c64cc402-2d06-47a7-a8d4-8d6d316b9654/Laudo72-Bemol-2026-AdamiltonSenaDosSantos-Ajustado-Assinado.pdf?expires_on=1785434474&amp;signature=p0PKtwKFCR%2F8qsu8hrASfcZdFRVFQMBOlnSkBCrSJuA%3D</t>
         </is>
       </c>
       <c r="V4">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/28f3f575-1d5a-4e86-ad32-c81591e8b666/Laudo214-Bemol-2026-AdecildaBatistaMartins.pdf?expires_on=1785434314&amp;signature=njMKMDYqvZ7TTjdNO8aogjV%2FqnWUl%2BFatr%2FdDkqnt38%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/28f3f575-1d5a-4e86-ad32-c81591e8b666/Laudo214-Bemol-2026-AdecildaBatistaMartins.pdf?expires_on=1785434474&amp;signature=8HXLxmbUwwlPtyUOq8GHPs1hQD8rXEC1CyWa7ypQw%2Fg%3D</t>
         </is>
       </c>
       <c r="V5">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/007f511d-a50e-4f56-8bc0-d55bf3536e2a/LaudoR05-2026-BEMOL-AdelinoChavesDeSouza.pdf?expires_on=1785434314&amp;signature=Xfn%2F8CIRIPgDJR5ugqpnRVzy1bQdRTToKJdX4Z50X%2BA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/007f511d-a50e-4f56-8bc0-d55bf3536e2a/LaudoR05-2026-BEMOL-AdelinoChavesDeSouza.pdf?expires_on=1785434474&amp;signature=utvf%2B7xr36Z1mizFEJpp4UurICex%2BYGDX8fF4Et%2B0pI%3D</t>
         </is>
       </c>
       <c r="V6">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4c7e9ab9-04ab-4035-b58f-e9d7c51050a0/LaudoITA20-Bemol-2026-AdemardosSantoslima.pdf?expires_on=1785434314&amp;signature=78sZU%2B8v7GA8D3DeRr5HQiJhAlsvicLW%2BhE%2BnfSqvy4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4c7e9ab9-04ab-4035-b58f-e9d7c51050a0/LaudoITA20-Bemol-2026-AdemardosSantoslima.pdf?expires_on=1785434474&amp;signature=BNGKPcGLCiVvlTEqniltLeRxs%2B6Lix1ayNlA1LvsLZw%3D</t>
         </is>
       </c>
       <c r="V7">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2ed10a7b-df53-4f57-889d-f247e65f45e0/BEMOL-PV074-ADRIELGEOVANEDINIZLOPES.pdf?expires_on=1785434314&amp;signature=lP0PBjj9ORURXwxHf0a5mjfZbxOnoRiUCVVTfnngRmI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2ed10a7b-df53-4f57-889d-f247e65f45e0/BEMOL-PV074-ADRIELGEOVANEDINIZLOPES.pdf?expires_on=1785434474&amp;signature=WMnM574kcs5y%2F5lHjGJr0Id%2BDlSqmm01CxwpOEGv%2FkE%3D</t>
         </is>
       </c>
       <c r="V8">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf495517-b334-42ed-8ad8-1436aedcf87b/LaudoB26-2026-BEMOL-ALAIRESGOMESDASILVA.pdf?expires_on=1785434314&amp;signature=nqAKcaEDI%2BVSUU2VzGWbRTlLB0o8fUF%2BpT6bTrcvPM0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf495517-b334-42ed-8ad8-1436aedcf87b/LaudoB26-2026-BEMOL-ALAIRESGOMESDASILVA.pdf?expires_on=1785434474&amp;signature=yED7y1Oxj6mg860VihXQJG1ATEEhRbB%2BIuN1hyK55gQ%3D</t>
         </is>
       </c>
       <c r="V9">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d7df2939-a94a-467e-b7eb-ecca8304cf47/Laudo_AC_17-2026_-_ALCILENE_DE_PAULA_MARTINS_assinado.pdf?expires_on=1785434314&amp;signature=CYla9vwdNo44nDlR5KF5swgk93YJTMPqV6c39MzZxVg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d7df2939-a94a-467e-b7eb-ecca8304cf47/Laudo_AC_17-2026_-_ALCILENE_DE_PAULA_MARTINS_assinado.pdf?expires_on=1785434474&amp;signature=qxrOS7u1lGw7z5xOVts2WJO8nWdnxypFjB2ZnsVdWm0%3D</t>
         </is>
       </c>
       <c r="V10">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6622b85e-a02d-4f58-aa43-4aba7096b139/Laudo204-Bemol-2026-AlcioneBarbosadaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=dp27RMlzM4kzCBMlrYuH8C4Gkqwjmc0MNY%2BaqvAyAbw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6622b85e-a02d-4f58-aa43-4aba7096b139/Laudo204-Bemol-2026-AlcioneBarbosadaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=%2BkWDetnfFFhfGdg09ykaxBwD%2FrEO0Bg5SGU5BVpTs8s%3D</t>
         </is>
       </c>
       <c r="V11">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4f7398f0-8d1f-42d6-9060-4d6315bcbd49/Laudo131-Bemol-2026-AldoReisDeAraujoLucenaJunior.pdf?expires_on=1785434314&amp;signature=Q06aB9mQ06BCnQVOEL9MmPMF1ByE2ffqIgAGoffCwdI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4f7398f0-8d1f-42d6-9060-4d6315bcbd49/Laudo131-Bemol-2026-AldoReisDeAraujoLucenaJunior.pdf?expires_on=1785434474&amp;signature=RXCxUxvDnX5UW6LMOu8czK5ov%2F9brfYVvVAU76yHuzI%3D</t>
         </is>
       </c>
       <c r="V12">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4c25e1f6-3188-4ad8-aa5d-55a018fdef0c/LaudoB52-2026-BEMOL-ALESSANDRAAZEVEDOMACHADO.pdf?expires_on=1785434314&amp;signature=r3d9DZHbbaPktgNdBxUDGFCL8nPBMClRKsjddtdPQGM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4c25e1f6-3188-4ad8-aa5d-55a018fdef0c/LaudoB52-2026-BEMOL-ALESSANDRAAZEVEDOMACHADO.pdf?expires_on=1785434474&amp;signature=fXaJSRRo%2BZzrY0LyzB2zlwAH9Y0ME9T1Y5WJFtzdUSg%3D</t>
         </is>
       </c>
       <c r="V13">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/11642d66-cefc-4048-8b08-d1d694e52a90/Laudo121-Bemol-2026-AlessandroPereiraNeves-Assinado.pdf?expires_on=1785434314&amp;signature=sJRii5gGRoG7r9cEYl7X2oYSXVT1qVwgWdb2xcav0LQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/11642d66-cefc-4048-8b08-d1d694e52a90/Laudo121-Bemol-2026-AlessandroPereiraNeves-Assinado.pdf?expires_on=1785434474&amp;signature=hVvLCZPUxnwXIQ6gj42%2B%2FhbkPy0OEQoNP6hBUrutpEw%3D</t>
         </is>
       </c>
       <c r="V14">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/21646528-58cb-4dc7-bd86-dbc8bec22b62/LAUDOALEXANDREBATISTAajustado.pdf?expires_on=1785434314&amp;signature=cS68T4XOP0WwRQqf3U%2F4HLv9s9UvT8X0Yn5vGqOzJI0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/21646528-58cb-4dc7-bd86-dbc8bec22b62/LAUDOALEXANDREBATISTAajustado.pdf?expires_on=1785434474&amp;signature=O4jA%2BJ4K%2F8cNbWkDLFPQQOfIeHgDyb5ZDUnBshTQQ6U%3D</t>
         </is>
       </c>
       <c r="V15">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0bd12d7c-5f4d-4f99-ad05-3148b07a3fa2/Laudo155-Bemol-2026-AlexandreMedinaNoronha-Assinado.pdf?expires_on=1785434314&amp;signature=WNb%2BGcoI%2BdhIX%2FonSrLWcU6sbDikaWuxrZWjJm%2BrkqM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0bd12d7c-5f4d-4f99-ad05-3148b07a3fa2/Laudo155-Bemol-2026-AlexandreMedinaNoronha-Assinado.pdf?expires_on=1785434474&amp;signature=Njpx7zlsCOWOO5%2BraCmUAehkfu0bUqQE%2FWnkbLnyUeI%3D</t>
         </is>
       </c>
       <c r="V16">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c5df5341-74e8-4b47-9a72-4b1e7f9a236e/Laudo462-Bemol-2025-AlexsandroCarneiroCapote-Assinado.pdf?expires_on=1785434314&amp;signature=tIRH7YnulbDsh5X7bvnReyFkT%2BpKyaALeaWoO7S8Eac%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c5df5341-74e8-4b47-9a72-4b1e7f9a236e/Laudo462-Bemol-2025-AlexsandroCarneiroCapote-Assinado.pdf?expires_on=1785434474&amp;signature=DYhDTfCIF%2BUIFX8sNpKZQUtQwlB3OjS0Q096zStcWnQ%3D</t>
         </is>
       </c>
       <c r="V17">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a7bccc3a-8cae-407c-b16c-944931f134be/BEMOL-PV091-ALEXSANDRODASILVACHAGAS.pdf?expires_on=1785434314&amp;signature=ZANCJICCrgkW%2Fxz3vUI23p08Of%2Be0F0Zf838Ef3Iiu8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a7bccc3a-8cae-407c-b16c-944931f134be/BEMOL-PV091-ALEXSANDRODASILVACHAGAS.pdf?expires_on=1785434474&amp;signature=1wBoQr52epxQtPBkdm0IEzeIP8JNlz3GWn%2BB41h2DSs%3D</t>
         </is>
       </c>
       <c r="V18">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ec2f8020-e636-4ee4-a818-ab6ba5513c9f/LaudoBRT01-Bemol-2026-AlineSilvaRodrigues_signed.pdf?expires_on=1785434314&amp;signature=tcnP8GEagaJDcJIKbmSCvIBpZcoNAAM%2BZs%2Fkflgygmg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ec2f8020-e636-4ee4-a818-ab6ba5513c9f/LaudoBRT01-Bemol-2026-AlineSilvaRodrigues_signed.pdf?expires_on=1785434474&amp;signature=MRltNONe1ZR13FE8WxB9MUOY2c9IZPZcWpn8nK0tU64%3D</t>
         </is>
       </c>
       <c r="V19">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b7143741-9582-4509-af2b-f1331879e859/Laudo47-Bemol-2026-AlinyLeite-Assinado.pdf?expires_on=1785434314&amp;signature=g0UMaNzs9tlMM0KecI9UhAqcTJ8R%2FQj8frVNgu3yGkU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b7143741-9582-4509-af2b-f1331879e859/Laudo47-Bemol-2026-AlinyLeite-Assinado.pdf?expires_on=1785434474&amp;signature=Q2gP0Z5VmQBg3GGfh26OFTSKWZ80fbY0yj%2BKk7iCerE%3D</t>
         </is>
       </c>
       <c r="V20">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a26d2b4-76c4-4c49-a38c-f8bdc3c83919/LaudoB24-2026-BEMOL-ALTAMIROPEREIRADASILVA_2corrigido.pdf?expires_on=1785434314&amp;signature=%2BVcgVxe%2BA%2BL1FG9ZWYLcvT2H%2FcfjRimyRfitRvmPmI0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a26d2b4-76c4-4c49-a38c-f8bdc3c83919/LaudoB24-2026-BEMOL-ALTAMIROPEREIRADASILVA_2corrigido.pdf?expires_on=1785434474&amp;signature=JFggJ1YdVOdLuOC5wamuQS78GoQ4vLRKeT8wCstvbl4%3D</t>
         </is>
       </c>
       <c r="V21">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/29e682ce-6607-46f7-a12d-e06a2d8dcd18/LaudoJP08-Bemol-2026-AlzenirFreire_signed.pdf?expires_on=1785434314&amp;signature=DGH1wlVCbq65RHLoX65CsuRo3SFfxTeEaOr%2FFhnLwDA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/29e682ce-6607-46f7-a12d-e06a2d8dcd18/LaudoJP08-Bemol-2026-AlzenirFreire_signed.pdf?expires_on=1785434474&amp;signature=09m0ijhXSSqECINoWwHoASrMgklq1tKZj5UmCOP0v3I%3D</t>
         </is>
       </c>
       <c r="V22">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0b88abaf-3393-4d08-86bb-e7551aa40e79/Laudo_AC_19-2026_-_ROSEANE_IDALINA_DE_FREITAS_assinado.pdf?expires_on=1785434314&amp;signature=YtJhg0eVZLMNdhiGpMJk3pvTYU4Ehj9GmlFUB2lCat0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0b88abaf-3393-4d08-86bb-e7551aa40e79/Laudo_AC_19-2026_-_ROSEANE_IDALINA_DE_FREITAS_assinado.pdf?expires_on=1785434474&amp;signature=Z0lCgQjIHiU97zsrJrox0yha38wGkQtr3A9cn7ygT9s%3D</t>
         </is>
       </c>
       <c r="V23">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/360cfb85-8c70-4b37-bf95-eafd6a4cd2f1/BEMOL-PV076-AMARILDOJUNIORCORTEZDESOUZA.pdf?expires_on=1785434314&amp;signature=AbiQnDtUmvU%2BI3RKi3y5QovWnA3dhfGNWBJJ9of%2F1%2Bk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/360cfb85-8c70-4b37-bf95-eafd6a4cd2f1/BEMOL-PV076-AMARILDOJUNIORCORTEZDESOUZA.pdf?expires_on=1785434474&amp;signature=xIuDX7Pi%2BriBKxwmBhrRO9qslONaNpxHuYP8SlJcSGQ%3D</t>
         </is>
       </c>
       <c r="V24">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1f94317e-a38b-482f-a0e4-955c796831df/Laudo126-Bemol-2026-AmauryCezarMenezesCavalcante-Assinado.pdf?expires_on=1785434314&amp;signature=fS0%2BH%2BP%2Fj1CdNZOnn8p52s4jzjzGNBWurn8%2FF1yIvCg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1f94317e-a38b-482f-a0e4-955c796831df/Laudo126-Bemol-2026-AmauryCezarMenezesCavalcante-Assinado.pdf?expires_on=1785434474&amp;signature=%2FTibs%2F24MFSoWAfgTvnU%2BRL0tmifMwN70mij9oUP%2Bp8%3D</t>
         </is>
       </c>
       <c r="V25">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5f9e9ec0-64d0-4bf9-8a65-58ac51a05454/LAUDOANACAMILA.pdf?expires_on=1785434314&amp;signature=St5F%2Bfpl%2B0RCcsAVFT97NNBcUiRZ7QHbFfeG2nQJPqo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5f9e9ec0-64d0-4bf9-8a65-58ac51a05454/LAUDOANACAMILA.pdf?expires_on=1785434474&amp;signature=KR7JdvEelhVtf1lPIZLJIahyU9pEFrho%2FyeomUc8bWU%3D</t>
         </is>
       </c>
       <c r="V26">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b530c704-d818-489a-9000-ce31d7ad0322/Laudo78-Bemol-2026-AnaCeciliaPereiraSilveiraLima.pdf?expires_on=1785434314&amp;signature=cNzpbT8RY8NgrDBBcOAy4EJ%2B9ZBoJrAdA95gQsua%2BaE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b530c704-d818-489a-9000-ce31d7ad0322/Laudo78-Bemol-2026-AnaCeciliaPereiraSilveiraLima.pdf?expires_on=1785434474&amp;signature=dL91240dZCI578PV7O%2BiSChgfSqbjtld4EWwpWS2hIo%3D</t>
         </is>
       </c>
       <c r="V27">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b8465407-ab08-4f67-af8f-ed0d03ae4011/Laudo91-Bemol-2026-AnaCristinaAzulayCardosoSoares-Assinado.pdf?expires_on=1785434314&amp;signature=o%2FdCd3zlgniglstq7LIKk6%2FIRQUjqS9F8CnsE9W1Fu0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b8465407-ab08-4f67-af8f-ed0d03ae4011/Laudo91-Bemol-2026-AnaCristinaAzulayCardosoSoares-Assinado.pdf?expires_on=1785434474&amp;signature=QuIF%2F8zN48PPBKlHkNUxR6VwBRlnJLaNmKt1XDghcNw%3D</t>
         </is>
       </c>
       <c r="V28">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/64fef612-4cec-4eaf-91a7-e811c9e2f740/BEMOL-JP038-ANALUCIASILVADEJESUS.pdf?expires_on=1785434314&amp;signature=UtAVSeP0c%2FiGXnyVbuf9cFgD5wyiB5mWdMXTZpQFaYg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/64fef612-4cec-4eaf-91a7-e811c9e2f740/BEMOL-JP038-ANALUCIASILVADEJESUS.pdf?expires_on=1785434474&amp;signature=YXZhAt3zryRrEvXln7i%2BX698%2Brbs4q8tmtOtfH6FwxA%3D</t>
         </is>
       </c>
       <c r="V29">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3458991a-dae2-4c8f-a75c-030be3f7330d/Laudo35-Bemol-2026-AnaLuciaSousaDaSilva-assinado-ajustado.pdf?expires_on=1785434314&amp;signature=j%2FouKExLKjDFrqQ6TelUILreSfnQH%2B80bbkxPB8Yf9k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3458991a-dae2-4c8f-a75c-030be3f7330d/Laudo35-Bemol-2026-AnaLuciaSousaDaSilva-assinado-ajustado.pdf?expires_on=1785434474&amp;signature=qidjo4lv8oZK8NefdtsqEorXUXunCsPkXfhQV%2FVTfmQ%3D</t>
         </is>
       </c>
       <c r="V30">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/83193c81-cbef-42a4-b6e8-da9ed23d74b5/Laudo161-Bemol-2026-AnaMaraVieiraDosSantos-Assinado.pdf?expires_on=1785434314&amp;signature=am9psWiTmeO2aOny3QEM18lpQmICLsTA9kk1UtDIyCM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/83193c81-cbef-42a4-b6e8-da9ed23d74b5/Laudo161-Bemol-2026-AnaMaraVieiraDosSantos-Assinado.pdf?expires_on=1785434474&amp;signature=c07NZHc%2B6Xu6B0LZ9QUgLfqyjmeTuVpq%2FGB3OSLSHCs%3D</t>
         </is>
       </c>
       <c r="V31">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/454108b6-dede-46a6-be10-ec0a5377199a/M02-2026-AnaMarciaSantosMacielajustado.pdf?expires_on=1785434314&amp;signature=bWzOBK%2FWGVOaTezEbWsZYpq01vsOAIAPp%2B1HaDrkpJ8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/454108b6-dede-46a6-be10-ec0a5377199a/M02-2026-AnaMarciaSantosMacielajustado.pdf?expires_on=1785434474&amp;signature=A8%2FnoBxLnFCW%2FofozlCLqfbXtn4Ezl6VweVXGkzOEZY%3D</t>
         </is>
       </c>
       <c r="V32">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d468c22b-1ac0-4333-acb1-4e848898420b/Laudo183-Bemol-2026-AnaMariadaSilvaMoraes-Assinado.pdf?expires_on=1785434314&amp;signature=F3%2F89U6Msa7Bm4Acd516uvd7Ec9PALEyGTH8MqFY%2BLk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d468c22b-1ac0-4333-acb1-4e848898420b/Laudo183-Bemol-2026-AnaMariadaSilvaMoraes-Assinado.pdf?expires_on=1785434474&amp;signature=uQsghV7Y4EKcMGdDPuoI1NPYfKY4zokEx11d9szqqo4%3D</t>
         </is>
       </c>
       <c r="V33">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f58e04e2-d303-4ee1-8f5e-c361252c5994/LAUDOANAPAULAAMORIN.pdf?expires_on=1785434314&amp;signature=WndE0ZymhgVz7MiVWPwyfOHdxeq0fqWabxCnj204oYE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f58e04e2-d303-4ee1-8f5e-c361252c5994/LAUDOANAPAULAAMORIN.pdf?expires_on=1785434474&amp;signature=2%2BJuGy2ajJs%2BVK6KkguddVshwD3Tp8%2BGfc9PhRrBHhY%3D</t>
         </is>
       </c>
       <c r="V34">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b4faed57-f07c-4b7e-a1ec-06f5c6967038/LaudoB51-2026-BEMOL-AnaPaulaCoelhodaSilva.pdf?expires_on=1785434314&amp;signature=zVxQBrrglCA8REOGJTuQUEkOAygOpcxkgsdyo48%2Fw20%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b4faed57-f07c-4b7e-a1ec-06f5c6967038/LaudoB51-2026-BEMOL-AnaPaulaCoelhodaSilva.pdf?expires_on=1785434474&amp;signature=0ceR3RGiRxcNTSbjh4AK6ChkkcmnLxU%2BIuke0LLYBqs%3D</t>
         </is>
       </c>
       <c r="V35">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/07f9e40d-4fae-4b74-b002-9c105d003d96/LaudoP04-Bemol-2026-AnaPaulaFortesDaSilvaFerreira_signed.pdf?expires_on=1785434314&amp;signature=JrVWD2YdNXZFPsZFJUCaZMGwnvMeLcDXSmwczb1MxWY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/07f9e40d-4fae-4b74-b002-9c105d003d96/LaudoP04-Bemol-2026-AnaPaulaFortesDaSilvaFerreira_signed.pdf?expires_on=1785434474&amp;signature=RLAZQ7WqE8J4UfV4DqtHFvAxCz6ZdzWRntPXf57%2FgU8%3D</t>
         </is>
       </c>
       <c r="V36">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/150f97b8-750e-4816-a503-3f030bc41231/LaudoMAN06-Bemol-2026-AnazioPirangadaSilva.pdf?expires_on=1785434314&amp;signature=iIj4ouDn%2BlT5exeJ786Ep158HGJuMPTeSj2SPrP3oBg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/150f97b8-750e-4816-a503-3f030bc41231/LaudoMAN06-Bemol-2026-AnazioPirangadaSilva.pdf?expires_on=1785434474&amp;signature=mtskFn1pvu1Vvocco8vaylI5GxHCH7YM%2F4BuAh7SDho%3D</t>
         </is>
       </c>
       <c r="V37">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/58745fa5-7f1e-4632-b9db-619b07fb06a0/Laudo194-Bemol-2026-AnderclicydaSilvaAraujo.pdf?expires_on=1785434314&amp;signature=VDycZ2TMu14KCngHAkaGcAscWPzgwY0wNxXSYfhnnzA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/58745fa5-7f1e-4632-b9db-619b07fb06a0/Laudo194-Bemol-2026-AnderclicydaSilvaAraujo.pdf?expires_on=1785434474&amp;signature=M0utq8rqOMzrK8rhspAlF0radxqWdyRNFFZlwJnRZVg%3D</t>
         </is>
       </c>
       <c r="V38">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cee94394-328f-4b94-bee9-bbf5d9c9939e/Laudo111-Bemol-2026-AndreiaRodriguesRibeiroAndrade.pdf?expires_on=1785434314&amp;signature=DI7n8dhTMDNSwYIbqU8%2B3t7a10RzatZj%2F8g8O%2BQ%2BZh4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cee94394-328f-4b94-bee9-bbf5d9c9939e/Laudo111-Bemol-2026-AndreiaRodriguesRibeiroAndrade.pdf?expires_on=1785434474&amp;signature=7ZVUmC95TFLc1KN3ND7N%2FiCTdzE9Tbhnv%2FtOUfgK2Ks%3D</t>
         </is>
       </c>
       <c r="V39">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e2aa1510-0364-40ee-bd4a-67e2d5e116c3/Laudo165-Bemol-2026-AndrezaLimaMota-Assinado.pdf?expires_on=1785434314&amp;signature=WFYasV7RPLq3xeCIUO0SpngbBQcJyUVoXMSUj2nsBgI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e2aa1510-0364-40ee-bd4a-67e2d5e116c3/Laudo165-Bemol-2026-AndrezaLimaMota-Assinado.pdf?expires_on=1785434474&amp;signature=okwcB44qw7ODcABQpWQIbb%2BW5DTZ%2BeOgZH2%2FmSJv8oE%3D</t>
         </is>
       </c>
       <c r="V40">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/68882f52-8495-4cb1-bebf-e8dae87d1f86/LAUDOCORRIGIDOANDREZZADESOUSAMARIALVA.pdf?expires_on=1785434314&amp;signature=en3BFw7sTTe67S70oHjk8yElGOp4UnQ%2BhKrPJQgILII%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/68882f52-8495-4cb1-bebf-e8dae87d1f86/LAUDOCORRIGIDOANDREZZADESOUSAMARIALVA.pdf?expires_on=1785434474&amp;signature=7fc63vTXox3MrlvDuMdL0jLu7wOSrPT8IXoPunYUjp0%3D</t>
         </is>
       </c>
       <c r="V41">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8cf8037a-f95b-4c30-90b6-82ac5cd0a25e/Laudo107-Bemol-2026-AneCarolinedosSantosSilva-Assinado.pdf?expires_on=1785434314&amp;signature=v2hCiZ17qnImfY9UFaOulTbqstMyn45N3elPqbG9W88%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8cf8037a-f95b-4c30-90b6-82ac5cd0a25e/Laudo107-Bemol-2026-AneCarolinedosSantosSilva-Assinado.pdf?expires_on=1785434474&amp;signature=GW07kBTa5c8%2BnIeGPZAHRtH4XeT03AKP9t%2B5kBBubLo%3D</t>
         </is>
       </c>
       <c r="V42">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8b724798-462d-40bc-ab0b-0dcf8179109b/LAUDOANGELAMARIAcorrigido.pdf?expires_on=1785434314&amp;signature=JYSYwx4Uo%2Bb8fiUaB7%2Bb7g3%2FFTEY9rkRw7Bq6WuEABc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8b724798-462d-40bc-ab0b-0dcf8179109b/LAUDOANGELAMARIAcorrigido.pdf?expires_on=1785434474&amp;signature=%2FeqAdvYPPkSF2za52t8fpa%2FOuHDmQZarDqMKw6Z%2FN1w%3D</t>
         </is>
       </c>
       <c r="V43">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f9e14e1e-f280-4a43-9a64-94dd20275c3e/Laudo129-Bemol-2026-AnneCarolinePadronRocha.pdf?expires_on=1785434314&amp;signature=VUf1Z4%2FSnrQ3Dxu%2FLMr%2BReZeESlUeLZUhEbAuA209o8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f9e14e1e-f280-4a43-9a64-94dd20275c3e/Laudo129-Bemol-2026-AnneCarolinePadronRocha.pdf?expires_on=1785434474&amp;signature=dHh5OeoFsbyFoM1VjeJnxCo%2BjiQj8v04amG4bQvY7xQ%3D</t>
         </is>
       </c>
       <c r="V44">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/54a0dd7f-fea8-4d1b-bc26-3ca986081c2a/Laudo_AC_23-2026_-_ANTONIA_SUELI_BRAZ_FONSECA_assinado.pdf?expires_on=1785434314&amp;signature=Q8tfBFpQnZC4cYQuK12l8SvQWMqgyIhBjj9Fh0PKruU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/54a0dd7f-fea8-4d1b-bc26-3ca986081c2a/Laudo_AC_23-2026_-_ANTONIA_SUELI_BRAZ_FONSECA_assinado.pdf?expires_on=1785434474&amp;signature=bsr7iabR7OB4GtBkZ5uPNfR5SOWvz2J%2FCvZIySCqOuI%3D</t>
         </is>
       </c>
       <c r="V45">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/83a953a8-c9ee-42e3-a99f-17fb29197818/LaudoB1-2026-BEMOL-ANTONIADASILVABEZERRA.pdf?expires_on=1785434314&amp;signature=ZGpjwgg%2BsazxfX75dmRileRi498u4fksOnBJaXODZh0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/83a953a8-c9ee-42e3-a99f-17fb29197818/LaudoB1-2026-BEMOL-ANTONIADASILVABEZERRA.pdf?expires_on=1785434474&amp;signature=UQsmb2uF8t1ZRnm3umaUT%2Bo1ZTh3KTDPPzaKexigVis%3D</t>
         </is>
       </c>
       <c r="V46">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/98e7eb46-c27e-43c7-a3c7-69fbe8f42055/Laudo480-Bemol-2025-AntonioAugustinhoDaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=uC8uA4di5tIgjdMNgtql%2FnNGSOgQRHOeKv0GVlJLqFo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/98e7eb46-c27e-43c7-a3c7-69fbe8f42055/Laudo480-Bemol-2025-AntonioAugustinhoDaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=H2gYN0kWqrzDn5S3OWZukUY52UIc4xbhN%2BVL3NHwy2o%3D</t>
         </is>
       </c>
       <c r="V47">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d223f792-5416-4201-acfb-ad428f0f989f/LAUDOANTONIO.pdf?expires_on=1785434314&amp;signature=gaV5TLUzVCv5Em9tP3r9PsIz87KwV0xK8N%2B7TTGCmCI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d223f792-5416-4201-acfb-ad428f0f989f/LAUDOANTONIO.pdf?expires_on=1785434474&amp;signature=yrKkahmAFQpF7tDwWe44n7O0Vvr3i5sqPl1PHk8AWdY%3D</t>
         </is>
       </c>
       <c r="V48">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3b18d347-7f8e-4239-9b1a-ed2ef9ea9280/BEMOL-PV079-ANTONIOCARLOSPONTESSILVAnovomodelo.pdf?expires_on=1785434314&amp;signature=%2Bcji%2BeWWctE%2BUaVIL2OWb87A8joZMPMXULHKVDMqidg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3b18d347-7f8e-4239-9b1a-ed2ef9ea9280/BEMOL-PV079-ANTONIOCARLOSPONTESSILVAnovomodelo.pdf?expires_on=1785434474&amp;signature=MUoIu3GEw9Ud%2BjH3sKY6b%2B1ehax1KihrNkOF%2B1J2X5M%3D</t>
         </is>
       </c>
       <c r="V49">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/07b55276-2e98-4927-84ee-b47cd386d90e/LAUDOANTONIOFLOREScorrigido.pdf?expires_on=1785434314&amp;signature=o2%2Fy26SsKoAWi9DJEcyryHAMTNuiWB0gNGWbk52TRfc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/07b55276-2e98-4927-84ee-b47cd386d90e/LAUDOANTONIOFLOREScorrigido.pdf?expires_on=1785434474&amp;signature=8fFpXxK3sLgJ0wqJ6TNkCgJZehteNPD8%2FJQcYHnyaJw%3D</t>
         </is>
       </c>
       <c r="V50">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6943e82d-4aa3-440c-9bcc-6a3af33cfa1a/Laudo109-Bemol-2026-AntonioMoraisSantiago-Assinado.pdf?expires_on=1785434314&amp;signature=1OsH%2BVSyElBS2xUb2Z%2B5LAMOwV84gIRu%2FGcLHYIBnAY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6943e82d-4aa3-440c-9bcc-6a3af33cfa1a/Laudo109-Bemol-2026-AntonioMoraisSantiago-Assinado.pdf?expires_on=1785434474&amp;signature=sBTa6uS0YDyXzzUTebnLgJPTo40HQ2amaO782GSYSKo%3D</t>
         </is>
       </c>
       <c r="V51">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3cd6d343-0f0d-4405-a4a8-76e307f481fe/LaudoB39-2026-BEMOL-ANTONIORIBEIROVIANA.pdf?expires_on=1785434314&amp;signature=RE5J1Wl5wHXGKfsT74SNQmHVU4m%2BwC4FU1LimE2y6eQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3cd6d343-0f0d-4405-a4a8-76e307f481fe/LaudoB39-2026-BEMOL-ANTONIORIBEIROVIANA.pdf?expires_on=1785434474&amp;signature=8%2FTKAZ6IA5OCCv4AIK1GWASjqnxP16HpKFBu4udBcgo%3D</t>
         </is>
       </c>
       <c r="V52">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/724f0153-2776-46e4-9a40-21b0e37ecae9/Laudo182-Bemol-2026-AntonioSousaCosta.pdf?expires_on=1785434314&amp;signature=OopoPGSAMhmm46xeSlmifhKc1i%2BDk6b8VXpQmGcqY9A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/724f0153-2776-46e4-9a40-21b0e37ecae9/Laudo182-Bemol-2026-AntonioSousaCosta.pdf?expires_on=1785434474&amp;signature=tDDDZ9GD2gdYrr8lFwj884QXkdDy89bAXAStmQ1ussI%3D</t>
         </is>
       </c>
       <c r="V53">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9a5a54fe-e4a9-45a3-92f7-c8f8aca9905d/Laudo192-Bemol-2026-AntonioVitalMarinhoFilho.pdf?expires_on=1785434314&amp;signature=rOdXb2KV4goU70JSkjY1RCTBy20cA4U5gPYrZTp16JU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9a5a54fe-e4a9-45a3-92f7-c8f8aca9905d/Laudo192-Bemol-2026-AntonioVitalMarinhoFilho.pdf?expires_on=1785434474&amp;signature=2SxS6jpc51kAOKrJXAhKl27Zz%2BEtw0wZSSiNPHyeVCI%3D</t>
         </is>
       </c>
       <c r="V54">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/43f8142c-6f01-4ed5-b781-c26dec473638/Laudo210-Bemol-2026-ApoenaCristinaBrasilSousa-Assinado.pdf?expires_on=1785434314&amp;signature=e7GH94WbuYtbEdZAbtAITkLiwOIcxI3ZzelIE%2F995hI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/43f8142c-6f01-4ed5-b781-c26dec473638/Laudo210-Bemol-2026-ApoenaCristinaBrasilSousa-Assinado.pdf?expires_on=1785434474&amp;signature=nIVRlBnVskhpzvGu1V4OPmvD3aIfpyjvhBmERh61Tg4%3D</t>
         </is>
       </c>
       <c r="V55">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ce99b0a7-5272-4bd5-bdf7-93a48cd76678/Laudo137-Bemol-2026-ArleiseDaSilvaFigueira.pdf?expires_on=1785434314&amp;signature=hRrpVpo3qvNGDNP%2BdO3U8D0UPnCVIUMt%2FPFZ67s4lxU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ce99b0a7-5272-4bd5-bdf7-93a48cd76678/Laudo137-Bemol-2026-ArleiseDaSilvaFigueira.pdf?expires_on=1785434474&amp;signature=yQXyKTlesn9JUFi6VXLDqZP%2Bp23QTyhwY%2FT50HbJrFc%3D</t>
         </is>
       </c>
       <c r="V56">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/93e611b9-4214-4f17-9144-6b8f78b7aab7/Laudo123-Bemol-2026-ArlindoSouzaDeHolanda.pdf?expires_on=1785434314&amp;signature=yiFJwaemdYhNeba0twydiMFbLLnoZ971Wi6guHfAvqg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/93e611b9-4214-4f17-9144-6b8f78b7aab7/Laudo123-Bemol-2026-ArlindoSouzaDeHolanda.pdf?expires_on=1785434474&amp;signature=5oXe31XhCmz6%2FmreWCHskOk8Di%2FlRCfTUfLsXGUOJDE%3D</t>
         </is>
       </c>
       <c r="V57">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3fb83548-7366-484a-a6ab-54f2f8f6f488/Laudo98-Bemol-2026-AureaDaSilvaTrindadeSoares.pdf?expires_on=1785434314&amp;signature=SYA5ZbJzz4q4Jh3wV%2Fj4ijjBHE%2Ft8p2T2YcO%2FfI8Khw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3fb83548-7366-484a-a6ab-54f2f8f6f488/Laudo98-Bemol-2026-AureaDaSilvaTrindadeSoares.pdf?expires_on=1785434474&amp;signature=PeYtvWW840oggjl5fk8AmX437lclV2Lvrp1lvly9huI%3D</t>
         </is>
       </c>
       <c r="V58">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7fcc6830-a61c-4edb-b8de-cb677550fd4d/Laudo115-Bemol-2026-AureliaBentesFerreira-Assinado.pdf?expires_on=1785434314&amp;signature=YpdYHlRpvtCKE0zDADgZqeRDkE6I2J5THFSQk%2FVDcxc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7fcc6830-a61c-4edb-b8de-cb677550fd4d/Laudo115-Bemol-2026-AureliaBentesFerreira-Assinado.pdf?expires_on=1785434474&amp;signature=jWykxNk1dzXPEwziGT2Fb5KQsxSvmNGo2nOVbtm2HvY%3D</t>
         </is>
       </c>
       <c r="V59">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1f0ac28-c405-4bba-93cb-319510e9e1cf/Laudo_AC_24-2026_-_AURELIO_DA_SILVA_AZEVEDO_assinado.pdf?expires_on=1785434314&amp;signature=G3oynyl5ljrEDWCG0lgyBRrlwTqY8691y2l%2Baqo%2BJqA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1f0ac28-c405-4bba-93cb-319510e9e1cf/Laudo_AC_24-2026_-_AURELIO_DA_SILVA_AZEVEDO_assinado.pdf?expires_on=1785434474&amp;signature=RVGToFHfuJVm6tEuY2ECnbADsCyk%2FQqycgrrlG8zC2Q%3D</t>
         </is>
       </c>
       <c r="V60">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6a44e1f9-a59e-4ba4-91e1-781a7c146ff4/LaudoITA14-Bemol-2026-AureniceRabelodoNascimento-Assinadoajustado.pdf?expires_on=1785434314&amp;signature=rEXGEgQRu7jGm1f1HI2J4pe4Xlz26nJpRMpKokRaIfo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6a44e1f9-a59e-4ba4-91e1-781a7c146ff4/LaudoITA14-Bemol-2026-AureniceRabelodoNascimento-Assinadoajustado.pdf?expires_on=1785434474&amp;signature=eq9g4%2BJOrQrZD79rJNYbGmeKeVT5%2FPXaF%2BB01QDkXjI%3D</t>
         </is>
       </c>
       <c r="V61">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c0214175-8f29-4f87-a45d-ffd2e4444f1e/Laudo34-Bemol-2026-AuxiliadoraCruzDosSantos-Assinado.pdf?expires_on=1785434314&amp;signature=Gwo2G6XpkweQBb2Eh9gdP15WmqNL19vJD4VpUhg%2FHD8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c0214175-8f29-4f87-a45d-ffd2e4444f1e/Laudo34-Bemol-2026-AuxiliadoraCruzDosSantos-Assinado.pdf?expires_on=1785434474&amp;signature=9jPeM%2Fy0wgt92k%2FwIYmq%2BWQb6GiTttK4SKZ9yrN5AEQ%3D</t>
         </is>
       </c>
       <c r="V62">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/24701e8a-44ce-40d1-b05e-f5411c37c44a/LaudoB32-2026-BEMOL-BETTYIARAGAMAGONZALEZ.pdf?expires_on=1785434314&amp;signature=emCPq%2BBIZbDOFWx9Zm3kcjg5MKD7dHcCFzK75nYqAA0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/24701e8a-44ce-40d1-b05e-f5411c37c44a/LaudoB32-2026-BEMOL-BETTYIARAGAMAGONZALEZ.pdf?expires_on=1785434474&amp;signature=QsabuaHL3MyhtQfiq%2BGtytSuhBbhx3l81et%2BX0Zps%2Fw%3D</t>
         </is>
       </c>
       <c r="V63">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5c1781be-ac10-40e0-907d-c08e78226152/Laudo20-2025-Bemol-BrenoSoaresFeitoza-Assinado.pdf?expires_on=1785434314&amp;signature=7Tk5hQ8f0%2FK9LSjbv7QI6Vlk9qhq8ybolFbE2TDsst0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5c1781be-ac10-40e0-907d-c08e78226152/Laudo20-2025-Bemol-BrenoSoaresFeitoza-Assinado.pdf?expires_on=1785434474&amp;signature=jqcMksnVKSX7%2BCq0Y9xiRocn6%2BefQ9hVWARHb5OzCqY%3D</t>
         </is>
       </c>
       <c r="V64">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/543005fc-4f9c-40b7-a4b2-d509df3d1fc1/LaudoP25-Bemol-2026-BrunaBentodeOliveira_signed.pdf?expires_on=1785434314&amp;signature=sUn0z4tG6uuSYavsYWVuwXV6oxyuXSNznDWuiwSj0IE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/543005fc-4f9c-40b7-a4b2-d509df3d1fc1/LaudoP25-Bemol-2026-BrunaBentodeOliveira_signed.pdf?expires_on=1785434474&amp;signature=ugq51IMw4MJsf51DQTZthXxMtaGFJNbMHZf8YecLP8Y%3D</t>
         </is>
       </c>
       <c r="V65">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/43fbbba4-c8cf-4337-a16a-a2e4f4edaab2/Laudo200-Bemol-2026-BrunaJannainaSilvaMendonca-Assinado.pdf?expires_on=1785434314&amp;signature=sUvFkbnlsaOdN14ysrxL8uBEKDJdfK0%2FCoxoVu0BHb0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/43fbbba4-c8cf-4337-a16a-a2e4f4edaab2/Laudo200-Bemol-2026-BrunaJannainaSilvaMendonca-Assinado.pdf?expires_on=1785434474&amp;signature=MxkjlOT0j7%2FwKoQVZZw4l1f1Ty4I9YzmWr2g7ZOZFxs%3D</t>
         </is>
       </c>
       <c r="V66">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3ce22068-ea71-4640-8b9a-60f8b01f5f29/Laudo184-Bemol-2026-CaloivaPaesDeLemosOliveira.pdf?expires_on=1785434314&amp;signature=I0wTTxNaO5ekOFr5f7fvs4aVWMA8fGwon13hN81LovI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3ce22068-ea71-4640-8b9a-60f8b01f5f29/Laudo184-Bemol-2026-CaloivaPaesDeLemosOliveira.pdf?expires_on=1785434474&amp;signature=ctfuCDoiOyKjL%2BDjCmHicOKMwOqJLYTIR7frXjMCNt4%3D</t>
         </is>
       </c>
       <c r="V67">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ccd7d189-c4f8-4347-a8d8-1cb8b0341517/Laudo139-Bemol-2026-CarliceBarbosaDoAmaral.pdf?expires_on=1785434314&amp;signature=D6efOcBDllPEEVJ0Q9H8v%2F34GDHAr23um5OqOHc%2FPeg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ccd7d189-c4f8-4347-a8d8-1cb8b0341517/Laudo139-Bemol-2026-CarliceBarbosaDoAmaral.pdf?expires_on=1785434474&amp;signature=xpCnak1OBR677fCXTeIZcoUN1WlcVpRoz6eF6qLS2zQ%3D</t>
         </is>
       </c>
       <c r="V68">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/799a3761-767b-4676-acfb-c5d34affbb1a/LaudoITA06-Bemol-2026-CarlosEleoteriodeMoraes.pdf?expires_on=1785434314&amp;signature=%2FUQPqDACuRg3ehLVm%2FO%2FU3paC7G8vaBCk4i5i15m7ks%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/799a3761-767b-4676-acfb-c5d34affbb1a/LaudoITA06-Bemol-2026-CarlosEleoteriodeMoraes.pdf?expires_on=1785434474&amp;signature=7veCplzEvLnxLzLOTL5aWZPQ%2Fqw2zuLFyIBLZ7UIIGA%3D</t>
         </is>
       </c>
       <c r="V69">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e02f445a-3246-4a56-b961-162d323a94de/LaudoA06-Bemol-2026-CarolinaDeFreitas_signed.pdf?expires_on=1785434314&amp;signature=ByHWO1juqhkK60hQuRNT0XcMUqMp%2FLypFF%2BA1zt7QRY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e02f445a-3246-4a56-b961-162d323a94de/LaudoA06-Bemol-2026-CarolinaDeFreitas_signed.pdf?expires_on=1785434474&amp;signature=kQX39o%2FM59I27FlG0ga%2BLiLwXTTKQ%2B7%2FgxmVx4WCIxg%3D</t>
         </is>
       </c>
       <c r="V70">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/552485d5-095d-4a91-8fce-d18d7115158f/LaudoP23-Bemol-2026-CerlonValentedoNascimentoPacheco_signed.pdf?expires_on=1785434314&amp;signature=1phrMqWydufB9SiUznkzmhZ7nhl5Ez4zOFI2Mz6Fy8I%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/552485d5-095d-4a91-8fce-d18d7115158f/LaudoP23-Bemol-2026-CerlonValentedoNascimentoPacheco_signed.pdf?expires_on=1785434474&amp;signature=tW7iz17rRIKiaBnIfV68eamw7zwFtn0U7BV4YXz6cEA%3D</t>
         </is>
       </c>
       <c r="V71">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6796f8e5-ad95-4505-9f99-b94181fa1f0a/LAUDOCICERO.pdf?expires_on=1785434314&amp;signature=taj0SCzrdbXbyNt5qbsvEU1F75M031Rxsl2mxt%2BknLg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6796f8e5-ad95-4505-9f99-b94181fa1f0a/LAUDOCICERO.pdf?expires_on=1785434474&amp;signature=XTcLaRs3hmqfYO%2FWeIri%2Fcq54rDuxKFmVApEGNJ4x0s%3D</t>
         </is>
       </c>
       <c r="V72">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ce7e1e2c-27ee-4882-8f47-124631792dde/Laudo21-Bemol-2026-CinthiaCristinaDoNascimentoPereira-Assinado.pdf?expires_on=1785434314&amp;signature=KPEdLBUW5UO%2BRpdAK2eRaDh9yMi6d%2FWd%2F81Kh9glTdw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ce7e1e2c-27ee-4882-8f47-124631792dde/Laudo21-Bemol-2026-CinthiaCristinaDoNascimentoPereira-Assinado.pdf?expires_on=1785434474&amp;signature=AA0pyH1pLVtB0z3I1lZk7IK8BtjsvIZXWjttyxCIQAE%3D</t>
         </is>
       </c>
       <c r="V73">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4bb0e515-b13b-4c27-9d12-c8f2d63450e7/LAUDOCLAUDIAMARIASOUZADECASTRO.pdf?expires_on=1785434314&amp;signature=2kt9ESbWP8rgyNX4tWq4PwnlTmXdMJbDx%2F9zI8fzYow%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4bb0e515-b13b-4c27-9d12-c8f2d63450e7/LAUDOCLAUDIAMARIASOUZADECASTRO.pdf?expires_on=1785434474&amp;signature=T8f1uLL6M51CWPV0I0M2hL4hW7ySjbVkMwnbh%2F2AG%2Fs%3D</t>
         </is>
       </c>
       <c r="V74">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/797e54fa-75a0-4c64-88de-07c01838b7c3/Laudo18-Bemol-2026-ClaudiaMatosDaCruzCoelho-Assinado.pdf?expires_on=1785434314&amp;signature=kRCPv%2FBDdjYPq1wIsHu%2FpKlsywzQAJ6t%2BDcSZz8pwiU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/797e54fa-75a0-4c64-88de-07c01838b7c3/Laudo18-Bemol-2026-ClaudiaMatosDaCruzCoelho-Assinado.pdf?expires_on=1785434474&amp;signature=yrM%2FtIv1Nc59s46FDuUSPIV37pwDxrNMtvNvYsLQptk%3D</t>
         </is>
       </c>
       <c r="V75">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ecc81d50-7c4a-4d1f-9347-37258e35d44b/LaudoJP10-Bemol-2026-CleideCustodioDeSouza_signed.pdf?expires_on=1785434314&amp;signature=xZM9xY2K34o2%2Bw8%2F4ABuNyCugbVs2qUxTtJrz8pwA2k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ecc81d50-7c4a-4d1f-9347-37258e35d44b/LaudoJP10-Bemol-2026-CleideCustodioDeSouza_signed.pdf?expires_on=1785434474&amp;signature=4ZBV0LJeQTgUjfv5gM8G76vtDVatycL%2BCiaJUc40iVQ%3D</t>
         </is>
       </c>
       <c r="V76">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a32e3ff-6194-41cf-89bc-5d6c4f86838f/LaudoPA47-Bemol-2025-CleitonDosSantosRodrigues-Assinado.pdf?expires_on=1785434314&amp;signature=Lbch7Fm4EpdpQxIdyaxsJKRWoDh10CCdq1%2F27JcZnZA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a32e3ff-6194-41cf-89bc-5d6c4f86838f/LaudoPA47-Bemol-2025-CleitonDosSantosRodrigues-Assinado.pdf?expires_on=1785434474&amp;signature=dqtCJAvsiJMK10NIypKDLyuIgLMdndmlcJcpTpMAFhs%3D</t>
         </is>
       </c>
       <c r="V77">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0aa2e8f4-6c0b-421f-b58e-33066fa09f27/BEMOL-PV087-CleitondaSilva.pdf?expires_on=1785434314&amp;signature=SHse9rmchyufVBeMEawP9%2FYZGiuStTyFioajOjRmro4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0aa2e8f4-6c0b-421f-b58e-33066fa09f27/BEMOL-PV087-CleitondaSilva.pdf?expires_on=1785434474&amp;signature=2%2B6TFfctbP8gQo1LzUPZ9ToEAKfx3CQ2BWpNLeknUrU%3D</t>
         </is>
       </c>
       <c r="V78">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f072c23d-6575-42e8-9558-1681be8a79da/Laudo41-Bemol-2026-CleomardePaulaLima-Assinado.pdf?expires_on=1785434314&amp;signature=AEGbMIs77wUAUvoFft0LhyB3HVutT%2BWustfNwp0ks4A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f072c23d-6575-42e8-9558-1681be8a79da/Laudo41-Bemol-2026-CleomardePaulaLima-Assinado.pdf?expires_on=1785434474&amp;signature=OzvkO1FBrv3gcTRhbjMf6NM4LEmxNvnlfDP3G3ztm2Q%3D</t>
         </is>
       </c>
       <c r="V79">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f29e6a7-765f-46a0-8fee-f160391a2f0a/Laudo_AC_22-2026_-_CLODOALDA_LEANDRO_GOMES_SOUZA_assinado.pdf?expires_on=1785434314&amp;signature=Zer3PrAYT4twFma%2FToheIJS9NtBPkoa900sFZZ%2BY34I%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f29e6a7-765f-46a0-8fee-f160391a2f0a/Laudo_AC_22-2026_-_CLODOALDA_LEANDRO_GOMES_SOUZA_assinado.pdf?expires_on=1785434474&amp;signature=xPlHX2iaGGTedmc8qBkdBStg%2FOY%2FY%2BlK5XVvInsJXnU%3D</t>
         </is>
       </c>
       <c r="V80">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/acd15778-bfd8-495a-aff0-21f42f8fd97b/LaudoITA01-Bemol-2026-CristhianeMayaraPrestesdosAnjosdaSilva.pdf?expires_on=1785434314&amp;signature=zj80htJqq8EBwOAdIOAVhNx8TIAafEyzL%2FLXtJpriqE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/acd15778-bfd8-495a-aff0-21f42f8fd97b/LaudoITA01-Bemol-2026-CristhianeMayaraPrestesdosAnjosdaSilva.pdf?expires_on=1785434474&amp;signature=%2B8Ujkli1wpDRfNH9hUjaCw2CrlKhnj8jAMVLkkUiUA8%3D</t>
         </is>
       </c>
       <c r="V81">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/805f26ff-356d-41f0-8840-d8a0018997cc/RelatriodeValordeRefernciaRVR03-Bemol-2026-DaianaMacariodaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=H6%2FJz0xSav9YtmUitcebUm8NwPJgHKEITX%2BBIRDvqwg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/805f26ff-356d-41f0-8840-d8a0018997cc/RelatriodeValordeRefernciaRVR03-Bemol-2026-DaianaMacariodaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=l2317gBjNmTW4z%2F0DRQ9Lw1fj5jkgg1tuF8MxtZhRhY%3D</t>
         </is>
       </c>
       <c r="V82">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f9d89784-edd5-48d5-8590-fd86ea5ded67/LaudoB29-2026-BEMOL-DAMASIOCARNEIROLARANJEIRA.pdf?expires_on=1785434314&amp;signature=2doycwu2wLI0wgy%2B4Ui66G1YvlMSydS27dhgd3s0jBE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f9d89784-edd5-48d5-8590-fd86ea5ded67/LaudoB29-2026-BEMOL-DAMASIOCARNEIROLARANJEIRA.pdf?expires_on=1785434474&amp;signature=Sqw3GH%2BDFZ2hH41DeKQ9xjrw%2BTqVq%2B292plXxl1GofQ%3D</t>
         </is>
       </c>
       <c r="V83">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e5dd5af0-5eec-4ab7-93a4-97d619a27b96/M4-2026-DANIELALVESajustado.pdf?expires_on=1785434314&amp;signature=N7Nlz8YbYmIvNkq4MSgo4cJasR1LxrBgrREM0mYD8QA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e5dd5af0-5eec-4ab7-93a4-97d619a27b96/M4-2026-DANIELALVESajustado.pdf?expires_on=1785434474&amp;signature=%2FB5t8Ww0G%2FvtuJtCeAlgElxby84BBULLJVrD8rj7ldo%3D</t>
         </is>
       </c>
       <c r="V84">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1e229a70-a871-4616-896f-5cff1574d528/M5-2026-DANIELALVESajustado.pdf?expires_on=1785434314&amp;signature=PHXGVNz5WxdNa1i8St0TWCnNrX0icAUvbH8IWmmcKoI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1e229a70-a871-4616-896f-5cff1574d528/M5-2026-DANIELALVESajustado.pdf?expires_on=1785434474&amp;signature=vgsieNJND52iMQskj1gxJovJ2XBMKJDVy7UCmhFwoYY%3D</t>
         </is>
       </c>
       <c r="V85">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c271d4d4-53bc-45ce-8161-5360ceb3b3ef/Laudo138-Bemol-2026-DanielaDosReisSeixasCoelho.pdf?expires_on=1785434314&amp;signature=maGulFwF%2FT83rxPC%2BTw2zUPDg9IR8sUzZAkyTueceDU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c271d4d4-53bc-45ce-8161-5360ceb3b3ef/Laudo138-Bemol-2026-DanielaDosReisSeixasCoelho.pdf?expires_on=1785434474&amp;signature=3u4qI%2Blgd2IPUkLW7ebLkWPympdz2FRWrUXrl%2Frr51E%3D</t>
         </is>
       </c>
       <c r="V86">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1ce44eb-deec-40a1-a06b-868ba469526b/LAUDODANIELE.pdf?expires_on=1785434314&amp;signature=LWpiNE7ldsQoJ16DBSRzLBIq2YMb1fOFCGN0Nbnlg5g%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1ce44eb-deec-40a1-a06b-868ba469526b/LAUDODANIELE.pdf?expires_on=1785434474&amp;signature=AmBHlsm1V2fR8tpsexn87hiTsldSHAAEz6Nx%2BdTcafs%3D</t>
         </is>
       </c>
       <c r="V87">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0fee6b3f-94fb-4183-aa3e-1d0677399840/Laudo84-Bemol-2026-DarisonDeSouzaRamos-Assinado.pdf?expires_on=1785434314&amp;signature=0GmQEjoIzE67paBYGROZHnXf2c0K6s%2B6Or4xs1tQojw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0fee6b3f-94fb-4183-aa3e-1d0677399840/Laudo84-Bemol-2026-DarisonDeSouzaRamos-Assinado.pdf?expires_on=1785434474&amp;signature=VQwbRGP%2FMBarG1q5ymBCzVvInoR%2FdkuApwag0S7%2FN08%3D</t>
         </is>
       </c>
       <c r="V88">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b2d6b3a5-51a5-45fb-b5ab-0271d4525878/BEMOL-PV088-DARLINGENUNESNASCIMENTO.pdf?expires_on=1785434314&amp;signature=riXzUduNU7swRgeS825Bp5J9j14jqxi0iLnP0YiARZ4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b2d6b3a5-51a5-45fb-b5ab-0271d4525878/BEMOL-PV088-DARLINGENUNESNASCIMENTO.pdf?expires_on=1785434474&amp;signature=9eWhK%2BZVS0pxIwQUGIoyaiKp3Vra7mqXRcVRkLQQL6A%3D</t>
         </is>
       </c>
       <c r="V89">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ca9e25cf-e868-4944-a385-0c98e80dd3e4/Laudo173-Bemol-2026-DaviCastroGarcia.pdf?expires_on=1785434314&amp;signature=GLFMgVuxA3%2BbUEmufB7hOCEWzTEYCF8%2BUEAk10vkzbw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ca9e25cf-e868-4944-a385-0c98e80dd3e4/Laudo173-Bemol-2026-DaviCastroGarcia.pdf?expires_on=1785434474&amp;signature=IbYziGbFeMw2aVF31Ap5UPNlMj5ix9OnJghnOuNTf%2B0%3D</t>
         </is>
       </c>
       <c r="V90">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/52d0962b-f1b4-4859-a26e-2686aebba31f/Laudo29-Bemol-2026-DavidLimaDeAraujo-Assinado.pdf?expires_on=1785434314&amp;signature=gaHbg4quJpmlNwuQfpWue23B2Mc%2FdpjTmufPL9Kkj9A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/52d0962b-f1b4-4859-a26e-2686aebba31f/Laudo29-Bemol-2026-DavidLimaDeAraujo-Assinado.pdf?expires_on=1785434474&amp;signature=qeHW3KrKKK6qr22QOV2IYsoWMxuXCNJVRK6%2FxA8TPFs%3D</t>
         </is>
       </c>
       <c r="V91">
@@ -12410,7 +12410,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fc282ab4-7de8-44dc-b0d2-8db2cf5fa4d1/LaudoB11-2026-BEMOL-DAYSENAYARAGONALVESDIAS.pdf?expires_on=1785434314&amp;signature=TFQk45rNVn1VCtPf2UbeTfsuqYv2HAGv%2B9NpeUj1M%2Bw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fc282ab4-7de8-44dc-b0d2-8db2cf5fa4d1/LaudoB11-2026-BEMOL-DAYSENAYARAGONALVESDIAS.pdf?expires_on=1785434474&amp;signature=mIvcJYj3V2zdMfaE7XRyncG4LaK%2F71nuVbiauPC8bF0%3D</t>
         </is>
       </c>
       <c r="V92">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/63cabcc8-ee70-49ef-807f-0c102ae8dc77/LaudoP02-Bemol-2026-DelcimarGamaDaFonseca_signed.pdf?expires_on=1785434314&amp;signature=rzLcd5Eq4TFaqvMyIJ2bx6i2X75nN7XkUM0sd2mmDQo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/63cabcc8-ee70-49ef-807f-0c102ae8dc77/LaudoP02-Bemol-2026-DelcimarGamaDaFonseca_signed.pdf?expires_on=1785434474&amp;signature=blrCyo5ZauNH5uYILX40ciE0R0kpEzoD2U2BM3k%2FWTg%3D</t>
         </is>
       </c>
       <c r="V93">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a74a35b-62b8-4181-8173-e8b4ce482191/LAUDODENILDO.pdf?expires_on=1785434314&amp;signature=ux%2Bc49R%2BL4rn9wnFY%2F5%2FHllgGNqyBx6QFsUlkm%2F3LH0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a74a35b-62b8-4181-8173-e8b4ce482191/LAUDODENILDO.pdf?expires_on=1785434474&amp;signature=F5YvhTwnKEOJYPxRUf22XpQX%2B%2FszhdwiANHmULv3VZI%3D</t>
         </is>
       </c>
       <c r="V94">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/15ba2ece-19de-4196-9767-72294a7b33e6/Laudo170-Bemol-2026-DeusalinaVasconcelosLima.pdf?expires_on=1785434314&amp;signature=n0A7hybVoYM2NZXMi11SfuZTV5DtxL8jXfy3jtk%2FCtQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/15ba2ece-19de-4196-9767-72294a7b33e6/Laudo170-Bemol-2026-DeusalinaVasconcelosLima.pdf?expires_on=1785434474&amp;signature=JdNe2kl4DX3hh3ENHFqAfI9Wr53fW6PIzm5kojZQ758%3D</t>
         </is>
       </c>
       <c r="V95">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b05fb8f4-a555-4d72-8c6e-bbe7d4a9436e/LaudoRVR07-Bemol-2026-DeusdeteCastroPessoa-Assinado.pdf?expires_on=1785434314&amp;signature=2up5wWV0aAkTubX7aosV6bDCd%2FecG0P1%2BlqmIFdA3Cw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b05fb8f4-a555-4d72-8c6e-bbe7d4a9436e/LaudoRVR07-Bemol-2026-DeusdeteCastroPessoa-Assinado.pdf?expires_on=1785434474&amp;signature=llyp0%2F5H9FusdlqEwzxBf6csmn0p%2BRtH929CIqLxVRY%3D</t>
         </is>
       </c>
       <c r="V96">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e697831f-2be1-4bdb-a91a-fb21547d4b26/LaudoP12-Bemol-2026-DezianeAraujodaSilva_signed.pdf?expires_on=1785434314&amp;signature=m5VVojK6E6JMeuBlDAvZ0ABedch5u%2BOpH1fAE8jsEdg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e697831f-2be1-4bdb-a91a-fb21547d4b26/LaudoP12-Bemol-2026-DezianeAraujodaSilva_signed.pdf?expires_on=1785434474&amp;signature=NXcJPYk%2F3RSIfVLEqtq56qI0n4SCmPm0sglEGjSiLp0%3D</t>
         </is>
       </c>
       <c r="V97">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/de8f14f1-b4f9-44cb-a7f1-1a2c7ea28b17/LAUDODHIJANA2corrigido.pdf?expires_on=1785434314&amp;signature=zBdEKmgF3nITr9NCHEYPNK1xd7X03ONXAgysF9obbBA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/de8f14f1-b4f9-44cb-a7f1-1a2c7ea28b17/LAUDODHIJANA2corrigido.pdf?expires_on=1785434474&amp;signature=50u5322A9B3RbViPp0ZBh3gNOz0CRLsn6ZRcild0%2FjQ%3D</t>
         </is>
       </c>
       <c r="V98">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5552317c-4a4d-4a89-b4f6-8cd323b9d6e5/LAUDODHIJANA1corrigido.pdf?expires_on=1785434314&amp;signature=2RDmakILS8LVR3ktUWOuFCEsLOCQNRcV3twWrql%2F7Gk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5552317c-4a4d-4a89-b4f6-8cd323b9d6e5/LAUDODHIJANA1corrigido.pdf?expires_on=1785434474&amp;signature=qvoZshQqfQhd7Zm1gaLisU7Vzqr71dbn9IFf6xZ3aOI%3D</t>
         </is>
       </c>
       <c r="V99">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2c236bc5-75ef-4ae1-8301-675053e1c06c/Laudo_AC_09-2026_-_DIANA_CAROLINE_DA_SILVA_SANTOS_assinado.pdf?expires_on=1785434314&amp;signature=W9Lh1JbbQ2bGfqcMlSQs2lY7FKN5fGxeOP2FJsIMvwo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2c236bc5-75ef-4ae1-8301-675053e1c06c/Laudo_AC_09-2026_-_DIANA_CAROLINE_DA_SILVA_SANTOS_assinado.pdf?expires_on=1785434474&amp;signature=Dt1GDWclx0VOJkvIphu6UbK6pYOs43EphOQiLUffTGg%3D</t>
         </is>
       </c>
       <c r="V100">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/62813463-d44a-4700-8adc-561de9ba2477/LAUDODIANE.pdf?expires_on=1785434314&amp;signature=sFPXJfY6N9WXBNIlOcJjYAiwmKraYWRPzwGS1b%2FDsxw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/62813463-d44a-4700-8adc-561de9ba2477/LAUDODIANE.pdf?expires_on=1785434474&amp;signature=BB6P1mngHAaJEj09%2FH8yeFdJTEcYTJ0FffHf3qNxi%2Fs%3D</t>
         </is>
       </c>
       <c r="V101">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/604019c1-0351-4825-93c2-d471ec3dd995/LAUDODIEGO.pdf?expires_on=1785434314&amp;signature=NpVoV7SpUIMhhwl2Nd1AkkLI21%2FIBl4Jg%2BEs1mjqr4I%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/604019c1-0351-4825-93c2-d471ec3dd995/LAUDODIEGO.pdf?expires_on=1785434474&amp;signature=CEh6yCHJJSX9js73j1U51qD4KURnCndxavykGUVl%2FVA%3D</t>
         </is>
       </c>
       <c r="V102">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ebde28be-d8fc-46a9-9ac3-20bd6763718a/LaudoA17-Bemol-2025-DinalvaLacerdaDeSouza_signed.pdf?expires_on=1785434314&amp;signature=Ix%2FXJ2LiAiVFHGmE79hcsupUJ4pVyuHBAWKRBFKkgRM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ebde28be-d8fc-46a9-9ac3-20bd6763718a/LaudoA17-Bemol-2025-DinalvaLacerdaDeSouza_signed.pdf?expires_on=1785434474&amp;signature=8bT2ulyZ9S%2BG6j4SkPqtvnMmc4bEcssBtBkgtFWrjn4%3D</t>
         </is>
       </c>
       <c r="V103">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/82ae2b33-0927-43a7-81b6-dbd12bb745b8/Laudo_AC_29-2026_-_DOUVINA_COSTA_DA_SILVA_assinadoajustado.pdf?expires_on=1785434314&amp;signature=Upbc8HqA6PnhRP4uJ8j8JYu4gsbMWWqqCPYETuC5C20%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/82ae2b33-0927-43a7-81b6-dbd12bb745b8/Laudo_AC_29-2026_-_DOUVINA_COSTA_DA_SILVA_assinadoajustado.pdf?expires_on=1785434474&amp;signature=4zv6iU%2F%2FSs7z2HAM3zfxBrYs70Fx%2BHoOgfalha465Rg%3D</t>
         </is>
       </c>
       <c r="V104">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/806e066e-4cc0-4b10-805f-af20789d5423/BEMOL-PV070-DYANAJHENIFFERRAMOSTORRES.pdf?expires_on=1785434314&amp;signature=XlxLddFcbciGTUBcyl10v2SWb9Roe8%2Ba4OYvmFtOoGA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/806e066e-4cc0-4b10-805f-af20789d5423/BEMOL-PV070-DYANAJHENIFFERRAMOSTORRES.pdf?expires_on=1785434474&amp;signature=TAcb1gODLn6umx9nmvrSZGfW5GdfcIX99Q%2FJM4LYq%2FQ%3D</t>
         </is>
       </c>
       <c r="V105">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ee8f616f-928d-41ae-91b3-649b02ced3ce/Laudo482-Bemol-2025-DyhonySiqueiraFigueiredo-Assinado1.pdf?expires_on=1785434314&amp;signature=GhM1weeQU1lO1qWiueF7Hczti6E0p1bkw16Xb9Ransc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ee8f616f-928d-41ae-91b3-649b02ced3ce/Laudo482-Bemol-2025-DyhonySiqueiraFigueiredo-Assinado1.pdf?expires_on=1785434474&amp;signature=PgOWY1ejTNbPBX7Z8nYZoAm0aBmmeORFeuYmJY6iYzI%3D</t>
         </is>
       </c>
       <c r="V106">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6b66f5cb-54de-4cf6-bf8c-b345b4805945/LaudoP05-Bemol-2026-EderlanyaCardosoDosSantos_signed.pdf?expires_on=1785434314&amp;signature=fdcUvF9SihFo0T2tj1vfVohrBO6mpmbU1W6%2FsTVYlk0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6b66f5cb-54de-4cf6-bf8c-b345b4805945/LaudoP05-Bemol-2026-EderlanyaCardosoDosSantos_signed.pdf?expires_on=1785434474&amp;signature=kNf7l5gbcpbRHeKqGGpyug%2FzXgqKw%2BPF%2BAejHaIOuK4%3D</t>
         </is>
       </c>
       <c r="V107">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4a88bd99-8088-4036-8302-bbba9e6cda37/LAUDOEDILENE1.pdf?expires_on=1785434314&amp;signature=0%2Bmsd%2Bi6z7s4VxSDNL5l%2BEdPwrxohlTg13M3Q%2BZGtGk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4a88bd99-8088-4036-8302-bbba9e6cda37/LAUDOEDILENE1.pdf?expires_on=1785434474&amp;signature=%2F6%2FUD7iCNHCjc59%2BlebzLBOEcEYBV6PfEkGWx1dgNwg%3D</t>
         </is>
       </c>
       <c r="V108">
@@ -14664,7 +14664,7 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c5d0dc18-bb72-415b-8237-d8f0c2100c21/Laudo156-Bemol-2026-EdileneMeloVieira.pdf?expires_on=1785434314&amp;signature=suvX4XNy6fxttkSgzbmbyzozWQNTmpiYMIA3sLXRZ24%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c5d0dc18-bb72-415b-8237-d8f0c2100c21/Laudo156-Bemol-2026-EdileneMeloVieira.pdf?expires_on=1785434474&amp;signature=ZP3W7XooMqHGxC%2BNx18QaTswuG4GyGMEN05jy8pIs%2Bo%3D</t>
         </is>
       </c>
       <c r="V109">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4bc7496e-b2c6-4bbb-aa43-08a93f74b3bc/BEMOL-JP039-EDILEUZAALEXANDREDEFIGUEIREDO.pdf?expires_on=1785434314&amp;signature=nWvaCPsMzNeEnkERp7I7FY4TRLakrTw8eCGuiLFUtig%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4bc7496e-b2c6-4bbb-aa43-08a93f74b3bc/BEMOL-JP039-EDILEUZAALEXANDREDEFIGUEIREDO.pdf?expires_on=1785434474&amp;signature=pz8lclQB%2B6nUcgHyI0nviUf21yJkmLRuo3ngP%2FZL3tA%3D</t>
         </is>
       </c>
       <c r="V110">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e50e3f5e-ff8a-4bc2-8f96-bb87ed524c4a/Laudo419-Bemol-2025-EdinaLimaSoares-Assinado.pdf?expires_on=1785434314&amp;signature=ixVE4Sy58ZnTpbdKTsIEnvuODN%2BrDi82QIAkYBe0nYs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e50e3f5e-ff8a-4bc2-8f96-bb87ed524c4a/Laudo419-Bemol-2025-EdinaLimaSoares-Assinado.pdf?expires_on=1785434474&amp;signature=VLFt58Z5QlSd2OSLk%2B5BQMyAvLbeVUinIQXtvNB0P1E%3D</t>
         </is>
       </c>
       <c r="V111">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0781f381-a5b8-4cc0-9c64-955154cc185e/LaudoB49-2026-BEMOL-EdinaldoMoraesdaCruz.pdf?expires_on=1785434314&amp;signature=tZ78wXsk5Mzs8AIXotWZe3wCnnnWg%2Bu%2FOzD3G3MeNvo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0781f381-a5b8-4cc0-9c64-955154cc185e/LaudoB49-2026-BEMOL-EdinaldoMoraesdaCruz.pdf?expires_on=1785434474&amp;signature=IBA7%2BlK64x6A8WrSTrTo7cNfzIAMFY2U2Xdp9skvG6A%3D</t>
         </is>
       </c>
       <c r="V112">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4605b442-6252-4740-9bef-1c907a3122f3/Laudo_AC_15-2026_-_EDINALVA_FURTADO_DO_NASCIMENTO_assinado.pdf?expires_on=1785434314&amp;signature=E%2BQo22t8kQsEQK0u5pHUJsD0oceKqEH1RLpCDlN9x5Q%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4605b442-6252-4740-9bef-1c907a3122f3/Laudo_AC_15-2026_-_EDINALVA_FURTADO_DO_NASCIMENTO_assinado.pdf?expires_on=1785434474&amp;signature=R2hvjEaes1vpaELuLucvJYv%2B0xaRRC3R97c9T%2BcqTb0%3D</t>
         </is>
       </c>
       <c r="V113">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fd0013a3-4c79-4eed-9ad5-011dc0531ef0/LaudoITA05-Bemol-2026-EdinelzaNogueiraMota-Assinado.pdf?expires_on=1785434314&amp;signature=b0Z5saFO2XYHaK%2FkywrpoyEdVq5g5%2BHgKYMhJvYQzb4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fd0013a3-4c79-4eed-9ad5-011dc0531ef0/LaudoITA05-Bemol-2026-EdinelzaNogueiraMota-Assinado.pdf?expires_on=1785434474&amp;signature=qJ1rtu4Lf9CBGFFY0iti5%2FmTRxlvX752XEQ2%2Bl0D2lw%3D</t>
         </is>
       </c>
       <c r="V114">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f1c9b3a-952f-438e-83dd-1e11af526203/Laudo73-Bemol-2026-EdmarDiasDeSouza-Assinado.pdf?expires_on=1785434314&amp;signature=t5jvCecXAQNxtwL9FEJXu77%2FZJiKN1o2326BsHcOX2k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f1c9b3a-952f-438e-83dd-1e11af526203/Laudo73-Bemol-2026-EdmarDiasDeSouza-Assinado.pdf?expires_on=1785434474&amp;signature=ovETiNYiczmGeObh5xwCw9RUXltZ%2BI1Nk7onKutdIPI%3D</t>
         </is>
       </c>
       <c r="V115">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5ee14984-2d04-41e9-a6f5-7aa939a43689/LaudoCO02-Bemol-2025-EdnaGomesMaciel-Assinado.pdf?expires_on=1785434314&amp;signature=YNaZiyYhn5ZLYROoQ3X4o8%2BO3WyL7DwkYicWjFHvpvI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5ee14984-2d04-41e9-a6f5-7aa939a43689/LaudoCO02-Bemol-2025-EdnaGomesMaciel-Assinado.pdf?expires_on=1785434474&amp;signature=Q0cEJjejobKPyRLen9PjVWS3oSPg7Ug648vsERdiZr0%3D</t>
         </is>
       </c>
       <c r="V116">
@@ -15695,7 +15695,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/bc5d0a32-2beb-4f27-951e-ba01c364ae7f/LaudoR04-2026-BEMOL-EdnaJanuriadeMoraisdaSilva.pdf?expires_on=1785434314&amp;signature=ShiJ%2B3HJ6KCTsFfywlgtZGO90P7TcY6fHfKpNpHwbbE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/bc5d0a32-2beb-4f27-951e-ba01c364ae7f/LaudoR04-2026-BEMOL-EdnaJanuriadeMoraisdaSilva.pdf?expires_on=1785434474&amp;signature=n%2B%2FN6UhaNKoRv%2F4nLUmo3cAlvdWIiBOTmHQHS5eX1ls%3D</t>
         </is>
       </c>
       <c r="V117">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/310b284b-d250-49c4-b0d5-ac80a7ddcdcb/BEMOL-JP042-EDNEIASOARESOLIVEIRA.pdf?expires_on=1785434314&amp;signature=HQJCM9L5gGwYSNsLSsmp65PZUQYr1OaSwQR3Wc1Y01Q%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/310b284b-d250-49c4-b0d5-ac80a7ddcdcb/BEMOL-JP042-EDNEIASOARESOLIVEIRA.pdf?expires_on=1785434474&amp;signature=qHHXaqp6AI44KDP6V5JoLxeXPDxseG%2BOX0CpbDKJtw8%3D</t>
         </is>
       </c>
       <c r="V118">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3c082cb5-667c-4b2e-bb35-a623d0457346/Laudo133-Bemol-2026-EduardoJorgeFerreiraBarroso-Assinado.pdf?expires_on=1785434314&amp;signature=yNrZ%2BzTv71%2B4Pll5v5UAXsmK22jmW4Qg2XZyfBMqL60%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3c082cb5-667c-4b2e-bb35-a623d0457346/Laudo133-Bemol-2026-EduardoJorgeFerreiraBarroso-Assinado.pdf?expires_on=1785434474&amp;signature=nF8wzGssmvqNinxXT8rt9OnsdHP%2FS%2BwznD7qMEDxLnU%3D</t>
         </is>
       </c>
       <c r="V119">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/20deaef0-ad14-478d-a46f-491eb319ea63/LaudoP03-Bemol-2026-EdvarJoseModesto_signed.pdf?expires_on=1785434314&amp;signature=LJJ89GsvmHTMR%2FdDJf7IQCGAcII8uN16FHDwR4L3i34%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/20deaef0-ad14-478d-a46f-491eb319ea63/LaudoP03-Bemol-2026-EdvarJoseModesto_signed.pdf?expires_on=1785434474&amp;signature=ZMpgp7zK7VSkvqy%2FBfKncdx3GEYVIKhV4o%2Bs9xLEfug%3D</t>
         </is>
       </c>
       <c r="V120">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf9fd50d-3718-43e5-bdab-94a4b729f59a/BEMOL-JP036-ELAINECRISTINAMARGARIDADOSSANTOS.pdf?expires_on=1785434314&amp;signature=aM2AqrOsawv%2BN9wUXxFoepleQYvaR%2FAWl0CZNcthEVI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf9fd50d-3718-43e5-bdab-94a4b729f59a/BEMOL-JP036-ELAINECRISTINAMARGARIDADOSSANTOS.pdf?expires_on=1785434474&amp;signature=E0aZB5fAznixw2loas0a0gRwjQAKJG6GY1MHahdNbf0%3D</t>
         </is>
       </c>
       <c r="V121">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/374aef79-93b6-4bad-ab45-bc3709b69cd6/RelatriodeValordeReferncia-Bemol-2026-RVR09-ElaneCristinaFerreiradaSilva.pdf?expires_on=1785434314&amp;signature=GX0HbgN4vQD4bAFSfmmKCvOmO1fqNa4L9TF4KsEYjLs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/374aef79-93b6-4bad-ab45-bc3709b69cd6/RelatriodeValordeReferncia-Bemol-2026-RVR09-ElaneCristinaFerreiradaSilva.pdf?expires_on=1785434474&amp;signature=3aP7XMNv3bymSdAzwb9dBfpVrBPbx%2BGnNRuhPS6t0p0%3D</t>
         </is>
       </c>
       <c r="V122">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a7e37b6-ec4a-4cee-848c-2f23939b6dc2/BEMOL-PV095-ELANEFELICIOESANTOS.pdf?expires_on=1785434314&amp;signature=%2FxP28CChotFELXW0XscyVoksYfVlzWAkI3vhUYq6HUI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a7e37b6-ec4a-4cee-848c-2f23939b6dc2/BEMOL-PV095-ELANEFELICIOESANTOS.pdf?expires_on=1785434474&amp;signature=kdk9yDoFR0ppd3i1Zcpo81eeJEKzJRpgKAIvoVnn8t8%3D</t>
         </is>
       </c>
       <c r="V123">
@@ -16624,7 +16624,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f6ac25c-5053-42c5-8335-3b4052274121/M13-2026-ELCIELI.pdf?expires_on=1785434314&amp;signature=8zDmEaD3oo4zfTcHhKIWGY9UYpPwfIUodZEakiz4wR8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f6ac25c-5053-42c5-8335-3b4052274121/M13-2026-ELCIELI.pdf?expires_on=1785434474&amp;signature=ALJBx%2FJeMUlDpVvZhH0zo0Z8KsY%2BQFYm6m4HmIXr1Lo%3D</t>
         </is>
       </c>
       <c r="V124">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/56655338-63fa-409a-ad4f-9701712f7289/LaudoA03-Bemol-2026-ElenizeLima_signed.pdf?expires_on=1785434314&amp;signature=BYNWFepiXDtVZOIIk7FjoeHJBl%2BW1m7Fo93ry3i5P1I%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/56655338-63fa-409a-ad4f-9701712f7289/LaudoA03-Bemol-2026-ElenizeLima_signed.pdf?expires_on=1785434474&amp;signature=U7F%2BUXxSWN9AbDrM%2BuuIhXp1c01FFIAtMoQNH6nAPnI%3D</t>
         </is>
       </c>
       <c r="V125">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3a34b841-1745-4596-bc96-5707bb3090b6/LaudoPA19-Bemol-2026-EliSilvaDoCarmo.pdf?expires_on=1785434314&amp;signature=oBs4TWL0kHdsY4d2g%2BuHxvSucmSmokvwxt3Gxz9oelg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3a34b841-1745-4596-bc96-5707bb3090b6/LaudoPA19-Bemol-2026-EliSilvaDoCarmo.pdf?expires_on=1785434474&amp;signature=nnXFNoWWdts0xk5t78wfc3a7HKVWgIu936o5lLvEIHE%3D</t>
         </is>
       </c>
       <c r="V126">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/39bcef5c-d16c-4530-8807-f44667684a79/BEMOL-PV077-ELIANASANTOSDASILVAMACEDO.pdf?expires_on=1785434314&amp;signature=QKcnT2bvv5RtnsaSnnM8Hoga664Zv2%2F6NkDnUcsS2ms%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/39bcef5c-d16c-4530-8807-f44667684a79/BEMOL-PV077-ELIANASANTOSDASILVAMACEDO.pdf?expires_on=1785434474&amp;signature=IrjxSCX02z%2BbeZxo6qQUhuOzQm8DJ0ypeW2z%2FL%2F4ZEg%3D</t>
         </is>
       </c>
       <c r="V127">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/369aee73-674f-4435-954e-6d24f1e0907f/Laudo49-Bemol-2026-ElianaVieiraDaSilvacorrigido.pdf?expires_on=1785434314&amp;signature=ypARuDc1iUAWwz5x12dnYgDPvNDlXAs0k5DP2v4vdlk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/369aee73-674f-4435-954e-6d24f1e0907f/Laudo49-Bemol-2026-ElianaVieiraDaSilvacorrigido.pdf?expires_on=1785434474&amp;signature=51eb6kCrVm0NqgOcFkTf%2BbEi6H6EClSM6lC0U5hxP74%3D</t>
         </is>
       </c>
       <c r="V128">
@@ -17241,7 +17241,7 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0c43cc50-9a5b-40e2-bc16-680923cf6563/BEMOL-PV066-ELIASBALDOINOTORRESCALVALCANTE.pdf?expires_on=1785434314&amp;signature=wVxFJr0ErqhWTaUH%2BL1Mwl9FMS3H4BCVju9SLBT79jo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0c43cc50-9a5b-40e2-bc16-680923cf6563/BEMOL-PV066-ELIASBALDOINOTORRESCALVALCANTE.pdf?expires_on=1785434474&amp;signature=SYbpJX5leDYl6oKHS%2F0%2BOn7zAuxMxrMutcpU27Y5hk8%3D</t>
         </is>
       </c>
       <c r="V129">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/80e69f1b-0185-4993-8a09-a32d65e2c2f7/LaudoP22-Bemol-2026-ElielChagasdeSantana_signed.pdf?expires_on=1785434314&amp;signature=KEUcfjZgXxUcUqCj4jPW2wGKHgzOEbOgepbMTKxQ25M%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/80e69f1b-0185-4993-8a09-a32d65e2c2f7/LaudoP22-Bemol-2026-ElielChagasdeSantana_signed.pdf?expires_on=1785434474&amp;signature=YEfBuvpbpiWrF%2FqRYtf3aEMjr6Ox25lQ7hUncxRVyT4%3D</t>
         </is>
       </c>
       <c r="V130">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/22e5c65c-adf6-43af-b03d-c4be6d2b5f27/Laudo168-Bemol-2026-ElivelttonDaSilvaMoura-Assinado.pdf?expires_on=1785434314&amp;signature=6BjkUPft2HnVoExe3llKyBhjLiKLNDDUogchmomur1A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/22e5c65c-adf6-43af-b03d-c4be6d2b5f27/Laudo168-Bemol-2026-ElivelttonDaSilvaMoura-Assinado.pdf?expires_on=1785434474&amp;signature=TF71%2BDkuQLNribMMt%2FpfruFdmavLcEcv9Eq3ZD2Vjho%3D</t>
         </is>
       </c>
       <c r="V131">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d93add82-377b-4bf6-8170-0f2fd94a7b95/PA04-2026-ELIZETEajustado.pdf?expires_on=1785434314&amp;signature=USpAmlqYO2ifb9eCef4b0YUtPvO3kFEyn%2B1%2Btadf3Jk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d93add82-377b-4bf6-8170-0f2fd94a7b95/PA04-2026-ELIZETEajustado.pdf?expires_on=1785434474&amp;signature=MRuT%2BG8I1bedcDeMa8k%2BKlQQzH5Pkcetxoxtfn4qcaw%3D</t>
         </is>
       </c>
       <c r="V132">
@@ -17762,7 +17762,7 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/071c0338-2e41-4690-96cc-b4f54cb42db6/Laudo07-Bemol-2026-EliziaDoSocorroDeSouzaCarvalho-Assinado1.pdf?expires_on=1785434314&amp;signature=sS4Y6ze88c7WC0nl7Ujcbm9WAQybF8GzxkpehomZaq0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/071c0338-2e41-4690-96cc-b4f54cb42db6/Laudo07-Bemol-2026-EliziaDoSocorroDeSouzaCarvalho-Assinado1.pdf?expires_on=1785434474&amp;signature=uz1jlgoxv%2BMlfjhbhaBSfHxYt8LBmctYwBSCBNf1JAI%3D</t>
         </is>
       </c>
       <c r="V133">
@@ -17903,7 +17903,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/bb092190-5c08-4b45-a55a-a363d3a978f6/LAUDOEMIRRUIZ.pdf?expires_on=1785434314&amp;signature=JgsO8Km8CUuRe72Wo2poLIzga4GVO110z%2F2ywbT720s%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/bb092190-5c08-4b45-a55a-a363d3a978f6/LAUDOEMIRRUIZ.pdf?expires_on=1785434474&amp;signature=%2BbYbcuFTlGOcjSRF%2FQCtbhXVGbLAPp7pUoGcxTl9BO4%3D</t>
         </is>
       </c>
       <c r="V134">
@@ -18040,7 +18040,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a8cfb96f-e29c-44a8-ace1-c0b45bef5640/Laudo15-Bemol-2026-EricaMarciaBezerradeAraujoBastos-Assinadocorrigido.pdf?expires_on=1785434314&amp;signature=ytLqo5Cit%2FuGBvUWoTD98jpv7yiACGQS9pFIzzkAVW8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a8cfb96f-e29c-44a8-ace1-c0b45bef5640/Laudo15-Bemol-2026-EricaMarciaBezerradeAraujoBastos-Assinadocorrigido.pdf?expires_on=1785434474&amp;signature=u%2B04VuK2l7o3rAVZ5UDXQbZB8ZAoqiKxzFULeK3LHCM%3D</t>
         </is>
       </c>
       <c r="V135">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5518488a-e8de-410c-8b82-a36223ef2561/LaudoB41-2026-BEMOL-ERICKFABIANODEALMEIDACHAGAS.pdf?expires_on=1785434314&amp;signature=NRg9GB%2BjnQrCWf81SWDmrnMcfzw3SV2XQYcl186292E%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5518488a-e8de-410c-8b82-a36223ef2561/LaudoB41-2026-BEMOL-ERICKFABIANODEALMEIDACHAGAS.pdf?expires_on=1785434474&amp;signature=9RA0RB08dmuiA5gKIrzF2kep6dT6HCjeEqn7JLFfiTs%3D</t>
         </is>
       </c>
       <c r="V136">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/553196f4-a964-47c8-a3e0-509a649bb7d5/Laudo_AC_30-2026_-_ERINALDA_FERREIRA_DA_SILVA_assinado.pdf?expires_on=1785434314&amp;signature=hNuRYkQUNweZSb6rczi832PaJdXAF2LwSkZ62WGPMNQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/553196f4-a964-47c8-a3e0-509a649bb7d5/Laudo_AC_30-2026_-_ERINALDA_FERREIRA_DA_SILVA_assinado.pdf?expires_on=1785434474&amp;signature=WD%2BOCupa%2FZ4MKCI6NOpoS%2B%2FIYqsDvJa7O3NggcWSQkg%3D</t>
         </is>
       </c>
       <c r="V137">
@@ -18414,7 +18414,7 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d62f8ab1-5332-4111-a02b-84b41c4cd850/Laudo132-Bemol-2026-ErismarDaSilvaFeitoza.pdf?expires_on=1785434314&amp;signature=zx7j8kfS8b3BGLLNehrcX1A900s1iUcevJef040YZSk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d62f8ab1-5332-4111-a02b-84b41c4cd850/Laudo132-Bemol-2026-ErismarDaSilvaFeitoza.pdf?expires_on=1785434474&amp;signature=%2FqAQGNHCNFSKlzgf0ojY%2Fs2zM1tFTTX9xcEu8M4uiD8%3D</t>
         </is>
       </c>
       <c r="V138">
@@ -18540,7 +18540,7 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6261012a-89c8-4106-add5-9a22f7e2887a/Laudo39-Bemol-2026-EritondaCruzDaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=0gpfVh9tcRcaGMlz1y1rNlhACAUXq3c5E%2FpNAmYnOkg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6261012a-89c8-4106-add5-9a22f7e2887a/Laudo39-Bemol-2026-EritondaCruzDaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=wtN7Zdo0KlPCu1mkJ1AUe0vCc6MQlEy5p2HBw3MbDwk%3D</t>
         </is>
       </c>
       <c r="V139">
@@ -18677,7 +18677,7 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9c6d0dc3-6284-4cde-a28c-51bfe9f145eb/Laudo110-Bemol-2026-ErnaneSargesCabral-Assinado.pdf?expires_on=1785434314&amp;signature=8uNiPblTwOtfNQ62%2FVcYOZ8WR0dcXPQkShs1LpDSLaE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9c6d0dc3-6284-4cde-a28c-51bfe9f145eb/Laudo110-Bemol-2026-ErnaneSargesCabral-Assinado.pdf?expires_on=1785434474&amp;signature=xPvh71sK54Sd9FNPoZqBMWq2OJwTjIT0AplbLN81E8A%3D</t>
         </is>
       </c>
       <c r="V140">
@@ -18807,7 +18807,7 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5b350b88-dafc-489d-8c5b-0a187ec4efb1/Laudo40-Bemol-2026-EugeniaOlimpioMenezes-Assinado.pdf?expires_on=1785434314&amp;signature=J43kxEvJnUJx60q947o%2FDvyVGrg6W%2FZQ89HhRX9l48c%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5b350b88-dafc-489d-8c5b-0a187ec4efb1/Laudo40-Bemol-2026-EugeniaOlimpioMenezes-Assinado.pdf?expires_on=1785434474&amp;signature=6DRQ%2FnNC98JBa6ejzUZE%2FypYHImJKwn7ehbPd9xKGR0%3D</t>
         </is>
       </c>
       <c r="V141">
@@ -18931,7 +18931,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/de6e3d6f-1327-44f0-b564-dde96154d9d7/MP2-2026-EVAIajustado.pdf?expires_on=1785434314&amp;signature=6L9ky4MVxQLIi13zbGcBTi%2FwPobOC3zwZmpyc8IsbMQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/de6e3d6f-1327-44f0-b564-dde96154d9d7/MP2-2026-EVAIajustado.pdf?expires_on=1785434474&amp;signature=wVKuCjbW1OWgQJNfmXTdUEgQxu%2F29YM10IlXhdC2Flk%3D</t>
         </is>
       </c>
       <c r="V142">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2eb5ac99-11bc-4b0e-9c5f-119846bc5aa2/Laudo185-Bemol-2026-EvandoCamurcaDoNascimento.pdf?expires_on=1785434314&amp;signature=Yx8LEj7sCkeNQZVaoAHnKoT2cVz1uT3ms9ZeyBLEoCE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2eb5ac99-11bc-4b0e-9c5f-119846bc5aa2/Laudo185-Bemol-2026-EvandoCamurcaDoNascimento.pdf?expires_on=1785434474&amp;signature=FqWoqPBMvPVcgqL15hWO5yT%2BLMjuM2hnmHVOJeqG4BQ%3D</t>
         </is>
       </c>
       <c r="V143">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b46c9cdd-afef-4d37-bd38-04b70c1aced7/Laudo158-Bemol-2026-FabianeDaCostaMatos.pdf?expires_on=1785434314&amp;signature=nLiw2%2FRPCDtmQ5bb7db6nM3N7DmO3Jg1PgfGERqRde4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b46c9cdd-afef-4d37-bd38-04b70c1aced7/Laudo158-Bemol-2026-FabianeDaCostaMatos.pdf?expires_on=1785434474&amp;signature=pDCMZGw8yWeaYUy2M9ygtMRLz4nAM30fIKMJD75cXY0%3D</t>
         </is>
       </c>
       <c r="V144">
@@ -19320,7 +19320,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fded754d-f2ac-4c93-9387-04ab8656c650/Laudo33-Bemol-2026-FabioCesarPimentaGoulart-Assinado.pdf?expires_on=1785434314&amp;signature=5ZWS24bH58Gv4IVlO%2F2Gy7vGi1EdpbyWNSHH8kw8njg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fded754d-f2ac-4c93-9387-04ab8656c650/Laudo33-Bemol-2026-FabioCesarPimentaGoulart-Assinado.pdf?expires_on=1785434474&amp;signature=us%2FQTkx8QvuuEpKYdG1lTYxaJ6BbANGIJlXLVK5sgns%3D</t>
         </is>
       </c>
       <c r="V145">
@@ -19462,7 +19462,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c58213ad-7761-4ae6-9870-546591f93a06/LAUDOFABIOLAcorrigido.pdf?expires_on=1785434314&amp;signature=%2Fd1X%2BzSQpaS2rKLet5hYSRRyJLRe%2BcefjC1%2B1UEtPSw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c58213ad-7761-4ae6-9870-546591f93a06/LAUDOFABIOLAcorrigido.pdf?expires_on=1785434474&amp;signature=KVoRKxjXnf5KaRtJ696%2BcZH3V%2F1wT8%2BAI2XCcHEqegA%3D</t>
         </is>
       </c>
       <c r="V146">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2a3a19e0-19b0-4095-bf3f-8a7be5a4c3ab/LaudoB129-2025-BEMOL-FABRICIAFELIXBEZERRA.pdf?expires_on=1785434314&amp;signature=8We1prTaQ7xI%2FafqLsx8b9RuJgZ9f5WOOeFXonwXXZ8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2a3a19e0-19b0-4095-bf3f-8a7be5a4c3ab/LaudoB129-2025-BEMOL-FABRICIAFELIXBEZERRA.pdf?expires_on=1785434474&amp;signature=kEskgOD47SB6qrIJSUKqMIGY0v1v4UokOCRCJJGEWRA%3D</t>
         </is>
       </c>
       <c r="V147">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fbd53a6d-2555-48b3-a7eb-db3130ed48eb/LaudoA07-Bemol-2026-FabricioBrazDeOliveira_signed.pdf?expires_on=1785434314&amp;signature=oaDhTrMoKMBlcCIc8qWa%2FXoe9RdsXC9bbKXZxGYgNjg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fbd53a6d-2555-48b3-a7eb-db3130ed48eb/LaudoA07-Bemol-2026-FabricioBrazDeOliveira_signed.pdf?expires_on=1785434474&amp;signature=Z19HOjo6AYfzExkHpZI1jABAPp5dm%2B3zSV8O8G0IpO8%3D</t>
         </is>
       </c>
       <c r="V148">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/17b79224-a2d0-4ed1-bccd-8be40d372c0c/LaudoPA02-Bemol-2026-FatimaBentesDeSouza-Assinado.pdf?expires_on=1785434314&amp;signature=VZcMluq16moBf5tjzxwGQ4wM1ayMbJV3Dd4RPDKvGk0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/17b79224-a2d0-4ed1-bccd-8be40d372c0c/LaudoPA02-Bemol-2026-FatimaBentesDeSouza-Assinado.pdf?expires_on=1785434474&amp;signature=BVuv7zgP4fNwgKhWDbBmw7i67B%2BKhFlhS1SesZd2HxY%3D</t>
         </is>
       </c>
       <c r="V149">
@@ -20009,7 +20009,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e38cf222-5503-4e97-bbef-238ef7056e68/LaudoB10-2026-BEMOL-FAUEZFLAVIOPAIOLA_2.pdf?expires_on=1785434314&amp;signature=oOEd1DucgRm9aSvYhl6F6Y3lXmqonnNBzmAfDF6Wgqs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e38cf222-5503-4e97-bbef-238ef7056e68/LaudoB10-2026-BEMOL-FAUEZFLAVIOPAIOLA_2.pdf?expires_on=1785434474&amp;signature=%2BWeq%2BpEfdvcKmHXyPwRGVbz9Lyj3JQM9J5D3JRUF3CM%3D</t>
         </is>
       </c>
       <c r="V150">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cc113fdd-7aca-4e34-82ce-e8009e845604/Laudo46-Bemol-2026-FernandaPrestesDeLima-Assinado.pdf?expires_on=1785434314&amp;signature=NUE4x6jxu9Ck8KQM5Jr9FFdUzH4MklVGbrPHRiIbG3M%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cc113fdd-7aca-4e34-82ce-e8009e845604/Laudo46-Bemol-2026-FernandaPrestesDeLima-Assinado.pdf?expires_on=1785434474&amp;signature=vSs3n33hNirINP5f85wvvSTJjfLgLUkCs%2FQ5wDWOGNs%3D</t>
         </is>
       </c>
       <c r="V151">
@@ -20269,7 +20269,7 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e0f0ad2f-9e01-417c-a8f9-c1ca243eb234/LaudoJP05-Bemol-2026-ClaudiaBatistaDaCosta_signed.pdf?expires_on=1785434314&amp;signature=hd6pHVm47WiAGWGK7fp0FCAliBmKi8pFYcE2QsWmqLs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e0f0ad2f-9e01-417c-a8f9-c1ca243eb234/LaudoJP05-Bemol-2026-ClaudiaBatistaDaCosta_signed.pdf?expires_on=1785434474&amp;signature=%2FiqqJMQfHI5THDvUfcb2mIwBcsPn83P8tBSFka7QyFw%3D</t>
         </is>
       </c>
       <c r="V152">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/76f476fd-df6d-46b3-b38f-f6dd09998f3f/LAUDOFILEMON.pdf?expires_on=1785434314&amp;signature=vn5tVSl3ceY8YKICInwuZo%2FIRJRS%2BBXaLOHNHX%2FanLw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/76f476fd-df6d-46b3-b38f-f6dd09998f3f/LAUDOFILEMON.pdf?expires_on=1785434474&amp;signature=vGvaTHIuiDLCGPGbT9wEy4KnJgKym864g3dv8j0uw74%3D</t>
         </is>
       </c>
       <c r="V153">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/91d22aa8-c9b2-4d21-b3bd-d33060fc5321/Laudo116-Bemol-2026-FelipeCelaMoraesFilho-Assinado.pdf?expires_on=1785434314&amp;signature=qGBW1LPA%2FWy9AchEJWc1VJhGgWP2gieLZIyaQo%2B3244%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/91d22aa8-c9b2-4d21-b3bd-d33060fc5321/Laudo116-Bemol-2026-FelipeCelaMoraesFilho-Assinado.pdf?expires_on=1785434474&amp;signature=dsiZOlb1vRj4RiA7Ri%2FSLV0QhCly2XXEa6VA1Dw8D1E%3D</t>
         </is>
       </c>
       <c r="V154">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7b14bcf2-d078-42ca-9a36-bc05ae8b7690/Laudo61-Bemol-2026-FlaviaQueirozdaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=2T1cXMS1S2Gg%2BeZr8otkVQxHul3nELP4HL1X4T%2BMSfk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7b14bcf2-d078-42ca-9a36-bc05ae8b7690/Laudo61-Bemol-2026-FlaviaQueirozdaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=zkinNmQbjGJ%2BHY3awq89BY%2BDqH%2BuFZa411nLdj%2Fkhkw%3D</t>
         </is>
       </c>
       <c r="V155">
@@ -20779,7 +20779,7 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/30219338-9c6b-4770-b8ea-27a5cbf60368/M18-2026-FLAVIO.pdf?expires_on=1785434314&amp;signature=WicFYamDwakkd1w80xSAdNwOoHx3jZUe5DXcLYbVVtk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/30219338-9c6b-4770-b8ea-27a5cbf60368/M18-2026-FLAVIO.pdf?expires_on=1785434474&amp;signature=3QsOQQBsiNg4xSUYSNn%2FeGkk1pOZVNZTCrMfn6GXdA8%3D</t>
         </is>
       </c>
       <c r="V156">
@@ -20910,7 +20910,7 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c10fe8dc-e55f-465e-b1ea-81d40b9e1233/Laudo89-Bemol-2026-FrancibertoBandeiraDaCosta-Assinado.pdf?expires_on=1785434314&amp;signature=rbDCNnJCVXPCLIsl4yMPVzUg7pmxT4wFc7RFUs9rRLQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c10fe8dc-e55f-465e-b1ea-81d40b9e1233/Laudo89-Bemol-2026-FrancibertoBandeiraDaCosta-Assinado.pdf?expires_on=1785434474&amp;signature=A1VHtHggbMCI1XCmhi7vNzt%2FgtVUc9mhVcT8tLwx2KM%3D</t>
         </is>
       </c>
       <c r="V157">
@@ -21039,7 +21039,7 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/aadac529-7fed-4e2d-bd52-b67b4f7726f3/BEMOL-JP035-FRANCIELYBATISTADEALMEIDA.pdf?expires_on=1785434314&amp;signature=aI22OBncCb9QnFSN4aFMV%2B06MY9BGeNLlj%2Bu4%2B79cSI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/aadac529-7fed-4e2d-bd52-b67b4f7726f3/BEMOL-JP035-FRANCIELYBATISTADEALMEIDA.pdf?expires_on=1785434474&amp;signature=Ra%2Bv5VmkkcoFg5y1H5lg9xQGIlw3iU64lr9bZezMEmw%3D</t>
         </is>
       </c>
       <c r="V158">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/696900ba-642e-4a87-ac33-a5a2122e6553/Laudo177-Bemol-2026-FrancimaraCordeiroCelada.pdf?expires_on=1785434314&amp;signature=OFEHetX8TvuBOcTF9OyighhNKqdezZwQG4BZQgJ7nfM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/696900ba-642e-4a87-ac33-a5a2122e6553/Laudo177-Bemol-2026-FrancimaraCordeiroCelada.pdf?expires_on=1785434474&amp;signature=P1WbTwDQ7MuUx5SalBUz0b1fsryjJzZYHlEdhLtM91Q%3D</t>
         </is>
       </c>
       <c r="V159">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a285153-7890-4129-bd45-e2b8b03d378a/Laudo24-Bemol-2026-FranciscaCostaDoAmaral-Assinado.pdf?expires_on=1785434314&amp;signature=AAhE%2FfWm%2F26YWRYodguvmC%2FcZb53Bs4CVt8u0El3B3k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a285153-7890-4129-bd45-e2b8b03d378a/Laudo24-Bemol-2026-FranciscaCostaDoAmaral-Assinado.pdf?expires_on=1785434474&amp;signature=UzaYfbqZMR%2FeoyBrDOQC4IgVau1MOkgqkYrbmnDAVtQ%3D</t>
         </is>
       </c>
       <c r="V160">
@@ -21433,7 +21433,7 @@
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/59088886-f0ae-4236-8b1a-e1ffe17e49fd/LaudoB38-2026-BEMOL-FRANCISCADASCHAGASSILVADOSSANTOS.pdf?expires_on=1785434314&amp;signature=70WXQefVOCanN6BI2n1RjnCmVY5v9TIOaOqoCxYmVZE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/59088886-f0ae-4236-8b1a-e1ffe17e49fd/LaudoB38-2026-BEMOL-FRANCISCADASCHAGASSILVADOSSANTOS.pdf?expires_on=1785434474&amp;signature=jDgwqL4N%2BaweH%2FkXe4XMc6T6n%2FKaQ5Gmm2LEoCYd%2F%2BI%3D</t>
         </is>
       </c>
       <c r="V161">
@@ -21571,7 +21571,7 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7f9fefc9-e1ae-43f6-9d90-569732f82957/LaudoB56-2026-BEMOL-FranciscaVianaCabral.pdf?expires_on=1785434314&amp;signature=3e2Ueys5nTGgN0fYpi32o6S0vPROugQwfpH5BmuYIHs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7f9fefc9-e1ae-43f6-9d90-569732f82957/LaudoB56-2026-BEMOL-FranciscaVianaCabral.pdf?expires_on=1785434474&amp;signature=bpbO9GqZGeocqt8zvBRJRwN4cjnrsKXkwWOfjdLfSnk%3D</t>
         </is>
       </c>
       <c r="V162">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/46015ed7-e8ee-4fcf-81c2-dce488b66f97/LaudoB37-2026-BEMOL-FRANCISCOALVESDECARVALHOFILHO.pdf?expires_on=1785434314&amp;signature=7f3AAdhRvd%2BvDu6UcmViS4vG1MNqApIgh4Dtm0Ntq0k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/46015ed7-e8ee-4fcf-81c2-dce488b66f97/LaudoB37-2026-BEMOL-FRANCISCOALVESDECARVALHOFILHO.pdf?expires_on=1785434474&amp;signature=785u3OLszdKT9g0hAAqPQ9FuW2i9lmgx8EOYqcIKRvw%3D</t>
         </is>
       </c>
       <c r="V163">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e6d71bf1-06a5-438c-88d3-a62e47e95a34/Laudo48-Bemol-2026-FranciscoBandeiraPrestes-Assinado.pdf?expires_on=1785434314&amp;signature=49d8Qn0PyJq4gzCG4%2Bd3XplEKtchnvLSf7%2B4mUWOWyQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e6d71bf1-06a5-438c-88d3-a62e47e95a34/Laudo48-Bemol-2026-FranciscoBandeiraPrestes-Assinado.pdf?expires_on=1785434474&amp;signature=%2FpfvffdZ3i4OjEjke%2Bj9WVUySC%2BxTJEjBoAtL%2BxUOsU%3D</t>
         </is>
       </c>
       <c r="V164">
@@ -21950,7 +21950,7 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/404a2496-5d75-47a3-8332-0a14a23dd08a/LaudoP21-Bemol-2026-FranciscoDasChagasRodrigues_signed.pdf?expires_on=1785434314&amp;signature=kfOyzl4aFM2gxmG228VnvLZKjEk6PBPIW0m%2FSYjvXxM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/404a2496-5d75-47a3-8332-0a14a23dd08a/LaudoP21-Bemol-2026-FranciscoDasChagasRodrigues_signed.pdf?expires_on=1785434474&amp;signature=922LMvKDjkzPouzjUgchmxWJrInAqfRPbEet0JdAfgw%3D</t>
         </is>
       </c>
       <c r="V165">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/25200ae2-be9b-48e6-b520-802786df80dc/B135-2024-BEMOL-FRANCISCODEASSISDACONCEIO.pdf?expires_on=1785434314&amp;signature=ucotg0%2BM%2BNljsNU5xTQzXhqmMztKIxjuH0z%2Btd98EYg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/25200ae2-be9b-48e6-b520-802786df80dc/B135-2024-BEMOL-FRANCISCODEASSISDACONCEIO.pdf?expires_on=1785434474&amp;signature=z8tR06d3bPBxk7ukE2yeXen4Xk6PNv2IEpaeoC4EeXE%3D</t>
         </is>
       </c>
       <c r="V166">
@@ -22198,7 +22198,7 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/344fb1c8-16f0-4427-94fa-0961e47993c5/BEMOL-PV075-FRANCISCOMAIABATISTA.pdf?expires_on=1785434314&amp;signature=3mdzRxfw69wpeZchsGFNfMwhjO8cnfQFZ%2F0NqvseDSM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/344fb1c8-16f0-4427-94fa-0961e47993c5/BEMOL-PV075-FRANCISCOMAIABATISTA.pdf?expires_on=1785434474&amp;signature=uPyD%2Ba0kU4cCOjCy01WE0IKxKcVeR%2BWbcM3Cex6O%2Bo4%3D</t>
         </is>
       </c>
       <c r="V167">
@@ -22317,7 +22317,7 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/388ec1b4-83f3-441c-967f-ceb7668fb045/LAUDOFRANCISCODONASCIMENTODASILVA.pdf?expires_on=1785434314&amp;signature=u8k1fmmBJMGCfLx3%2Ftp%2Fk%2FyP7B3Kyt6xj15D1%2BIaycA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/388ec1b4-83f3-441c-967f-ceb7668fb045/LAUDOFRANCISCODONASCIMENTODASILVA.pdf?expires_on=1785434474&amp;signature=M32%2BF391Mr9MMi%2FhUzqZDeWq2k236aRdIk%2Bc2dXU2DI%3D</t>
         </is>
       </c>
       <c r="V168">
@@ -22443,7 +22443,7 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9fcbba4c-0bc2-4661-acce-3c1f7cf014e4/Laudo112-Bemol-2026-FranciscoPereiraChaul-Assinado.pdf?expires_on=1785434314&amp;signature=d2wONO5%2BNNHoAr264OLVPgdc3sF5UOdSm4kzUof51qc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9fcbba4c-0bc2-4661-acce-3c1f7cf014e4/Laudo112-Bemol-2026-FranciscoPereiraChaul-Assinado.pdf?expires_on=1785434474&amp;signature=jSHD0rt%2Fn1NcklyWAV0kWlf%2F3ajwrBvyi%2FDcPXR3gLA%3D</t>
         </is>
       </c>
       <c r="V169">
@@ -22592,7 +22592,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f5ec4f52-4ff3-4961-a180-72f6941834e9/franciscoregilsoncorrigido.pdf?expires_on=1785434314&amp;signature=SO3PIKDkm3P2SIm1tGl9risjMFvbjkq4tNnghRn5cZ4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f5ec4f52-4ff3-4961-a180-72f6941834e9/franciscoregilsoncorrigido.pdf?expires_on=1785434474&amp;signature=qDQ5fDuUpai4wA%2BavVXgngFuo1Z682KGnE2DtDDI3wU%3D</t>
         </is>
       </c>
       <c r="V170">
@@ -22727,7 +22727,7 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9e0c7418-7661-4dd8-91d2-8a739caee94f/Laudo25-Bemol-2026-FrankChavesDeAraujo-Assinado.pdf?expires_on=1785434314&amp;signature=enyLHgNlQtZKlQRmcYzFIYkIXZ7gqSgVyOzmF5XvBpE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9e0c7418-7661-4dd8-91d2-8a739caee94f/Laudo25-Bemol-2026-FrankChavesDeAraujo-Assinado.pdf?expires_on=1785434474&amp;signature=JUegy4JT8zmBqc8inmykIqpa0A5hTh5DZ3nIjH2yhuw%3D</t>
         </is>
       </c>
       <c r="V171">
@@ -22859,7 +22859,7 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7d625810-a63c-4e31-b581-22989af9a8c9/LAUDOFRANKLINcorrigido.pdf?expires_on=1785434314&amp;signature=%2F1AjLpAvTSRJjfTmTa8f%2F3b888u8PfSiciDqVpop7E0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7d625810-a63c-4e31-b581-22989af9a8c9/LAUDOFRANKLINcorrigido.pdf?expires_on=1785434474&amp;signature=IjOyaifam%2BDJT7dALB%2FPlh61ku7ok2E1W1HQ%2BE7raO8%3D</t>
         </is>
       </c>
       <c r="V172">
@@ -22987,7 +22987,7 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0c8e504e-71a8-4d99-a84c-820633f6f537/Laudo149-Bemol-2026-GabrielaOliveiraDeSouza.pdf?expires_on=1785434314&amp;signature=JlQIG2gpGAxWS4MRbqZb8eeyYbYk0aN6j72GuvQWFkY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0c8e504e-71a8-4d99-a84c-820633f6f537/Laudo149-Bemol-2026-GabrielaOliveiraDeSouza.pdf?expires_on=1785434474&amp;signature=FvB%2BpN6TAQFVYKrUWla3%2Bv2oEjbXjLqAINGmceTEp6Q%3D</t>
         </is>
       </c>
       <c r="V173">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/45997a27-288e-4063-a9cb-2c25e998c9ea/LAUDOGERSON.pdf?expires_on=1785434314&amp;signature=RWMa1SSDwHqfmy6LmHNnWyl%2B8LofF42KT70LZAGNoac%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/45997a27-288e-4063-a9cb-2c25e998c9ea/LAUDOGERSON.pdf?expires_on=1785434474&amp;signature=Em6xfGufr8STusAYT2m%2FObudAh2mIL16eG3CusVnMdU%3D</t>
         </is>
       </c>
       <c r="V174">
@@ -23239,7 +23239,7 @@
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a3800c1e-5776-499b-aa65-72bc5d5c7e84/LaudoB55-2026-BEMOL-GERVANIADOSREISRIBEIROFRANCA.pdf?expires_on=1785434314&amp;signature=ZIFbO9NLNMBS5i84BIAJEVL1A%2FtcMP2G97YsIj%2BkyxU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a3800c1e-5776-499b-aa65-72bc5d5c7e84/LaudoB55-2026-BEMOL-GERVANIADOSREISRIBEIROFRANCA.pdf?expires_on=1785434474&amp;signature=n66JDmXFiF%2FNYjYE3Y%2F0Q6vEDipocCQnIdEWEvNYq7E%3D</t>
         </is>
       </c>
       <c r="V175">
@@ -23379,7 +23379,7 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/acacdca6-3cbd-4beb-8e6a-550a96cd4457/Laudo06-Bemol-2026-GilbersonFigueiraBarbosa-Assinado.pdf?expires_on=1785434314&amp;signature=Os72sFMyaKkxJg3MycXAIfWy7NHymE9yNVW60EWYYb4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/acacdca6-3cbd-4beb-8e6a-550a96cd4457/Laudo06-Bemol-2026-GilbersonFigueiraBarbosa-Assinado.pdf?expires_on=1785434474&amp;signature=NaoBzH6ard4eWRLWdkNxBQrXgBeMKw2IRw%2F6O%2BsD%2FJE%3D</t>
         </is>
       </c>
       <c r="V176">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/985f7116-d23f-4aee-8607-12f7ae4f306e/BEMOL-PV064-GilbsonPereiradeMorais.pdf?expires_on=1785434314&amp;signature=MwS0H%2BmbsmJMpqxx7ugMgg8Y8IfIRo8QEf8SBuQdRS0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/985f7116-d23f-4aee-8607-12f7ae4f306e/BEMOL-PV064-GilbsonPereiradeMorais.pdf?expires_on=1785434474&amp;signature=AtmvSvTdYzxp2u6uv%2Bunf2zH3q0ZCTig8lUwboSgdl8%3D</t>
         </is>
       </c>
       <c r="V177">
@@ -23673,7 +23673,7 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e20bd625-bdff-49a2-982c-0f83256d23d2/Laudo70-Bemol-2026-GilmaraBrasilDeSeixas-Assinado.pdf?expires_on=1785434314&amp;signature=%2BbbGLSaiKDE9pW6i%2FGNNAxUMfVUTXt3cKf324dLtV5c%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e20bd625-bdff-49a2-982c-0f83256d23d2/Laudo70-Bemol-2026-GilmaraBrasilDeSeixas-Assinado.pdf?expires_on=1785434474&amp;signature=NCH02iP4o%2Bp4PyOfSqdFF5sMOj3lC4OPYP22qWNAtL4%3D</t>
         </is>
       </c>
       <c r="V178">
@@ -23813,7 +23813,7 @@
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1187e87b-ca2a-4edf-a915-c1e1bf6ac0a3/Laudo148-Bemol-2026-GiovannaOliveiradosSantos.pdf?expires_on=1785434314&amp;signature=8F6qBWKLoQeHa8c4%2BUmWZaXGJE7uv1a50I%2F7wOvBZKo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1187e87b-ca2a-4edf-a915-c1e1bf6ac0a3/Laudo148-Bemol-2026-GiovannaOliveiradosSantos.pdf?expires_on=1785434474&amp;signature=xNqszpyQ4vbHIdMitVzECvI192IQM01Y3ms6SPROmDw%3D</t>
         </is>
       </c>
       <c r="V179">
@@ -23950,7 +23950,7 @@
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7dc6bd5c-fe1c-4d6b-a0ef-77e8ad596c6e/LaudoRVR02-Bemol-2026-GiseleSilvaDeLima-Assinado.pdf?expires_on=1785434314&amp;signature=m24DBmXB5ga3poWWA1l37jLVA2bYkQnkOMm2wJILZDI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7dc6bd5c-fe1c-4d6b-a0ef-77e8ad596c6e/LaudoRVR02-Bemol-2026-GiseleSilvaDeLima-Assinado.pdf?expires_on=1785434474&amp;signature=qBIlfcXMBp9F4YYpdo0nvE1CEHKqO9DySWa1hhjSiCM%3D</t>
         </is>
       </c>
       <c r="V180">
@@ -24074,7 +24074,7 @@
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3a55d15e-7280-429f-8bb5-14c737b4a32e/BEMOL-AR023-GLAUCIADEARRUDADOMINGUEScorrigido.pdf?expires_on=1785434314&amp;signature=PfXP56iMWUJeZ%2BQc0JOdo9jzXOT%2FAJ15gn5vxxLCvcA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3a55d15e-7280-429f-8bb5-14c737b4a32e/BEMOL-AR023-GLAUCIADEARRUDADOMINGUEScorrigido.pdf?expires_on=1785434474&amp;signature=qFRWu70xQNR9cgeOQtkL3ERAhQXKKuydtToeLTTOIHo%3D</t>
         </is>
       </c>
       <c r="V181">
@@ -24213,7 +24213,7 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f884ee63-cf10-4b1e-910d-ea270de3b978/LAUDOGLAUCO.pdf?expires_on=1785434314&amp;signature=CHf%2FCqBUewCCSOw4UWrhcC78qfMhbbRbe4NJu4Zhkgw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f884ee63-cf10-4b1e-910d-ea270de3b978/LAUDOGLAUCO.pdf?expires_on=1785434474&amp;signature=%2F84E8jNqxMAKER6eHPFSI2Kd0GMad8SO1RFSD95JNpI%3D</t>
         </is>
       </c>
       <c r="V182">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7bc1af1f-4d89-4f54-81c4-e0a39a33e154/Laudo153-Bemol-2026-GliciaCardosoDosSantosCabral-Assinado.pdf?expires_on=1785434314&amp;signature=pZUN1T70NjFMCmM95Z%2BXtozBjgE7olvl%2BHWgIf3mdcA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7bc1af1f-4d89-4f54-81c4-e0a39a33e154/Laudo153-Bemol-2026-GliciaCardosoDosSantosCabral-Assinado.pdf?expires_on=1785434474&amp;signature=ZrSe7VYFb93EfHDNCUa9S6dDQ6zkF9NkWDryv0zrdzE%3D</t>
         </is>
       </c>
       <c r="V183">
@@ -24476,7 +24476,7 @@
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/91c2a256-8df1-47ab-9b2c-21e2da22aa03/LaudoITA07-Bemol-2026-GustavoDosSantosCorreaDeAzevedo-Assinado.pdf?expires_on=1785434314&amp;signature=hR9nm9dKJxmCgzcBKBX1qODn%2FcO5%2FYeqe62a3jg%2BP7A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/91c2a256-8df1-47ab-9b2c-21e2da22aa03/LaudoITA07-Bemol-2026-GustavoDosSantosCorreaDeAzevedo-Assinado.pdf?expires_on=1785434474&amp;signature=4gEf7bLQH7Y60ucxcU1pNHX219uzpd4dmZdXNj9iVyU%3D</t>
         </is>
       </c>
       <c r="V184">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/84e417bf-6e94-401d-a747-8df0b5a6545d/Laudo_AC_10-2026_-_DEUSIMAR_MENEZES_DA_SILVA_assinado.pdf?expires_on=1785434314&amp;signature=hf9ouLFoxIUI%2BTYiXaSdizpRbzrA2mF0pu%2BE3F8XVOE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/84e417bf-6e94-401d-a747-8df0b5a6545d/Laudo_AC_10-2026_-_DEUSIMAR_MENEZES_DA_SILVA_assinado.pdf?expires_on=1785434474&amp;signature=xYmYU29igh%2FFA09m%2FQTe%2FW144nFT67O%2BgNJ8WSneNuA%3D</t>
         </is>
       </c>
       <c r="V185">
@@ -24747,7 +24747,7 @@
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f56afaf9-298b-4a77-a9f2-8187b2f0360a/LaudoP07-Bemol-2026-GustavoVianaDaSilva_signed.pdf?expires_on=1785434314&amp;signature=XrUkXl%2F82PSxpgr71pSHspFBKtsX%2B7yRI7KPuG7SKUw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f56afaf9-298b-4a77-a9f2-8187b2f0360a/LaudoP07-Bemol-2026-GustavoVianaDaSilva_signed.pdf?expires_on=1785434474&amp;signature=mJ7EPv14JGauASBuCHA4c7eRNeFcd78w4fZXUfmDFsI%3D</t>
         </is>
       </c>
       <c r="V186">
@@ -24879,7 +24879,7 @@
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7c23a673-4290-4995-9960-a4b6a6384bcf/Laudo350-Bemol-2025-HelanieCascaesAbreu-Assinado.pdf?expires_on=1785434314&amp;signature=Mcj%2B5H1FEaVrfYrwuvslYXtn%2FmB90%2B3CTVLiJ%2FYRHZs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7c23a673-4290-4995-9960-a4b6a6384bcf/Laudo350-Bemol-2025-HelanieCascaesAbreu-Assinado.pdf?expires_on=1785434474&amp;signature=Mr8P0hlgLXmy5GFJGUEx6ocqV8bF2pGIjPfj6HrtNig%3D</t>
         </is>
       </c>
       <c r="V187">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a91aa31e-d799-4e5a-bcf3-891b838e0803/Laudo160-Bemol-2026-HeliodoroFonsecaGuerreiroFilho-Assinado.pdf?expires_on=1785434314&amp;signature=T34GaIPCz4QPhPByqmxSmPgHrNQVjtWturkEcsrvK0A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a91aa31e-d799-4e5a-bcf3-891b838e0803/Laudo160-Bemol-2026-HeliodoroFonsecaGuerreiroFilho-Assinado.pdf?expires_on=1785434474&amp;signature=ujJrbHoXeGGV1wCOTszIVtX%2FQfs2dC%2F2lTPq5YkhHx4%3D</t>
         </is>
       </c>
       <c r="V188">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8844ac9a-59bb-4f2c-aff8-72fb3f9c9eeb/LaudoPA21-Bemol-2026-HernandesJesusdosSantos-Assinado.pdf?expires_on=1785434314&amp;signature=n1ZyfohWcFetfROjEUk4gbg9xZHT3%2BO6glCMrcXKI1c%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8844ac9a-59bb-4f2c-aff8-72fb3f9c9eeb/LaudoPA21-Bemol-2026-HernandesJesusdosSantos-Assinado.pdf?expires_on=1785434474&amp;signature=6kPyTd3UpFzg2zXkA47FkmpJCkQEAI6bXAJwTezKOyA%3D</t>
         </is>
       </c>
       <c r="V189">
@@ -25278,7 +25278,7 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ea1b9e95-887a-4691-a5b4-6bc283ebade6/Laudo140-Bemol-2026-IagoDaSilvaRodrigues.pdf?expires_on=1785434314&amp;signature=f%2B4hj1gaRnhRSnb7x0NfkKx%2BZqsRgy52UPR%2BE%2BDtX3A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ea1b9e95-887a-4691-a5b4-6bc283ebade6/Laudo140-Bemol-2026-IagoDaSilvaRodrigues.pdf?expires_on=1785434474&amp;signature=mmLhqT1UPKM3aE6xdKeq5%2FeqJlT%2FkghQ1P4lC5I1Yqw%3D</t>
         </is>
       </c>
       <c r="V190">
@@ -25410,7 +25410,7 @@
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a3957666-2105-4c3c-8ef9-39e77bc1dc39/LaudoA02-Bemol-2026-IaraDosSantosSchimanech_signed.pdf?expires_on=1785434314&amp;signature=gRqAQZly1fLwc7N09GP9jgI8nrk0FAaAfxcwUAj21Wg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a3957666-2105-4c3c-8ef9-39e77bc1dc39/LaudoA02-Bemol-2026-IaraDosSantosSchimanech_signed.pdf?expires_on=1785434474&amp;signature=rhk9iBRzrNRP8ZkNzKIJ8aosvHsJVo5dkLNyzdbpOiE%3D</t>
         </is>
       </c>
       <c r="V191">
@@ -25533,7 +25533,7 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/34f61018-bea2-4b9b-b81c-3f276e3c94f2/LaudoITA13-Bemol-2026-IdelfonsoMonteiroRibeiro.pdf?expires_on=1785434314&amp;signature=VFUy1cZDTZRUyvj5thqJVdQ7lmIi%2BrfjX7FDTf50PQk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/34f61018-bea2-4b9b-b81c-3f276e3c94f2/LaudoITA13-Bemol-2026-IdelfonsoMonteiroRibeiro.pdf?expires_on=1785434474&amp;signature=KmHpVOrHF8XZZghncniPmrRto9oEWCTo5E4nwhKr0l8%3D</t>
         </is>
       </c>
       <c r="V192">
@@ -25659,7 +25659,7 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c3f2997b-58e6-441e-bad9-6dd576d60062/LAUDOINEZ.pdf?expires_on=1785434314&amp;signature=kPqX5xN%2FPa%2BLf%2BAjm9PbY1PMueIuzXpyJKbNAZvBHrQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c3f2997b-58e6-441e-bad9-6dd576d60062/LAUDOINEZ.pdf?expires_on=1785434474&amp;signature=G7kILNL2r0zXV6cIPWfxmWmjMZNEV7HF1JHqC34Nx9c%3D</t>
         </is>
       </c>
       <c r="V193">
@@ -25789,7 +25789,7 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/adb8967f-721a-44b2-b57c-06dba882887a/Laudo67-Bemol-2026-IolandaBasilioBenevides-Assinado.pdf?expires_on=1785434314&amp;signature=UT68bLJS8dt0jBD9ya9GNvpqwXajJBAyjXkgErqONHk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/adb8967f-721a-44b2-b57c-06dba882887a/Laudo67-Bemol-2026-IolandaBasilioBenevides-Assinado.pdf?expires_on=1785434474&amp;signature=0ooM%2F3OFUzEP5oOv352wkEVu%2Fo2h8fmvg3fCLrAqP7g%3D</t>
         </is>
       </c>
       <c r="V194">
@@ -25922,7 +25922,7 @@
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f283e60d-0fe6-4679-9509-fe8f620eac06/LaudoB6-2026-BEMOL-IRANCARNEIRODEMACEDO.pdf?expires_on=1785434314&amp;signature=9OJganUI8GV%2FygEonB1shMKCdMXfXtSd%2B0IfNn9Sg6k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f283e60d-0fe6-4679-9509-fe8f620eac06/LaudoB6-2026-BEMOL-IRANCARNEIRODEMACEDO.pdf?expires_on=1785434474&amp;signature=3s3HH2kBaFwr0Yv7CYVWSVAq3YH6DQVBEHOOCTaIobU%3D</t>
         </is>
       </c>
       <c r="V195">
@@ -26059,7 +26059,7 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/057596ee-eb69-4dab-9a70-4c6bc66742b2/Laudo113-Bemol-2026-IraunaMaiconaBarrosdeCarvalho-Assinado.pdf?expires_on=1785434314&amp;signature=BleEs0DZXBzorjNiyNlEpBk7%2BeC7A4NP6MCuz2rBSTs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/057596ee-eb69-4dab-9a70-4c6bc66742b2/Laudo113-Bemol-2026-IraunaMaiconaBarrosdeCarvalho-Assinado.pdf?expires_on=1785434474&amp;signature=%2BOvw%2FfR0%2Brv2l2SAzhzrM1wvF%2BLBfkEjXwyf6OjzPTg%3D</t>
         </is>
       </c>
       <c r="V196">
@@ -26196,7 +26196,7 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/021e50b4-e24d-4ebb-8d0b-11127fb4eb05/RelatriodeValordeRefernciaRVR01-Bemol-2026-IrisFrotaDaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=TXQdW%2BC8aV%2FrrtbHi%2Bs7hG3%2B0U8%2BcpNvRHTcuuy655A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/021e50b4-e24d-4ebb-8d0b-11127fb4eb05/RelatriodeValordeRefernciaRVR01-Bemol-2026-IrisFrotaDaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=iy8QxUsTF52oW9BT51PowYm600Eb7wBIyAUdTRUmaSk%3D</t>
         </is>
       </c>
       <c r="V197">
@@ -26335,7 +26335,7 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/974e6369-461f-4ecf-960e-99a4e3c5062d/LaudoR01-2026-BEMOL-ISAIASARAUJOCRUZ_2corrigido.pdf?expires_on=1785434314&amp;signature=D4g%2B5Sj1S3%2BkNPfNNXvUQPv9GUaMiqxm2xFV8A57GMs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/974e6369-461f-4ecf-960e-99a4e3c5062d/LaudoR01-2026-BEMOL-ISAIASARAUJOCRUZ_2corrigido.pdf?expires_on=1785434474&amp;signature=MIny7sCWFmkN3XldKZMtGrfJOWMyiRxoUkxPc8LD690%3D</t>
         </is>
       </c>
       <c r="V198">
@@ -26488,7 +26488,7 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/26f94ea3-7ef7-4db4-b5be-72429fc6b275/Laudo11-Bemol-2026-IsaiasBritoDaRochaFilho-Assinado.pdf?expires_on=1785434314&amp;signature=iQKO39UuOhj7w0D2R5Vkj1XtljshDNaVFo2QAlSeOmc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/26f94ea3-7ef7-4db4-b5be-72429fc6b275/Laudo11-Bemol-2026-IsaiasBritoDaRochaFilho-Assinado.pdf?expires_on=1785434474&amp;signature=W9jkK4a0oFqV84INw3pCnxD7TM8%2Fm7ZPZIzGTC13cX4%3D</t>
         </is>
       </c>
       <c r="V199">
@@ -26618,7 +26618,7 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1501f5db-4f26-4c17-b525-cc5d06d5bae0/Laudo187-Bemol-2026-IvaMarcelinoDeSouza-Assinado.pdf?expires_on=1785434314&amp;signature=lN%2FKzP8imGPWq%2BRQp024X7RIZ4PmyM1TdjwwjpBDIC4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1501f5db-4f26-4c17-b525-cc5d06d5bae0/Laudo187-Bemol-2026-IvaMarcelinoDeSouza-Assinado.pdf?expires_on=1785434474&amp;signature=PEREKlu9TQdIXKt418THf7mjHZviC6gd3HVwjWQh70Y%3D</t>
         </is>
       </c>
       <c r="V200">
@@ -26747,7 +26747,7 @@
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/80c26842-a8a3-4839-ae2a-fec3d1ab4e70/LAUDOIVANETE.pdf?expires_on=1785434314&amp;signature=i2UJVE5xk8Mx0QSAxAEHNwLo3zRAv9MENQCW9O%2Fn1uo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/80c26842-a8a3-4839-ae2a-fec3d1ab4e70/LAUDOIVANETE.pdf?expires_on=1785434474&amp;signature=miUJjPxSqJ1OzK0Ti4jXpQ5sY1PS55rPZ9T1bwrHXVo%3D</t>
         </is>
       </c>
       <c r="V201">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f3c44a28-580d-4073-a0dc-e1ec71bfd207/LaudoT02-Bemol-2026-IvanildodeAraujoFerreira.pdf?expires_on=1785434314&amp;signature=qj0TraL7KJQwAcToG0GzVFWW2haeCCJeeVfnY5bRzuM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f3c44a28-580d-4073-a0dc-e1ec71bfd207/LaudoT02-Bemol-2026-IvanildodeAraujoFerreira.pdf?expires_on=1785434474&amp;signature=dSDwIrQaxLkxLVmnXhEzzpBDRbnbXROqO8HUALu3qH0%3D</t>
         </is>
       </c>
       <c r="V202">
@@ -27002,7 +27002,7 @@
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c335268a-013b-427f-bc2b-e716b9abbdbb/Laudo117-Bemol-2026-IvoneteGoncalvesDosSantos-Assinado.pdf?expires_on=1785434314&amp;signature=KwR%2BVjOC%2FUSXSabmel2XHcXBZpo7k6fS0nVEkhRrUvY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c335268a-013b-427f-bc2b-e716b9abbdbb/Laudo117-Bemol-2026-IvoneteGoncalvesDosSantos-Assinado.pdf?expires_on=1785434474&amp;signature=3CHqMv0LdPIyzsIck7DX6C68gYSoed0Tcyk2rXnsY6Y%3D</t>
         </is>
       </c>
       <c r="V203">
@@ -27121,7 +27121,7 @@
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/59cc3c3d-f732-4d4f-859d-0187a585b480/Laudo186-Bemol-2026-IvoneteMagalhaesDaSilva-Assinadoajustado.pdf?expires_on=1785434314&amp;signature=xei4CwGJ4OXVQTxURHgUhPmjl4cBp9k88HQ2lMU2Jak%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/59cc3c3d-f732-4d4f-859d-0187a585b480/Laudo186-Bemol-2026-IvoneteMagalhaesDaSilva-Assinadoajustado.pdf?expires_on=1785434474&amp;signature=uiCN9aYEaXUV%2BSt1xdxbNHIzDmZqWHG0xAAoa58MbJ4%3D</t>
         </is>
       </c>
       <c r="V204">
@@ -27245,7 +27245,7 @@
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/366567fd-fc3b-4139-9946-1127871896bb/LaudoB21-2026-BEMOL-IZABELAPARECIDAMACHADO.pdf?expires_on=1785434314&amp;signature=IYFOs2sT378PismxqOpIAK%2FtOrVb4qNJkgE2zzp1c94%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/366567fd-fc3b-4139-9946-1127871896bb/LaudoB21-2026-BEMOL-IZABELAPARECIDAMACHADO.pdf?expires_on=1785434474&amp;signature=%2B0%2F%2BNnp6dZfcdlf0twqzKnv5mL0fUY264t8me5MUzQo%3D</t>
         </is>
       </c>
       <c r="V205">
@@ -27363,7 +27363,7 @@
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/eaf87586-e6fe-4b9a-b754-385b00a87480/LAUDOIZABELE.pdf?expires_on=1785434314&amp;signature=82nxjpWGKyzRZCr9GLTzrhHvUqZci19sWiciwrWMr5Q%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/eaf87586-e6fe-4b9a-b754-385b00a87480/LAUDOIZABELE.pdf?expires_on=1785434474&amp;signature=Q2JShb38gGvJLb3KE%2FE%2BD63%2Fl8v58rc6L%2BvPEbYfq6g%3D</t>
         </is>
       </c>
       <c r="V206">
@@ -27482,7 +27482,7 @@
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a4cbc1de-57d1-4401-bbe3-bca8d904640d/Laudo142-Bemol-2026-IzabeleMaiadaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=3oeFLE2QGWw1sc0pSeiXQPUeR03qb6gv8D2olNsHViE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a4cbc1de-57d1-4401-bbe3-bca8d904640d/Laudo142-Bemol-2026-IzabeleMaiadaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=hH8XFkntCXWdUzSmjKTPuMs3FEOHjuYrLjhMabrA%2BcI%3D</t>
         </is>
       </c>
       <c r="V207">
@@ -27622,7 +27622,7 @@
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/482720e0-da58-4939-b51d-a6a2e0af0272/RelatriodeValordeRefernciaRVR07-Bemol-2025-IzadoraSantosNascimento-Assinado.pdf?expires_on=1785434314&amp;signature=zIte4fx19XbTEniBMeWkCXUSexqKUR33MPa6Dy9sxIU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/482720e0-da58-4939-b51d-a6a2e0af0272/RelatriodeValordeRefernciaRVR07-Bemol-2025-IzadoraSantosNascimento-Assinado.pdf?expires_on=1785434474&amp;signature=NlR7Js70DLoP4nDBc6ZKTYrKqH05FLRhMzP179cqyIs%3D</t>
         </is>
       </c>
       <c r="V208">
@@ -27761,7 +27761,7 @@
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1c8152d9-03f7-45fb-9bab-c6cfa31249d3/LaudoP11-Bemol-2026-IzamaraVieiraBraga_signed.pdf?expires_on=1785434314&amp;signature=5EbS5uEnK93aox1gWDN3B1z4KXvcQ3A29kecNWRNMDU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1c8152d9-03f7-45fb-9bab-c6cfa31249d3/LaudoP11-Bemol-2026-IzamaraVieiraBraga_signed.pdf?expires_on=1785434474&amp;signature=Rb23bdJSpg8YoWdBokcPDgoKYjoUskDrk4anj1kyjY4%3D</t>
         </is>
       </c>
       <c r="V209">
@@ -27892,7 +27892,7 @@
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/dded52eb-bf72-4b8b-91b5-814e5d7289a1/LaudoITA39-Bemol-2025-IzomarFariasRamos_signed.pdf?expires_on=1785434314&amp;signature=MvjFu9ADshoRcdOfi%2FHI%2BRcCLtVhvKktJiI2mYmfhr0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/dded52eb-bf72-4b8b-91b5-814e5d7289a1/LaudoITA39-Bemol-2025-IzomarFariasRamos_signed.pdf?expires_on=1785434474&amp;signature=%2B8T%2FghPCs92dqqklGDcIc7Q%2FZIJasDmHwkyZEUv74tk%3D</t>
         </is>
       </c>
       <c r="V210">
@@ -28035,7 +28035,7 @@
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1aef0609-59d2-4183-92d2-5a7eebabad95/Laudo197-Bemol-2026-JacquelineSalesSantos.pdf?expires_on=1785434314&amp;signature=Ipci9SJZ%2BsvlwjI0mSIBKXtoYquWlj3HEt1sKb57UnQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1aef0609-59d2-4183-92d2-5a7eebabad95/Laudo197-Bemol-2026-JacquelineSalesSantos.pdf?expires_on=1785434474&amp;signature=9Xj0fYDwFLf68%2FvLx8V3WvxzlJuOIkTCvo5pn0S1wJA%3D</t>
         </is>
       </c>
       <c r="V211">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e609c540-9083-4e3f-9019-8c5e5b127f44/Laudo172-Bemol-2026-JailsonDaSilvaPontes-Assinado.pdf?expires_on=1785434314&amp;signature=8y3TTkESzpe65nFlC7u%2FZ6qP%2FLwu4O7De95Izz04LvI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e609c540-9083-4e3f-9019-8c5e5b127f44/Laudo172-Bemol-2026-JailsonDaSilvaPontes-Assinado.pdf?expires_on=1785434474&amp;signature=GZNb%2FRIDWBGzxXTt1MA0HOn%2FBvAk%2B1ofMmf3o%2B34M18%3D</t>
         </is>
       </c>
       <c r="V212">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/eeab7072-bd88-492b-bfe5-746cd9ff8e4d/Laudo191-Bemol-2026-JamilysSantanaDeSouza-Assinado.pdf?expires_on=1785434314&amp;signature=jMDZQanxYmM8VZo39zQFB2o5GJxNn0aVF1uyNKXrm3E%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/eeab7072-bd88-492b-bfe5-746cd9ff8e4d/Laudo191-Bemol-2026-JamilysSantanaDeSouza-Assinado.pdf?expires_on=1785434474&amp;signature=%2FYVYLbJyag99B8KoATaE%2FXgJyzRFHoBA95DjeITtp%2FY%3D</t>
         </is>
       </c>
       <c r="V213">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2ff6e778-db4e-4b7e-9589-a6a856fcc77a/Laudo69-Bemol-2026-JandersonFreitasLopes-Assinado.pdf?expires_on=1785434314&amp;signature=Q4Hb9hNXpGu52JzB6tO7iHM10BScmhIwTtoRn9DdyDo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2ff6e778-db4e-4b7e-9589-a6a856fcc77a/Laudo69-Bemol-2026-JandersonFreitasLopes-Assinado.pdf?expires_on=1785434474&amp;signature=Xjk44nMkH5eYXTeVXMah3w4l%2F2VhOy4aqDw3PCJVi0w%3D</t>
         </is>
       </c>
       <c r="V214">
@@ -28567,7 +28567,7 @@
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7de45570-38f1-4e03-bcab-9ba99b412379/LAUDOJANDERSON.pdf?expires_on=1785434314&amp;signature=UuW5tPQ6ku%2BLexbQlA99mLYd5KXJ7TXGsOgn6bx9fOc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7de45570-38f1-4e03-bcab-9ba99b412379/LAUDOJANDERSON.pdf?expires_on=1785434474&amp;signature=9lQ%2FaS8S%2FxSsN1MrnKcw%2BmBdXvUC15zWyAfjsBflDnA%3D</t>
         </is>
       </c>
       <c r="V215">
@@ -28704,7 +28704,7 @@
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ae607539-6bfa-484c-b67f-61b2da93636f/LaudoJane.pdf?expires_on=1785434314&amp;signature=tSiFwybhV1O70FvUZ2wN3bREOHJE7RFlqNf7KWeezSo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ae607539-6bfa-484c-b67f-61b2da93636f/LaudoJane.pdf?expires_on=1785434474&amp;signature=QoYoT87ZItnmRpgn4pIegtnd3n9ioM3ZWuFa%2BNRcdzk%3D</t>
         </is>
       </c>
       <c r="V216">
@@ -28841,7 +28841,7 @@
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/233271c5-70ab-469d-9b5f-eca2e8156db9/LaudoB131-2025-BEMOL-JANEDEOLIVEIRABORGES.pdf?expires_on=1785434314&amp;signature=Hoc03%2FQlvurD3nQCwq7WqJ0fpAcH5Ggw2fdfYm%2F81%2B0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/233271c5-70ab-469d-9b5f-eca2e8156db9/LaudoB131-2025-BEMOL-JANEDEOLIVEIRABORGES.pdf?expires_on=1785434474&amp;signature=RM2qLdFAadnIelHg3yhFz1zx%2B8NN0GOP%2BqZFBuHeKxU%3D</t>
         </is>
       </c>
       <c r="V217">
@@ -28987,7 +28987,7 @@
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/179e2d31-7675-4b25-9c3e-2d79ecd0038d/Laudo79-Bemol-2026-JaneteBastosFarias-Assinado.pdf?expires_on=1785434314&amp;signature=D%2FPdRPS07YWiithOUiDeJzvGZXALWWOpaWsoJtN9APw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/179e2d31-7675-4b25-9c3e-2d79ecd0038d/Laudo79-Bemol-2026-JaneteBastosFarias-Assinado.pdf?expires_on=1785434474&amp;signature=xX0ETqccQnifrW5amfvrSS%2BE8ESiPucWuilnlGMHHMM%3D</t>
         </is>
       </c>
       <c r="V218">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4c6aef96-b97d-461b-8228-8b4005055ba9/LaudoB44-2026-BEMOL-JANUSAMENDESFERREIRA.pdf?expires_on=1785434314&amp;signature=5RkRePF6VCae0uImf%2FpXMhfQrODPpNlpBZZX6D1B1eQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4c6aef96-b97d-461b-8228-8b4005055ba9/LaudoB44-2026-BEMOL-JANUSAMENDESFERREIRA.pdf?expires_on=1785434474&amp;signature=W%2F8ppLk%2FNMWwtpocZBdYomzgmMHZPVb%2BIDxkr1d8g2k%3D</t>
         </is>
       </c>
       <c r="V219">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4f5bb51e-ffda-4368-b86c-c7ba99f854f0/Laudo16-Bemol-2026-JaquelineSantanaSoares-Assinadocorrigido.pdf?expires_on=1785434314&amp;signature=jGvmdZqUHpxjyVWfaa5zJCzR%2BSEmUPrwLg4gj%2BSfocQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4f5bb51e-ffda-4368-b86c-c7ba99f854f0/Laudo16-Bemol-2026-JaquelineSantanaSoares-Assinadocorrigido.pdf?expires_on=1785434474&amp;signature=RqACTtZjsPxRobNrRESc7pH4Vh8BO9bp%2FUMJhqIrYdI%3D</t>
         </is>
       </c>
       <c r="V220">
@@ -29374,7 +29374,7 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/484caac2-18d3-497b-9b11-2b22c8c01adf/LaudoPA12-Bemol-2026-JarbasPessoaFerreira.pdf?expires_on=1785434314&amp;signature=IA6%2FL6sj%2FeZZ4wXIKDr9AVD2coPjAWgWLwwcErtX7y8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/484caac2-18d3-497b-9b11-2b22c8c01adf/LaudoPA12-Bemol-2026-JarbasPessoaFerreira.pdf?expires_on=1785434474&amp;signature=X98zKuE0nBk7%2FCMmfEAWDzDLwDphUZ9Lw%2F1%2Flg3ejpY%3D</t>
         </is>
       </c>
       <c r="V221">
@@ -29500,7 +29500,7 @@
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/69cd1182-bfed-4f9b-ab50-ae0cc6f03093/LaudoB18-2026-BEMOL-JEANEANALIADASILVA.pdf?expires_on=1785434314&amp;signature=JkqazMrPJ8sjXbwWplm9uL6Ttb%2FSqPy90GreRCSL6gI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/69cd1182-bfed-4f9b-ab50-ae0cc6f03093/LaudoB18-2026-BEMOL-JEANEANALIADASILVA.pdf?expires_on=1785434474&amp;signature=Chwzi4FQ9Q6stS5Iqk%2FHaNXeAexfM7Z%2FzmSQ%2F0IGrEQ%3D</t>
         </is>
       </c>
       <c r="V222">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf7fb4bf-787b-45be-bec2-db57c086c035/Laudo_AC_21-2026_-_JEFERSON_SILVA_DE_SOUZA_assinado.pdf?expires_on=1785434314&amp;signature=hZ%2F0qk3EYFxmdAfb%2FpI0GrLgAl42Q5gN0w4q%2Bhg3wbI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf7fb4bf-787b-45be-bec2-db57c086c035/Laudo_AC_21-2026_-_JEFERSON_SILVA_DE_SOUZA_assinado.pdf?expires_on=1785434474&amp;signature=hbs%2F9WCH2%2BoQJjOU2ophTblpOxRT8V6SDJIYoeMSxWQ%3D</t>
         </is>
       </c>
       <c r="V223">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3e3c27f6-ddba-4643-a52f-29ceedb48d1b/Laudo118-Bemol-2026-JessicaNogueiraDeLima-Assinado.pdf?expires_on=1785434314&amp;signature=zbT0U5DpccOA3MFsG0OoqAKvTW%2B5SDwbT7NaS%2FtWloE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3e3c27f6-ddba-4643-a52f-29ceedb48d1b/Laudo118-Bemol-2026-JessicaNogueiraDeLima-Assinado.pdf?expires_on=1785434474&amp;signature=PVnZesLNtoZxLZRmhQ3K96xztC4fvo6FgO7TBX9qXZk%3D</t>
         </is>
       </c>
       <c r="V224">
@@ -29908,7 +29908,7 @@
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ff906fd7-08d4-4538-ad9a-80c333493ce7/LaudoCO03-Bemol-2026-JheniferCristianRaulinodeAndrade-Assinado.pdf?expires_on=1785434314&amp;signature=lU9Au4UAOGcaYi7k9Sokuu7yWXbUhRmtgFHhdijKXcM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ff906fd7-08d4-4538-ad9a-80c333493ce7/LaudoCO03-Bemol-2026-JheniferCristianRaulinodeAndrade-Assinado.pdf?expires_on=1785434474&amp;signature=16JoDtBum6Kh72UjAzXjsbwb7nA%2BdKETVjD79MuNpj8%3D</t>
         </is>
       </c>
       <c r="V225">
@@ -30037,7 +30037,7 @@
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a7ef559f-9880-4bf8-a476-08bb3dc5a68f/Laudo207-Bemol-2026-JhullyFabianeRamosDaCosta.pdf?expires_on=1785434314&amp;signature=cwGNX%2F9B4G1UeDLcV%2F6g8holWkgiT4kkBPuCx9rryDU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a7ef559f-9880-4bf8-a476-08bb3dc5a68f/Laudo207-Bemol-2026-JhullyFabianeRamosDaCosta.pdf?expires_on=1785434474&amp;signature=qA80O4%2B285XmCInSDyNpj9GsDEbKZPK5MzAXk5uFOPU%3D</t>
         </is>
       </c>
       <c r="V226">
@@ -30174,7 +30174,7 @@
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b509385b-b1a1-461d-91a3-8708fc90b198/LaudoPA18-Bemol-2026-JoaoAlcineiPereiraVieira.pdf?expires_on=1785434314&amp;signature=cIqRXBVtz86VrqkG%2Fc02ziy2A0PcyoVnSPmJ4iI%2FnJI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b509385b-b1a1-461d-91a3-8708fc90b198/LaudoPA18-Bemol-2026-JoaoAlcineiPereiraVieira.pdf?expires_on=1785434474&amp;signature=b3i3I6l%2BP0%2BfuImtLb4W47cFdnTeOVuuT5SrEnUfGKk%3D</t>
         </is>
       </c>
       <c r="V227">
@@ -30305,7 +30305,7 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2e05645e-7aee-4df3-9f69-f22dde074690/LaudoRP01-Bemol-2026-JoaoSoaresFurtunato.pdf?expires_on=1785434314&amp;signature=hgjtePZecj8No9BPAp6K9HtqT6fX5oRGd15UMk%2FQTgY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2e05645e-7aee-4df3-9f69-f22dde074690/LaudoRP01-Bemol-2026-JoaoSoaresFurtunato.pdf?expires_on=1785434474&amp;signature=Jh4WGDX3zRIAvjehjB8xN%2FXcwmPwhRHdYXCpeZYambM%3D</t>
         </is>
       </c>
       <c r="V228">
@@ -30436,7 +30436,7 @@
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/02510d24-69da-4642-b9c8-8c1b61d32cab/Laudo388-Bemol-2025-JoaoMarioCarvalhoPessoa-Assinado.pdf?expires_on=1785434314&amp;signature=o82D59QMsImzHyqa4puOLT%2BF48WWb9eFzhOrv%2FehtvY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/02510d24-69da-4642-b9c8-8c1b61d32cab/Laudo388-Bemol-2025-JoaoMarioCarvalhoPessoa-Assinado.pdf?expires_on=1785434474&amp;signature=hdSQMeahgK0xCGyiyQoKHjSPe%2FbCTRdtscDGgE5SHQs%3D</t>
         </is>
       </c>
       <c r="V229">
@@ -30582,7 +30582,7 @@
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d6e52378-0b8e-4d53-af15-f4dd5edf3a6e/LaudoB54-2026-BEMOL-JOAOPAULODOSSANTOSVERAS.pdf?expires_on=1785434314&amp;signature=dKAOjskCAnlQdh%2Fg9ClYzNb6GSgjtH5YzF8t5ajkUxY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d6e52378-0b8e-4d53-af15-f4dd5edf3a6e/LaudoB54-2026-BEMOL-JOAOPAULODOSSANTOSVERAS.pdf?expires_on=1785434474&amp;signature=w6E0V8tOwOBdSj94cYN9fV4UbDyJhqfic97WryA30Bk%3D</t>
         </is>
       </c>
       <c r="V230">
@@ -30705,7 +30705,7 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a5369123-0a4a-4b85-8efb-523b4233b305/LaudoPA03-Bemol-2026-JoaoPauloPereiraSoares-Assinado.pdf?expires_on=1785434314&amp;signature=fqgmCDoktBsTUzXKOmloAAaXgBk%2BHIROZeWHpjpXehk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a5369123-0a4a-4b85-8efb-523b4233b305/LaudoPA03-Bemol-2026-JoaoPauloPereiraSoares-Assinado.pdf?expires_on=1785434474&amp;signature=h8ethube9vxGIj0grPNcSNIS21d7qc778bZyfyC0KjE%3D</t>
         </is>
       </c>
       <c r="V231">
@@ -30844,7 +30844,7 @@
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/40db7fb9-46cb-459c-a71b-b96f688cb5ab/Laudo193-Bemol-2026-JoaoSoaresDaSilva-Assinadoajustado.pdf?expires_on=1785434314&amp;signature=fRKjFtYactxDOhcDqFjndM%2BcRUkKjzeWeWhMm4xetao%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/40db7fb9-46cb-459c-a71b-b96f688cb5ab/Laudo193-Bemol-2026-JoaoSoaresDaSilva-Assinadoajustado.pdf?expires_on=1785434474&amp;signature=6TuKYDLfBwOAG9jxDksvpEiq%2BGJg83Jtu8m%2F0wFusck%3D</t>
         </is>
       </c>
       <c r="V232">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d93bf01b-08e9-4dcc-b01c-fe9aa02b02e9/Laudo125-Bemol-2026-JoaoVictorMagalhaesRamos.pdf?expires_on=1785434314&amp;signature=XIPzhHGb6BpSTd%2BYqD7Q1Qf0aqydnc5w10JnTn96afQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d93bf01b-08e9-4dcc-b01c-fe9aa02b02e9/Laudo125-Bemol-2026-JoaoVictorMagalhaesRamos.pdf?expires_on=1785434474&amp;signature=Z1xjD%2BMUHJNypTKxvr6f7zR6i9%2F2As1EiZGKqqmIsAE%3D</t>
         </is>
       </c>
       <c r="V233">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/24ffb2ee-bb9e-43e2-9918-9c6f71c5c0e8/Laudo_AC_-_02-2026_-_JOAQUIM_RODRIGUES_DE_MATOS_FILHO_assinado.pdf?expires_on=1785434314&amp;signature=ycPx8fecEdsfTYABK%2BNx5MZmpwxSiao%2BkKnaqh0xwXQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/24ffb2ee-bb9e-43e2-9918-9c6f71c5c0e8/Laudo_AC_-_02-2026_-_JOAQUIM_RODRIGUES_DE_MATOS_FILHO_assinado.pdf?expires_on=1785434474&amp;signature=DFATju9MYbLEy8unjgWh%2FXsB3KN7Hesi3%2BY%2BC8nsFFg%3D</t>
         </is>
       </c>
       <c r="V234">
@@ -31231,7 +31231,7 @@
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4b3c9bc8-2816-4bbc-8286-2cdf8381b780/Laudo80-Bemol-2026-JocimaraCorreaBenacon-Assinado.pdf?expires_on=1785434314&amp;signature=LTfShWBVicx%2BXGtGPGSywCSNN4RyM4GQri7CGghudy4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4b3c9bc8-2816-4bbc-8286-2cdf8381b780/Laudo80-Bemol-2026-JocimaraCorreaBenacon-Assinado.pdf?expires_on=1785434474&amp;signature=rMJ7Bx2J8f0rxPXSIjWgtyET5dclL4UVNKcSPYE7y9I%3D</t>
         </is>
       </c>
       <c r="V235">
@@ -31364,7 +31364,7 @@
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a0c0c102-66a4-4d89-9813-1801175523da/LAUDOJODENILDO1.pdf?expires_on=1785434314&amp;signature=L2O%2BFpcwAdNggUCLc9LGCKN1USwJLzJ%2FLb93q92I3Q0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a0c0c102-66a4-4d89-9813-1801175523da/LAUDOJODENILDO1.pdf?expires_on=1785434474&amp;signature=8MdigJJn%2BxwZhpNRWCovqXxdBTs6VbauHrCxjvsw3fQ%3D</t>
         </is>
       </c>
       <c r="V236">
@@ -31502,7 +31502,7 @@
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e14d207f-f757-48ec-8666-936793222082/Laudo12-Bemol-2026-JoncileideVieiraFalcao-Assinado.pdf?expires_on=1785434314&amp;signature=LNtlWOOvqKK23bHAHYgVNukMBLDSCAhuyf53JutknPE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e14d207f-f757-48ec-8666-936793222082/Laudo12-Bemol-2026-JoncileideVieiraFalcao-Assinado.pdf?expires_on=1785434474&amp;signature=749YQ65cGYRQ2m256pjX%2FctkQ0Yh6yVE2o4D8p12lHM%3D</t>
         </is>
       </c>
       <c r="V237">
@@ -31638,7 +31638,7 @@
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1e27824b-03e2-4d5e-96e8-63566e7c9c41/Laudo141-Bemol-2026-JorgeManuelLoureiroDosSantos-Assinadocorrigido.pdf?expires_on=1785434314&amp;signature=aMd9BwB94jue5%2BWkapJFeEhVyu3cvUuFMQKm0yoPH0c%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1e27824b-03e2-4d5e-96e8-63566e7c9c41/Laudo141-Bemol-2026-JorgeManuelLoureiroDosSantos-Assinadocorrigido.pdf?expires_on=1785434474&amp;signature=SeuyxObKF6uaqFLMKdnwfxcQ2mL4uC5VM%2FqZuGemH38%3D</t>
         </is>
       </c>
       <c r="V238">
@@ -31756,7 +31756,7 @@
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8e7825cd-2fcb-4c6f-a5fd-68c1dff60b8f/Laudo64-Bemol-2026-JorgeMartinsDosSantos-Assinado.pdf?expires_on=1785434314&amp;signature=SRbUPy3x4O02%2FLkML%2FQlIekSuSG6Oux98%2BmLZrNyDx4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8e7825cd-2fcb-4c6f-a5fd-68c1dff60b8f/Laudo64-Bemol-2026-JorgeMartinsDosSantos-Assinado.pdf?expires_on=1785434474&amp;signature=ZwAW0OpEXojybbfwpD4KHoXPDM%2FxNj7Q6BdstSxg1GM%3D</t>
         </is>
       </c>
       <c r="V239">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0d15c1a7-7003-41de-9e5c-23703991fa5a/Laudo203-Bemol-2026-JoseAntonioFernandesDaMota-Assinado.pdf?expires_on=1785434314&amp;signature=mdBhFIxyhgquHCAN4yDp1WFakPeLE3i21c%2FwIz7z4Y0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0d15c1a7-7003-41de-9e5c-23703991fa5a/Laudo203-Bemol-2026-JoseAntonioFernandesDaMota-Assinado.pdf?expires_on=1785434474&amp;signature=7VA%2FhXqJkatWVF1MYS5muCZpGvO54gm8COp0TOEW5Qg%3D</t>
         </is>
       </c>
       <c r="V240">
@@ -32003,7 +32003,7 @@
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/63b023ef-e3e1-432c-be42-8d0b5dc993b8/LaudoITA11-Bemol-2026-JoseAriloDeCastroRabeloFilho-Assinado.pdf?expires_on=1785434314&amp;signature=C7XRH%2BFnvsBSzsxZkLEQraHYd844FottqEhfwMCn2e0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/63b023ef-e3e1-432c-be42-8d0b5dc993b8/LaudoITA11-Bemol-2026-JoseAriloDeCastroRabeloFilho-Assinado.pdf?expires_on=1785434474&amp;signature=9%2BoHNevInBDRnx6DM9JDJMj5KTdSRT5jaBNCgUw5360%3D</t>
         </is>
       </c>
       <c r="V241">
@@ -32134,7 +32134,7 @@
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/44a581da-23a2-43d4-bec7-85d68d6c1e4b/LaudoP19-Bemol-2026-JosedenysondaSilvabarros_signed.pdf?expires_on=1785434314&amp;signature=GQ19BiUD%2BktEMGvGseT6hFHITtkkchGFOvr5dDu4jxw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/44a581da-23a2-43d4-bec7-85d68d6c1e4b/LaudoP19-Bemol-2026-JosedenysondaSilvabarros_signed.pdf?expires_on=1785434474&amp;signature=InYxMwblySi%2BgVXVDbNMqyx9BykPzfrUVj2v4lQox%2B4%3D</t>
         </is>
       </c>
       <c r="V242">
@@ -32257,7 +32257,7 @@
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f9ffca4f-c0f4-40e5-a3f9-cb3e0a54d3af/Laudo_AC_-_03-2026_-_JOSE_FERREIRA_DA_SILVA_assinado.pdf?expires_on=1785434314&amp;signature=Mp1ZDzuk8yepCmxRZAPNKrciJlcH4BHeL11LbBAntzw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f9ffca4f-c0f4-40e5-a3f9-cb3e0a54d3af/Laudo_AC_-_03-2026_-_JOSE_FERREIRA_DA_SILVA_assinado.pdf?expires_on=1785434474&amp;signature=Merl6UgMkt73193NPGA11Fo%2FxuXZ2sSiUTeTSz0DSGQ%3D</t>
         </is>
       </c>
       <c r="V243">
@@ -32401,7 +32401,7 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/32e67383-9a53-47a3-a8a3-f3924affe338/BEMOL-AR024-JOSEGUILHERMEDASILVA.pdf?expires_on=1785434314&amp;signature=TZCt4sIyZ4LNhJ9Tozs9LltnmP9UVJoKaFkMHxA%2F%2FdU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/32e67383-9a53-47a3-a8a3-f3924affe338/BEMOL-AR024-JOSEGUILHERMEDASILVA.pdf?expires_on=1785434474&amp;signature=WxcJEHrQKmAkPpX276OcQ75Cfxgyml1SM%2F4Ha1COpGw%3D</t>
         </is>
       </c>
       <c r="V244">
@@ -32531,7 +32531,7 @@
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b445fa54-a64b-4377-8b13-d1a2678ff739/Laudo32-Bemol-2026-JoseHiltonDeAzevedo-Assinado.pdf?expires_on=1785434314&amp;signature=mHrBHDW01OEGLw6Ma1bHkxripjppIImegD5zvKrHcIc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b445fa54-a64b-4377-8b13-d1a2678ff739/Laudo32-Bemol-2026-JoseHiltonDeAzevedo-Assinado.pdf?expires_on=1785434474&amp;signature=ZSeDsjguw1FtLRafaXNa7Y2yF3d0UigSaHhRgDlFmJg%3D</t>
         </is>
       </c>
       <c r="V245">
@@ -32663,7 +32663,7 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a78e75e1-9bc8-41af-a915-51ff7bbc9720/LaudoJP20-Bemol-2025-JoselitoGoncalvesPonponet_signed.pdf?expires_on=1785434314&amp;signature=QYj8Zq0svb8BoHk58j%2Bw30Jh4wislS5bm7uh8hImEIE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a78e75e1-9bc8-41af-a915-51ff7bbc9720/LaudoJP20-Bemol-2025-JoselitoGoncalvesPonponet_signed.pdf?expires_on=1785434474&amp;signature=RWCzG7T63VQ41KW%2BsTA3gV9ZMbhz9ilScD9RtYialdA%3D</t>
         </is>
       </c>
       <c r="V246">
@@ -32802,7 +32802,7 @@
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/59cf8cc8-d359-4624-80cc-358e01243f17/Laudo51-Bemol-2026-JosianeSouzaDaRocha.pdf?expires_on=1785434314&amp;signature=fCVHVrJDymAsmYkbVIRCrkTdNkORo6zFUwUxZZhHVVI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/59cf8cc8-d359-4624-80cc-358e01243f17/Laudo51-Bemol-2026-JosianeSouzaDaRocha.pdf?expires_on=1785434474&amp;signature=pRYR4dL4gIM83uTyGazfhl6fZ2exw7enUOPo22CFCO0%3D</t>
         </is>
       </c>
       <c r="V247">
@@ -32931,7 +32931,7 @@
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3083643d-bcb1-4c34-8d2b-b413a5548f3d/LaudoPA10-Bemol-2026-JosiasConceicaoSoares.pdf?expires_on=1785434314&amp;signature=UT704V7cHjXUb4%2Fdie%2B45V8ApqFAE%2F8JEk79L2zcIjA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3083643d-bcb1-4c34-8d2b-b413a5548f3d/LaudoPA10-Bemol-2026-JosiasConceicaoSoares.pdf?expires_on=1785434474&amp;signature=faCxOcAIw4uQKC%2F1FdGLKLOMeGHNlFhRXYN6ahjpR%2BM%3D</t>
         </is>
       </c>
       <c r="V248">
@@ -33055,7 +33055,7 @@
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0a061aa3-403a-4950-9fe5-220a66442a39/Laudo105-Bemol-2026-JoyceKellyBezerraRozeno-Assinado.pdf?expires_on=1785434314&amp;signature=PgcJUewGMxTvBBiufqbVxYtC7wcEjpYx7nYG6zz75oM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0a061aa3-403a-4950-9fe5-220a66442a39/Laudo105-Bemol-2026-JoyceKellyBezerraRozeno-Assinado.pdf?expires_on=1785434474&amp;signature=DcxKtlbRgQSgdjglrAtn6WJaFcXpj22zSxl9aitOGrQ%3D</t>
         </is>
       </c>
       <c r="V249">
@@ -33179,7 +33179,7 @@
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fcf9d45a-32f5-4428-a169-dbab8039b5c5/LAUDOJUCILEIDEcorrigido.pdf?expires_on=1785434314&amp;signature=8wDLhMdftP7i%2FVJ%2FMxgSaVmgos2gcZk035jXLZ90pjE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fcf9d45a-32f5-4428-a169-dbab8039b5c5/LAUDOJUCILEIDEcorrigido.pdf?expires_on=1785434474&amp;signature=IEpsKk%2FfR%2FsAmxGRRQpW%2BScPbgihWPE%2FJ6kbp9FRpqQ%3D</t>
         </is>
       </c>
       <c r="V250">
@@ -33297,7 +33297,7 @@
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fd5fc2e4-28eb-409f-9703-7cac56ee39c5/LaudoMAN01-Bemol-2026-JucimarDeSouzaFreitas.pdf?expires_on=1785434314&amp;signature=JdlsW9x1eezEwGW3R62MnNtUEKX%2BHJhSMKIUkkK2WSA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fd5fc2e4-28eb-409f-9703-7cac56ee39c5/LaudoMAN01-Bemol-2026-JucimarDeSouzaFreitas.pdf?expires_on=1785434474&amp;signature=ZNc0B8TimjcOenX8zQh1waBsjYiOV1ZBFjkcu4wMGtU%3D</t>
         </is>
       </c>
       <c r="V251">
@@ -33429,7 +33429,7 @@
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/102a799e-a3eb-4b9f-b5b3-0ba81687c5f6/BEMOL-PV083-KALWANNEALVESDEMEDEIROS.pdf?expires_on=1785434314&amp;signature=LpT3Lxsq6x%2FEsdwoOScQZ469Gpj%2FJee4EbmfxaPAxBE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/102a799e-a3eb-4b9f-b5b3-0ba81687c5f6/BEMOL-PV083-KALWANNEALVESDEMEDEIROS.pdf?expires_on=1785434474&amp;signature=ZTD4dTKMsMBrhJ5HyIiyhDG3xKM1HiihC6L9B9iwogk%3D</t>
         </is>
       </c>
       <c r="V252">
@@ -33552,7 +33552,7 @@
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9bfc239f-7e6e-4054-9233-9b1d5637f829/LaudoMAN05-Bemol-2026-KarenSuzyOliveiraLimaVerde.pdf?expires_on=1785434314&amp;signature=uDiUNVNYH5%2BIGPYeYv45HU7lvdOslMmcUo7vPn%2FaPMU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9bfc239f-7e6e-4054-9233-9b1d5637f829/LaudoMAN05-Bemol-2026-KarenSuzyOliveiraLimaVerde.pdf?expires_on=1785434474&amp;signature=z2aqnyeRjeXzQmIk0bqHlsRE2Knd5%2BUqbb4WrILsPm4%3D</t>
         </is>
       </c>
       <c r="V253">
@@ -33689,7 +33689,7 @@
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c4fe8ca8-baf2-4efc-83a7-233980c73c44/Laudo74-Bemol-2026-KarinaTaliaDaSilvaAlbuquerque-Assinado.pdf?expires_on=1785434314&amp;signature=O1tXrsbSOTU1rhsiB3zr8FW%2FqMhZWIb6XmVLFct2gRo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c4fe8ca8-baf2-4efc-83a7-233980c73c44/Laudo74-Bemol-2026-KarinaTaliaDaSilvaAlbuquerque-Assinado.pdf?expires_on=1785434474&amp;signature=BMMmtgobN8rSfhHUPq8ckoeNKlJ4vLpNuvhUIowQnHY%3D</t>
         </is>
       </c>
       <c r="V254">
@@ -33832,7 +33832,7 @@
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/09b4be70-22fc-4cd7-845b-ce60b34422f5/Laudo44-Bemol-2026-KathyLinneOliveiraQueiroz-Assinado.pdf?expires_on=1785434314&amp;signature=yELBUr3WkElbnTs9T%2BipbDW4wOqyDAPTZzN74HJDBZ0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/09b4be70-22fc-4cd7-845b-ce60b34422f5/Laudo44-Bemol-2026-KathyLinneOliveiraQueiroz-Assinado.pdf?expires_on=1785434474&amp;signature=2myEXtzuVNYHoB6AWEAEtB3VErNUr44bUuyxcps8zMs%3D</t>
         </is>
       </c>
       <c r="V255">
@@ -33970,7 +33970,7 @@
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/eb1e71be-7dea-4067-ac02-45cc31dc2747/LaudoB74-2025-BEMOL-KATIACRISTINASOARESCORDOVIL-ajustado.pdf?expires_on=1785434314&amp;signature=lrSoGvSmYOojLqqsmi6KaY%2BbsyOZNuDhoB%2BzchSUA5I%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/eb1e71be-7dea-4067-ac02-45cc31dc2747/LaudoB74-2025-BEMOL-KATIACRISTINASOARESCORDOVIL-ajustado.pdf?expires_on=1785434474&amp;signature=fotTZF99n70AhA8tr9pmArJboDdM8YItk0Ft8GsDshs%3D</t>
         </is>
       </c>
       <c r="V256">
@@ -34110,7 +34110,7 @@
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/18a0acbb-231a-4adb-ad19-867d57322b0e/LAUDOKATIASILVEIRA.pdf?expires_on=1785434314&amp;signature=vepFX%2B6W38%2FqnMb15cY05i5Qv1pdfnwtg5%2BZ%2FOALy%2FI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/18a0acbb-231a-4adb-ad19-867d57322b0e/LAUDOKATIASILVEIRA.pdf?expires_on=1785434474&amp;signature=%2FyY7C6h2tFI07zUtilsrEL8CKBfuHYEu3HobWVXF%2FFQ%3D</t>
         </is>
       </c>
       <c r="V257">
@@ -34242,7 +34242,7 @@
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0960719a-5454-4cf9-8daf-ba22e26bd11b/Laudo211-Bemol-2026-KatilaCorreiaDaCosta-Assinado.pdf?expires_on=1785434314&amp;signature=Ba5SiXIc6pvm7rQGLEAMvVV%2Fre5VySQyRQTgP0nb6Dk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0960719a-5454-4cf9-8daf-ba22e26bd11b/Laudo211-Bemol-2026-KatilaCorreiaDaCosta-Assinado.pdf?expires_on=1785434474&amp;signature=wSyw5r1seDA7O%2B2Wjt03bi%2BhDAp%2FJxzpLAuGeoKf98Q%3D</t>
         </is>
       </c>
       <c r="V258">
@@ -34365,7 +34365,7 @@
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/78047af0-3a8a-47f5-96c5-2011fa327014/LaudoB5-2026-BEMOL-KAUYTABRENDAVIANAAGOSTINHO.pdf?expires_on=1785434314&amp;signature=HkYFUgMwyBqJi59tEauOCGfdhuyqAcL1K5RzbOPIAUg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/78047af0-3a8a-47f5-96c5-2011fa327014/LaudoB5-2026-BEMOL-KAUYTABRENDAVIANAAGOSTINHO.pdf?expires_on=1785434474&amp;signature=HZM6jlWSYOWhzYYCn2opvIr%2Fx%2FE6nazi0gFKa43%2Frdw%3D</t>
         </is>
       </c>
       <c r="V259">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f14757f5-bf32-46e7-ba0b-2bca9310519f/LaudoP18-Bemol-2026-KeitianeSoaresMenezes_signed.pdf?expires_on=1785434314&amp;signature=VHkiNaIDLF%2Bzr5q2yvqJJQgf1sa9d1TvItQSpBy7ewQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f14757f5-bf32-46e7-ba0b-2bca9310519f/LaudoP18-Bemol-2026-KeitianeSoaresMenezes_signed.pdf?expires_on=1785434474&amp;signature=rB1H9v1puUHLUvrHHAij%2B9w2X8qtfD350qk0Ibu0KbI%3D</t>
         </is>
       </c>
       <c r="V260">
@@ -34620,7 +34620,7 @@
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4589162a-b138-4232-9001-d6e6f23710f0/Laudo127-Bemol-2026-KelcianeSantosDeAraujo.pdf?expires_on=1785434314&amp;signature=2fHOWTBT9lQrbK6bYA7Yz%2BJo4RE8FRByZHz%2B%2FwGVkVA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4589162a-b138-4232-9001-d6e6f23710f0/Laudo127-Bemol-2026-KelcianeSantosDeAraujo.pdf?expires_on=1785434474&amp;signature=PNoqis4tRC37PrPSjIZCFlv4c6cbubOWm4Z57IrBY9k%3D</t>
         </is>
       </c>
       <c r="V261">
@@ -34752,7 +34752,7 @@
       </c>
       <c r="U262" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3d8c9a1f-7784-4fd4-b6ef-324016118989/BEMOL-JP040-KleitonOliveiraGonalves.pdf?expires_on=1785434314&amp;signature=V2F%2FqYJYZAPa8sO3d0MGWOABxY8AM9ONVI3Swg8iBlM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3d8c9a1f-7784-4fd4-b6ef-324016118989/BEMOL-JP040-KleitonOliveiraGonalves.pdf?expires_on=1785434474&amp;signature=%2BrIeUPkxcBKcPqkwLUMXRuY%2FoHPiOCwgK0B4k190X%2BU%3D</t>
         </is>
       </c>
       <c r="V262">
@@ -34889,7 +34889,7 @@
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/84888d6c-08d7-4445-805f-82232e205d61/Laudo55-Bemol-2026-LacyAugustaDeOliveiraPereira-Assinadocorrigido.pdf?expires_on=1785434314&amp;signature=BcwXfLo%2FUqQXAXpCV7Si7Rn7Jygn8JMxuEHbxBjXM9o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/84888d6c-08d7-4445-805f-82232e205d61/Laudo55-Bemol-2026-LacyAugustaDeOliveiraPereira-Assinadocorrigido.pdf?expires_on=1785434474&amp;signature=kATGtwu2Z7%2BNFZQZklnaOAfcbr9qAtWDEY9i12TZHsc%3D</t>
         </is>
       </c>
       <c r="V263">
@@ -35027,7 +35027,7 @@
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c57e2482-e0ab-4ffd-8d4b-e915535f39a0/BEMOL-PV067-LAELSONDASILVALIMA.pdf?expires_on=1785434314&amp;signature=8rgyA%2BdvvHzmo4KOfPl4%2BIyRwsPQjG5fpC6Ln670j8M%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c57e2482-e0ab-4ffd-8d4b-e915535f39a0/BEMOL-PV067-LAELSONDASILVALIMA.pdf?expires_on=1785434474&amp;signature=kAVSoNhakQ8tDJSNwdIi4UBdSoGxY10kbdo4FOqvb0w%3D</t>
         </is>
       </c>
       <c r="V264">
@@ -35161,7 +35161,7 @@
       </c>
       <c r="U265" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9cdd9b63-6138-421d-a7d5-59b099832833/M21-2026-LAERCIOajustado02.pdf?expires_on=1785434314&amp;signature=kDi0gkWi%2BQ92Jbc1Du1%2Ft6HbezNi7ffAUOF09D8Z1A8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9cdd9b63-6138-421d-a7d5-59b099832833/M21-2026-LAERCIOajustado02.pdf?expires_on=1785434474&amp;signature=MHkWX2Yjmi0xEhJlayBt8uTTeOTJlz1RumHerU1AjwY%3D</t>
         </is>
       </c>
       <c r="V265">
@@ -35298,7 +35298,7 @@
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/51d2732a-d4f3-4ceb-93db-604dec01b804/Laudo384-Bemol-2025-LaraKarinaFreitasDaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=dD2KupCM7VJyYwhbRl5x6atVEW%2Fn4lG%2FiSE01r1wFnI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/51d2732a-d4f3-4ceb-93db-604dec01b804/Laudo384-Bemol-2025-LaraKarinaFreitasDaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=5m6Vgo%2FlzpM2GAU2uSJu%2BH%2BBYBXNRRvLem9CQnDiA8g%3D</t>
         </is>
       </c>
       <c r="V266">
@@ -35432,7 +35432,7 @@
       </c>
       <c r="U267" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ad09fc29-0c35-49fa-903f-463ed726a278/LaudoB53-2026-BEMOL-LARISSADESOUZAPINHEIRO.pdf?expires_on=1785434314&amp;signature=T3AC5WMNcYJPSuc8UEgLQzfCfvZ34NiPvv%2FvoqCJXQc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ad09fc29-0c35-49fa-903f-463ed726a278/LaudoB53-2026-BEMOL-LARISSADESOUZAPINHEIRO.pdf?expires_on=1785434474&amp;signature=tMDKAZPu8P32QMkUN9s9xzgdUi5UKyeVROOf4QKnMFg%3D</t>
         </is>
       </c>
       <c r="V267">
@@ -35564,7 +35564,7 @@
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5c263ebd-cfce-4688-a60b-2bf294c5af42/LaudoB7-2026-BEMOL-LELIANEBEZERRACOSTA.pdf?expires_on=1785434314&amp;signature=oaYW2g0867gghp63zIjpH76U14qNm8YaPC7TBczwCKM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5c263ebd-cfce-4688-a60b-2bf294c5af42/LaudoB7-2026-BEMOL-LELIANEBEZERRACOSTA.pdf?expires_on=1785434474&amp;signature=zagj2kxn9Rac%2BG%2BDKqKCOBDno%2BlqIGvqSQpBjjFmuPs%3D</t>
         </is>
       </c>
       <c r="V268">
@@ -35700,7 +35700,7 @@
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/227d992b-9e09-49b9-aa03-055a9ef77a5c/LAUDOLENAGIANI.pdf?expires_on=1785434314&amp;signature=5CfqOZnUuL5z3%2F6a60%2B%2BXBX3hTqZOyJNGbF2Pi5XR3g%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/227d992b-9e09-49b9-aa03-055a9ef77a5c/LAUDOLENAGIANI.pdf?expires_on=1785434474&amp;signature=%2BOb0Xpy4opVnb8scpslI9ErhM3zGf6r3Ic8tc86sBuM%3D</t>
         </is>
       </c>
       <c r="V269">
@@ -35829,7 +35829,7 @@
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e683766e-4fa9-40fd-bf56-e1e1d699e2b3/LaudoA12-Bemol-2026-LenilzadeSousaQuintino_signed.pdf?expires_on=1785434314&amp;signature=E6YyIiU2PL5uOZGvWyNWYMjs%2B0Bk1kVFBDfpWJX5Yf0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e683766e-4fa9-40fd-bf56-e1e1d699e2b3/LaudoA12-Bemol-2026-LenilzadeSousaQuintino_signed.pdf?expires_on=1785434474&amp;signature=zU47nFp1LaQRhBFAbZPiXdQJO56rVSrcPk5ypL2cPfQ%3D</t>
         </is>
       </c>
       <c r="V270">
@@ -35952,7 +35952,7 @@
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6a6c242c-a92f-4d3a-9f89-5f9a233e116a/Laudo145-Bemol-2026-LeonoraSuelmaSantosDeMatos-Assinado.pdf?expires_on=1785434314&amp;signature=lY%2FISXut8wy5SIfJYb%2F8Q8LURADjxetsnG9BwBOpOpk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6a6c242c-a92f-4d3a-9f89-5f9a233e116a/Laudo145-Bemol-2026-LeonoraSuelmaSantosDeMatos-Assinado.pdf?expires_on=1785434474&amp;signature=palCSI34dTMT66jcIjaZ6MXR5Y3kqEQANby8M6FPP3c%3D</t>
         </is>
       </c>
       <c r="V271">
@@ -36089,7 +36089,7 @@
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/187a3450-7d8c-42db-9247-701e3aac79f7/Laudo151-Bemol-2026-LeuzaFeijoCardoso-Assinado.pdf?expires_on=1785434314&amp;signature=7Fg5fQbkA9pwDxY17ok0jNVLSu3wzvlkjuYT4jmxKeQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/187a3450-7d8c-42db-9247-701e3aac79f7/Laudo151-Bemol-2026-LeuzaFeijoCardoso-Assinado.pdf?expires_on=1785434474&amp;signature=FapZZdQkRCzQc%2F88yHQfKC8b6AKdE9Gs08n80f%2F58j8%3D</t>
         </is>
       </c>
       <c r="V272">
@@ -36226,7 +36226,7 @@
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e93d351e-ee9f-4c5b-a064-86d8d270c79c/M03-2026-LIANDRASIMOESANDRADE.pdf?expires_on=1785434314&amp;signature=B1DApsrFC9zYgyfXKKk%2FbosqB4mgIJeNlMMAOjdto2M%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e93d351e-ee9f-4c5b-a064-86d8d270c79c/M03-2026-LIANDRASIMOESANDRADE.pdf?expires_on=1785434474&amp;signature=tkN7I8AnGasn5%2Bz8SUTDoxR7lYW8IRRuTTu8zpEzUZ4%3D</t>
         </is>
       </c>
       <c r="V273">
@@ -36355,7 +36355,7 @@
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/78175ac0-ba4c-4491-95af-85e37ce609d6/LAUDOLILIANEOLIVEIRA.pdf?expires_on=1785434314&amp;signature=PDImTgj3Afhkoaw3pMRld9rchWEtYePVYSkeMKg%2FWNw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/78175ac0-ba4c-4491-95af-85e37ce609d6/LAUDOLILIANEOLIVEIRA.pdf?expires_on=1785434474&amp;signature=loWFYIUwqydSxM%2FEOS9k71d0m1l3EiO%2BgwLhVFMIDFM%3D</t>
         </is>
       </c>
       <c r="V274">
@@ -36482,7 +36482,7 @@
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c9572df0-c295-4af0-84b7-59f8390b6a33/LAUDOLIZANDRA.pdf?expires_on=1785434314&amp;signature=I%2F9DMVMdVLz0QWjaZgnOne2jazUcoGBXQFbo3%2BwtQ2U%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c9572df0-c295-4af0-84b7-59f8390b6a33/LAUDOLIZANDRA.pdf?expires_on=1785434474&amp;signature=O1NraOrR6eIoG2gZUgoXeYAg2nR%2FUpnE0WiBErXF09E%3D</t>
         </is>
       </c>
       <c r="V275">
@@ -36611,7 +36611,7 @@
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0c32db42-3c2d-4e82-bcdf-ee3e1e4642dd/Laudo_AC_07-2026_-_LOURISMAR_MOTA_DE_ANDRADE_assinado.pdf?expires_on=1785434314&amp;signature=hy8%2FYa5zSbc7TY5tmFEY0IirlHIGZFvHLADI9wTxFCg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0c32db42-3c2d-4e82-bcdf-ee3e1e4642dd/Laudo_AC_07-2026_-_LOURISMAR_MOTA_DE_ANDRADE_assinado.pdf?expires_on=1785434474&amp;signature=%2BUi8vetSqJKnNaGO2gI40Wzl0%2BkHZ7mBRIAk7VXIgCo%3D</t>
         </is>
       </c>
       <c r="V276">
@@ -36748,7 +36748,7 @@
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4673b4e7-a446-4d17-84eb-15204c8d504a/LaudoMAN07-Bemol-2026-LucasEmanuelMenezesDaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=Bs5%2F8HOLtOluuj1O3o41vN4tG%2FfSz8cMb1JCHyxY640%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4673b4e7-a446-4d17-84eb-15204c8d504a/LaudoMAN07-Bemol-2026-LucasEmanuelMenezesDaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=WFILdZhQYriXaZAE1%2F8IbRaav3c9Htq7ORcSloYG8CM%3D</t>
         </is>
       </c>
       <c r="V277">
@@ -36879,7 +36879,7 @@
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/01776b88-00aa-47b8-a354-40ea5c6624a7/Laudo_AC_20-2026_-_LUCIANO_SILVA_DE_OLIVEIRA_assinado.pdf?expires_on=1785434314&amp;signature=xDOuTWzrHglCLhXz5fZUEtSGjYoYfJ7n3nB0BUrRx64%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/01776b88-00aa-47b8-a354-40ea5c6624a7/Laudo_AC_20-2026_-_LUCIANO_SILVA_DE_OLIVEIRA_assinado.pdf?expires_on=1785434474&amp;signature=UURJVjypfA%2Ft%2BQ1ecn66Sv9tgPpMzPLUXCGFYkgH3mc%3D</t>
         </is>
       </c>
       <c r="V278">
@@ -37002,7 +37002,7 @@
       </c>
       <c r="U279" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/85fefdea-23eb-40e2-b07f-356afda61752/LaudoITA16-Bemol-2026-LucimaraMoraesdeMeloFerreira-Assinado.pdf?expires_on=1785434314&amp;signature=yZa3savdPuKrFrj%2BghzBbr8HkVySKTo75FguiZ7GgcY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/85fefdea-23eb-40e2-b07f-356afda61752/LaudoITA16-Bemol-2026-LucimaraMoraesdeMeloFerreira-Assinado.pdf?expires_on=1785434474&amp;signature=2P%2FECs0TJUBxRSs%2FXDuL0%2BUd8UAeDML4meQ%2BLV4AFVw%3D</t>
         </is>
       </c>
       <c r="V279">
@@ -37128,7 +37128,7 @@
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e72b7a5e-51ec-4d8b-a69e-1ac05dec87a6/M01-2026-LUCYLENEPEREIRASILVAajuste02.pdf?expires_on=1785434314&amp;signature=AytDai2wd7VAsM3ZA6RyYbOtgsr8UZIgFMqsCZimbyo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e72b7a5e-51ec-4d8b-a69e-1ac05dec87a6/M01-2026-LUCYLENEPEREIRASILVAajuste02.pdf?expires_on=1785434474&amp;signature=0Imi4iswTAycPjuox%2FQ%2BBMXaUVp7KeigBcjMT%2FQ5rqc%3D</t>
         </is>
       </c>
       <c r="V280">
@@ -37257,7 +37257,7 @@
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/00beab08-f07e-438a-8591-56c5da193dab/LAUDOCORRIGIDOLUIZCLAUDIO.pdf?expires_on=1785434314&amp;signature=c%2Fxmp7almBvv1x2mYoYh1cxhUo8o55eBzdQTcwBWmqc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/00beab08-f07e-438a-8591-56c5da193dab/LAUDOCORRIGIDOLUIZCLAUDIO.pdf?expires_on=1785434474&amp;signature=y0hsbbnvzVlP3SUQbDlHxog7ue7eTM4td%2Bd6ZvZ3cF8%3D</t>
         </is>
       </c>
       <c r="V281">
@@ -37388,7 +37388,7 @@
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e36cb59c-0bf9-441a-bca2-a7e482279dd7/LAUDOMAIQUE.pdf?expires_on=1785434314&amp;signature=86uWkUx0D6rOkfP%2FvN5IE2yyjcgWk0mRtDE2JzTlvRU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e36cb59c-0bf9-441a-bca2-a7e482279dd7/LAUDOMAIQUE.pdf?expires_on=1785434474&amp;signature=EehGfaYI04z3c20mNKzTwfJuqI3yyQcPutYHRK%2B5p0c%3D</t>
         </is>
       </c>
       <c r="V282">
@@ -37515,7 +37515,7 @@
       </c>
       <c r="U283" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/702cee98-29a4-45c7-a98b-fac086e165d2/LaudoA13-Bemol-2026-ManoelBarbosadosSantosFilho_signed.pdf?expires_on=1785434314&amp;signature=0LdFB8Vz8fkMkCrFFAe7fiTyTrUNuO%2FAl8rz25rwPxs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/702cee98-29a4-45c7-a98b-fac086e165d2/LaudoA13-Bemol-2026-ManoelBarbosadosSantosFilho_signed.pdf?expires_on=1785434474&amp;signature=W5HzaEZ2xj1E7W0PNS%2B2GVMVwWRe%2Fn22Uehcr5145hg%3D</t>
         </is>
       </c>
       <c r="V283">
@@ -37633,7 +37633,7 @@
       </c>
       <c r="U284" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9477ddfb-29ad-40ca-8f39-8dda636c6eca/Laudo106-Bemol-2026-MaraLindolfoGomes.pdf?expires_on=1785434314&amp;signature=OXEk8gzXnbg%2FqeS4VKwwO3j1Fo0PmYa%2FjTW6R5snBlM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9477ddfb-29ad-40ca-8f39-8dda636c6eca/Laudo106-Bemol-2026-MaraLindolfoGomes.pdf?expires_on=1785434474&amp;signature=m4xZqkxF9p9qLn%2F9Obubq06MQ%2BeeBRdYZRkfFZ%2BzLHg%3D</t>
         </is>
       </c>
       <c r="V284">
@@ -37774,7 +37774,7 @@
       </c>
       <c r="U285" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f5caf246-e228-41a7-bf46-0334613fbf28/Laudo_AC_68-2025_assinado1.pdf?expires_on=1785434314&amp;signature=Pif6Bg%2BB8neeflPZG277BQtVMwpVv9qEVCmayWUJqQk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f5caf246-e228-41a7-bf46-0334613fbf28/Laudo_AC_68-2025_assinado1.pdf?expires_on=1785434474&amp;signature=bTbcOcYlV02qmrDZcp930OjDCpss%2BYnqDOR%2FXGd936I%3D</t>
         </is>
       </c>
       <c r="V285">
@@ -37914,7 +37914,7 @@
       </c>
       <c r="U286" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c5e2cb6f-067e-45c0-9a3b-6cca00097d4e/Laudo208-Bemol-2026-MarceloBatistaMotta-Assinadoajustado.pdf?expires_on=1785434314&amp;signature=1y6qRPzXtUoW9fx6YlX1GOCbd36gNwuwLFOwRTadfn0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c5e2cb6f-067e-45c0-9a3b-6cca00097d4e/Laudo208-Bemol-2026-MarceloBatistaMotta-Assinadoajustado.pdf?expires_on=1785434474&amp;signature=5eFIE%2B9MRZUbRdVUUfO9p6KbTC4A9yGE%2BHaqtq19ZIg%3D</t>
         </is>
       </c>
       <c r="V286">
@@ -38048,7 +38048,7 @@
       </c>
       <c r="U287" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/84bd3365-968b-4a72-9c39-5864a865401b/LAUDOMARCELO.pdf?expires_on=1785434314&amp;signature=tyA0McKbBJXg%2FEgyZ%2FGEvyKhuqo3ZhoGb3a6SZTeClA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/84bd3365-968b-4a72-9c39-5864a865401b/LAUDOMARCELO.pdf?expires_on=1785434474&amp;signature=85os4w%2F9DwQZzR%2BGbY%2BqMB%2FJUKgBn8iHNPMkbNZoPMA%3D</t>
         </is>
       </c>
       <c r="V287">
@@ -38190,7 +38190,7 @@
       </c>
       <c r="U288" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/989623be-06f7-43f9-add6-ae7f521d4740/BEMOL-PV073-MARCIASOUZADASILVA.pdf?expires_on=1785434314&amp;signature=4PCUs%2FP1FxzrXR2vbyRowSiadxNQgj%2F6EPh2%2FDPf9yk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/989623be-06f7-43f9-add6-ae7f521d4740/BEMOL-PV073-MARCIASOUZADASILVA.pdf?expires_on=1785434474&amp;signature=jK2NPxqGeLJg4%2FM94driOyP9KQbUjEBUaY4%2BeU1gJ0M%3D</t>
         </is>
       </c>
       <c r="V288">
@@ -38325,7 +38325,7 @@
       </c>
       <c r="U289" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/40cb37e9-67f2-4604-b382-8ac209843588/Laudo146-Bemol-2026-MarcioDaSilvaRocha-Assinado.pdf?expires_on=1785434314&amp;signature=qv41imT217SXuBwsljvoHWmO2WllJ3FgLuRuDZum1k8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/40cb37e9-67f2-4604-b382-8ac209843588/Laudo146-Bemol-2026-MarcioDaSilvaRocha-Assinado.pdf?expires_on=1785434474&amp;signature=IV%2Bq1gD1xCw6ZqYrNVc9E6ZIVEEtfGqC2MBqexFCXng%3D</t>
         </is>
       </c>
       <c r="V289">
@@ -38443,7 +38443,7 @@
       </c>
       <c r="U290" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/abf6b4df-ae4e-4b23-84da-e0c88652c21a/Laudo195-Bemol-2026-MarcioRomuloSousaRodrigues-Assinado.pdf?expires_on=1785434314&amp;signature=xAACs2UqdpgmZlgWTTUAnF7eHsepj%2BkBkkZb6MDEx14%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/abf6b4df-ae4e-4b23-84da-e0c88652c21a/Laudo195-Bemol-2026-MarcioRomuloSousaRodrigues-Assinado.pdf?expires_on=1785434474&amp;signature=D%2B1O8cjoIAlTgYiJ18kwAGsZ6nfgvB%2BXNo%2BOvTDc62k%3D</t>
         </is>
       </c>
       <c r="V290">
@@ -38561,7 +38561,7 @@
       </c>
       <c r="U291" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/488c405c-0f90-456c-82c2-4c7f48712df8/Laudo_AC_18-2026_-_MARCLEISON_JOSE_FACANHA_DA_SILVA_assinado.pdf?expires_on=1785434314&amp;signature=j2VpbadG5BIo1c5vex7g1fJ0dfwiJE%2BHYYPdAfTWRyE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/488c405c-0f90-456c-82c2-4c7f48712df8/Laudo_AC_18-2026_-_MARCLEISON_JOSE_FACANHA_DA_SILVA_assinado.pdf?expires_on=1785434474&amp;signature=4O79MZpRGGfA9J2PTdz1TiM%2BPlMDFe0GVk1iNpvLkVI%3D</t>
         </is>
       </c>
       <c r="V291">
@@ -38693,7 +38693,7 @@
       </c>
       <c r="U292" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/75f87a88-1433-446c-acdc-913951147d2d/Laudo124-Bemol-2026-MarcoAurelioEspindolaLimaJunior.pdf?expires_on=1785434314&amp;signature=DubgFZW93ixquqTXUKOMZpCoU2CBp7QiQfFGQndzXGI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/75f87a88-1433-446c-acdc-913951147d2d/Laudo124-Bemol-2026-MarcoAurelioEspindolaLimaJunior.pdf?expires_on=1785434474&amp;signature=CTm7D1h%2B6va6JmPic4JFUR%2FNOtQqAiUeIwY558UY4Ec%3D</t>
         </is>
       </c>
       <c r="V292">
@@ -38811,7 +38811,7 @@
       </c>
       <c r="U293" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/75b0c736-29a3-4de6-b907-a5e31a9e212a/BEMOL-AR025-MARCOSJOSEDOSSANTOS.pdf?expires_on=1785434314&amp;signature=9TKd5R6D1Te0G2sfY47agPwvthM1V5RYTEDcVEBAJKs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/75b0c736-29a3-4de6-b907-a5e31a9e212a/BEMOL-AR025-MARCOSJOSEDOSSANTOS.pdf?expires_on=1785434474&amp;signature=7r8Lf4cWCdcJAcplM%2F2uZaXXm5ESyU23mknMw6lP9Pk%3D</t>
         </is>
       </c>
       <c r="V293">
@@ -38944,7 +38944,7 @@
       </c>
       <c r="U294" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5dcfd913-bbca-4933-acfe-9c8a4d7c67e0/LAUDOMARCOSSENA.pdf?expires_on=1785434314&amp;signature=SgYrdq7qIuEEIc0itZwyWuYl1tpJmMqhOAQHYnHhPc0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5dcfd913-bbca-4933-acfe-9c8a4d7c67e0/LAUDOMARCOSSENA.pdf?expires_on=1785434474&amp;signature=s0verKeWAdKo88guKjXP2aNse2KSULGv6Jvy782pV%2F0%3D</t>
         </is>
       </c>
       <c r="V294">
@@ -39080,7 +39080,7 @@
       </c>
       <c r="U295" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/59501b5e-240f-4121-b2e9-d91ca2559083/Laudo87-Bemol-2026-MarcusJoseQueirozFerreira-Assinado.pdf?expires_on=1785434314&amp;signature=D2AKhSxkoh9jnMEDJ%2BMKzgHOVuglcqBNkua%2BCnG2fuA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/59501b5e-240f-4121-b2e9-d91ca2559083/Laudo87-Bemol-2026-MarcusJoseQueirozFerreira-Assinado.pdf?expires_on=1785434474&amp;signature=D%2BhF5Kxx4QFQr8%2BnMgSrhYvXpLquuaXvQzcwKdusHlQ%3D</t>
         </is>
       </c>
       <c r="V295">
@@ -39209,7 +39209,7 @@
       </c>
       <c r="U296" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/18f92f5b-5095-4626-9698-ea475b991094/Laudo_AC_26-2026_-_MARIA_ALZENIRA_BONIFACIO_DA_SILVA_assinado.pdf?expires_on=1785434314&amp;signature=NuJoGEkLFx38NNiL6oD320huIfitYPxFAwPqy1J%2BYg4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/18f92f5b-5095-4626-9698-ea475b991094/Laudo_AC_26-2026_-_MARIA_ALZENIRA_BONIFACIO_DA_SILVA_assinado.pdf?expires_on=1785434474&amp;signature=PX%2FaDm2KB04to8z8WtDIAjnZyC4C6C3d4qrsre8kk2U%3D</t>
         </is>
       </c>
       <c r="V296">
@@ -39335,7 +39335,7 @@
       </c>
       <c r="U297" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ebf883e2-2f7f-4aea-b252-a41bee85ae54/LaudoJP09-Bemol-2026-MariaAparecidaJoseBarbosa_signed.pdf?expires_on=1785434314&amp;signature=QTnosFjMsmmmnFArGN7HDajGW9R0KehczXk8IWiTF38%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ebf883e2-2f7f-4aea-b252-a41bee85ae54/LaudoJP09-Bemol-2026-MariaAparecidaJoseBarbosa_signed.pdf?expires_on=1785434474&amp;signature=GGzeUU%2FEgKNNxxALgKaIouyLlenQDMyDM1diItOfGkI%3D</t>
         </is>
       </c>
       <c r="V297">
@@ -39472,7 +39472,7 @@
       </c>
       <c r="U298" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e233ac0a-899d-42ec-b244-ca470c80f0e0/LaudoP35-Bemol-2026-MariaArleneAlvesCavalcantePietrobeli_signed.pdf?expires_on=1785434314&amp;signature=M49lirPlo8ncv%2FoRDaliEFTGQHpqzdqWX7mHvhJrzOw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e233ac0a-899d-42ec-b244-ca470c80f0e0/LaudoP35-Bemol-2026-MariaArleneAlvesCavalcantePietrobeli_signed.pdf?expires_on=1785434474&amp;signature=03nBN7bn6sfJo2iPcRTg3BI%2BHWcdj0yg7iL8UpBlJaE%3D</t>
         </is>
       </c>
       <c r="V298">
@@ -39601,7 +39601,7 @@
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e095a2b6-f97b-421b-962a-6e32da7deddf/Laudo202-Bemol-2026-MariaAssuncaodaSilvaAlfaia-Assinado.pdf?expires_on=1785434314&amp;signature=DoiVa8szKaCCNHiplZq4aFazk%2F9pAI3q8DKl0cZew4Q%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e095a2b6-f97b-421b-962a-6e32da7deddf/Laudo202-Bemol-2026-MariaAssuncaodaSilvaAlfaia-Assinado.pdf?expires_on=1785434474&amp;signature=UJaJl8iYSxNpBzoVZGH7nShCBCjPR94A1h0g%2BPHsyRY%3D</t>
         </is>
       </c>
       <c r="V299">
@@ -39727,7 +39727,7 @@
       </c>
       <c r="U300" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b6aac934-c406-4470-93f1-187fcfd0cc05/Laudo71-Bemol-2026-MariaAuxiliadoraDosSantosFreire-Assinado.pdf?expires_on=1785434314&amp;signature=mZQZGKRjfZ%2BXQxoaza%2Fapbzv9BUJGqjQs5VtWA%2B194Y%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b6aac934-c406-4470-93f1-187fcfd0cc05/Laudo71-Bemol-2026-MariaAuxiliadoraDosSantosFreire-Assinado.pdf?expires_on=1785434474&amp;signature=jdkDQeoKniGQhNxTkaPzklgaNcscnkMrECKfGOEjtcM%3D</t>
         </is>
       </c>
       <c r="V300">
@@ -39861,7 +39861,7 @@
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1d3061c5-cecb-4711-9151-c91be3c95c96/LaudoP08-Bemol-2026-MariaDaConceicaoAguiarLeiteDeLima_signed.pdf?expires_on=1785434314&amp;signature=xD%2FYKHZPkmr26bLeQWg%2BzbTiaYaHVdgk1D9Nplys18k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1d3061c5-cecb-4711-9151-c91be3c95c96/LaudoP08-Bemol-2026-MariaDaConceicaoAguiarLeiteDeLima_signed.pdf?expires_on=1785434474&amp;signature=YlqrhBh6lP87MS49%2BcG6PFHaXA%2BKvktr6yLdbey1yHI%3D</t>
         </is>
       </c>
       <c r="V301">
@@ -39984,7 +39984,7 @@
       </c>
       <c r="U302" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/dd88613a-1fcd-48ee-9de8-35f993dcfef6/B9-2026-BEMOL-MARIADASGRAASCEZARIODAVILA_2.PDF?expires_on=1785434314&amp;signature=B5UFfT6p9LveOeGSvmt8GlFX4FUdP1Q2Wmvr3Pb5eY0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/dd88613a-1fcd-48ee-9de8-35f993dcfef6/B9-2026-BEMOL-MARIADASGRAASCEZARIODAVILA_2.PDF?expires_on=1785434474&amp;signature=0StPVn47%2BUXnUxYh3JITOCnCNsFFyvJg%2BSJASDwiqdg%3D</t>
         </is>
       </c>
       <c r="V302">
@@ -40115,7 +40115,7 @@
       </c>
       <c r="U303" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cab14ac9-6a56-4849-a10c-6152088d26df/LaudoP14-Bemol-2026-MariaDeFatimaVieiraFrazao_signed.pdf?expires_on=1785434314&amp;signature=HtvYbYHyVoYsae6%2BOcIpKw6MGIwP54%2FBRyUtahggdKc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cab14ac9-6a56-4849-a10c-6152088d26df/LaudoP14-Bemol-2026-MariaDeFatimaVieiraFrazao_signed.pdf?expires_on=1785434474&amp;signature=JynnqPbDwDME5tUjSmwcTtma1Mqha1meX2ONEXIXNa4%3D</t>
         </is>
       </c>
       <c r="V303">
@@ -40239,7 +40239,7 @@
       </c>
       <c r="U304" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ff304689-adf2-4093-b0be-aecc6313af56/Laudo_AC_33-2026_-_MARIA_DE_JESUS_LIMA_FELIPE_assinado.pdf?expires_on=1785434314&amp;signature=OK62rK7m4l10ikBhRxlGMx%2BYSDR71w6dnP1RQK1YVJ8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ff304689-adf2-4093-b0be-aecc6313af56/Laudo_AC_33-2026_-_MARIA_DE_JESUS_LIMA_FELIPE_assinado.pdf?expires_on=1785434474&amp;signature=UI1KAbgdW4%2FeVlnzeltDJJgIxy2IDHyDLYB%2B9ZQ%2B9hM%3D</t>
         </is>
       </c>
       <c r="V304">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="U305" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c55fb3c0-a15d-418a-adf5-ca601b20fd7d/Laudo483-Bemol-2025-MariaDeLourdesOliveiraDosSantos-Assinado.pdf?expires_on=1785434314&amp;signature=tW8dztYwX9zaicxP3ZTGTtmOdQwH2Etdyo08aVDOCtQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c55fb3c0-a15d-418a-adf5-ca601b20fd7d/Laudo483-Bemol-2025-MariaDeLourdesOliveiraDosSantos-Assinado.pdf?expires_on=1785434474&amp;signature=SEG1u6vR8fklp1ASsq1NegG1f6upf%2Fmt%2B3w%2FW6AJYxA%3D</t>
         </is>
       </c>
       <c r="V305">
@@ -40500,7 +40500,7 @@
       </c>
       <c r="U306" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/82e2bfef-4c26-4ff1-a502-d802344e71e8/LAUDOMARIADENAZARcorrigido.pdf?expires_on=1785434314&amp;signature=jg7MA3ZhlKla0mX%2FX%2FIM0iBXLXHBv14Elu7f64z%2FlW4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/82e2bfef-4c26-4ff1-a502-d802344e71e8/LAUDOMARIADENAZARcorrigido.pdf?expires_on=1785434474&amp;signature=zgdy98EIU6PpF6nMvzrJaDjiGr%2F3Btx3dSyQWsF%2F%2F1A%3D</t>
         </is>
       </c>
       <c r="V306">
@@ -40632,7 +40632,7 @@
       </c>
       <c r="U307" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4ebdc764-7aae-430f-859d-fd287b74f5c4/RelatriodeRefernciaRVR06-Bemol-2025-MariaDoPerpetuoSocorroNoronhaPeixoto-Assinado.pdf?expires_on=1785434314&amp;signature=bFn6Kvqj%2FQRlVv%2Bk0vLyTrt8Mn2c6lOIjGgWQlWmIKs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4ebdc764-7aae-430f-859d-fd287b74f5c4/RelatriodeRefernciaRVR06-Bemol-2025-MariaDoPerpetuoSocorroNoronhaPeixoto-Assinado.pdf?expires_on=1785434474&amp;signature=98UO6oFBvUDwuePKNXIohL0Q9URSpKgifiuRYJWieAc%3D</t>
         </is>
       </c>
       <c r="V307">
@@ -40761,7 +40761,7 @@
       </c>
       <c r="U308" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/742ca05a-a665-4c71-a272-4e082a6347fe/M15-2026-MARIADOSOCORROajustado.pdf?expires_on=1785434314&amp;signature=QumhJ7BT4h6mvtLzFHnFfLwI5vW86k1Y3IzV0oTv6aQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/742ca05a-a665-4c71-a272-4e082a6347fe/M15-2026-MARIADOSOCORROajustado.pdf?expires_on=1785434474&amp;signature=iGCtxSAl9mFhHajEHKarUgzFaqijvUcNXdy1%2BHtLjY8%3D</t>
         </is>
       </c>
       <c r="V308">
@@ -40887,7 +40887,7 @@
       </c>
       <c r="U309" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3897fd9c-1b1c-409e-a1e3-4693c1e2031b/LaudoPA01-Bemol-2026-MariaDulcileneReisdeSouza-Assinado1.pdf?expires_on=1785434314&amp;signature=VEc%2BQFJMv05Q7m6hkTuP3W4tyHxiYC%2BrcHsQFDirNmE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3897fd9c-1b1c-409e-a1e3-4693c1e2031b/LaudoPA01-Bemol-2026-MariaDulcileneReisdeSouza-Assinado1.pdf?expires_on=1785434474&amp;signature=YAp6qECzSWZkSqyeVIGQGw8Nw3boe8wXsnM9%2FHnx1hg%3D</t>
         </is>
       </c>
       <c r="V309">
@@ -41031,7 +41031,7 @@
       </c>
       <c r="U310" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7ed173fa-cddd-4d05-8f4f-902f54d5ca8a/laudoB46-2026-BEMOL-MARIAFERNANDALARRANAGASEGOVIA.pdf?expires_on=1785434314&amp;signature=W3N9GQtAZZQj%2B5xg1cYFMYKAt7T7lVHk9R5RLQaGOUU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7ed173fa-cddd-4d05-8f4f-902f54d5ca8a/laudoB46-2026-BEMOL-MARIAFERNANDALARRANAGASEGOVIA.pdf?expires_on=1785434474&amp;signature=QlaJXDAhvijTZ7SyKwVen4bV38Iz3%2Fdw0CIVG%2FyECeI%3D</t>
         </is>
       </c>
       <c r="V310">
@@ -41162,7 +41162,7 @@
       </c>
       <c r="U311" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c7d38b5a-cbf9-4dda-aa89-7ed36b998de7/LAUDOMARIAFRANCISCA.pdf?expires_on=1785434314&amp;signature=Tv0gkqyEQFD7Iw6oediXy331UnIkfEhwVlyVWULhG5Q%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c7d38b5a-cbf9-4dda-aa89-7ed36b998de7/LAUDOMARIAFRANCISCA.pdf?expires_on=1785434474&amp;signature=WNvbCDvjupx0mVSE257C%2BCeeARJ%2BzQIhNhjyb%2FPjoxI%3D</t>
         </is>
       </c>
       <c r="V311">
@@ -41299,7 +41299,7 @@
       </c>
       <c r="U312" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2d546a2b-3b56-41e1-a9c7-8913a61d5532/Laudo_AC_08-2026_-_MARIA_HELENA_BRAGA_PINHEIRO_assinado.pdf?expires_on=1785434314&amp;signature=ddu7DjEgc3fcDnTTNQm3V4dL3kBh3qiNAyIb%2BKDFhgU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2d546a2b-3b56-41e1-a9c7-8913a61d5532/Laudo_AC_08-2026_-_MARIA_HELENA_BRAGA_PINHEIRO_assinado.pdf?expires_on=1785434474&amp;signature=PRzYMfQv2LPgF31PdUP2byL7zAMMCZYvs8pZzOL3xp0%3D</t>
         </is>
       </c>
       <c r="V312">
@@ -41436,7 +41436,7 @@
       </c>
       <c r="U313" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e79fdb40-909f-4b3a-8481-13e641450f31/M7-2026-MARIAINESSOARESJACINTOajustado.pdf?expires_on=1785434314&amp;signature=k%2FiI9f7gaHJJX%2FPiQDlkdj2YZ%2BSuEqCukB%2FRxWk%2B9N0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e79fdb40-909f-4b3a-8481-13e641450f31/M7-2026-MARIAINESSOARESJACINTOajustado.pdf?expires_on=1785434474&amp;signature=3%2BLsyl%2BWAzVoOg22i6Jzt1KBSjoxYXCBZKpYjrSIUGM%3D</t>
         </is>
       </c>
       <c r="V313">
@@ -41567,7 +41567,7 @@
       </c>
       <c r="U314" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/26d64727-9685-4583-8a1e-089c96c70bb9/LAUDOMARIAITAEMA.pdf?expires_on=1785434314&amp;signature=e8N3Hv9cp0N5813iSlS9UmPlla9bzueCtwMW1qv6UkQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/26d64727-9685-4583-8a1e-089c96c70bb9/LAUDOMARIAITAEMA.pdf?expires_on=1785434474&amp;signature=dQjGpBHzYoS9IM7h4HUdpsz5F3nvtVrAZRATYUahieo%3D</t>
         </is>
       </c>
       <c r="V314">
@@ -41704,7 +41704,7 @@
       </c>
       <c r="U315" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6dfdf02b-74f0-4e41-a6bf-33541f0becc3/LAUDOMariaIvone.pdf?expires_on=1785434314&amp;signature=9GTpwY1LFolX95o8vcJn%2FkGJjzq0OFDwDp48uhzvbOI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6dfdf02b-74f0-4e41-a6bf-33541f0becc3/LAUDOMariaIvone.pdf?expires_on=1785434474&amp;signature=QYUl%2BOfKtCEEKGB87JshagS36%2F7SvG0GoNSLeI%2Bg%2FI0%3D</t>
         </is>
       </c>
       <c r="V315">
@@ -41828,7 +41828,7 @@
       </c>
       <c r="U316" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1488dcea-b0af-4f7b-90cc-43750768830d/BEMOL-PV094-MARIAIVONEDESOUZAMARTINS.pdf?expires_on=1785434314&amp;signature=fnlsHNIkOow1%2ByXMA2ELgJlKrDu4iDU8II1dX5j3kVE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1488dcea-b0af-4f7b-90cc-43750768830d/BEMOL-PV094-MARIAIVONEDESOUZAMARTINS.pdf?expires_on=1785434474&amp;signature=pZs4ezj2Fvw73hwU5VFMKLMbF9KzN%2BY1OVuiX1W5OAA%3D</t>
         </is>
       </c>
       <c r="V316">
@@ -41960,7 +41960,7 @@
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e90feef1-e03d-4eb1-9742-f968486ba251/Laudo_AC_-_04-2026_-_MARIA_JACINTA_DE_SOUZA_assinado.pdf?expires_on=1785434314&amp;signature=HQXldFaSmsJGVBG1levOoFFbvOpv%2BBzDmS5LYwxZmwU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e90feef1-e03d-4eb1-9742-f968486ba251/Laudo_AC_-_04-2026_-_MARIA_JACINTA_DE_SOUZA_assinado.pdf?expires_on=1785434474&amp;signature=BOU5vZG66tD4YT9YkBqoAYEnXq6kNtkG9zvwal95XyM%3D</t>
         </is>
       </c>
       <c r="V317">
@@ -42102,7 +42102,7 @@
       </c>
       <c r="U318" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/dc51577b-2631-4975-8584-9becda3d52e2/Laudo147-Bemol-2026-MariaJosePiresCorrea.pdf?expires_on=1785434314&amp;signature=Ox%2B0UNN3t0J1%2ByjiFioyTFiOp6pcj2XjSgJVtpuRC34%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/dc51577b-2631-4975-8584-9becda3d52e2/Laudo147-Bemol-2026-MariaJosePiresCorrea.pdf?expires_on=1785434474&amp;signature=1Wk9xWkxT0lDo4FZXXywT5KpbHKXh0Rf5Te244Dpi4A%3D</t>
         </is>
       </c>
       <c r="V318">
@@ -42239,7 +42239,7 @@
       </c>
       <c r="U319" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1ef0eda4-befd-4e84-92fb-074a2d65ecfc/LaudoB17-2026-BEMOL-MARIALUCIAFEITOSAFERREIRA.pdf?expires_on=1785434314&amp;signature=dV9ZGB1C2qi5GtoXo6R5qFv7EXwcZOEe3%2Fp1t0XYkYk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1ef0eda4-befd-4e84-92fb-074a2d65ecfc/LaudoB17-2026-BEMOL-MARIALUCIAFEITOSAFERREIRA.pdf?expires_on=1785434474&amp;signature=q2yBXhcxtpSAnU%2BV10qnJUzERpi8A4sfLuB5La2RC6A%3D</t>
         </is>
       </c>
       <c r="V319">
@@ -42368,7 +42368,7 @@
       </c>
       <c r="U320" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0176fe84-495c-4590-a49f-aa8c95b5d25a/MARIALUZIADEARAJOGOMESLAUDO.pdf?expires_on=1785434314&amp;signature=5oyouO6%2FwjEs7smlBBQQW1ZNMHX0Z1D9lNjtXOqulv0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0176fe84-495c-4590-a49f-aa8c95b5d25a/MARIALUZIADEARAJOGOMESLAUDO.pdf?expires_on=1785434474&amp;signature=DlpmelmFC3n6dPCta86AIBNOEresNoXZ6%2BYWqJG8lzY%3D</t>
         </is>
       </c>
       <c r="V320">
@@ -42511,7 +42511,7 @@
       </c>
       <c r="U321" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f41c57b3-2b18-4937-aea4-3f825fea861e/LaudoB34-2026-BEMOL-MARIAPONTESDEARAUJO.pdf?expires_on=1785434314&amp;signature=OZgzj7LQzRckKwRw6YAnetgUhepnxaaWWQzlPrTU4%2BU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f41c57b3-2b18-4937-aea4-3f825fea861e/LaudoB34-2026-BEMOL-MARIAPONTESDEARAUJO.pdf?expires_on=1785434474&amp;signature=Pa5iT7%2BTV4dq1Yx%2F45NH%2BR%2FXfShPhOOjELhy9zO0IKI%3D</t>
         </is>
       </c>
       <c r="V321">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="U322" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/01fb9855-c9d4-43d1-946a-8878501765cc/LaudoPA16-Bemol-2026-MariaRaquelTravassosDeCarvalho.pdf?expires_on=1785434314&amp;signature=KBunFKfxFzA04Tih5Ci534JSFlSHMCZnU5i9YWqIbIo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/01fb9855-c9d4-43d1-946a-8878501765cc/LaudoPA16-Bemol-2026-MariaRaquelTravassosDeCarvalho.pdf?expires_on=1785434474&amp;signature=9QxM51ZIxqEgMPkxeiTqn7kTuPFPP7aSHDhk02jMfs8%3D</t>
         </is>
       </c>
       <c r="V322">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="U323" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2be0b85f-6106-432d-b849-622ad4c020fd/Laudo17-Bemol-2026-MariaRobertinaDosSantosDaSilva-Assinadocorrigido.pdf?expires_on=1785434314&amp;signature=OR07OUtaIHhbKrQlRqUBREW495newWJsotRy5xyb%2BW4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2be0b85f-6106-432d-b849-622ad4c020fd/Laudo17-Bemol-2026-MariaRobertinaDosSantosDaSilva-Assinadocorrigido.pdf?expires_on=1785434474&amp;signature=V43x8Ps02BvFhWJBhVLe%2B%2FMS%2Bd1LtwjTBFTiZl8rBKY%3D</t>
         </is>
       </c>
       <c r="V323">
@@ -42909,7 +42909,7 @@
       </c>
       <c r="U324" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/25f8132e-7927-4fb6-afa7-a19ee524fab5/Laudo205-Bemol-2026-MariaSuzeirMatosdeAraujo.pdf?expires_on=1785434314&amp;signature=nr8GFCvAPfblvi3dsyWFOYUL6h8Jz5lAOZA98lqi2ac%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/25f8132e-7927-4fb6-afa7-a19ee524fab5/Laudo205-Bemol-2026-MariaSuzeirMatosdeAraujo.pdf?expires_on=1785434474&amp;signature=Bn376BF3Qx1CPewgnbp2fawavuH2Lrufx3Kesz%2B%2BhBs%3D</t>
         </is>
       </c>
       <c r="V324">
@@ -43038,7 +43038,7 @@
       </c>
       <c r="U325" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/89e4b8fb-6d1c-4b18-bc41-4769822c7418/Laudo27-Bemol-2026-MariaValcyDomingosDeOliveira-Assinado.pdf?expires_on=1785434314&amp;signature=Njipfwzrepc14qWpj6FvF3vUU9i93RJHCU59toViOtQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/89e4b8fb-6d1c-4b18-bc41-4769822c7418/Laudo27-Bemol-2026-MariaValcyDomingosDeOliveira-Assinado.pdf?expires_on=1785434474&amp;signature=yiF5No9lqRUSwyswM8u%2FGfnuGN2A8Be%2BEdqL0ZnBWSg%3D</t>
         </is>
       </c>
       <c r="V325">
@@ -43180,7 +43180,7 @@
       </c>
       <c r="U326" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1cad3662-f03c-43ae-9d4f-684594cfd025/Laudo73-2025-Bemol-MarielzadaSilvaFerreira-Assinado11.pdf?expires_on=1785434314&amp;signature=67RqFLrl53h1Sq6HD8y3mRb6qzIgCcV6iiVb6rgOAqM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1cad3662-f03c-43ae-9d4f-684594cfd025/Laudo73-2025-Bemol-MarielzadaSilvaFerreira-Assinado11.pdf?expires_on=1785434474&amp;signature=P0zBtvLx1aWscakUqbIUdoA28fq038XgOjwpG8fG%2FXw%3D</t>
         </is>
       </c>
       <c r="V326">
@@ -43312,7 +43312,7 @@
       </c>
       <c r="U327" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf95cf60-3c00-4a3e-a759-39ea4dd22760/LaudoPA20-Bemol-2026-MarileiaAraujodosSantos.pdf?expires_on=1785434314&amp;signature=EpHtDMJ%2FY95z9hBZB4JjPRPgJo7g9GQ7qhNoCbeIVnU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf95cf60-3c00-4a3e-a759-39ea4dd22760/LaudoPA20-Bemol-2026-MarileiaAraujodosSantos.pdf?expires_on=1785434474&amp;signature=dRQW%2BmuqLsXeJyAB8Npunaj%2Be%2FNk4FrHPvAm3eAM11U%3D</t>
         </is>
       </c>
       <c r="V327">
@@ -43444,7 +43444,7 @@
       </c>
       <c r="U328" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/aecf4ecf-3b93-4133-970d-1739cf867dfd/LaudoB134-2025-BEMOL-MARILENAFERNANDESRIBEIRO.pdf?expires_on=1785434314&amp;signature=ih9BS0S1Qwu21LeeKtg6dvPSjQsqCmz2LPEJaauYPx8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/aecf4ecf-3b93-4133-970d-1739cf867dfd/LaudoB134-2025-BEMOL-MARILENAFERNANDESRIBEIRO.pdf?expires_on=1785434474&amp;signature=nZOkuCkVOmBH%2BpJ7v0s4%2FfH90L6WY2kiW7lR%2Bfv13JU%3D</t>
         </is>
       </c>
       <c r="V328">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="U329" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/dc55bd44-8950-4c50-baaa-6544f1d1f586/LAUDOCORRIGIDOMARILZA.pdf?expires_on=1785434314&amp;signature=Klxrj317%2BdkKUziaMQWabYgNLjQS3pt833%2F64BOedYk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/dc55bd44-8950-4c50-baaa-6544f1d1f586/LAUDOCORRIGIDOMARILZA.pdf?expires_on=1785434474&amp;signature=M%2F9vu%2F5AoHXCD0KoF%2BTQCsHgfb%2FuAh9kOphTTuM4gUY%3D</t>
         </is>
       </c>
       <c r="V329">
@@ -43727,7 +43727,7 @@
       </c>
       <c r="U330" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/815429c2-8ea7-4f05-a029-d9793ed024bd/Laudo154-Bemol-2026-MarioJorgeLouzadaCarvalhoSobrinho-Assinadoajustado.pdf?expires_on=1785434314&amp;signature=Jj1lpCbGo6prr2ol%2FwYCnIwoCXjvcphW%2Fwj75SaFSKo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/815429c2-8ea7-4f05-a029-d9793ed024bd/Laudo154-Bemol-2026-MarioJorgeLouzadaCarvalhoSobrinho-Assinadoajustado.pdf?expires_on=1785434474&amp;signature=B%2BdYayuqkDKkwfsisU7Yus2sxiarCf%2F9J3h5PPH%2F%2Fgk%3D</t>
         </is>
       </c>
       <c r="V330">
@@ -43853,7 +43853,7 @@
       </c>
       <c r="U331" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e0a77309-5262-4b3a-9110-b2e64bc37988/Laudo_AC_13-2026_-_MARIZELIA_PEREIRA_DE_SOUZA_assinado.pdf?expires_on=1785434314&amp;signature=nFb8nZn72Mh8%2Fg6yLanmCMVm8yaJ2QwfGUwFsicNGfI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e0a77309-5262-4b3a-9110-b2e64bc37988/Laudo_AC_13-2026_-_MARIZELIA_PEREIRA_DE_SOUZA_assinado.pdf?expires_on=1785434474&amp;signature=QStzO6QNq3o6xruCCGm4zSAjGVa%2BuODlJgxMc52B34A%3D</t>
         </is>
       </c>
       <c r="V331">
@@ -43984,7 +43984,7 @@
       </c>
       <c r="U332" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/bdbeccee-6613-48e7-a1f7-3c17a756b47b/Laudo484-Bemol-2025-MauricioAlexCastro-Assinado.pdf?expires_on=1785434314&amp;signature=3oB5wQakuMgdBKHjO%2BMDGiTGEMiWgztRr3wOUTGJzlw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/bdbeccee-6613-48e7-a1f7-3c17a756b47b/Laudo484-Bemol-2025-MauricioAlexCastro-Assinado.pdf?expires_on=1785434474&amp;signature=COl2bjoOH4J5nyYp2BBVgeCGE%2BUrkvDB6yoOaBD1moE%3D</t>
         </is>
       </c>
       <c r="V332">
@@ -44124,7 +44124,7 @@
       </c>
       <c r="U333" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e3911817-dca4-4120-a786-d15a97470ae5/Laudo93-Bemol-2026-MerciaTatielleDosSantosPereira-Assinado.pdf?expires_on=1785434314&amp;signature=SNpbZ0UMWBaeoCMY0vHxVhI4a9abvGCkLsHnLbLP%2B6M%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e3911817-dca4-4120-a786-d15a97470ae5/Laudo93-Bemol-2026-MerciaTatielleDosSantosPereira-Assinado.pdf?expires_on=1785434474&amp;signature=SGv%2BDQBCDBxeiwfatBeOrIyMO5jBaaWeKyh2gDNMduA%3D</t>
         </is>
       </c>
       <c r="V333">
@@ -44262,7 +44262,7 @@
       </c>
       <c r="U334" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b2112f19-0019-4577-a273-dc2e41acb014/LaudoITA17-Bemol-2025-MilsonDaSilvaMatos-Assinado.pdf?expires_on=1785434314&amp;signature=KG1ZXQm7NJXIcxhV5IrU36SQWaLRF5mIh%2FAMXu3764A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b2112f19-0019-4577-a273-dc2e41acb014/LaudoITA17-Bemol-2025-MilsonDaSilvaMatos-Assinado.pdf?expires_on=1785434474&amp;signature=OLjRHFMxUbpSgfytyUGhOQkzTyFIi8VDK8gTo0gfxpA%3D</t>
         </is>
       </c>
       <c r="V334">
@@ -44400,7 +44400,7 @@
       </c>
       <c r="U335" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b2da76eb-c630-4d64-b529-e207ec5274d5/BEMOL-AR029-MIQUEIASPEREIRALIMA.pdf?expires_on=1785434314&amp;signature=dCeSVndikDHjv5%2BiQ9qajUUHz5o%2BlzzysR9r2NRXdDs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b2da76eb-c630-4d64-b529-e207ec5274d5/BEMOL-AR029-MIQUEIASPEREIRALIMA.pdf?expires_on=1785434474&amp;signature=IwzOP3oWGrlJnm%2Fei3TO0seIMVB9nd8xsMkAOGMxBRQ%3D</t>
         </is>
       </c>
       <c r="V335">
@@ -44531,7 +44531,7 @@
       </c>
       <c r="U336" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/713476f3-cbfc-4874-878b-5d07d66cacc8/Laudo_AC_01-2026_-_MIRLANE_NUNES_LEITE_assinado.pdf?expires_on=1785434314&amp;signature=hr7bkUSU%2FBFmNB0VqtG00KHyf2TyJtK67JdVGucaXZ8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/713476f3-cbfc-4874-878b-5d07d66cacc8/Laudo_AC_01-2026_-_MIRLANE_NUNES_LEITE_assinado.pdf?expires_on=1785434474&amp;signature=fu4Ym1dYVXKeODrMaswR%2BAwper5590m%2BumRvRe8E4GE%3D</t>
         </is>
       </c>
       <c r="V336">
@@ -44668,7 +44668,7 @@
       </c>
       <c r="U337" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/dbecde08-ca35-444e-8b4f-8ed06a8e1c19/LaudoB132-2024-BEMOL-NAIADSONPEREIRANASCIMENTO_2.pdf?expires_on=1785434314&amp;signature=OCkbYAppGMpuqd1QbqHzftDuzDThnGzdAbeWKBcMFNg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/dbecde08-ca35-444e-8b4f-8ed06a8e1c19/LaudoB132-2024-BEMOL-NAIADSONPEREIRANASCIMENTO_2.pdf?expires_on=1785434474&amp;signature=eYqv7E1yy0bCK0K21KgnmtV%2FuwMaHc2ufu3CpM17ghc%3D</t>
         </is>
       </c>
       <c r="V337">
@@ -44817,7 +44817,7 @@
       </c>
       <c r="U338" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/406a23dd-f506-456c-af1a-be9bd4ee11c4/B19-2026-BEMOL-NARACRISTINADASILVANUNES.pdf?expires_on=1785434314&amp;signature=7jd0pflUnwcWXgXAwZaqpfsx6sAVq55gdeEbg2f105E%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/406a23dd-f506-456c-af1a-be9bd4ee11c4/B19-2026-BEMOL-NARACRISTINADASILVANUNES.pdf?expires_on=1785434474&amp;signature=3%2BYt%2FHMTTyjgVS92%2FV1gSxy%2F028XeiGBEpXGejF5xWk%3D</t>
         </is>
       </c>
       <c r="V338">
@@ -44946,7 +44946,7 @@
       </c>
       <c r="U339" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/927e466a-c43d-4bcb-9aad-fd878691e392/Laudo50-Bemol-2026-NarleyAdsonPaivaGuedes-Assinado.pdf?expires_on=1785434314&amp;signature=5Zl4HdpKacjJ5xF8osrDeAUmoyK%2Bbdg4sD0yESWzZNM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/927e466a-c43d-4bcb-9aad-fd878691e392/Laudo50-Bemol-2026-NarleyAdsonPaivaGuedes-Assinado.pdf?expires_on=1785434474&amp;signature=DT88sFV66plCEGzHrRyoDqWTGbA7JUIsY7YlEYO06nQ%3D</t>
         </is>
       </c>
       <c r="V339">
@@ -45076,7 +45076,7 @@
       </c>
       <c r="U340" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e4619ba4-b243-47e3-b1bc-53dbd3d3000c/BEMOL-PV084-NATALIAGONALVESSANTOSFARIA.pdf?expires_on=1785434314&amp;signature=HLAPxkv5uJ9uh%2FfG1kH5rkF5wOu4RO%2FQNxApB8B7xTY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e4619ba4-b243-47e3-b1bc-53dbd3d3000c/BEMOL-PV084-NATALIAGONALVESSANTOSFARIA.pdf?expires_on=1785434474&amp;signature=SdJxxXbl0CnypShYUwWS0qgCfRQvA%2FLzSyHcPHloyfE%3D</t>
         </is>
       </c>
       <c r="V340">
@@ -45199,7 +45199,7 @@
       </c>
       <c r="U341" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f8dc64fc-c4ec-47ce-a46e-4bf527db31c2/Laudo152-Bemol-2026-NatanCavalcanteGama.pdf?expires_on=1785434314&amp;signature=P6CfSNBL6vs%2F%2Fdv7WMjJpHqOyjsCViSMSqVBYVGChks%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f8dc64fc-c4ec-47ce-a46e-4bf527db31c2/Laudo152-Bemol-2026-NatanCavalcanteGama.pdf?expires_on=1785434474&amp;signature=x25d6bWbw3VjZh7Kf8D4JhhpG3H70ciBb75xpDSidq4%3D</t>
         </is>
       </c>
       <c r="V341">
@@ -45328,7 +45328,7 @@
       </c>
       <c r="U342" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6e94f045-e010-4542-bebf-ff40b226f280/Laudo57-Bemol-2026-NeimarRodriguesDaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=PjuxqcxJBuPkd61d43Rl6ojDDdsYVp%2B1CztAQWpLhfU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6e94f045-e010-4542-bebf-ff40b226f280/Laudo57-Bemol-2026-NeimarRodriguesDaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=uenKq%2FRpW9ptfNOp6%2BoM2cUpuP%2B3FDOc%2FzrvEvVVnLY%3D</t>
         </is>
       </c>
       <c r="V342">
@@ -45462,7 +45462,7 @@
       </c>
       <c r="U343" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/bd20bab3-e8b5-4ac4-b46e-e12eb8aa2f69/Laudo378-Bemol-2025-ThaisDoNascimentoSantos-Assinado.pdf?expires_on=1785434314&amp;signature=ZgxZt4WUfmUIvXJElU1dzwEHCLFj0dUtst7oywiBuWo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/bd20bab3-e8b5-4ac4-b46e-e12eb8aa2f69/Laudo378-Bemol-2025-ThaisDoNascimentoSantos-Assinado.pdf?expires_on=1785434474&amp;signature=L3zThctLwi2c%2FvBYcafv3beI8PP2oKMW1BbVopAkWM8%3D</t>
         </is>
       </c>
       <c r="V343">
@@ -45610,7 +45610,7 @@
       </c>
       <c r="U344" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9bbfd341-5438-4cf5-8a27-6f1088766197/LAUDONILTONCEZAR.pdf?expires_on=1785434314&amp;signature=d8haXp3Oj7QVNge%2F250A3VGvYKKwOM6vdaeK%2Fdpp8J4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9bbfd341-5438-4cf5-8a27-6f1088766197/LAUDONILTONCEZAR.pdf?expires_on=1785434474&amp;signature=6YONAz6qG6Z1%2BG9q0Rv9vkkMGu0CWDK2ERJ5IS%2FO9XI%3D</t>
         </is>
       </c>
       <c r="V344">
@@ -45751,7 +45751,7 @@
       </c>
       <c r="U345" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d302a9e8-291d-42ac-aac8-8b33e1708abd/Laudo119-Bemol-2026-NiseMarinhoMacedo-Assinadoajustado.pdf?expires_on=1785434314&amp;signature=YYe%2FR85w2dhhMTtj%2F7iqcnnBguduRAr27iIXmJ0ZMjk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d302a9e8-291d-42ac-aac8-8b33e1708abd/Laudo119-Bemol-2026-NiseMarinhoMacedo-Assinadoajustado.pdf?expires_on=1785434474&amp;signature=LAs5GSZFhvRLxtx4i6aI1bD4dWWkpMxp3GIA6gqVf04%3D</t>
         </is>
       </c>
       <c r="V345">
@@ -45869,7 +45869,7 @@
       </c>
       <c r="U346" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e3585691-556b-4fe7-8f1a-44e30851b443/LaudoB30-2026-BEMOL-NoelinadosSantosChavesLopescorrigido.pdf?expires_on=1785434314&amp;signature=JTKjcBwAX9X9%2FNzKZ5W2xaZxwVcqQGiR2oZQzUfSATw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e3585691-556b-4fe7-8f1a-44e30851b443/LaudoB30-2026-BEMOL-NoelinadosSantosChavesLopescorrigido.pdf?expires_on=1785434474&amp;signature=NPfjBrE2cw3%2FnCzkE%2BjJPQjDoU5o0S06avcHTPKbX4U%3D</t>
         </is>
       </c>
       <c r="V346">
@@ -46003,7 +46003,7 @@
       </c>
       <c r="U347" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a128a1e1-9341-4b9c-91d2-c85521f18cee/Laudo175-Bemol-2026-NormaCoutinhoBastos.pdf?expires_on=1785434314&amp;signature=RozPbzeaoXn5KaD%2FhnQYleEizs66t7j1LgVKYzYyObg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a128a1e1-9341-4b9c-91d2-c85521f18cee/Laudo175-Bemol-2026-NormaCoutinhoBastos.pdf?expires_on=1785434474&amp;signature=iZ5bYM6oY6bFRuMXfG4P8jsGNvrPX1swOr3pQ0Iqllw%3D</t>
         </is>
       </c>
       <c r="V347">
@@ -46126,7 +46126,7 @@
       </c>
       <c r="U348" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/06a7e280-3b67-4984-9236-756331283a96/IT1-2026-NORMA.pdf?expires_on=1785434314&amp;signature=J%2BsLRMpa%2Bf1KYBWG7SZmyGPe4YrkpBsW2wUlKpPX62U%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/06a7e280-3b67-4984-9236-756331283a96/IT1-2026-NORMA.pdf?expires_on=1785434474&amp;signature=AY1%2BCEitI7z5OP8SvL3Zq9rvtuRSqq5z4L9zwGVoBno%3D</t>
         </is>
       </c>
       <c r="V348">
@@ -46252,7 +46252,7 @@
       </c>
       <c r="U349" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/957c2ec2-8a18-4aa5-ab94-04809d837653/LaudoB123-2025-BEMOL-ODEIBIANANASCIMENTOSOUSA2.pdf?expires_on=1785434314&amp;signature=IGTkwP10K3h1Uc%2Bdl3pn2bQPmn3ed3eeFHw57IAc41o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/957c2ec2-8a18-4aa5-ab94-04809d837653/LaudoB123-2025-BEMOL-ODEIBIANANASCIMENTOSOUSA2.pdf?expires_on=1785434474&amp;signature=uI8RnCZUVJeXkMQIsFGW2R1jusOiNXguA%2FOiuC0iv4A%3D</t>
         </is>
       </c>
       <c r="V349">
@@ -46388,7 +46388,7 @@
       </c>
       <c r="U350" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f4c56a88-7cfd-486d-9871-ff069fccc652/Laudo02-Bemol-2026-OdelitaDosSantosAraujo-Assinado.pdf?expires_on=1785434314&amp;signature=vLsSIqGNvPuW8Wyw5pKfAujX%2By2BmyXdTaB8sJExY5k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f4c56a88-7cfd-486d-9871-ff069fccc652/Laudo02-Bemol-2026-OdelitaDosSantosAraujo-Assinado.pdf?expires_on=1785434474&amp;signature=SEy9ok7%2FhYdU44VFIt6HFFTa0symXRzyXa3%2FgXQjpNQ%3D</t>
         </is>
       </c>
       <c r="V350">
@@ -46511,7 +46511,7 @@
       </c>
       <c r="U351" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/29b628c0-63cf-4205-9b90-717ca5d97f3f/LaudoMAN08-Bemol-2026-OrlenBarrosoDaSilva.pdf?expires_on=1785434314&amp;signature=IZWvgmsb%2FRti7EiYjr8i6SMCphWDE0jCjvUnYMlRw9k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/29b628c0-63cf-4205-9b90-717ca5d97f3f/LaudoMAN08-Bemol-2026-OrlenBarrosoDaSilva.pdf?expires_on=1785434474&amp;signature=yLBKDtnSLhKEtb%2Bzf7xy%2F7mSBvoQH5iYy1TtIFVdw4s%3D</t>
         </is>
       </c>
       <c r="V351">
@@ -46640,7 +46640,7 @@
       </c>
       <c r="U352" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/049aa76b-eb15-4b22-975a-b99954f6425b/LAUDOOSMARPANTOJAcorrigido.pdf?expires_on=1785434314&amp;signature=Hd5zkDjjkIR8jD4Ha%2B%2F0rZfDRiQrEzUGNg0O7BlBOxg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/049aa76b-eb15-4b22-975a-b99954f6425b/LAUDOOSMARPANTOJAcorrigido.pdf?expires_on=1785434474&amp;signature=xDM2thENzs78jWOrLIACA8Jj7wJfC98DvoAEMg1g8cg%3D</t>
         </is>
       </c>
       <c r="V352">
@@ -46758,7 +46758,7 @@
       </c>
       <c r="U353" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6e70ff3e-1f36-4a2a-ad63-edb54a074bb6/LaudoMAN02-Bemol-2026-OsvaldoFDaSilvaJunior-Assinado-Ajustado.pdf?expires_on=1785434314&amp;signature=5OjIUml%2FCJCNC2JV60OrOv51KM36nSFf7hChnefmcw4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6e70ff3e-1f36-4a2a-ad63-edb54a074bb6/LaudoMAN02-Bemol-2026-OsvaldoFDaSilvaJunior-Assinado-Ajustado.pdf?expires_on=1785434474&amp;signature=ONtWea8hWkjgXZGqwtv9WjwVTIchEf2Hhtu3nFsgXxw%3D</t>
         </is>
       </c>
       <c r="V353">
@@ -46876,7 +46876,7 @@
       </c>
       <c r="U354" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5cd11b0a-bf3e-469a-9020-53993be3de6f/LaudoB27-2026-BEMOL-OsvaldoRodriguesMendesJunior.pdf?expires_on=1785434314&amp;signature=mobkMWoWzUwa5y5nvFgZf50rRdD46PTjjmOv%2BZSKmxQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5cd11b0a-bf3e-469a-9020-53993be3de6f/LaudoB27-2026-BEMOL-OsvaldoRodriguesMendesJunior.pdf?expires_on=1785434474&amp;signature=A0nLPPdHG26kXQyC79AE4eXUAYxj1SI%2BMk6DaOIpWHU%3D</t>
         </is>
       </c>
       <c r="V354">
@@ -47008,7 +47008,7 @@
       </c>
       <c r="U355" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/90e3641b-68c8-411b-85c2-af435523c2d7/LaudoB12-2026-BEMOL-OzielTavaresdeAraujoNeto.pdf?expires_on=1785434314&amp;signature=7JuZOgQDIbd3tWbXcHrTaP6hwsxeFof2%2FrgJdnTJaUg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/90e3641b-68c8-411b-85c2-af435523c2d7/LaudoB12-2026-BEMOL-OzielTavaresdeAraujoNeto.pdf?expires_on=1785434474&amp;signature=YZC%2BrZd7Z%2F2a9xiwl4p8tXGBOUHz9dimuSrCT4OZD84%3D</t>
         </is>
       </c>
       <c r="V355">
@@ -47140,7 +47140,7 @@
       </c>
       <c r="U356" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d9d11df7-bc9d-448a-a227-13e1880ddfa0/Laudo481-Bemol-2025-PamellaProcopioDaFonsecaLuiz-Assinado.pdf?expires_on=1785434314&amp;signature=hutsQ2kWMFywxjVAQ23almfyLMSo8y2I%2FfG3Bv19YNk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d9d11df7-bc9d-448a-a227-13e1880ddfa0/Laudo481-Bemol-2025-PamellaProcopioDaFonsecaLuiz-Assinado.pdf?expires_on=1785434474&amp;signature=ANouz8QxyZBiNjxivSXj7O4CKOtK2o7snA4WEyzr3D0%3D</t>
         </is>
       </c>
       <c r="V356">
@@ -47287,7 +47287,7 @@
       </c>
       <c r="U357" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0cd8693b-faeb-4b2c-a562-70e748431a36/LaudoP09-Bemol-2026-PatriciaRodriguesDeSouza_signed.pdf?expires_on=1785434314&amp;signature=nzQS8xxtOs5Ai%2FcJwfTud7JArEwZLNwkEKCw8L4OeyU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0cd8693b-faeb-4b2c-a562-70e748431a36/LaudoP09-Bemol-2026-PatriciaRodriguesDeSouza_signed.pdf?expires_on=1785434474&amp;signature=nuqWhrmDaooJUepYp1nlGWWVWlUnKehGioiRAH2Zn3Q%3D</t>
         </is>
       </c>
       <c r="V357">
@@ -47419,7 +47419,7 @@
       </c>
       <c r="U358" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/71755bfc-5154-4ffa-aeef-6147e7e548cd/LaudoCORRIGIDOPA09-Bemol-2026-PatrickWendeelRibeiroDeLima-Assinado1.pdf?expires_on=1785434314&amp;signature=ehRjVMT2yiYEEeKrsaorp%2FKjpLzhYwtZCtM%2B%2ByAiADA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/71755bfc-5154-4ffa-aeef-6147e7e548cd/LaudoCORRIGIDOPA09-Bemol-2026-PatrickWendeelRibeiroDeLima-Assinado1.pdf?expires_on=1785434474&amp;signature=MtVROdfxgjT8eMr2EZxZjc7TWq5169BW57LuKuxo2cQ%3D</t>
         </is>
       </c>
       <c r="V358">
@@ -47542,7 +47542,7 @@
       </c>
       <c r="U359" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a6840bb8-6f41-491e-86da-94110360b62e/Laudo30corrigido-Bemol-2026-PaulaJussaraDosSantosPortela.pdf?expires_on=1785434314&amp;signature=7P7w75fadSS5%2B4UKH54Jge1aqsoUQHwHk%2Fd1yBPeyp8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a6840bb8-6f41-491e-86da-94110360b62e/Laudo30corrigido-Bemol-2026-PaulaJussaraDosSantosPortela.pdf?expires_on=1785434474&amp;signature=a8Ni2G2FcpRBL6%2FJccF9nmK0F98L4WrtnGxFQ0ma%2BQc%3D</t>
         </is>
       </c>
       <c r="V359">
@@ -47672,7 +47672,7 @@
       </c>
       <c r="U360" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/956352cb-2de4-4540-b97a-c355dd5d85ee/LaudoR02-2026-BEMOL-PAULOCEZARRAMOSDASILVA.pdf?expires_on=1785434314&amp;signature=0powKsBB12SreXGad4gLnJEXD%2FnOibR27W0j%2BnUG%2BXs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/956352cb-2de4-4540-b97a-c355dd5d85ee/LaudoR02-2026-BEMOL-PAULOCEZARRAMOSDASILVA.pdf?expires_on=1785434474&amp;signature=yIzEOeUcvmSYvZ2s2HkS%2BA9YGaDqlYTE%2B17pAqdrytU%3D</t>
         </is>
       </c>
       <c r="V360">
@@ -47797,7 +47797,7 @@
       </c>
       <c r="U361" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d522f012-8c04-4896-92a4-214bc1194f74/M10-2026-PAULOCHRISTIAN.pdf?expires_on=1785434314&amp;signature=FGfQfpPLNwao9ICqwiMEhEGbxERSzrpNkYhTs78d%2BqQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d522f012-8c04-4896-92a4-214bc1194f74/M10-2026-PAULOCHRISTIAN.pdf?expires_on=1785434474&amp;signature=3QorEV4QhTbOx%2FQql4%2BHK%2BJplmBs%2FtzzZQaBZsGk9zw%3D</t>
         </is>
       </c>
       <c r="V361">
@@ -47920,7 +47920,7 @@
       </c>
       <c r="U362" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4ca6194d-c4bc-485f-8b4d-68f8b3b9a216/LAUDOPAULOROBERTOcorrigido02.pdf?expires_on=1785434314&amp;signature=BAqdnd%2F4IRNFxsjHOabaj2CPP%2BjmQu91F%2FgABvc7U8A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4ca6194d-c4bc-485f-8b4d-68f8b3b9a216/LAUDOPAULOROBERTOcorrigido02.pdf?expires_on=1785434474&amp;signature=FuHPYNxILHANXjH1yuSDDhjKo%2BdxKILZBXbIZaWRtO0%3D</t>
         </is>
       </c>
       <c r="V362">
@@ -48056,7 +48056,7 @@
       </c>
       <c r="U363" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f4445083-ab81-47ff-802f-df65996f45c1/Laudo189-Bemol-2026-PedroAugustoRibeiroTavares-Assinado.pdf?expires_on=1785434314&amp;signature=MXzJ%2B4KBA2mLaXtUsRXDdUKpPB9pqi0OhD9fV%2Fe9pMo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f4445083-ab81-47ff-802f-df65996f45c1/Laudo189-Bemol-2026-PedroAugustoRibeiroTavares-Assinado.pdf?expires_on=1785434474&amp;signature=3wekycyuCEJivJM5%2Fy6Ctotv%2F8Z%2B023gJ7rOguMFEJQ%3D</t>
         </is>
       </c>
       <c r="V363">
@@ -48185,7 +48185,7 @@
       </c>
       <c r="U364" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1d60b079-24d2-4aec-9716-87170632877d/BEMOL-AR022-POLIANAVIEIRADASILVA.pdf?expires_on=1785434314&amp;signature=h2F1Sf3UqEs1cwSrEw4fuKR7JABDguqI%2BzHtXdJAXX4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1d60b079-24d2-4aec-9716-87170632877d/BEMOL-AR022-POLIANAVIEIRADASILVA.pdf?expires_on=1785434474&amp;signature=y0ECJUaVH8lpIIw26Gw7Y%2FfSpOecQSHaaN2uHmKJtdg%3D</t>
         </is>
       </c>
       <c r="V364">
@@ -48317,7 +48317,7 @@
       </c>
       <c r="U365" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/63d9c535-82c6-4117-b3d6-e7f2c247e6e0/RelatriodeValordeRefernciaRVR04-Bemol-2026-RafaelaBatalhaDeCastroSantos-Assinado.pdf?expires_on=1785434314&amp;signature=2q2iBUzwiQ%2B4F%2F5kR4Rcn7pj0D0wrHiT4ZJwvOHmEBA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/63d9c535-82c6-4117-b3d6-e7f2c247e6e0/RelatriodeValordeRefernciaRVR04-Bemol-2026-RafaelaBatalhaDeCastroSantos-Assinado.pdf?expires_on=1785434474&amp;signature=KIy69JhCfbZy43X89pDUiY892SOBKButoeav0%2F03ENI%3D</t>
         </is>
       </c>
       <c r="V365">
@@ -48446,7 +48446,7 @@
       </c>
       <c r="U366" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/494b7e69-62fb-4fc7-8195-67cc571ac962/LaudoPF01-Bemol-2026-RaimundaDaConceicaoDaMotaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=tbJdiL0jgZSWBarYa5scAv1ACJ1d%2FSxveP78rdsls1g%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/494b7e69-62fb-4fc7-8195-67cc571ac962/LaudoPF01-Bemol-2026-RaimundaDaConceicaoDaMotaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=WYjq9Vks8GaShGzTqhnu7C9leADzVFX6rgdEN5j%2BejY%3D</t>
         </is>
       </c>
       <c r="V366">
@@ -48577,7 +48577,7 @@
       </c>
       <c r="U367" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d81f64de-ca9a-4f04-99de-226a9b718a79/Laudo282-Bemol-2025-RaimundaEmiliaVenceslauDaCosta-Assinado.pdf?expires_on=1785434314&amp;signature=QMRQk9bpNfa%2FxFxxSXKUdWnjb%2BpZnLlqQKO3wuR8GKc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d81f64de-ca9a-4f04-99de-226a9b718a79/Laudo282-Bemol-2025-RaimundaEmiliaVenceslauDaCosta-Assinado.pdf?expires_on=1785434474&amp;signature=KqecfRLmByYMUVFQudu%2B5sOgTjPR1%2FeURm2TP6iXe60%3D</t>
         </is>
       </c>
       <c r="V367">
@@ -48718,7 +48718,7 @@
       </c>
       <c r="U368" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1566149-eab3-4bd8-950f-23f13ef298c0/Laudo_AC_12-2026_-_RAIMUNDA_FRANCISCA_CONCEICAO_SOUSA_assinadocorrigido.pdf?expires_on=1785434314&amp;signature=ONI4U%2BTqohn1kDHv5ylred3fdsXjYMompnGXQQ0Zytk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1566149-eab3-4bd8-950f-23f13ef298c0/Laudo_AC_12-2026_-_RAIMUNDA_FRANCISCA_CONCEICAO_SOUSA_assinadocorrigido.pdf?expires_on=1785434474&amp;signature=OiFtCOZ6YN1JI6NyHpxjJaak5DZUoW%2BkkxSUv%2BSKZxo%3D</t>
         </is>
       </c>
       <c r="V368">
@@ -48854,7 +48854,7 @@
       </c>
       <c r="U369" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e11c7382-2c26-44d3-8e01-7eb6427e9aa8/Laudo60-Bemol-2026-RaimundaLopesMacielLeao-Assinado.pdf?expires_on=1785434314&amp;signature=vw1Kc0TzE1oX7IoVLJD9u5FEbt4RNW24%2FY6lkfsJ1B4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e11c7382-2c26-44d3-8e01-7eb6427e9aa8/Laudo60-Bemol-2026-RaimundaLopesMacielLeao-Assinado.pdf?expires_on=1785434474&amp;signature=oMttDruIHVFYiWpWNShTVxbVDsBo5e7iyDykn7C%2BwdU%3D</t>
         </is>
       </c>
       <c r="V369">
@@ -48977,7 +48977,7 @@
       </c>
       <c r="U370" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3e434f54-e252-422b-85b7-02202943d64c/LAUDOMELCINIRAcorrigido.pdf?expires_on=1785434314&amp;signature=gijXpY5SdCtXe8ERS6ie64F0HP0OskGhE3iejGITk8U%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3e434f54-e252-422b-85b7-02202943d64c/LAUDOMELCINIRAcorrigido.pdf?expires_on=1785434474&amp;signature=%2Bcm%2F%2FpgYKRcnoJYRt3nIUNSJ1gbmRF2jnTZ%2FNlOkFeQ%3D</t>
         </is>
       </c>
       <c r="V370">
@@ -49095,7 +49095,7 @@
       </c>
       <c r="U371" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b101fd87-d809-47ca-90f1-ad0770d144e4/Laudo136-Bemol-2026-RaimundaNonataMonteiroDaSilva.pdf?expires_on=1785434314&amp;signature=JivieChyv8BzgF2WI8MMOyrpb9P5h3QO0oan2Bc9I5Y%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b101fd87-d809-47ca-90f1-ad0770d144e4/Laudo136-Bemol-2026-RaimundaNonataMonteiroDaSilva.pdf?expires_on=1785434474&amp;signature=8qg8JELgUXi3ymGuMTFQ73iihpZkZgQ5slwcfIgJB74%3D</t>
         </is>
       </c>
       <c r="V371">
@@ -49226,7 +49226,7 @@
       </c>
       <c r="U372" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1b4d4b9-fd6c-438e-832d-95e654f5ed7f/Laudo174-Bemol-2026-RaimundoDeSouzaCabral-Assinado.pdf?expires_on=1785434314&amp;signature=N0YDkxV6eD9UIomnYnQczN25HdVQ3WwO9aOPp3S9L5o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1b4d4b9-fd6c-438e-832d-95e654f5ed7f/Laudo174-Bemol-2026-RaimundoDeSouzaCabral-Assinado.pdf?expires_on=1785434474&amp;signature=nyCvP8DvReWPBUOq7fJuv9PQmrfAy1LxwaeEiIuwNuI%3D</t>
         </is>
       </c>
       <c r="V372">
@@ -49357,7 +49357,7 @@
       </c>
       <c r="U373" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/db7d1af0-2b30-4244-849a-2cbba8563f18/Laudo390-Bemol-2025-RaimundoErasmoDoCarmoDeSousa-Assinado.pdf?expires_on=1785434314&amp;signature=Wu2tm35t5bkjnSttmYumiVMQKlXf%2BhVIs%2BWTQ%2BPdZUc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/db7d1af0-2b30-4244-849a-2cbba8563f18/Laudo390-Bemol-2025-RaimundoErasmoDoCarmoDeSousa-Assinado.pdf?expires_on=1785434474&amp;signature=qM3yZN15ryglqc7nCbhweElDys9Pq6m6AHo44E%2FnGxM%3D</t>
         </is>
       </c>
       <c r="V373">
@@ -49493,7 +49493,7 @@
       </c>
       <c r="U374" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e66d51aa-7a0b-460b-99dd-b2d322db2292/LaudoB13-2026-BEMOL-RAIMUNDOSOARESDESOUZA.pdf?expires_on=1785434314&amp;signature=7mzF96r58bo4EJtJrwZGYCbb%2BlivVD6mUaiY1kFxX7s%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e66d51aa-7a0b-460b-99dd-b2d322db2292/LaudoB13-2026-BEMOL-RAIMUNDOSOARESDESOUZA.pdf?expires_on=1785434474&amp;signature=PnAuXPPzfUD1zOLzf2z98oXd7I5B3V63awF3jZt1dko%3D</t>
         </is>
       </c>
       <c r="V374">
@@ -49631,7 +49631,7 @@
       </c>
       <c r="U375" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fb4c65a4-ec50-4573-87b6-74205b566cad/Laudo90-Bemol-2026-RaimundoSocorroCosta.pdf?expires_on=1785434314&amp;signature=TSsZi7nA%2FvpKIFl61CWCl34DUfbZMJ4GIYoVIOaSdvY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fb4c65a4-ec50-4573-87b6-74205b566cad/Laudo90-Bemol-2026-RaimundoSocorroCosta.pdf?expires_on=1785434474&amp;signature=MrkDKuge2tf%2B%2ByVl6pj5BU93f7O%2Ffcn6kGYSmxGiWq4%3D</t>
         </is>
       </c>
       <c r="V375">
@@ -49763,7 +49763,7 @@
       </c>
       <c r="U376" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3cdfb747-3eb8-462c-9fa2-81808d55b5c2/LaudoPA06-Bemol-2026-RaquelDaCostaMoutinho-Assinado.pdf?expires_on=1785434314&amp;signature=J4quTA6L5PEKgfPK2MmIsBzQWncmhjzruzEDw1RHT%2FA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3cdfb747-3eb8-462c-9fa2-81808d55b5c2/LaudoPA06-Bemol-2026-RaquelDaCostaMoutinho-Assinado.pdf?expires_on=1785434474&amp;signature=NGV1OPi1FcvFu3ZGrW4bE00Qi%2BrwfTvM5TqgkNaaqUw%3D</t>
         </is>
       </c>
       <c r="V376">
@@ -49893,7 +49893,7 @@
       </c>
       <c r="U377" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/290237ff-97b8-48db-a808-e517e6c8ffa6/LaudoB40-2026-BEMOL-REBECACRISTINABRECKENFELDDEMELO.pdf?expires_on=1785434314&amp;signature=efMTTYOVncbMIcrH15AqcgHLXsIW8Bd81bisp7x7YIk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/290237ff-97b8-48db-a808-e517e6c8ffa6/LaudoB40-2026-BEMOL-REBECACRISTINABRECKENFELDDEMELO.pdf?expires_on=1785434474&amp;signature=oufEKalV9HDvYcRrxY3%2FwuBqPCV0bdTpoE7gJQ1f9OQ%3D</t>
         </is>
       </c>
       <c r="V377">
@@ -50023,7 +50023,7 @@
       </c>
       <c r="U378" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5ebd6219-e5f4-4e59-bc39-c551536c695e/LaudoB25-2026-BEMOL-RELMASILVADESOUSA.pdf?expires_on=1785434314&amp;signature=8qFxO38MxRMnRfGP%2FCLrShhEk9%2F4To0yVBKtWlLWIvc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5ebd6219-e5f4-4e59-bc39-c551536c695e/LaudoB25-2026-BEMOL-RELMASILVADESOUSA.pdf?expires_on=1785434474&amp;signature=DqjmI9M2QnNfCAhzg%2Fq48amCUGKlQGDAdOBt8npJBvg%3D</t>
         </is>
       </c>
       <c r="V378">
@@ -50155,7 +50155,7 @@
       </c>
       <c r="U379" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2793b988-aff4-46a0-9b41-b4e708236aa0/Laudo56-Bemol-2026-RenatoGadelhaLima-Assinado.pdf?expires_on=1785434314&amp;signature=b6PXDZrmqSS4WYbpkVd2r8WZ6xto9Ob3D%2BZ%2Bxw09KWs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2793b988-aff4-46a0-9b41-b4e708236aa0/Laudo56-Bemol-2026-RenatoGadelhaLima-Assinado.pdf?expires_on=1785434474&amp;signature=yusM2MqO2S95yJujKWPi8rO3mAe7EbSN3DsFM8s6qM8%3D</t>
         </is>
       </c>
       <c r="V379">
@@ -50295,7 +50295,7 @@
       </c>
       <c r="U380" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/045c54ae-250b-41cf-8d59-a3f25ea628bd/LaudoP13-Bemol-2026-RenildoDeSouzaMoreiraretificado_signedcorrigido.pdf?expires_on=1785434314&amp;signature=B4%2Fz5JKUBAREjVvQ1ITV2mnJBxUD4LD32K3QD1hFHnU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/045c54ae-250b-41cf-8d59-a3f25ea628bd/LaudoP13-Bemol-2026-RenildoDeSouzaMoreiraretificado_signedcorrigido.pdf?expires_on=1785434474&amp;signature=YaY%2B%2FENBFlTVFpKRnhpvefAzCxXHefPJt7niXIUHdco%3D</t>
         </is>
       </c>
       <c r="V380">
@@ -50413,7 +50413,7 @@
       </c>
       <c r="U381" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/75b50ec4-3e3c-4f16-a5b9-92acb1766ee2/Laudo99-Bemol-2026-ReulySilvaFerreira.pdf?expires_on=1785434314&amp;signature=UqrLdjmRdCkp4EUU966uFwX5KQOKE7jg5vT%2F%2Faq%2B6vQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/75b50ec4-3e3c-4f16-a5b9-92acb1766ee2/Laudo99-Bemol-2026-ReulySilvaFerreira.pdf?expires_on=1785434474&amp;signature=u1jsYhIKRJHD1JxBjinu%2FP8RdAcPmtU5uXnkz6p25dE%3D</t>
         </is>
       </c>
       <c r="V381">
@@ -50546,7 +50546,7 @@
       </c>
       <c r="U382" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5aa360d1-e719-4ef1-b477-64124b1d5874/LaudoJP06-Bemol-2026-RilcelaradaSilva_signed.pdf?expires_on=1785434314&amp;signature=DoxZUiqQ9A0%2FlA1m8USCsdqFk8oEK%2Buz0y5TpAjH2UE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5aa360d1-e719-4ef1-b477-64124b1d5874/LaudoJP06-Bemol-2026-RilcelaradaSilva_signed.pdf?expires_on=1785434474&amp;signature=Uy9q8DJqO6id8p7vSei2PegccVmk94Avo2F%2BBnXuY0w%3D</t>
         </is>
       </c>
       <c r="V382">
@@ -50675,7 +50675,7 @@
       </c>
       <c r="U383" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/11b0329b-6c83-4634-9dcf-045d3091dffb/LaudoITA10-Bemol-2026-RitaEvaniaDaMataOliveira-Assinado.pdf?expires_on=1785434314&amp;signature=aaKRN3iSaa%2B%2Fg7NXW0zM1exgZgiXIrbRpVMxbovZ3%2B4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/11b0329b-6c83-4634-9dcf-045d3091dffb/LaudoITA10-Bemol-2026-RitaEvaniaDaMataOliveira-Assinado.pdf?expires_on=1785434474&amp;signature=m3XHvfC8TMXOzipm2Kuo%2FSDAKy5CKp7DpzFc1U%2Fe3io%3D</t>
         </is>
       </c>
       <c r="V383">
@@ -50804,7 +50804,7 @@
       </c>
       <c r="U384" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ee0a3d24-611f-4afb-94d5-d0714d4a7a2a/M19-2026-ROBERLANDE.pdf?expires_on=1785434314&amp;signature=3noOAEw5nkq0fx7ZsItM0hkR5HaD6AUs0UuUr4YXIxM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ee0a3d24-611f-4afb-94d5-d0714d4a7a2a/M19-2026-ROBERLANDE.pdf?expires_on=1785434474&amp;signature=5PmcyD%2FWA9l4Ebrz7hNH%2FvJRTcnE0iY2nBCuud1Id9g%3D</t>
         </is>
       </c>
       <c r="V384">
@@ -50930,7 +50930,7 @@
       </c>
       <c r="U385" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/510d5bae-319e-4402-a6d6-9638e4ef01a3/Laudo463-Bemol-2025-RobervalEmersonOliveiraDePaulaFilho-Assinado.pdf?expires_on=1785434314&amp;signature=ODtjFegrZfFBdLyGTaUwyeLNTIoY0p9NaBd4ShwAO9Y%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/510d5bae-319e-4402-a6d6-9638e4ef01a3/Laudo463-Bemol-2025-RobervalEmersonOliveiraDePaulaFilho-Assinado.pdf?expires_on=1785434474&amp;signature=oM0Kga%2Fwi6QGGs50%2FZ7w7PG63rwxbyLt05wVOxxZ2Ic%3D</t>
         </is>
       </c>
       <c r="V385">
@@ -51079,7 +51079,7 @@
       </c>
       <c r="U386" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b044c921-bcbf-4744-8fcc-d2fbbded2660/LAUDOROBSONMOTA.pdf?expires_on=1785434314&amp;signature=pgsloRfIk6XfY9eKdUDIAoalXOfERvQxNrY8pjwlf90%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b044c921-bcbf-4744-8fcc-d2fbbded2660/LAUDOROBSONMOTA.pdf?expires_on=1785434474&amp;signature=odPI4zmS6wQFpB70ATUK%2FiEtKncnX7j9ddOHosEb0j8%3D</t>
         </is>
       </c>
       <c r="V386">
@@ -51210,7 +51210,7 @@
       </c>
       <c r="U387" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/bf51751a-e147-48b5-8613-d4b117602a99/LAUDOROBSONcorrigido.pdf?expires_on=1785434314&amp;signature=3SYETwOvz9DyFt4bpYobMX%2BwKNlgonv4DK3i1aUKqvY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/bf51751a-e147-48b5-8613-d4b117602a99/LAUDOROBSONcorrigido.pdf?expires_on=1785434474&amp;signature=RrrVxEfjBAehfUG6AXlAhKz8oZfJslCm2W%2BGgj2afeM%3D</t>
         </is>
       </c>
       <c r="V387">
@@ -51334,7 +51334,7 @@
       </c>
       <c r="U388" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b0eba187-eaf3-4f90-ae25-ba460f7d8f35/BEMOL-PV068-ROBSONSENACRUZCOMERCIAL.pdf?expires_on=1785434314&amp;signature=rFPdTojMlA95KqUuITKUX8m%2BmR6Br80YESNYCCqbdbc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b0eba187-eaf3-4f90-ae25-ba460f7d8f35/BEMOL-PV068-ROBSONSENACRUZCOMERCIAL.pdf?expires_on=1785434474&amp;signature=VFN5eUe3Cxuq%2FXtaj9V4wCj5jmlWMGU3LUj3Ch6XCB0%3D</t>
         </is>
       </c>
       <c r="V388">
@@ -51461,7 +51461,7 @@
       </c>
       <c r="U389" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a076174-2a26-43a7-9c07-df4f54c1ffb1/LAUDOCORRIGIDORODRIGOLEO1.pdf?expires_on=1785434314&amp;signature=v6TB8JdiF8BxWyletxjZJzTHJVPCYUFzpnSmJdiFt20%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a076174-2a26-43a7-9c07-df4f54c1ffb1/LAUDOCORRIGIDORODRIGOLEO1.pdf?expires_on=1785434474&amp;signature=DvC7k9psfK0YrV18FibgWIGtvNDKIh4GErCX8hWWKqM%3D</t>
         </is>
       </c>
       <c r="V389">
@@ -51584,7 +51584,7 @@
       </c>
       <c r="U390" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/eac647e3-1371-4d6d-ab01-b54f520f6c13/LaudoB35-2026-BEMOL-ROMULOFREITASVASCONCELOS.pdf?expires_on=1785434314&amp;signature=Im0MPuwPlfOKLKGEs35XofSz1FbutfMUzHqd%2BcjcmI8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/eac647e3-1371-4d6d-ab01-b54f520f6c13/LaudoB35-2026-BEMOL-ROMULOFREITASVASCONCELOS.pdf?expires_on=1785434474&amp;signature=VIDMCH0%2BxQMsM7rWPhHAcpGzr3k9yt0cpnv0xw2PaJE%3D</t>
         </is>
       </c>
       <c r="V390">
@@ -51707,7 +51707,7 @@
       </c>
       <c r="U391" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0205a4bf-b863-461c-9aa1-51c6c2d3a48d/LAUDOCORRIGIDORONALDOLOPESDOSSANTOS.pdf?expires_on=1785434314&amp;signature=mQfywKtVk7G1Rr3uAVSdWei7nttFVKDeBZPL6PVBduY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0205a4bf-b863-461c-9aa1-51c6c2d3a48d/LAUDOCORRIGIDORONALDOLOPESDOSSANTOS.pdf?expires_on=1785434474&amp;signature=Kxc%2Fo2UFVCHj2uiXw71bGOhQo7FFRAiCPzFCsECgX%2FI%3D</t>
         </is>
       </c>
       <c r="V391">
@@ -51836,7 +51836,7 @@
       </c>
       <c r="U392" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/742ef22b-947c-4b2f-b655-a049050fa04d/Laudo201-Bemol-2026-RonaldoLucioDeLimaMarquesFilho.pdf?expires_on=1785434314&amp;signature=1R9Ro1lNIDzQ8RBvtdaOn39EhvHZlIiRPqQ5Zt85ks0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/742ef22b-947c-4b2f-b655-a049050fa04d/Laudo201-Bemol-2026-RonaldoLucioDeLimaMarquesFilho.pdf?expires_on=1785434474&amp;signature=aeH%2F62F0QHUYlI0EAYKR1%2B3Dw%2FkU45KMTOoQaqYh%2Fvk%3D</t>
         </is>
       </c>
       <c r="V392">
@@ -51959,7 +51959,7 @@
       </c>
       <c r="U393" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a24cada2-42fc-4f3a-8128-e23e4566cee5/LaudoB45-2026-BEMOL-ROSAMARIABATISTADOSSANTOS.pdf?expires_on=1785434314&amp;signature=RKKsXa7iZT1xodLS1YixfG4hGoUsD%2BUosKIPtIewy1E%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a24cada2-42fc-4f3a-8128-e23e4566cee5/LaudoB45-2026-BEMOL-ROSAMARIABATISTADOSSANTOS.pdf?expires_on=1785434474&amp;signature=0gbedDC13sdN5cipdHnBbxTYvXZbIyWunn5WjTa9cUs%3D</t>
         </is>
       </c>
       <c r="V393">
@@ -52091,7 +52091,7 @@
       </c>
       <c r="U394" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/00d4329e-1be0-4ca9-80b8-14423a168202/Laudo68-Bemol-2026-RosaMariaMartinsCorreia.pdf?expires_on=1785434314&amp;signature=tzZXcESQkVQOt8ejJFIX%2BFxHGpuQPZSR05JQWIBEfRU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/00d4329e-1be0-4ca9-80b8-14423a168202/Laudo68-Bemol-2026-RosaMariaMartinsCorreia.pdf?expires_on=1785434474&amp;signature=xfVqJK6I9qulEYR99CJFsecri9yqxQ2qIpiyd0vaC5c%3D</t>
         </is>
       </c>
       <c r="V394">
@@ -52234,7 +52234,7 @@
       </c>
       <c r="U395" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a5affc9-5efa-4b05-9ad8-3e6533d4f3bb/LAUDOROSARODRIGUES.pdf?expires_on=1785434314&amp;signature=IjzvHjf%2Bh2x%2BlASEE1a0rciOT%2FSuWDKoY3suvSQKaxM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a5affc9-5efa-4b05-9ad8-3e6533d4f3bb/LAUDOROSARODRIGUES.pdf?expires_on=1785434474&amp;signature=EB48aFzWKexv40i6ms3IWg93RA9mROg8E0RYxbdcW9g%3D</t>
         </is>
       </c>
       <c r="V395">
@@ -52365,7 +52365,7 @@
       </c>
       <c r="U396" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f2b56fd5-9e5c-4418-9e2d-56f9dfbf06f3/Laudo_AC_31-2026_-_ROSA_VASQUES_DA_SILVA_SANTOS_assinado.pdf?expires_on=1785434314&amp;signature=C9pW7cZHEpU1a5Bn8nddmCGoV364km8d7MoS0w9X%2FEg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f2b56fd5-9e5c-4418-9e2d-56f9dfbf06f3/Laudo_AC_31-2026_-_ROSA_VASQUES_DA_SILVA_SANTOS_assinado.pdf?expires_on=1785434474&amp;signature=17s3bYyWHKIj2nWP%2B0UW397KKFgAw78gANBtYab7fJA%3D</t>
         </is>
       </c>
       <c r="V396">
@@ -52488,7 +52488,7 @@
       </c>
       <c r="U397" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3c4d8694-e4f6-4617-b493-395f3cd9d236/BEMOL-PV093-RosaneMunizBezerra.pdf?expires_on=1785434314&amp;signature=ICcxCEUBn03LQ8zYDpac%2F6ZwvQJCOlxiAk1lILOrslM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3c4d8694-e4f6-4617-b493-395f3cd9d236/BEMOL-PV093-RosaneMunizBezerra.pdf?expires_on=1785434474&amp;signature=SL1NaVBld%2F%2Fhp%2B751If52t1amNnhI4s1%2Bk2sTYOta4A%3D</t>
         </is>
       </c>
       <c r="V397">
@@ -52614,7 +52614,7 @@
       </c>
       <c r="U398" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1b16191a-86bc-42c1-ad81-956b778e918f/M14-2026-ROSEMBERG.pdf?expires_on=1785434314&amp;signature=Daz74J34c2P7O6tyq1%2FmX5xGsy9tiVUWuXqWU8dO3Vc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1b16191a-86bc-42c1-ad81-956b778e918f/M14-2026-ROSEMBERG.pdf?expires_on=1785434474&amp;signature=5znPASYuu5EQSZa2lqYRPK96kiR5vPPHT18If7kNsH0%3D</t>
         </is>
       </c>
       <c r="V398">
@@ -52737,7 +52737,7 @@
       </c>
       <c r="U399" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ed590550-e36b-4c89-960e-07f9f76ba9b2/LAUDOROSEMIRO.pdf?expires_on=1785434314&amp;signature=iGLk2gPZciPW3bXXksUZmQrONFFWC569aImV6emuIv4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ed590550-e36b-4c89-960e-07f9f76ba9b2/LAUDOROSEMIRO.pdf?expires_on=1785434474&amp;signature=0OAxROVqSkqSkajWC%2FH%2FLQkCphRnqU4Nu4KD%2BMwvSUc%3D</t>
         </is>
       </c>
       <c r="V399">
@@ -52855,7 +52855,7 @@
       </c>
       <c r="U400" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/52bcdd6c-c8cf-48c8-b72a-72e3b3408c04/M16-2026-ROSICLEUDE.pdf?expires_on=1785434314&amp;signature=zCJKE9Pxt78Gwja7gX71YEVgjth82Kxla6FDN3WQDQc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/52bcdd6c-c8cf-48c8-b72a-72e3b3408c04/M16-2026-ROSICLEUDE.pdf?expires_on=1785434474&amp;signature=b1anWMejAAfbYzc3Lf%2F9M9kpogDv96Z1d3prjAu2f%2B4%3D</t>
         </is>
       </c>
       <c r="V400">
@@ -52986,7 +52986,7 @@
       </c>
       <c r="U401" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/17095173-da4d-4d28-ae1c-836a1fbb2eea/Laudo22-Bemol-2026-RosileneDosSantosAntunes-Assinado.pdf?expires_on=1785434314&amp;signature=vDrLCjT48W9QGagPoXVwoetm%2BwUxqrXHKMoC2twdoqM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/17095173-da4d-4d28-ae1c-836a1fbb2eea/Laudo22-Bemol-2026-RosileneDosSantosAntunes-Assinado.pdf?expires_on=1785434474&amp;signature=tPSTkmD8EZGa%2BU97FSQ4CsmF2PHarJWNHnsOKNjbu7A%3D</t>
         </is>
       </c>
       <c r="V401">
@@ -53117,7 +53117,7 @@
       </c>
       <c r="U402" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f21cd10a-5e4b-48a8-a63b-6b37522a52ae/LAUDOROSINALDOcorrigido.pdf?expires_on=1785434314&amp;signature=sp%2FOOapKg8qImxkT9%2BHZqGUMHyziLByqTjvTW%2BmJX%2BA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f21cd10a-5e4b-48a8-a63b-6b37522a52ae/LAUDOROSINALDOcorrigido.pdf?expires_on=1785434474&amp;signature=2RPhuNM9devpEAaiG0QHdSMeNrrJjq4vjZCbVSBKJBI%3D</t>
         </is>
       </c>
       <c r="V402">
@@ -53247,7 +53247,7 @@
       </c>
       <c r="U403" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5c3aa0b6-4fe3-4d41-a19e-39ad454e553e/Laudo181-Bemol-2026-RosinildoFonsecaMoreiraJunior-Assinado.pdf?expires_on=1785434314&amp;signature=uHqbNTdGkFVX4w9P7xZ%2BNRRe%2B4LDZYqF98us2K%2BMjTc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5c3aa0b6-4fe3-4d41-a19e-39ad454e553e/Laudo181-Bemol-2026-RosinildoFonsecaMoreiraJunior-Assinado.pdf?expires_on=1785434474&amp;signature=Mgz5qcUY1oWtrGSs7OHqXYBbFnaa%2FvC6ooSDcckc930%3D</t>
         </is>
       </c>
       <c r="V403">
@@ -53378,7 +53378,7 @@
       </c>
       <c r="U404" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9b283502-2002-4b61-a7df-8bb0e28bf455/M8-2026-RUTHRODRIGUESajustado02.pdf?expires_on=1785434314&amp;signature=X2kopYARt3jKUFNLe4B9GeWM5IaixmsIc%2F55ujgTAiA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9b283502-2002-4b61-a7df-8bb0e28bf455/M8-2026-RUTHRODRIGUESajustado02.pdf?expires_on=1785434474&amp;signature=oYwprIvn%2FKz1XXBWAv%2FotThwgI7qWeUsjITSFHn1xHk%3D</t>
         </is>
       </c>
       <c r="V404">
@@ -53501,7 +53501,7 @@
       </c>
       <c r="U405" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/93c2225f-37ce-4285-b84e-62328919c829/Laudo34-Bemol-2026-SalomoRodriguesDaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=gmEzOoi%2FMr%2FCxYPS47WUalRscLytxks2%2BD3cMk1GlWk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/93c2225f-37ce-4285-b84e-62328919c829/Laudo34-Bemol-2026-SalomoRodriguesDaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=GMubRnXjzao8J%2B9VZ4AFXLdpHq15MTz6L0PQtbysXi4%3D</t>
         </is>
       </c>
       <c r="V405">
@@ -53639,7 +53639,7 @@
       </c>
       <c r="U406" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d0e21094-74a9-45e5-8ac5-eb49500d14cf/LaudoITA04-Bemol-2026-SamaraThailineDacioDeAbreu-Assinado.pdf?expires_on=1785434314&amp;signature=3NT4NZ4%2BUuHVZeqtCjAordkOW8iT4BddgP0LtpeLhoo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d0e21094-74a9-45e5-8ac5-eb49500d14cf/LaudoITA04-Bemol-2026-SamaraThailineDacioDeAbreu-Assinado.pdf?expires_on=1785434474&amp;signature=s0v%2BI%2FDICUFSllqALoNr4lI0VbOHoQi2qNyrSAfl%2Bj8%3D</t>
         </is>
       </c>
       <c r="V406">
@@ -53766,7 +53766,7 @@
       </c>
       <c r="U407" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/88e11925-d856-4251-a278-0e0caf54b67c/LaudoPA15-Bemol-2026-SandroSantosSilva-Assinado.pdf?expires_on=1785434314&amp;signature=z75eYrA6qagPpNdX6KM5Aix8iYO8or2ECszhwGPGSIg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/88e11925-d856-4251-a278-0e0caf54b67c/LaudoPA15-Bemol-2026-SandroSantosSilva-Assinado.pdf?expires_on=1785434474&amp;signature=1bodCVaCgAB3LTP04%2FhHk%2FLRzcq05LhI8uDl%2FumdD4s%3D</t>
         </is>
       </c>
       <c r="V407">
@@ -53884,7 +53884,7 @@
       </c>
       <c r="U408" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f7e1802-680f-4f77-9cf1-8ffa0116a435/Laudo221-Bemol-2025-SaneyPerreiraMoreira-Assinado.pdf?expires_on=1785434314&amp;signature=q03x5K0Z%2BBR0aTRsJMFPjWzE4o7%2FWcGh4YWEA%2FwjEYs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f7e1802-680f-4f77-9cf1-8ffa0116a435/Laudo221-Bemol-2025-SaneyPerreiraMoreira-Assinado.pdf?expires_on=1785434474&amp;signature=ZUaQn%2F7z4tIteWMAaob7v98ZWdxY94rW3Ni8M0acMAQ%3D</t>
         </is>
       </c>
       <c r="V408">
@@ -54017,7 +54017,7 @@
       </c>
       <c r="U409" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b1180a14-7c3a-47a5-b612-5b52b17ccc68/BEMOL-PV078-SARACOELHODASILVA.pdf?expires_on=1785434314&amp;signature=hmjSXBKY2HcoHIqexs4Pix34DblZYHr6UA%2BwPgG%2BjP0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b1180a14-7c3a-47a5-b612-5b52b17ccc68/BEMOL-PV078-SARACOELHODASILVA.pdf?expires_on=1785434474&amp;signature=h%2FfpkaS9FqEvZqkcHnBsOAMGrYxQ5wv%2BSYnuHwHLids%3D</t>
         </is>
       </c>
       <c r="V409">
@@ -54152,7 +54152,7 @@
       </c>
       <c r="U410" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f4aa410b-2d99-41a0-bed4-291a2b831b82/LAUDOSEBASTIANA.pdf?expires_on=1785434314&amp;signature=kfAaCbkCzXjwu6CuUsyN5WgA4thwfzoTlK6RQeYbHH8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f4aa410b-2d99-41a0-bed4-291a2b831b82/LAUDOSEBASTIANA.pdf?expires_on=1785434474&amp;signature=VwyH0z2tIpSdO0ObECkh98md3VRISQVYTvAqPOlSdJ4%3D</t>
         </is>
       </c>
       <c r="V410">
@@ -54293,7 +54293,7 @@
       </c>
       <c r="U411" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/295bf843-1893-44fc-be91-ae1169868e73/Laudo370-Bemol-2025-SebastianaTelesReigo-Assinado.pdf?expires_on=1785434314&amp;signature=%2BlLoVTpFgYqNIqlZKtRnZk3m0dJA9jQTNxu8LqNNEd4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/295bf843-1893-44fc-be91-ae1169868e73/Laudo370-Bemol-2025-SebastianaTelesReigo-Assinado.pdf?expires_on=1785434474&amp;signature=HnBm%2Ba8Z5h33NWVb5g4ahNzdPwbDtlQImfSURUks%2FYk%3D</t>
         </is>
       </c>
       <c r="V411">
@@ -54444,7 +54444,7 @@
       </c>
       <c r="U412" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ee251d2d-982d-4234-ad27-bf4b1f07ec1a/BEMOL-PV071-SEBASTIOLUIZBALAREZRIBEIROcorrigido.pdf?expires_on=1785434314&amp;signature=fSjY8%2BdlXCq2OZJBaNBJTi%2FjU%2BZdUznZmDdmCTWs5ws%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ee251d2d-982d-4234-ad27-bf4b1f07ec1a/BEMOL-PV071-SEBASTIOLUIZBALAREZRIBEIROcorrigido.pdf?expires_on=1785434474&amp;signature=rr0mgWViFzDjbF%2FkT5hsNq6oF5XNZDQJxdyxGJAs7n8%3D</t>
         </is>
       </c>
       <c r="V412">
@@ -54567,7 +54567,7 @@
       </c>
       <c r="U413" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0687e1f1-9daf-4739-9397-6ba62af1e47b/Laudo75-Bemol-2026-SelbiaCastroDaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=XtaiCskqom7RQCvE9Z%2Fod4d7uvfSMm3l4ydqqQq871g%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0687e1f1-9daf-4739-9397-6ba62af1e47b/Laudo75-Bemol-2026-SelbiaCastroDaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=FQRJaBruSQffc7zBhaeaNGZLt1RJ4irecM%2FisYS9G7g%3D</t>
         </is>
       </c>
       <c r="V413">
@@ -54699,7 +54699,7 @@
       </c>
       <c r="U414" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9d71ba3e-6ff9-496b-87ae-85d0fada0632/LaudoITA03-Bemol-2026-SelenaGranaTorres-Assinado.pdf?expires_on=1785434314&amp;signature=ygpr8SrQCYKsT0dPUe%2BJ7FtNifWV5JC54nhTNO5158Q%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9d71ba3e-6ff9-496b-87ae-85d0fada0632/LaudoITA03-Bemol-2026-SelenaGranaTorres-Assinado.pdf?expires_on=1785434474&amp;signature=xYRXlTCYULE2v2Qsv7XZJEKeipL1jTElyaBHHY8rodQ%3D</t>
         </is>
       </c>
       <c r="V414">
@@ -54826,7 +54826,7 @@
       </c>
       <c r="U415" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cb2f3f19-f054-4ffa-a025-85a15cf23aa0/LAUDOSERGIOPIGNATARIcorrigido.pdf?expires_on=1785434314&amp;signature=0I26BHAvOhOrerTUV55blfzyia7bQv6PM9M4s2m1z9k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cb2f3f19-f054-4ffa-a025-85a15cf23aa0/LAUDOSERGIOPIGNATARIcorrigido.pdf?expires_on=1785434474&amp;signature=vJ1SsbtEHrPcjBpizv7SqJhzA9fbMxE2cHvXmmvuLis%3D</t>
         </is>
       </c>
       <c r="V415">
@@ -54966,7 +54966,7 @@
       </c>
       <c r="U416" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/17b00c9d-e198-4b83-9a65-db38245d8064/LaudoJP02-Bemol-2026-SerliBerlandaMoreira_signed.pdf?expires_on=1785434314&amp;signature=3L6C6KScrqG3qfTHX4xJ67BAu5LTuagGPzz7emz%2FDPs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/17b00c9d-e198-4b83-9a65-db38245d8064/LaudoJP02-Bemol-2026-SerliBerlandaMoreira_signed.pdf?expires_on=1785434474&amp;signature=0MkwLcuM4nFS5Q08NqAczpi4dwINT6WshpLUKExVffA%3D</t>
         </is>
       </c>
       <c r="V416">
@@ -55090,7 +55090,7 @@
       </c>
       <c r="U417" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/da04e0d4-a624-4cf7-aa2e-f1983fd96999/LaudoMAN03-Bemol-2026-SevanildeBatalhaRabelo-Assinadoajustado.pdf?expires_on=1785434314&amp;signature=3e9JBMirh2emSr2lf%2BOWv%2FYa%2BXN5v4ieYeNPKxMEFhk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/da04e0d4-a624-4cf7-aa2e-f1983fd96999/LaudoMAN03-Bemol-2026-SevanildeBatalhaRabelo-Assinadoajustado.pdf?expires_on=1785434474&amp;signature=CJxMc8GIqmjA4kIoObdZO6fJIGsdWWhbSV%2FmdrPbZmc%3D</t>
         </is>
       </c>
       <c r="V417">
@@ -55208,7 +55208,7 @@
       </c>
       <c r="U418" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/80fb135e-1ea4-4edf-8ec7-a869af2f60d5/Laudo150-Bemol-2026-SeylaPalomaDaSilvaSantos-Assinado.pdf?expires_on=1785434314&amp;signature=w7UBkaCVtZ9GAzRJsoo0wnVwV2kpPGjZn2Y%2FG568itg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/80fb135e-1ea4-4edf-8ec7-a869af2f60d5/Laudo150-Bemol-2026-SeylaPalomaDaSilvaSantos-Assinado.pdf?expires_on=1785434474&amp;signature=w6oSj7D0tlgfpjB9CLcjPHOPpmz1bb8eE%2BEJKcrMmqo%3D</t>
         </is>
       </c>
       <c r="V418">
@@ -55337,7 +55337,7 @@
       </c>
       <c r="U419" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9cd57cf7-41f8-46f0-b888-22dbaf1a8535/Laudo_AC_34-2026_-_MARIA_FRANCINETE_FERREIRA_DE_ARAUJO_assinado.pdf?expires_on=1785434314&amp;signature=eFSH3Azhnsm4Hp15kG2zzy4yCfKkXv2tOVtwKTNKC%2Fc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9cd57cf7-41f8-46f0-b888-22dbaf1a8535/Laudo_AC_34-2026_-_MARIA_FRANCINETE_FERREIRA_DE_ARAUJO_assinado.pdf?expires_on=1785434474&amp;signature=1ie6LFIRw46F7M05S89iEgDCjoTl%2FSoF0I6UElWYxR8%3D</t>
         </is>
       </c>
       <c r="V419">
@@ -55469,7 +55469,7 @@
       </c>
       <c r="U420" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/41a84769-915b-4a55-801b-35d061f36cb2/LAUDOSHIRLEYPINTOcorrigido02.pdf?expires_on=1785434314&amp;signature=4fNfNgumTg4JOqaQKBX4fOacXkRPMpO61cmL6anyK5Q%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/41a84769-915b-4a55-801b-35d061f36cb2/LAUDOSHIRLEYPINTOcorrigido02.pdf?expires_on=1785434474&amp;signature=yayCIvZABdbxXcRa40ZD8Xu%2FyBaOc5lVrFZvqj026VM%3D</t>
         </is>
       </c>
       <c r="V420">
@@ -55598,7 +55598,7 @@
       </c>
       <c r="U421" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f353c835-99b4-4441-ba6d-3aaf391e2610/Laudo76-Bemol-2026-SidnaReginaDaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=3Akr00QRSRBAwvMj2yRFQhMZIdh%2F1Fubxg6GXaSiXFw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f353c835-99b4-4441-ba6d-3aaf391e2610/Laudo76-Bemol-2026-SidnaReginaDaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=30qPnfjewdTZnMo%2Fy3xCICsHfNi%2F%2FHEUswk6GoqNyuY%3D</t>
         </is>
       </c>
       <c r="V421">
@@ -55736,7 +55736,7 @@
       </c>
       <c r="U422" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/47bee4e2-792f-40c2-95a2-f11264c736aa/Laudo_AC_79-2025_assinado.pdf?expires_on=1785434314&amp;signature=76kFNQnQpFplRq7D9MPUosfVewHxjX240%2F6DWl4%2BJiE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/47bee4e2-792f-40c2-95a2-f11264c736aa/Laudo_AC_79-2025_assinado.pdf?expires_on=1785434474&amp;signature=1kxeTwaeP14RTXZGfvI9vEI8IXE8ZYGwjb3JbGbgsKs%3D</t>
         </is>
       </c>
       <c r="V422">
@@ -55882,7 +55882,7 @@
       </c>
       <c r="U423" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9d741fee-febe-4a5f-bfd5-95c526d57c04/BEMOL-PV072-SILVANAACACIABARBOSADESOUSA.pdf?expires_on=1785434314&amp;signature=PvMFrLyROVmu%2BZS%2BEQgu2v8pxy2Ew%2BL4WMZzTWkGGGU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9d741fee-febe-4a5f-bfd5-95c526d57c04/BEMOL-PV072-SILVANAACACIABARBOSADESOUSA.pdf?expires_on=1785434474&amp;signature=SRjUEVPqsnz6t7FwnlSccnrhb5aKReDAjfoDH76ki4I%3D</t>
         </is>
       </c>
       <c r="V423">
@@ -56005,7 +56005,7 @@
       </c>
       <c r="U424" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7c631f93-1bbc-41c6-9b3c-076fe1bfc2ef/LaudoA05-Bemol-2026-SilvanydeOliveiraSilva_signed.pdf?expires_on=1785434314&amp;signature=hoLO7Y0UraOEu%2F3x%2FSrC4sNl7CxYqYTMx8FuR9EdmVE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7c631f93-1bbc-41c6-9b3c-076fe1bfc2ef/LaudoA05-Bemol-2026-SilvanydeOliveiraSilva_signed.pdf?expires_on=1785434474&amp;signature=zoHFPlXTqXcPcBHw69WCkirqRHuAjXZU1LOV5Teqcis%3D</t>
         </is>
       </c>
       <c r="V424">
@@ -56128,7 +56128,7 @@
       </c>
       <c r="U425" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6aac0250-33e3-4d15-81b3-af551ead0b44/LaudoA04-Bemol-2026-SimoneSasso_signed.pdf?expires_on=1785434314&amp;signature=iFaxYpNc69NaYORSHvbxb4cgEGyB9F3agpp9CDMJgZg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6aac0250-33e3-4d15-81b3-af551ead0b44/LaudoA04-Bemol-2026-SimoneSasso_signed.pdf?expires_on=1785434474&amp;signature=ZRp%2BuVsB4XlB0Z1wtoxe6xhvIN6ucfDM6PjjBCK9NrI%3D</t>
         </is>
       </c>
       <c r="V425">
@@ -56254,7 +56254,7 @@
       </c>
       <c r="U426" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ea3193b7-dd76-4be5-a605-36af08e595ce/LaudoP01-Bemol-2026-SionedaCunhaBezerra_signed.pdf?expires_on=1785434314&amp;signature=JuHc0Nkkya7RAnOSsj%2B0%2B8u14pNkhhpcN20ESaoXMQE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ea3193b7-dd76-4be5-a605-36af08e595ce/LaudoP01-Bemol-2026-SionedaCunhaBezerra_signed.pdf?expires_on=1785434474&amp;signature=xP2a190vZmForhsIXfY4itwSQSKXgW0eUf7%2B1I%2Bh6Ew%3D</t>
         </is>
       </c>
       <c r="V426">
@@ -56397,7 +56397,7 @@
       </c>
       <c r="U427" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c8fd31fb-c95b-4bca-997e-643d93bbe519/BEMOL-JP032-SIRLEIRUFINODESOUZA.pdf?expires_on=1785434314&amp;signature=d4G%2FeS6GJ8fAqW%2F1qWQ%2Fl6Mj4TniBT2ocyreTJZtYNU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c8fd31fb-c95b-4bca-997e-643d93bbe519/BEMOL-JP032-SIRLEIRUFINODESOUZA.pdf?expires_on=1785434474&amp;signature=XYeaVoFmcfw6Id7qmBADyIZaxaskiLpb10aOK57G8Dg%3D</t>
         </is>
       </c>
       <c r="V427">
@@ -56536,7 +56536,7 @@
       </c>
       <c r="U428" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/94b84bd4-8b6a-4900-82a8-1389771a95ba/LaudoB14-2026-BEMOL-STHEFESONRONYLIMADASILVA_2.pdf?expires_on=1785434314&amp;signature=VSRFuI8xYacGUyMEu%2BT5Y0JVdEMorkrVP65bxfvOpwY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/94b84bd4-8b6a-4900-82a8-1389771a95ba/LaudoB14-2026-BEMOL-STHEFESONRONYLIMADASILVA_2.pdf?expires_on=1785434474&amp;signature=Hg2BmXJbzqt2A7vrGemSsgJeKjuDZRv35eA%2BIateqPM%3D</t>
         </is>
       </c>
       <c r="V428">
@@ -56665,7 +56665,7 @@
       </c>
       <c r="U429" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8a4da409-7bca-4787-ae06-0ba3582bcd45/Laudo45-Bemol-2026-SuelyRolimDosSantos-Assinado.pdf?expires_on=1785434314&amp;signature=o19ieM4jsFC%2F1EVGwj5eWg%2Bi0AdscgmV2bCV%2F1Vd46Q%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8a4da409-7bca-4787-ae06-0ba3582bcd45/Laudo45-Bemol-2026-SuelyRolimDosSantos-Assinado.pdf?expires_on=1785434474&amp;signature=N3wCr78%2FIfalD8dxFnU%2FnFU%2F%2BXVcrnkHaOuhu%2F3OHOU%3D</t>
         </is>
       </c>
       <c r="V429">
@@ -56797,7 +56797,7 @@
       </c>
       <c r="U430" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e72ce383-285b-415d-b836-74950b0b511e/LaudoI01-Bemol-2026-SuzeteDaSilvaDeOliveira-Assinado.pdf?expires_on=1785434314&amp;signature=aCqMWBoZIJJPL5j4tvPuRtNLPWp15%2B6wWDV1GngOgyo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e72ce383-285b-415d-b836-74950b0b511e/LaudoI01-Bemol-2026-SuzeteDaSilvaDeOliveira-Assinado.pdf?expires_on=1785434474&amp;signature=RQEYuaV8k7tRGllBHqyV7cq4HTstIIIu6mdY7AgPYJE%3D</t>
         </is>
       </c>
       <c r="V430">
@@ -56927,7 +56927,7 @@
       </c>
       <c r="U431" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0e4fa01b-528b-49ec-b4a8-5064e3866a36/BEMOL-AR028-TAMELACARVALHOMARQUESDEOLIVEIRA.pdf?expires_on=1785434314&amp;signature=S6m2PIOqMuIOZt%2FlgYLc8p47aVTFvbw76QhyCvDkknI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0e4fa01b-528b-49ec-b4a8-5064e3866a36/BEMOL-AR028-TAMELACARVALHOMARQUESDEOLIVEIRA.pdf?expires_on=1785434474&amp;signature=eQ75Vm4UOE3qrW96lwb9%2B1orWvx%2B5CrxneorwfFBOQY%3D</t>
         </is>
       </c>
       <c r="V431">
@@ -57045,7 +57045,7 @@
       </c>
       <c r="U432" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/761162e5-7668-44b1-b13c-ffcc122d7d4a/Laudo128-Bemol-2026-TatianeSoaresDeMagalhaes.pdf?expires_on=1785434314&amp;signature=dAnc%2FWdAXllI51lgv%2Bo91Sp0GPsPdP3M%2BOrGQULnxFo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/761162e5-7668-44b1-b13c-ffcc122d7d4a/Laudo128-Bemol-2026-TatianeSoaresDeMagalhaes.pdf?expires_on=1785434474&amp;signature=b8BtMikcsAPlAKvtDYOIvB4GegDU%2Bp%2F9VzJYtbTfd1U%3D</t>
         </is>
       </c>
       <c r="V432">
@@ -57171,7 +57171,7 @@
       </c>
       <c r="U433" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/356cc1cc-ebb3-4036-a919-346d083b5346/Laudo01-Bemol-2026-TayaneMenezesDaSilva-Assinado.pdf?expires_on=1785434314&amp;signature=SNpalO%2F49xdP1pFJZPCggW1nqHWwU4CfltHjkWgRz68%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/356cc1cc-ebb3-4036-a919-346d083b5346/Laudo01-Bemol-2026-TayaneMenezesDaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=gCFB3a9ZW%2BsnzlC%2BfaqSLg5BbvAgkya9%2FivzvyT4MtU%3D</t>
         </is>
       </c>
       <c r="V433">
@@ -57297,7 +57297,7 @@
       </c>
       <c r="U434" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3cd45676-ee86-489d-a025-f11e74827aca/Laudo114-Bemol-2026-ThaizeAlfaiaGuimaraes-Assinado-Ajustado.pdf?expires_on=1785434314&amp;signature=sCiW64eEmu2jjw9Uh%2BaR3Jv33zfQpBlv5cujeB2pC5o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3cd45676-ee86-489d-a025-f11e74827aca/Laudo114-Bemol-2026-ThaizeAlfaiaGuimaraes-Assinado-Ajustado.pdf?expires_on=1785434474&amp;signature=asSpXbgavtY2UDtZb0A3yJsvOzaRimFG5LvdqtxhP4s%3D</t>
         </is>
       </c>
       <c r="V434">
@@ -57428,7 +57428,7 @@
       </c>
       <c r="U435" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2b73c9ad-dc1a-4e85-b4bd-27ab6cea1143/Laudo179-Bemol-2026-ThiagoCruzDosSantos.pdf?expires_on=1785434314&amp;signature=Ig81Lf3Nu6GwJiYLQCyK%2Fci4ztYbXY4SnG5uVG2C54w%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2b73c9ad-dc1a-4e85-b4bd-27ab6cea1143/Laudo179-Bemol-2026-ThiagoCruzDosSantos.pdf?expires_on=1785434474&amp;signature=IIdU98mrB%2BvVyFOUW1LX1COwG7EB5InMbPrHVhZOZ60%3D</t>
         </is>
       </c>
       <c r="V435">
@@ -57551,7 +57551,7 @@
       </c>
       <c r="U436" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e65a6996-22f5-41de-ad7b-61de0a96c55a/LAUDOTHIAGOSILVAcorrigido.pdf?expires_on=1785434314&amp;signature=2JsqiabVqCAB47Vl%2B4D4bolRK7ueECJ3kUpcmCs5YhQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e65a6996-22f5-41de-ad7b-61de0a96c55a/LAUDOTHIAGOSILVAcorrigido.pdf?expires_on=1785434474&amp;signature=kGNJWRFnWOQsRW6FSkqR%2F5rA53lOW27MFwWOmJ%2BeCsk%3D</t>
         </is>
       </c>
       <c r="V436">
@@ -57670,7 +57670,7 @@
       </c>
       <c r="U437" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6aabf93a-1827-4934-913c-773405dad137/d6bee9f9-c4b4-4c19-a69b-8f003ad3d00b.pdf?expires_on=1785434314&amp;signature=VwnnMI5%2Bq%2BDM6NE3EcGlboCdl%2BZEnIEaqfeJ6zwbzsE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6aabf93a-1827-4934-913c-773405dad137/d6bee9f9-c4b4-4c19-a69b-8f003ad3d00b.pdf?expires_on=1785434474&amp;signature=OHgxwuMWTYEXVM0z5vQJUTE9w27R6QjQv1sjC3YB3AY%3D</t>
         </is>
       </c>
       <c r="V437">
@@ -57801,7 +57801,7 @@
       </c>
       <c r="U438" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/66fe5fa5-3384-4db8-a60f-c481720be4e7/Laudo476-Bemol-2025-AcadiaMariaPereiraDeAraujo-Assinado11.pdf?expires_on=1785434315&amp;signature=Iel%2FHzzkZtDxC1W%2F%2B%2FRKHVX9esmZ2iN7RJtZskHzQgM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/66fe5fa5-3384-4db8-a60f-c481720be4e7/Laudo476-Bemol-2025-AcadiaMariaPereiraDeAraujo-Assinado11.pdf?expires_on=1785434474&amp;signature=einP8Cgs%2B9fLCcocvM6qqAFRSdTEeGTm6Bw7bdObYTw%3D</t>
         </is>
       </c>
       <c r="V438">
@@ -57924,7 +57924,7 @@
       </c>
       <c r="U439" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/95532b56-07a0-4139-94b3-3991d2e25f88/LAUDOTONNYFRANKCORRIGIDO.pdf?expires_on=1785434315&amp;signature=aAdXzMk2cZAc9J9RCaVcKenZhFRe7EvYAxl1TajkfjI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/95532b56-07a0-4139-94b3-3991d2e25f88/LAUDOTONNYFRANKCORRIGIDO.pdf?expires_on=1785434474&amp;signature=eXYJdj1fSyOiDAUwyWxOaaYpCUPZjfQu2R7JmP5Ufig%3D</t>
         </is>
       </c>
       <c r="V439">
@@ -58055,7 +58055,7 @@
       </c>
       <c r="U440" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/34077b3d-5b77-4c70-ab45-6c00e62ef0af/LaudoB20-2026-BEMOL-URSULAERICATRAJANOCORREA.pdf?expires_on=1785434315&amp;signature=4AYx8qiS2HJ8pMJVr%2B3E%2BtiqTMsci2OPjsHtoszhRws%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/34077b3d-5b77-4c70-ab45-6c00e62ef0af/LaudoB20-2026-BEMOL-URSULAERICATRAJANOCORREA.pdf?expires_on=1785434474&amp;signature=f%2BJC2wcjeo78fRj9hPWcKCf7SyxBiMo6XM0PZ7u6ii4%3D</t>
         </is>
       </c>
       <c r="V440">
@@ -58183,7 +58183,7 @@
       </c>
       <c r="U441" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e0f6c590-e981-43b8-9d2c-ee329972b331/M23-2026-VALCINETE.pdf?expires_on=1785434315&amp;signature=lc5pLFdRKqQJODpbwV%2FkX9B962%2B5CZaVnmGL1dOS8fE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e0f6c590-e981-43b8-9d2c-ee329972b331/M23-2026-VALCINETE.pdf?expires_on=1785434474&amp;signature=rSUJpjFvaTEzIASHplVGlnoLEM7fjwXeWFL6CmNQlhU%3D</t>
         </is>
       </c>
       <c r="V441">
@@ -58315,7 +58315,7 @@
       </c>
       <c r="U442" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9a138eb9-54c9-43d9-b935-78e4c16c8c15/Laudo167-Bemol-2026-ValdemirSilvaDeBrito.pdf?expires_on=1785434315&amp;signature=Po06j5xWnoEyBPI2vC6Vrx8BR5CC%2F0FBXaiksDkoA5o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9a138eb9-54c9-43d9-b935-78e4c16c8c15/Laudo167-Bemol-2026-ValdemirSilvaDeBrito.pdf?expires_on=1785434474&amp;signature=8MEo0qyK1dHj5MVWfHMKW7TGnORzgrB6mgelYvxdgbw%3D</t>
         </is>
       </c>
       <c r="V442">
@@ -58452,7 +58452,7 @@
       </c>
       <c r="U443" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f41eb99d-6cd2-41bc-9fe1-8e421b2e451e/Laudo404-Bemol-2025-ValdenoraGomesDaSilva-Assinado.pdf?expires_on=1785434315&amp;signature=2ihFrMF550g042OOjHTHASqtAvCptt1zUuae2dj42C4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f41eb99d-6cd2-41bc-9fe1-8e421b2e451e/Laudo404-Bemol-2025-ValdenoraGomesDaSilva-Assinado.pdf?expires_on=1785434474&amp;signature=ZWnFlhRmvLyOKw08EKaVWb0AKGYT6RPVUDFYGQNP9VI%3D</t>
         </is>
       </c>
       <c r="V443">
@@ -58606,7 +58606,7 @@
       </c>
       <c r="U444" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8aad0ece-7144-40eb-8fbf-765df6d0a86e/Laudo38-Bemol-2026-ValdeteTaveiradePaula-Assinado.pdf?expires_on=1785434315&amp;signature=86snX03npr2FM8EYzlfIoDlTervnT8MCB057cTtCG7E%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8aad0ece-7144-40eb-8fbf-765df6d0a86e/Laudo38-Bemol-2026-ValdeteTaveiradePaula-Assinado.pdf?expires_on=1785434474&amp;signature=DWB6B1UN8RmhRL5urvYNjNoi%2Buw4eSnEXJ8I6AKVS30%3D</t>
         </is>
       </c>
       <c r="V444">
@@ -58736,7 +58736,7 @@
       </c>
       <c r="U445" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8b3225ea-031c-40da-b116-331fb129e1dc/LaudoPA13-Bemol-2026-ValdirTeixeiraNascimento-Assinado.pdf?expires_on=1785434315&amp;signature=SewKv2V0HQe8hEkTBpXz%2Fj5Li3hd3AADC%2FiHXOaPb3s%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8b3225ea-031c-40da-b116-331fb129e1dc/LaudoPA13-Bemol-2026-ValdirTeixeiraNascimento-Assinado.pdf?expires_on=1785434474&amp;signature=Hn3YgQNcWO5MA4FwHEwH0741YIorCBexm40EUlFmQSA%3D</t>
         </is>
       </c>
       <c r="V445">
@@ -58859,7 +58859,7 @@
       </c>
       <c r="U446" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/edbe4bef-e898-4b85-bb9f-d448777be229/LaudoP06-Bemol-2026-ValeriaPatriciaSouzaCastro_signed.pdf?expires_on=1785434315&amp;signature=EYQEZumkek4x8suEnB9A3JYugoGMaNaaJpeCXF2EIh4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/edbe4bef-e898-4b85-bb9f-d448777be229/LaudoP06-Bemol-2026-ValeriaPatriciaSouzaCastro_signed.pdf?expires_on=1785434474&amp;signature=OP599MeVVP79iDWcikgKVLIjrX672H6iHJtBo0ImMa8%3D</t>
         </is>
       </c>
       <c r="V446">
@@ -58985,7 +58985,7 @@
       </c>
       <c r="U447" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9a0b236a-d8da-46a1-abde-d03053959c44/LAUDOVALMIR.pdf?expires_on=1785434315&amp;signature=OkA3F2BB27sXhAknJBAnZE2VDl7nW8xXa6JQ%2F%2FSGjyg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9a0b236a-d8da-46a1-abde-d03053959c44/LAUDOVALMIR.pdf?expires_on=1785434474&amp;signature=Bjix7A3KBjC%2BZz9tQo6NTQvRyjeRq3XI9WNJgcrRr6U%3D</t>
         </is>
       </c>
       <c r="V447">
@@ -59119,7 +59119,7 @@
       </c>
       <c r="U448" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9d50de8b-4362-4419-8e11-3e29a2d24ea2/BEMOL-JP037-VANDERLEIFERREIRADASILVA.pdf?expires_on=1785434315&amp;signature=f6MckWVCiIE%2F6foKx%2BRb2hP9%2F2UtwF4k9LNZvgKBDiA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9d50de8b-4362-4419-8e11-3e29a2d24ea2/BEMOL-JP037-VANDERLEIFERREIRADASILVA.pdf?expires_on=1785434474&amp;signature=KiP0eijH9I1zFFzV0WDRLwfT3cxE8vaZOFJ3lzmO0dU%3D</t>
         </is>
       </c>
       <c r="V448">
@@ -59256,7 +59256,7 @@
       </c>
       <c r="U449" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/edfc3c76-b3ac-4b05-85e0-4564e1830f59/LaudoB133-2025-BEMOL-VANDERNAYLATHAINADEOLIVEIRA_2.pdf?expires_on=1785434315&amp;signature=MSVdiFydLK3hgj45xjpgU%2BDD7py0E7XtVQaq2gqTHn4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/edfc3c76-b3ac-4b05-85e0-4564e1830f59/LaudoB133-2025-BEMOL-VANDERNAYLATHAINADEOLIVEIRA_2.pdf?expires_on=1785434474&amp;signature=Gkxbivr9Qd%2B2ZJ4QIxMQeI8yp%2Bm8rYvf494CBfT66cs%3D</t>
         </is>
       </c>
       <c r="V449">
@@ -59401,7 +59401,7 @@
       </c>
       <c r="U450" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/234aaeae-ef51-42bf-b815-4234ee76a4e1/LAUDOVANDERSON.pdf?expires_on=1785434315&amp;signature=EcLXT8nYQ2RhEsJJWzZcTU0PdQO3SnjxNXFhFXAo%2Bm0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/234aaeae-ef51-42bf-b815-4234ee76a4e1/LAUDOVANDERSON.pdf?expires_on=1785434474&amp;signature=3mVMsPrzghoa%2FZWWhmOCdsaGgym5rpIyBSTxgVyI8R8%3D</t>
         </is>
       </c>
       <c r="V450">
@@ -59531,7 +59531,7 @@
       </c>
       <c r="U451" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/12219fa3-41df-4153-929d-be40314484c2/Laudo13-Bemol-2026-VanessaDeSouzaBendaham-Assinado.pdf?expires_on=1785434315&amp;signature=Vnb6HgoW7zxepps%2Bk1f586Gnr%2BNO5sSOxr6rcJt%2FwPQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/12219fa3-41df-4153-929d-be40314484c2/Laudo13-Bemol-2026-VanessaDeSouzaBendaham-Assinado.pdf?expires_on=1785434474&amp;signature=bZL%2BzjRU%2Bp3AnCPaZsr%2FIUTCwKYrWL03A8YOYZoN73A%3D</t>
         </is>
       </c>
       <c r="V451">
@@ -59671,7 +59671,7 @@
       </c>
       <c r="U452" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2aa16e66-6d0c-4794-8d98-59fd6c762a29/Laudo120-Bemol-2026-VanessaDiasAraujo.pdf?expires_on=1785434315&amp;signature=5AsiOwv7DCe5jFBwSb4uunoXtFyAf7XvFCf5nrlrgh0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2aa16e66-6d0c-4794-8d98-59fd6c762a29/Laudo120-Bemol-2026-VanessaDiasAraujo.pdf?expires_on=1785434474&amp;signature=KWD2JUeuYfaRTTrHdonJZwCBRTn%2BrKubPCt1IL9O3lc%3D</t>
         </is>
       </c>
       <c r="V452">
@@ -59808,7 +59808,7 @@
       </c>
       <c r="U453" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/65bd5fcb-023f-4fe5-b52b-064b23146334/Laudo_ITA49_-_Bemol_-_2025_-_Vanessa_Santana_Oda__assinado.pdf?expires_on=1785434315&amp;signature=2bEY59Fr8OVh%2BPzR75zwERMpRxGtQ7J2CCfkbOTKg8Q%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/65bd5fcb-023f-4fe5-b52b-064b23146334/Laudo_ITA49_-_Bemol_-_2025_-_Vanessa_Santana_Oda__assinado.pdf?expires_on=1785434474&amp;signature=Y6ErmsFPT2z6N5RCsakvkaNQseNv3uGAfEx86bL%2Blfc%3D</t>
         </is>
       </c>
       <c r="V453">
@@ -59954,7 +59954,7 @@
       </c>
       <c r="U454" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a7077da-18e3-4e0a-80f3-e59be7715aaf/BEMOL-AR026-VANILDAGOMESDOSSANTOSDUTRA.pdf?expires_on=1785434315&amp;signature=07eplg9xljcgL7sHR8nwPdFyYmSoD1QztBgLBET6Bm8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a7077da-18e3-4e0a-80f3-e59be7715aaf/BEMOL-AR026-VANILDAGOMESDOSSANTOSDUTRA.pdf?expires_on=1785434474&amp;signature=Tha6JmsVT7LJOV%2FJZKMtLZOwwQSZdD6xPdbn1N8fRS4%3D</t>
         </is>
       </c>
       <c r="V454">
@@ -60094,7 +60094,7 @@
       </c>
       <c r="U455" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/eec64e95-f6d9-4d2a-af6a-cb7a4cdc3fa0/LAUDOVENCESLAU.pdf?expires_on=1785434315&amp;signature=sJQ%2Bj4czA%2FOqsU%2BpctHfvOP45taEOd8Sp7AQYf6pSfQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/eec64e95-f6d9-4d2a-af6a-cb7a4cdc3fa0/LAUDOVENCESLAU.pdf?expires_on=1785434474&amp;signature=KjdAEDGLYflAsqR1JYHqSKsHemZ3NYzRLyuzjhLhAd8%3D</t>
         </is>
       </c>
       <c r="V455">
@@ -60231,7 +60231,7 @@
       </c>
       <c r="U456" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/434c6c17-6df9-42c7-a677-ffa3cedd7afa/LaudoPA07-Registro2420-VictorMeloMeza.pdf?expires_on=1785434315&amp;signature=U0RVUr2tlfxK%2FT5wNFJ3BLhoag%2FmqrJDmP%2BW%2B6Uh50s%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/434c6c17-6df9-42c7-a677-ffa3cedd7afa/LaudoPA07-Registro2420-VictorMeloMeza.pdf?expires_on=1785434474&amp;signature=e5x505fORkcn0wTlKF0bi9QwELYsU3k827Qhd9D5eTI%3D</t>
         </is>
       </c>
       <c r="V456">
@@ -60355,7 +60355,7 @@
       </c>
       <c r="U457" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/212a6647-ada5-43a8-9109-8f6690ce7685/Laudo143-Bemol-2026-VivaldoDantasDeSouza-Assinado.pdf?expires_on=1785434315&amp;signature=vlYePfsTmNjkOlwlJyeUbqoNN0hqjIYBfbi6gqy6z1c%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/212a6647-ada5-43a8-9109-8f6690ce7685/Laudo143-Bemol-2026-VivaldoDantasDeSouza-Assinado.pdf?expires_on=1785434474&amp;signature=vivVwJ%2BCJ2KzCPF8hlvonuJK3fTgZo772iJihlARr8c%3D</t>
         </is>
       </c>
       <c r="V457">
@@ -60487,7 +60487,7 @@
       </c>
       <c r="U458" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/76fc2a4f-ddfd-4df9-a469-38010ed513c6/M12-2026-WALDSON.pdf?expires_on=1785434315&amp;signature=%2FuWJItbrNN90AtVN5CwZvEMmMfX%2BTHhVE9R1vZ5OLlw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/76fc2a4f-ddfd-4df9-a469-38010ed513c6/M12-2026-WALDSON.pdf?expires_on=1785434474&amp;signature=8uj6wHifXKhJ7YNnlhYB37cZjdM%2Fng8zoNvjfN%2Fs27c%3D</t>
         </is>
       </c>
       <c r="V458">
@@ -60637,7 +60637,7 @@
       </c>
       <c r="U459" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b1f1e143-9515-45b9-8724-931e0d2cd46d/Laudo135-Bemol-2026-WalterAndreJunior-Ajustado.pdf?expires_on=1785434315&amp;signature=HjPcB%2Bs%2Bgl6zeI5mUfxmmqRIjle2zQioKXa8bJnNfjI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b1f1e143-9515-45b9-8724-931e0d2cd46d/Laudo135-Bemol-2026-WalterAndreJunior-Ajustado.pdf?expires_on=1785434474&amp;signature=Ilf1J3XWtzRIGbyhDz5oXQXUD%2F9N9UIJkunxeV2sQ1w%3D</t>
         </is>
       </c>
       <c r="V459">
@@ -60780,7 +60780,7 @@
       </c>
       <c r="U460" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0483d9d7-9552-49f9-953c-cfacb8ae61e8/Laudo37-Bemol-2026-WashigtonDeOliveiraJunior-Assinadocorrigido.pdf?expires_on=1785434315&amp;signature=ExfBlaQNFvWb7rIBdV3PbbcDDQFU0rNNd3Y47csJT5o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0483d9d7-9552-49f9-953c-cfacb8ae61e8/Laudo37-Bemol-2026-WashigtonDeOliveiraJunior-Assinadocorrigido.pdf?expires_on=1785434474&amp;signature=VYQ4NoP%2BdJn6Yjop5SIudXETmH2TVM7OX4i1kykb%2FLo%3D</t>
         </is>
       </c>
       <c r="V460">
@@ -60919,7 +60919,7 @@
       </c>
       <c r="U461" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/66793f38-05d7-4092-983e-de03c4f5322a/Laudo_B8-2026-BEMOL-_WASHINGTON_LUIZ_DA_COSTA_MAIA_2_assinado.pdf?expires_on=1785434315&amp;signature=V7r%2B%2F%2Bmqb6%2BNZcWB89FCp%2FXquBWEhBGDf3muu%2BsPxT0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/66793f38-05d7-4092-983e-de03c4f5322a/Laudo_B8-2026-BEMOL-_WASHINGTON_LUIZ_DA_COSTA_MAIA_2_assinado.pdf?expires_on=1785434474&amp;signature=Z8HryKRlJmbpdQIeDj89dbsxLZL0jtdq0AUbJsVpNRI%3D</t>
         </is>
       </c>
       <c r="V461">
@@ -61055,7 +61055,7 @@
       </c>
       <c r="U462" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/25793695-287a-42fb-8443-b3c434461848/BEMOL-AR021-WEFFERERSONGUEDESDASNEVES.pdf?expires_on=1785434315&amp;signature=eqbeC9pP5Ejg9RUzTj7MAhd6lsqfTEyogdIo7fg2znU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/25793695-287a-42fb-8443-b3c434461848/BEMOL-AR021-WEFFERERSONGUEDESDASNEVES.pdf?expires_on=1785434474&amp;signature=2IzNX%2BhEcrQICd%2ByA6GnK0YfsS%2B7qalnq8eMkYRcnAo%3D</t>
         </is>
       </c>
       <c r="V462">
@@ -61186,7 +61186,7 @@
       </c>
       <c r="U463" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2377cef7-fbe5-4b92-ab2b-6e60c2734f26/Laudo169-Bemol-2026-WilcinayraAlvesFerreira-Assinado.pdf?expires_on=1785434315&amp;signature=PXluoOksSbigWEmyj054noLPWbdhl1aU4INVbMPp8pc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2377cef7-fbe5-4b92-ab2b-6e60c2734f26/Laudo169-Bemol-2026-WilcinayraAlvesFerreira-Assinado.pdf?expires_on=1785434474&amp;signature=U6tw4fU%2FHbC1UofEvifmBz1Eq9DHXyoI%2FSNKtq2V8uA%3D</t>
         </is>
       </c>
       <c r="V463">
@@ -61315,7 +61315,7 @@
       </c>
       <c r="U464" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/65f4ad93-8dfd-4569-b462-b3eb04df94d4/BEMOL-JP043-WILSONCEZARPELLIZZETTI.pdf?expires_on=1785434315&amp;signature=o27DbLw3Vy2Su9OcQ7s3Cz1wLEz3FExsymlLhPBBF20%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/65f4ad93-8dfd-4569-b462-b3eb04df94d4/BEMOL-JP043-WILSONCEZARPELLIZZETTI.pdf?expires_on=1785434474&amp;signature=kEXOPcxEULU9uR9B9jZzs1gam75zuuGsjsOVsq3RysQ%3D</t>
         </is>
       </c>
       <c r="V464">
@@ -61441,7 +61441,7 @@
       </c>
       <c r="U465" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b260852b-4031-40bb-acf9-66ddccb26be5/BEMOL-AR30-WilsonCludioMelodaSilva.pdf?expires_on=1785434315&amp;signature=hDBddIUtbVsg9gW9ACBKfNu3d5QDuJLEQItO8JVhmYc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b260852b-4031-40bb-acf9-66ddccb26be5/BEMOL-AR30-WilsonCludioMelodaSilva.pdf?expires_on=1785434474&amp;signature=XTBFw6CZoWf9AiMPd26EMErEkhCh7hlFfCqma0gntOM%3D</t>
         </is>
       </c>
       <c r="V465">
@@ -61572,7 +61572,7 @@
       </c>
       <c r="U466" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/be15b9fd-6153-4e68-83ea-86d15b3aa336/LAUDOWILSONFERREIRANOGUEIRAcorrigido.pdf?expires_on=1785434315&amp;signature=lanYhrFH5zfLbADEZ0dMfT29gJQyxeQF96yCqKREa5s%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/be15b9fd-6153-4e68-83ea-86d15b3aa336/LAUDOWILSONFERREIRANOGUEIRAcorrigido.pdf?expires_on=1785434474&amp;signature=jD52k9WZTskgBNce8PSHS9Ss8FvJlJHJrLM%2FYMzjZnE%3D</t>
         </is>
       </c>
       <c r="V466">
@@ -61714,7 +61714,7 @@
       </c>
       <c r="U467" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4ac0d4ec-18c5-4f4c-8a4f-3f41f84ae112/Laudo_AC_75-2025_assinado.pdf?expires_on=1785434315&amp;signature=FWY6mgJt3EjnzZN4fAP0V9l6jheEwdWmUqZn7ndnfYk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4ac0d4ec-18c5-4f4c-8a4f-3f41f84ae112/Laudo_AC_75-2025_assinado.pdf?expires_on=1785434474&amp;signature=vekd4t%2FLg%2FuUGriLLg7Tgf5cYjuYxQlHYWVcpwpaxro%3D</t>
         </is>
       </c>
       <c r="V467">
@@ -61840,7 +61840,7 @@
       </c>
       <c r="U468" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f347b2e6-6687-4e4a-a567-9cb2929f140e/LaudoP24-Bemol-2026-YlenGrangeiroAtallah_signed.pdf?expires_on=1785434315&amp;signature=tSjRlqajs3FkLCPKUPUrsFiFBewIZ2upR6MHxvszgtc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f347b2e6-6687-4e4a-a567-9cb2929f140e/LaudoP24-Bemol-2026-YlenGrangeiroAtallah_signed.pdf?expires_on=1785434474&amp;signature=OQd%2BBRcX%2FME72J%2FlIkOvO5WkME0zKDvslZ8xZ4hY%2F9U%3D</t>
         </is>
       </c>
       <c r="V468">
@@ -61966,7 +61966,7 @@
       </c>
       <c r="U469" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/767c8ba7-7ed6-43db-a195-03bc90974a81/LAUDOYVELISEPREZBRAGA.pdf?expires_on=1785434315&amp;signature=7Ed65RxLAIUuQRC7mOiRs0%2B%2BqllR0wnAb6yDDRYDBR4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/767c8ba7-7ed6-43db-a195-03bc90974a81/LAUDOYVELISEPREZBRAGA.pdf?expires_on=1785434474&amp;signature=Pr0E6IeGOS91O%2BcPZQWVa%2BuH893Xw2leEK%2FnH8F27kY%3D</t>
         </is>
       </c>
       <c r="V469">
@@ -62109,7 +62109,7 @@
       </c>
       <c r="U470" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/770e1a99-8e08-4872-8418-9ff246a1ab84/LAUDOZIZAcorrigido03.pdf?expires_on=1785434315&amp;signature=Ljbd1PPJeVzu1HlgcRhskhkWuQIJKWh0ccytc13P7I4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/770e1a99-8e08-4872-8418-9ff246a1ab84/LAUDOZIZAcorrigido03.pdf?expires_on=1785434474&amp;signature=%2FWQoLh7CC5llst7KqMXin7PNliQLr1g9TlTLxKWjJRw%3D</t>
         </is>
       </c>
       <c r="V470">
@@ -62241,7 +62241,7 @@
       </c>
       <c r="U471" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/47448835-9a16-4629-9847-5fda1c53be58/M9-2026-ZULEIDE.pdf?expires_on=1785434315&amp;signature=T9J0EAiZO6mJ9teOHBAUsAZVWFD9cc7xCXUGPxKSUCo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/47448835-9a16-4629-9847-5fda1c53be58/M9-2026-ZULEIDE.pdf?expires_on=1785434474&amp;signature=of7lrd3d0VBr8Q%2FJLGNk2yggM72uDZi%2BL54Yqvpj3EA%3D</t>
         </is>
       </c>
       <c r="V471">

--- a/contratos.xlsx
+++ b/contratos.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7fb4d173-0b6b-461c-b96a-62443e97b31a/LaudoA01-Bemol-2026-AlicilaneBorgesPinheiroNascimento_signed.pdf?expires_on=1785445163&amp;signature=7gtxkvN83keQGVkLbVTm5siUM4Iuhii7%2BpvZQu5ooSM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7fb4d173-0b6b-461c-b96a-62443e97b31a/LaudoA01-Bemol-2026-AlicilaneBorgesPinheiroNascimento_signed.pdf?expires_on=1785445264&amp;signature=WcxlTfUB7WTBsx0Y%2BZ6BOPwjVhDtkJY2Oi8ajMlx9FI%3D</t>
         </is>
       </c>
       <c r="V2">
@@ -832,7 +832,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/66b67508-5546-4905-acdc-5d85735deb8e/LaudoB36-2026-BEMOL-ABDIASSIMIAODESOUZAFILHO.pdf?expires_on=1785445163&amp;signature=SPw8QIeMcnRAZCalnwuFC1uzPsJK2VCEx8PbdVZBwN4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/66b67508-5546-4905-acdc-5d85735deb8e/LaudoB36-2026-BEMOL-ABDIASSIMIAODESOUZAFILHO.pdf?expires_on=1785445264&amp;signature=kk6scgzuDtwR94YXqqx4RZcBZg4TKV4bCTUXSbryTmc%3D</t>
         </is>
       </c>
       <c r="V3">
@@ -961,7 +961,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c64cc402-2d06-47a7-a8d4-8d6d316b9654/Laudo72-Bemol-2026-AdamiltonSenaDosSantos-Ajustado-Assinado.pdf?expires_on=1785445163&amp;signature=uRr97sSKPCfN%2Bjs3TV468cXnkcAIYPsyx9DEGrlO%2F6o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c64cc402-2d06-47a7-a8d4-8d6d316b9654/Laudo72-Bemol-2026-AdamiltonSenaDosSantos-Ajustado-Assinado.pdf?expires_on=1785445264&amp;signature=OPLUxuvqhY78VTCbZdd8UxBtffWE%2FS9s%2BB3SjA7OEhs%3D</t>
         </is>
       </c>
       <c r="V4">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/28f3f575-1d5a-4e86-ad32-c81591e8b666/Laudo214-Bemol-2026-AdecildaBatistaMartins.pdf?expires_on=1785445163&amp;signature=jzpYcYIiMLboAWYO87QEay10XY8Q5Eom6Hv9wKxCqJA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/28f3f575-1d5a-4e86-ad32-c81591e8b666/Laudo214-Bemol-2026-AdecildaBatistaMartins.pdf?expires_on=1785445264&amp;signature=juY38%2BoiwoUX%2FQVxa%2BzUPSa2TFJ%2BwvcQ92Mt%2BhjQUqk%3D</t>
         </is>
       </c>
       <c r="V5">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/007f511d-a50e-4f56-8bc0-d55bf3536e2a/LaudoR05-2026-BEMOL-AdelinoChavesDeSouza.pdf?expires_on=1785445163&amp;signature=mW4xYJqzR%2BsfRl8LXY106eXtk3VeoG1DEKf0BcgLDcY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/007f511d-a50e-4f56-8bc0-d55bf3536e2a/LaudoR05-2026-BEMOL-AdelinoChavesDeSouza.pdf?expires_on=1785445264&amp;signature=I2tpFQS2OqwDCc5WizEy6CbJmLSidSiAE3hhyITM5Uk%3D</t>
         </is>
       </c>
       <c r="V6">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4c7e9ab9-04ab-4035-b58f-e9d7c51050a0/LaudoITA20-Bemol-2026-AdemardosSantoslima.pdf?expires_on=1785445163&amp;signature=69GByjw5FNQWQbZs%2BwqTpy1nWPnk31wqjm7m%2FHjI1Lc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4c7e9ab9-04ab-4035-b58f-e9d7c51050a0/LaudoITA20-Bemol-2026-AdemardosSantoslima.pdf?expires_on=1785445264&amp;signature=fxg65oqlSYqrzzJeGCLKdEk6L661gm6mngyXABbpvcs%3D</t>
         </is>
       </c>
       <c r="V7">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2ed10a7b-df53-4f57-889d-f247e65f45e0/BEMOL-PV074-ADRIELGEOVANEDINIZLOPES.pdf?expires_on=1785445163&amp;signature=bHXQ8jRcroJ7cNFM%2FkqLQ617oyIFHN5oLUIWNOjzP40%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2ed10a7b-df53-4f57-889d-f247e65f45e0/BEMOL-PV074-ADRIELGEOVANEDINIZLOPES.pdf?expires_on=1785445264&amp;signature=l2SpBSapPvG2srja2j%2BKQHbhGl7rpI6hrdpjO0G6%2BmY%3D</t>
         </is>
       </c>
       <c r="V8">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf495517-b334-42ed-8ad8-1436aedcf87b/LaudoB26-2026-BEMOL-ALAIRESGOMESDASILVA.pdf?expires_on=1785445163&amp;signature=Abg73PkDJ9KP0yrJ662C6%2BrZJckJMvEoTM8aljKKNjI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf495517-b334-42ed-8ad8-1436aedcf87b/LaudoB26-2026-BEMOL-ALAIRESGOMESDASILVA.pdf?expires_on=1785445264&amp;signature=i8vt02P6hek7jd7N8SCB6SjtEtiXfODmlYHW3%2FPaPGo%3D</t>
         </is>
       </c>
       <c r="V9">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d7df2939-a94a-467e-b7eb-ecca8304cf47/Laudo_AC_17-2026_-_ALCILENE_DE_PAULA_MARTINS_assinado.pdf?expires_on=1785445163&amp;signature=ZE17zdHNMBNvtjTtaos%2FEHzaQYB0JC%2BFVeywU%2F6d8LU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d7df2939-a94a-467e-b7eb-ecca8304cf47/Laudo_AC_17-2026_-_ALCILENE_DE_PAULA_MARTINS_assinado.pdf?expires_on=1785445264&amp;signature=pG24WFlZizY9%2F%2F4v5vnkvJSG7K6afbabGRyV8Fsu4JQ%3D</t>
         </is>
       </c>
       <c r="V10">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6622b85e-a02d-4f58-aa43-4aba7096b139/Laudo204-Bemol-2026-AlcioneBarbosadaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=K0Ezg0BI6yHFbk1XDIjx6TZcol%2Fzrm%2BbhnJhtyJNWrE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6622b85e-a02d-4f58-aa43-4aba7096b139/Laudo204-Bemol-2026-AlcioneBarbosadaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=IdbdlbaNWqqWYdsgK7AIT4oQ%2FvhwtC9JbwsZKPA4Hwo%3D</t>
         </is>
       </c>
       <c r="V11">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4f7398f0-8d1f-42d6-9060-4d6315bcbd49/Laudo131-Bemol-2026-AldoReisDeAraujoLucenaJunior.pdf?expires_on=1785445163&amp;signature=rsYu7%2FqzMpHCCvft9G2%2Bv8z2feig5L6GoQUbLx1%2BkGE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4f7398f0-8d1f-42d6-9060-4d6315bcbd49/Laudo131-Bemol-2026-AldoReisDeAraujoLucenaJunior.pdf?expires_on=1785445264&amp;signature=qAiGoRFlpW2ftcLdXL0wbbEbeZpkTslZD2dK%2Fg7vwok%3D</t>
         </is>
       </c>
       <c r="V12">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4c25e1f6-3188-4ad8-aa5d-55a018fdef0c/LaudoB52-2026-BEMOL-ALESSANDRAAZEVEDOMACHADO.pdf?expires_on=1785445163&amp;signature=CydhYPBv1I6kfCtYrYI6zg8SPubrH4iqmJ%2B2bgSRx48%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4c25e1f6-3188-4ad8-aa5d-55a018fdef0c/LaudoB52-2026-BEMOL-ALESSANDRAAZEVEDOMACHADO.pdf?expires_on=1785445264&amp;signature=ZWafMOZ151lht%2Fysb6jfsYVLDdaFAcaYoG5drO70vpQ%3D</t>
         </is>
       </c>
       <c r="V13">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/11642d66-cefc-4048-8b08-d1d694e52a90/Laudo121-Bemol-2026-AlessandroPereiraNeves-Assinado.pdf?expires_on=1785445163&amp;signature=3WuvmBFo237XXpmak4UIRiBLsGsa0LawujOLM5KKpb4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/11642d66-cefc-4048-8b08-d1d694e52a90/Laudo121-Bemol-2026-AlessandroPereiraNeves-Assinado.pdf?expires_on=1785445264&amp;signature=0iPL9%2FtG41tGRE%2BJjXqIZrsgO2isaceTwNmGgiCo1SA%3D</t>
         </is>
       </c>
       <c r="V14">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/21646528-58cb-4dc7-bd86-dbc8bec22b62/LAUDOALEXANDREBATISTAajustado.pdf?expires_on=1785445163&amp;signature=2rmZpMXzYTNqT2KsB0agZDR0k%2BAJc4VF7YSnz5XWbx8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/21646528-58cb-4dc7-bd86-dbc8bec22b62/LAUDOALEXANDREBATISTAajustado.pdf?expires_on=1785445264&amp;signature=89ho3IoLJbpqw%2Fu5xTmX1B0Mgh4sPKlKECox1clxbaE%3D</t>
         </is>
       </c>
       <c r="V15">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0bd12d7c-5f4d-4f99-ad05-3148b07a3fa2/Laudo155-Bemol-2026-AlexandreMedinaNoronha-Assinado.pdf?expires_on=1785445163&amp;signature=mjV8ma1MbQFl8cvHFzvc73IEnSivC3I%2BuQREuvSqSBw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0bd12d7c-5f4d-4f99-ad05-3148b07a3fa2/Laudo155-Bemol-2026-AlexandreMedinaNoronha-Assinado.pdf?expires_on=1785445264&amp;signature=Mx%2FDDpXDMiXX4BV0VSbyAl4iofxKdut97QnAg0EH%2Fb0%3D</t>
         </is>
       </c>
       <c r="V16">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c5df5341-74e8-4b47-9a72-4b1e7f9a236e/Laudo462-Bemol-2025-AlexsandroCarneiroCapote-Assinado.pdf?expires_on=1785445163&amp;signature=w08ZIrSf7Sa9QYb19ghoul2g2iwoJkGB1VImuK0TSNo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c5df5341-74e8-4b47-9a72-4b1e7f9a236e/Laudo462-Bemol-2025-AlexsandroCarneiroCapote-Assinado.pdf?expires_on=1785445264&amp;signature=DlnfuLsNQQnMss2oqr4Id5VsDnb7O%2F88cAMqwiRgd0g%3D</t>
         </is>
       </c>
       <c r="V17">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a7bccc3a-8cae-407c-b16c-944931f134be/BEMOL-PV091-ALEXSANDRODASILVACHAGAS.pdf?expires_on=1785445163&amp;signature=PhA6OzS7fcvTrfdkuJl4TPfkIkE0WWA6TIhvmRGP5G8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a7bccc3a-8cae-407c-b16c-944931f134be/BEMOL-PV091-ALEXSANDRODASILVACHAGAS.pdf?expires_on=1785445264&amp;signature=odNxVcj3zD2%2FbAFpoa7cLa2pk9w8uEM8iC0NiLsCFrI%3D</t>
         </is>
       </c>
       <c r="V18">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ec2f8020-e636-4ee4-a818-ab6ba5513c9f/LaudoBRT01-Bemol-2026-AlineSilvaRodrigues_signed.pdf?expires_on=1785445163&amp;signature=1qOsjD6QclkZPpcDGp%2Fp3qE1v3j5UMFPDJ9qNR5i9VQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ec2f8020-e636-4ee4-a818-ab6ba5513c9f/LaudoBRT01-Bemol-2026-AlineSilvaRodrigues_signed.pdf?expires_on=1785445264&amp;signature=OSvml33GGIgNXjF%2FXPhGpa%2BZU4EfKgm7lAyibtyTc6c%3D</t>
         </is>
       </c>
       <c r="V19">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b7143741-9582-4509-af2b-f1331879e859/Laudo47-Bemol-2026-AlinyLeite-Assinado.pdf?expires_on=1785445163&amp;signature=%2Fp97Qg8egOTDr9PVP6gz9hGZWgYBpYmZzpkEeGtckwY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b7143741-9582-4509-af2b-f1331879e859/Laudo47-Bemol-2026-AlinyLeite-Assinado.pdf?expires_on=1785445264&amp;signature=4yQCD6yTrNtPF7BmwEr6mMJGZRbmaMwbFmKW7jhoGBU%3D</t>
         </is>
       </c>
       <c r="V20">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a26d2b4-76c4-4c49-a38c-f8bdc3c83919/LaudoB24-2026-BEMOL-ALTAMIROPEREIRADASILVA_2corrigido.pdf?expires_on=1785445163&amp;signature=I44RAZP1dxnGF2oQZmhBrBtRPNjSesC82qr2b2JsCg0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a26d2b4-76c4-4c49-a38c-f8bdc3c83919/LaudoB24-2026-BEMOL-ALTAMIROPEREIRADASILVA_2corrigido.pdf?expires_on=1785445264&amp;signature=hpec%2F9fpscItCGHjuaIDESsukMAv9N8QAuN87cewAmo%3D</t>
         </is>
       </c>
       <c r="V21">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/29e682ce-6607-46f7-a12d-e06a2d8dcd18/LaudoJP08-Bemol-2026-AlzenirFreire_signed.pdf?expires_on=1785445163&amp;signature=2mS3a5WCLNHWzDSELSiWHokSZClDGezALoyw0ih1PJE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/29e682ce-6607-46f7-a12d-e06a2d8dcd18/LaudoJP08-Bemol-2026-AlzenirFreire_signed.pdf?expires_on=1785445264&amp;signature=MKxiwgcI9dEt4JM8RSmXdZLIX3QYbybBOr23cr5WI3Q%3D</t>
         </is>
       </c>
       <c r="V22">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0b88abaf-3393-4d08-86bb-e7551aa40e79/Laudo_AC_19-2026_-_ROSEANE_IDALINA_DE_FREITAS_assinado.pdf?expires_on=1785445163&amp;signature=G3xJuS8PY7DeA03%2FuhSAueN%2F%2B4XI772DBAnxzs1Y6hg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0b88abaf-3393-4d08-86bb-e7551aa40e79/Laudo_AC_19-2026_-_ROSEANE_IDALINA_DE_FREITAS_assinado.pdf?expires_on=1785445264&amp;signature=AXHdXzcScm%2BLikc%2FLSKcJh8QF2XAy7R1e7hVLCXN8o0%3D</t>
         </is>
       </c>
       <c r="V23">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/360cfb85-8c70-4b37-bf95-eafd6a4cd2f1/BEMOL-PV076-AMARILDOJUNIORCORTEZDESOUZA.pdf?expires_on=1785445163&amp;signature=XgG94bNqJuL2s3nvjdx5wucAazlmVMiiJ%2BFv0KmuvFc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/360cfb85-8c70-4b37-bf95-eafd6a4cd2f1/BEMOL-PV076-AMARILDOJUNIORCORTEZDESOUZA.pdf?expires_on=1785445264&amp;signature=uv%2Fj8WhsHDpK9qyiS3jt21EzlS7HtsCobB5C%2Bl06jxI%3D</t>
         </is>
       </c>
       <c r="V24">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1f94317e-a38b-482f-a0e4-955c796831df/Laudo126-Bemol-2026-AmauryCezarMenezesCavalcante-Assinado.pdf?expires_on=1785445163&amp;signature=tfpUVl9mqcqMmunEQkPVlGLGDxRAmBJymzkFVMloXo0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1f94317e-a38b-482f-a0e4-955c796831df/Laudo126-Bemol-2026-AmauryCezarMenezesCavalcante-Assinado.pdf?expires_on=1785445264&amp;signature=eMoL8UqhchAeGZgaRqcL2Emz6pj7TqagcgZtvdXb%2BcA%3D</t>
         </is>
       </c>
       <c r="V25">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5f9e9ec0-64d0-4bf9-8a65-58ac51a05454/LAUDOANACAMILA.pdf?expires_on=1785445163&amp;signature=H2%2BrqvE3F%2BQ7cOm%2FtygfNMOwV4QiakcjA1MhJJTYMtY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5f9e9ec0-64d0-4bf9-8a65-58ac51a05454/LAUDOANACAMILA.pdf?expires_on=1785445264&amp;signature=A44Rt2UOcXAFu4HkMsW4pxzFfl8jeRh2uTpCv%2FsG8gI%3D</t>
         </is>
       </c>
       <c r="V26">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b530c704-d818-489a-9000-ce31d7ad0322/Laudo78-Bemol-2026-AnaCeciliaPereiraSilveiraLima.pdf?expires_on=1785445163&amp;signature=JQpjs52HR%2BVWGzw%2BfILlWRhLZanfqHCJlg5tz5KTYhA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b530c704-d818-489a-9000-ce31d7ad0322/Laudo78-Bemol-2026-AnaCeciliaPereiraSilveiraLima.pdf?expires_on=1785445264&amp;signature=FZD8r72vjh8NhBXnc%2BZiU7q%2BqmyVZyAJu7CK8F0iol0%3D</t>
         </is>
       </c>
       <c r="V27">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b8465407-ab08-4f67-af8f-ed0d03ae4011/Laudo91-Bemol-2026-AnaCristinaAzulayCardosoSoares-Assinado.pdf?expires_on=1785445163&amp;signature=STSUHg2gHUxXZxffeDgY7OR3JpaURwnepF7tz8oR0SU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b8465407-ab08-4f67-af8f-ed0d03ae4011/Laudo91-Bemol-2026-AnaCristinaAzulayCardosoSoares-Assinado.pdf?expires_on=1785445264&amp;signature=SiJG82XxXczNaUpsBFG8K4DN4fScLy30Xxt6nromdPE%3D</t>
         </is>
       </c>
       <c r="V28">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/64fef612-4cec-4eaf-91a7-e811c9e2f740/BEMOL-JP038-ANALUCIASILVADEJESUS.pdf?expires_on=1785445163&amp;signature=NClqWQAHKzb51TRNwBTdCeNLfxqhZ3oMUdER5Uea0Gk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/64fef612-4cec-4eaf-91a7-e811c9e2f740/BEMOL-JP038-ANALUCIASILVADEJESUS.pdf?expires_on=1785445264&amp;signature=KUzO2ZZUG0BQKw%2BYN%2FFjZwthfgBoVg46Mg5XeKrEKG0%3D</t>
         </is>
       </c>
       <c r="V29">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3458991a-dae2-4c8f-a75c-030be3f7330d/Laudo35-Bemol-2026-AnaLuciaSousaDaSilva-assinado-ajustado.pdf?expires_on=1785445163&amp;signature=X4Ymn077pHvE6Rw9f0caB0iRfSZov10BSx59KP5r3j4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3458991a-dae2-4c8f-a75c-030be3f7330d/Laudo35-Bemol-2026-AnaLuciaSousaDaSilva-assinado-ajustado.pdf?expires_on=1785445264&amp;signature=Suvv%2F%2Fm9UzncIr1lY%2FRhp%2BTadUbVFmv1n3EqsCsoUPM%3D</t>
         </is>
       </c>
       <c r="V30">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/83193c81-cbef-42a4-b6e8-da9ed23d74b5/Laudo161-Bemol-2026-AnaMaraVieiraDosSantos-Assinado.pdf?expires_on=1785445163&amp;signature=vuoYDqn3OHBBYSjZ%2FPZFlC6xUB2BoXuK%2FC%2BJ7MqWjfE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/83193c81-cbef-42a4-b6e8-da9ed23d74b5/Laudo161-Bemol-2026-AnaMaraVieiraDosSantos-Assinado.pdf?expires_on=1785445264&amp;signature=Zv6UI4b1fr%2Fmr18C4siREJ891dE650iS2Wfr8ncrbWs%3D</t>
         </is>
       </c>
       <c r="V31">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/454108b6-dede-46a6-be10-ec0a5377199a/M02-2026-AnaMarciaSantosMacielajustado.pdf?expires_on=1785445163&amp;signature=45AM2nLLv7HJt%2FgyezDv2GMMGGXd2JtVBU275jrmheI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/454108b6-dede-46a6-be10-ec0a5377199a/M02-2026-AnaMarciaSantosMacielajustado.pdf?expires_on=1785445264&amp;signature=CG0Hw60SD7WL6eXTkPaPw7YxYJHvLh%2B3CsdC0U9rCHQ%3D</t>
         </is>
       </c>
       <c r="V32">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d468c22b-1ac0-4333-acb1-4e848898420b/Laudo183-Bemol-2026-AnaMariadaSilvaMoraes-Assinado.pdf?expires_on=1785445163&amp;signature=8YOjlQ0Bkt0BVAy1gGPTwR%2BedJnZ1Hcl1BHZ0VNtd2Q%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d468c22b-1ac0-4333-acb1-4e848898420b/Laudo183-Bemol-2026-AnaMariadaSilvaMoraes-Assinado.pdf?expires_on=1785445264&amp;signature=CT2%2BsZ%2FVyBDnUVhurca5iMVIvQ5CC32EMF6wrNUwtFg%3D</t>
         </is>
       </c>
       <c r="V33">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f58e04e2-d303-4ee1-8f5e-c361252c5994/LAUDOANAPAULAAMORIN.pdf?expires_on=1785445163&amp;signature=y0c2fnCTTwCbfmD1Lwu%2BIQwwpTMuR49zo0fTkZnm3zs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f58e04e2-d303-4ee1-8f5e-c361252c5994/LAUDOANAPAULAAMORIN.pdf?expires_on=1785445264&amp;signature=TuoNvQ0Wl%2FzvYI12p1e6RNrWGFSLHhPLt65%2BtFeNSv4%3D</t>
         </is>
       </c>
       <c r="V34">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b4faed57-f07c-4b7e-a1ec-06f5c6967038/LaudoB51-2026-BEMOL-AnaPaulaCoelhodaSilva.pdf?expires_on=1785445163&amp;signature=MF6KultsQzdUycjwpoj9GnUUfidClZqw%2FWFG5ZeR0zs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b4faed57-f07c-4b7e-a1ec-06f5c6967038/LaudoB51-2026-BEMOL-AnaPaulaCoelhodaSilva.pdf?expires_on=1785445264&amp;signature=EJGoXMqzQAr7caIi%2FvoW2MBndvo4M0gG52JofOggj9Q%3D</t>
         </is>
       </c>
       <c r="V35">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/07f9e40d-4fae-4b74-b002-9c105d003d96/LaudoP04-Bemol-2026-AnaPaulaFortesDaSilvaFerreira_signed.pdf?expires_on=1785445163&amp;signature=wDZpn0gSu43b1onhzhbZc2M1Z3VCV1A%2FjUA0ujzO4PE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/07f9e40d-4fae-4b74-b002-9c105d003d96/LaudoP04-Bemol-2026-AnaPaulaFortesDaSilvaFerreira_signed.pdf?expires_on=1785445264&amp;signature=cZ924iw0kRCuSkRlaqRpiepX2u%2Fesr0bhQJKqdmMth4%3D</t>
         </is>
       </c>
       <c r="V36">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/150f97b8-750e-4816-a503-3f030bc41231/LaudoMAN06-Bemol-2026-AnazioPirangadaSilva.pdf?expires_on=1785445163&amp;signature=lnYCIO5DK%2FEV9Dau%2Fd35Ui855xCsrdHfiHc28AqQKxc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/150f97b8-750e-4816-a503-3f030bc41231/LaudoMAN06-Bemol-2026-AnazioPirangadaSilva.pdf?expires_on=1785445264&amp;signature=Uy%2F1qBwEFEjotSrHvc7Cu2KtN7u59b%2Bk0q3QIDv4Owc%3D</t>
         </is>
       </c>
       <c r="V37">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/58745fa5-7f1e-4632-b9db-619b07fb06a0/Laudo194-Bemol-2026-AnderclicydaSilvaAraujo.pdf?expires_on=1785445163&amp;signature=0Y8zEODWeND5OSkDeFAYtJE%2FwHmIVX05qmTYURoAgyQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/58745fa5-7f1e-4632-b9db-619b07fb06a0/Laudo194-Bemol-2026-AnderclicydaSilvaAraujo.pdf?expires_on=1785445264&amp;signature=su1H8KAxs4%2FgSF81OZcs5D%2BBubOCWEQuS0RFKH%2FajCg%3D</t>
         </is>
       </c>
       <c r="V38">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cee94394-328f-4b94-bee9-bbf5d9c9939e/Laudo111-Bemol-2026-AndreiaRodriguesRibeiroAndrade.pdf?expires_on=1785445163&amp;signature=ajQh5Csj0q%2BlFv0vYUU5sBIGEDlWlnwjIGP%2Fu6OpFmA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cee94394-328f-4b94-bee9-bbf5d9c9939e/Laudo111-Bemol-2026-AndreiaRodriguesRibeiroAndrade.pdf?expires_on=1785445264&amp;signature=lr1tAyfy49OXz2S3fAF2sliByKFq23GT2JVPGk7J644%3D</t>
         </is>
       </c>
       <c r="V39">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e2aa1510-0364-40ee-bd4a-67e2d5e116c3/Laudo165-Bemol-2026-AndrezaLimaMota-Assinado.pdf?expires_on=1785445163&amp;signature=psB3fjfK58ADYMpu4DKlTr7hY4mTz9b99CgHfcjpgRU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e2aa1510-0364-40ee-bd4a-67e2d5e116c3/Laudo165-Bemol-2026-AndrezaLimaMota-Assinado.pdf?expires_on=1785445264&amp;signature=FrB0SNyvO0m5DJYhQ7eAcQ72x75FL1CTWqz5yF5iRuE%3D</t>
         </is>
       </c>
       <c r="V40">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/68882f52-8495-4cb1-bebf-e8dae87d1f86/LAUDOCORRIGIDOANDREZZADESOUSAMARIALVA.pdf?expires_on=1785445163&amp;signature=Ob2LnfFhQJlPxbONqzxRZkQilIs8dPPcI%2BrHVM5QoGY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/68882f52-8495-4cb1-bebf-e8dae87d1f86/LAUDOCORRIGIDOANDREZZADESOUSAMARIALVA.pdf?expires_on=1785445264&amp;signature=eMjbA6qcO%2BBhzkwCDqgDN7zKNVY0eUNXfV6mAkCmgoc%3D</t>
         </is>
       </c>
       <c r="V41">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8cf8037a-f95b-4c30-90b6-82ac5cd0a25e/Laudo107-Bemol-2026-AneCarolinedosSantosSilva-Assinado.pdf?expires_on=1785445163&amp;signature=8ag8W6XlXYAb4FDHoBBdYpN%2B6Dkw7iC%2B2kI43gZtgFw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8cf8037a-f95b-4c30-90b6-82ac5cd0a25e/Laudo107-Bemol-2026-AneCarolinedosSantosSilva-Assinado.pdf?expires_on=1785445264&amp;signature=MGFsHCwruqGIkDwbwbp3d8YcC4bmvbyjtQpD9oUUE0Y%3D</t>
         </is>
       </c>
       <c r="V42">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8b724798-462d-40bc-ab0b-0dcf8179109b/LAUDOANGELAMARIAcorrigido.pdf?expires_on=1785445163&amp;signature=5ElN5HSJ%2BZwjThqMTwF1xlNiCHT6A1Meb4YxeGrKOCg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8b724798-462d-40bc-ab0b-0dcf8179109b/LAUDOANGELAMARIAcorrigido.pdf?expires_on=1785445264&amp;signature=IrrWO%2B%2BV%2BHRcdY9yn%2BP3vKoYFQASxJCe%2BFMrmY%2Bkt1o%3D</t>
         </is>
       </c>
       <c r="V43">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f9e14e1e-f280-4a43-9a64-94dd20275c3e/Laudo129-Bemol-2026-AnneCarolinePadronRocha.pdf?expires_on=1785445163&amp;signature=2y7wM4uI7%2FWPUXOOXX1Oz9dHasKVHpo27uyk9X3CyXs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f9e14e1e-f280-4a43-9a64-94dd20275c3e/Laudo129-Bemol-2026-AnneCarolinePadronRocha.pdf?expires_on=1785445264&amp;signature=M3Sph6CY0KfY0io7B0z%2BCoYD46pCI1gB6s%2B1pFfg%2BiY%3D</t>
         </is>
       </c>
       <c r="V44">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/54a0dd7f-fea8-4d1b-bc26-3ca986081c2a/Laudo_AC_23-2026_-_ANTONIA_SUELI_BRAZ_FONSECA_assinado.pdf?expires_on=1785445163&amp;signature=xZnUEeGJGVIPkLjIIZPevRT1E3WHp3tOu4%2BLyv0UNg8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/54a0dd7f-fea8-4d1b-bc26-3ca986081c2a/Laudo_AC_23-2026_-_ANTONIA_SUELI_BRAZ_FONSECA_assinado.pdf?expires_on=1785445264&amp;signature=azYzVN269QgIeBWqlkLaEcrd0%2FBB4lKJA6A9R4iGMq8%3D</t>
         </is>
       </c>
       <c r="V45">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/83a953a8-c9ee-42e3-a99f-17fb29197818/LaudoB1-2026-BEMOL-ANTONIADASILVABEZERRA.pdf?expires_on=1785445163&amp;signature=JwmRip39OS%2BpEGYXL%2F1T7bUTTZYJqzzYXKCrLpDCb6A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/83a953a8-c9ee-42e3-a99f-17fb29197818/LaudoB1-2026-BEMOL-ANTONIADASILVABEZERRA.pdf?expires_on=1785445264&amp;signature=6odJ28VNwkm24iHZdKSAj2wv7KBFMg3%2F7ci0rLNWv7M%3D</t>
         </is>
       </c>
       <c r="V46">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/98e7eb46-c27e-43c7-a3c7-69fbe8f42055/Laudo480-Bemol-2025-AntonioAugustinhoDaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=i%2FMaz%2Ba9zfGXAl2SkSDAImUHUHInm82YPWFrmT1%2FTe4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/98e7eb46-c27e-43c7-a3c7-69fbe8f42055/Laudo480-Bemol-2025-AntonioAugustinhoDaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=O81JiQLB5Mlwpj2xPZDgSt465eidDNpvTIvG6TUj2uI%3D</t>
         </is>
       </c>
       <c r="V47">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d223f792-5416-4201-acfb-ad428f0f989f/LAUDOANTONIO.pdf?expires_on=1785445163&amp;signature=ptvICZ2zMSHwR%2BTqBxMe7qG2035NfTVFRYPDv3KvlZo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d223f792-5416-4201-acfb-ad428f0f989f/LAUDOANTONIO.pdf?expires_on=1785445264&amp;signature=9OdqnNOAtFBjguCLxz1uALIhYeiFeaO4esh4ea1w2lE%3D</t>
         </is>
       </c>
       <c r="V48">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3b18d347-7f8e-4239-9b1a-ed2ef9ea9280/BEMOL-PV079-ANTONIOCARLOSPONTESSILVAnovomodelo.pdf?expires_on=1785445163&amp;signature=Q4K%2FWJyowEp8KO7ASaylx9WoT6l7tL%2BwQ5WAu3qD42w%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3b18d347-7f8e-4239-9b1a-ed2ef9ea9280/BEMOL-PV079-ANTONIOCARLOSPONTESSILVAnovomodelo.pdf?expires_on=1785445264&amp;signature=g8tmVW3eBMXH1lV7qsN7u2rPXgUNC2zqFGlaWolMXnU%3D</t>
         </is>
       </c>
       <c r="V49">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/07b55276-2e98-4927-84ee-b47cd386d90e/LAUDOANTONIOFLOREScorrigido.pdf?expires_on=1785445163&amp;signature=Q8fjVclm6pVlKp7hdYhNTw4cIKteF45B%2BoTt69SLgkA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/07b55276-2e98-4927-84ee-b47cd386d90e/LAUDOANTONIOFLOREScorrigido.pdf?expires_on=1785445264&amp;signature=qRxbNn%2BchsaYaavqUC4mKizknyNO4NVwYUybHtwnJ5M%3D</t>
         </is>
       </c>
       <c r="V50">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6943e82d-4aa3-440c-9bcc-6a3af33cfa1a/Laudo109-Bemol-2026-AntonioMoraisSantiago-Assinado.pdf?expires_on=1785445163&amp;signature=ziKFO0JsJjHQpUVmXDfsfRXBr%2BMywc6cmhGCrRLxG2Y%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6943e82d-4aa3-440c-9bcc-6a3af33cfa1a/Laudo109-Bemol-2026-AntonioMoraisSantiago-Assinado.pdf?expires_on=1785445264&amp;signature=kbVN0nr6tOyS83IY9tUdcbiZxJ0Z8I4GwnjY4ZGe%2FpE%3D</t>
         </is>
       </c>
       <c r="V51">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3cd6d343-0f0d-4405-a4a8-76e307f481fe/LaudoB39-2026-BEMOL-ANTONIORIBEIROVIANA.pdf?expires_on=1785445163&amp;signature=SWIZZTDq6M9qc%2Fx8sEdnVIht7NXTPS7oubvDN1liVrc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3cd6d343-0f0d-4405-a4a8-76e307f481fe/LaudoB39-2026-BEMOL-ANTONIORIBEIROVIANA.pdf?expires_on=1785445264&amp;signature=kLhvLDyYfHHEqaNjZRDyiqy2lfsg9oCVSvNfnkG2OIA%3D</t>
         </is>
       </c>
       <c r="V52">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/724f0153-2776-46e4-9a40-21b0e37ecae9/Laudo182-Bemol-2026-AntonioSousaCosta.pdf?expires_on=1785445163&amp;signature=zoe9fqVjCAFNFRkNhO2QCmD49SswYYB4sNR%2FAzpU2Yg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/724f0153-2776-46e4-9a40-21b0e37ecae9/Laudo182-Bemol-2026-AntonioSousaCosta.pdf?expires_on=1785445264&amp;signature=fUfCAhVw5tO9YBYMcSNXvZi9lNuEjXYEmJugUCuDu5o%3D</t>
         </is>
       </c>
       <c r="V53">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9a5a54fe-e4a9-45a3-92f7-c8f8aca9905d/Laudo192-Bemol-2026-AntonioVitalMarinhoFilho.pdf?expires_on=1785445163&amp;signature=6fx2udmztKRP6xUlMpn9bM8%2BJq64szICo6wxCAV0jbg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9a5a54fe-e4a9-45a3-92f7-c8f8aca9905d/Laudo192-Bemol-2026-AntonioVitalMarinhoFilho.pdf?expires_on=1785445264&amp;signature=lVyXX0iSOEI5zBBxqct25Hg%2BqI3dYhHu2VfIWbPHDZc%3D</t>
         </is>
       </c>
       <c r="V54">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/43f8142c-6f01-4ed5-b781-c26dec473638/Laudo210-Bemol-2026-ApoenaCristinaBrasilSousa-Assinado.pdf?expires_on=1785445163&amp;signature=ZJLcu7D1ah0mnrd5syQu5ZAgAapKzlhIZzGpV2P599A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/43f8142c-6f01-4ed5-b781-c26dec473638/Laudo210-Bemol-2026-ApoenaCristinaBrasilSousa-Assinado.pdf?expires_on=1785445264&amp;signature=VWTFvAzTaUN89kj4A6JlAN1u1cecbA0sAZd5oo0HbUg%3D</t>
         </is>
       </c>
       <c r="V55">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ce99b0a7-5272-4bd5-bdf7-93a48cd76678/Laudo137-Bemol-2026-ArleiseDaSilvaFigueira.pdf?expires_on=1785445163&amp;signature=zayFIs%2BgPXmjBsfDerNKXPixs47lZetxyZC4rmcIFEo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ce99b0a7-5272-4bd5-bdf7-93a48cd76678/Laudo137-Bemol-2026-ArleiseDaSilvaFigueira.pdf?expires_on=1785445264&amp;signature=5t%2FalAs%2BhR9mLQo%2BGdmjDvOCQUyIbMNCRT20OJBrnNU%3D</t>
         </is>
       </c>
       <c r="V56">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/93e611b9-4214-4f17-9144-6b8f78b7aab7/Laudo123-Bemol-2026-ArlindoSouzaDeHolanda.pdf?expires_on=1785445163&amp;signature=KDFdOLK7nm7mtv6mMZinaxzPDNCAy7A16rbfURK1l%2B0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/93e611b9-4214-4f17-9144-6b8f78b7aab7/Laudo123-Bemol-2026-ArlindoSouzaDeHolanda.pdf?expires_on=1785445264&amp;signature=Q0syWYBS8T%2FOE9T0yReoYoO7eDgRP4tx%2BGApu2DIvKY%3D</t>
         </is>
       </c>
       <c r="V57">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3fb83548-7366-484a-a6ab-54f2f8f6f488/Laudo98-Bemol-2026-AureaDaSilvaTrindadeSoares.pdf?expires_on=1785445163&amp;signature=BN2swOis%2Fpz65srn3nzos3G2lY8mFxaFkFjzf%2Bnls0Y%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3fb83548-7366-484a-a6ab-54f2f8f6f488/Laudo98-Bemol-2026-AureaDaSilvaTrindadeSoares.pdf?expires_on=1785445264&amp;signature=1b9LfG86eB%2BoeHUivoq9s6phqrgoSzSvqngrBWVo4EY%3D</t>
         </is>
       </c>
       <c r="V58">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7fcc6830-a61c-4edb-b8de-cb677550fd4d/Laudo115-Bemol-2026-AureliaBentesFerreira-Assinado.pdf?expires_on=1785445163&amp;signature=RTq8ydSeAi2rA%2FrTwBlVVPddfFFJYhhGoCasB9K1VJk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7fcc6830-a61c-4edb-b8de-cb677550fd4d/Laudo115-Bemol-2026-AureliaBentesFerreira-Assinado.pdf?expires_on=1785445264&amp;signature=xVjc4fx%2Bac%2FPpUGONX7m5EYvOLCXQ2eUMyOyivvggdI%3D</t>
         </is>
       </c>
       <c r="V59">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1f0ac28-c405-4bba-93cb-319510e9e1cf/Laudo_AC_24-2026_-_AURELIO_DA_SILVA_AZEVEDO_assinado.pdf?expires_on=1785445163&amp;signature=RsKl0NcdQi8SIzynF%2Bwxh46mMDFjFFhc9WLSYWc2bEk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1f0ac28-c405-4bba-93cb-319510e9e1cf/Laudo_AC_24-2026_-_AURELIO_DA_SILVA_AZEVEDO_assinado.pdf?expires_on=1785445264&amp;signature=pY2qmp3btIk3rBSAB2JnlLjdRGLnZUGd8LJAfOQ0syw%3D</t>
         </is>
       </c>
       <c r="V60">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6a44e1f9-a59e-4ba4-91e1-781a7c146ff4/LaudoITA14-Bemol-2026-AureniceRabelodoNascimento-Assinadoajustado.pdf?expires_on=1785445163&amp;signature=sVfOwxSMFXX6Zekmvsiro6Q0Cfa3h77V9HpufddBxCc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6a44e1f9-a59e-4ba4-91e1-781a7c146ff4/LaudoITA14-Bemol-2026-AureniceRabelodoNascimento-Assinadoajustado.pdf?expires_on=1785445264&amp;signature=ejJYgX0lK%2FOXRhToq2qKyS77ngUG6VkKybfuY4X4R8U%3D</t>
         </is>
       </c>
       <c r="V61">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c0214175-8f29-4f87-a45d-ffd2e4444f1e/Laudo34-Bemol-2026-AuxiliadoraCruzDosSantos-Assinado.pdf?expires_on=1785445163&amp;signature=MdhABjnwkbqdEPzsbEsNriW53lwaWG2hHFDniduTgRA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c0214175-8f29-4f87-a45d-ffd2e4444f1e/Laudo34-Bemol-2026-AuxiliadoraCruzDosSantos-Assinado.pdf?expires_on=1785445264&amp;signature=11sjs88s7sVUBFanxMZtYDPQEG8hDNUeLAyN0hg3eMo%3D</t>
         </is>
       </c>
       <c r="V62">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/24701e8a-44ce-40d1-b05e-f5411c37c44a/LaudoB32-2026-BEMOL-BETTYIARAGAMAGONZALEZ.pdf?expires_on=1785445163&amp;signature=9S80gsPPMOaAgEd4AAyuWo%2BqHzaz1ZG3lHOSSUDfKEE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/24701e8a-44ce-40d1-b05e-f5411c37c44a/LaudoB32-2026-BEMOL-BETTYIARAGAMAGONZALEZ.pdf?expires_on=1785445264&amp;signature=ce8%2BH%2FIGLILQpulUOCsuGNOYXkaFOF363iIHnc1ISCs%3D</t>
         </is>
       </c>
       <c r="V63">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5c1781be-ac10-40e0-907d-c08e78226152/Laudo20-2025-Bemol-BrenoSoaresFeitoza-Assinado.pdf?expires_on=1785445163&amp;signature=ySP50MYszbD4uq8iRVteFX6Vf5DZOgWDiFqvXkAKj9o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5c1781be-ac10-40e0-907d-c08e78226152/Laudo20-2025-Bemol-BrenoSoaresFeitoza-Assinado.pdf?expires_on=1785445264&amp;signature=4%2BzpIGaA8UqdceEqyk12rNai5AOJJ1ft1xE7zYfQ1aY%3D</t>
         </is>
       </c>
       <c r="V64">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/543005fc-4f9c-40b7-a4b2-d509df3d1fc1/LaudoP25-Bemol-2026-BrunaBentodeOliveira_signed.pdf?expires_on=1785445163&amp;signature=zs8GboN6KxeecrMdAF%2BYUn0WOYDpdLUWqqADa9TrzqU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/543005fc-4f9c-40b7-a4b2-d509df3d1fc1/LaudoP25-Bemol-2026-BrunaBentodeOliveira_signed.pdf?expires_on=1785445264&amp;signature=unVJbW5xtePfMleHgAq7r77SzKZERjuMGMtNyfR0%2FYs%3D</t>
         </is>
       </c>
       <c r="V65">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/43fbbba4-c8cf-4337-a16a-a2e4f4edaab2/Laudo200-Bemol-2026-BrunaJannainaSilvaMendonca-Assinado.pdf?expires_on=1785445163&amp;signature=NbLmoZagjWVrHAOZG0MMO0tEXeFLZ0Gf6pjMmkDB38w%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/43fbbba4-c8cf-4337-a16a-a2e4f4edaab2/Laudo200-Bemol-2026-BrunaJannainaSilvaMendonca-Assinado.pdf?expires_on=1785445264&amp;signature=o0wJDSqpjy8%2FwIFCR4pfbhPOwnBPecvF8zqMy05md5c%3D</t>
         </is>
       </c>
       <c r="V66">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3ce22068-ea71-4640-8b9a-60f8b01f5f29/Laudo184-Bemol-2026-CaloivaPaesDeLemosOliveira.pdf?expires_on=1785445163&amp;signature=rpcHvWhExbc6lvc3yJ8pybJFoP6SCnqRaaXKlckgiUg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3ce22068-ea71-4640-8b9a-60f8b01f5f29/Laudo184-Bemol-2026-CaloivaPaesDeLemosOliveira.pdf?expires_on=1785445264&amp;signature=sKOspgiFQlGcZI2t9SjNFkhKYssWztJkxV7r2Lf%2Bkxk%3D</t>
         </is>
       </c>
       <c r="V67">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ccd7d189-c4f8-4347-a8d8-1cb8b0341517/Laudo139-Bemol-2026-CarliceBarbosaDoAmaral.pdf?expires_on=1785445163&amp;signature=p1XRsUaUh66HeiefccYFkZroLm2KAY8UQKbZPLdOvqk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ccd7d189-c4f8-4347-a8d8-1cb8b0341517/Laudo139-Bemol-2026-CarliceBarbosaDoAmaral.pdf?expires_on=1785445264&amp;signature=lE9PPPfoou3O24nRBRk65zNEKMSeRkVQdZhnBkSnBLU%3D</t>
         </is>
       </c>
       <c r="V68">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/799a3761-767b-4676-acfb-c5d34affbb1a/LaudoITA06-Bemol-2026-CarlosEleoteriodeMoraes.pdf?expires_on=1785445163&amp;signature=GPp7BiALnPlJUSZau50GawEh1YqCrdjMh7B%2BtN25TVk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/799a3761-767b-4676-acfb-c5d34affbb1a/LaudoITA06-Bemol-2026-CarlosEleoteriodeMoraes.pdf?expires_on=1785445264&amp;signature=gEQdcgAyhbevfMcLJ8nvq1rgBXWjgJj1RKxQ22L1G68%3D</t>
         </is>
       </c>
       <c r="V69">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e02f445a-3246-4a56-b961-162d323a94de/LaudoA06-Bemol-2026-CarolinaDeFreitas_signed.pdf?expires_on=1785445163&amp;signature=2oKlZfqBSYWY4PH9VLBeiXlf7PrzilyjhHEfyghV6bk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e02f445a-3246-4a56-b961-162d323a94de/LaudoA06-Bemol-2026-CarolinaDeFreitas_signed.pdf?expires_on=1785445264&amp;signature=j1DwXKv52xUVp%2FZ5DiHPQZjZYQbYA8Xi3bU2Sts9dI0%3D</t>
         </is>
       </c>
       <c r="V70">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/552485d5-095d-4a91-8fce-d18d7115158f/LaudoP23-Bemol-2026-CerlonValentedoNascimentoPacheco_signed.pdf?expires_on=1785445163&amp;signature=%2FOAzxtX1%2FmQ6JU4Yaa5d7zjV%2F%2Bxy3oEVpbuvOPXSJjQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/552485d5-095d-4a91-8fce-d18d7115158f/LaudoP23-Bemol-2026-CerlonValentedoNascimentoPacheco_signed.pdf?expires_on=1785445264&amp;signature=HSw8ATVYLmVwwjMwGnG7uzNCVy%2Fkj%2BGgtvfucu5D5ZM%3D</t>
         </is>
       </c>
       <c r="V71">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6796f8e5-ad95-4505-9f99-b94181fa1f0a/LAUDOCICERO.pdf?expires_on=1785445163&amp;signature=DtB7Xpk76D6DEwFYEFT0Fz3rgli%2Fpqq7KLsUlApPQ1w%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6796f8e5-ad95-4505-9f99-b94181fa1f0a/LAUDOCICERO.pdf?expires_on=1785445264&amp;signature=LOY9ODyz1OiyOTkSFiUyOV%2BFPvonSW1pWMjmrWTWH9U%3D</t>
         </is>
       </c>
       <c r="V72">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ce7e1e2c-27ee-4882-8f47-124631792dde/Laudo21-Bemol-2026-CinthiaCristinaDoNascimentoPereira-Assinado.pdf?expires_on=1785445163&amp;signature=dbP2%2BXXeYoNDfXxneK9KXrTHdBY0wl657rr%2B4g0I4vE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ce7e1e2c-27ee-4882-8f47-124631792dde/Laudo21-Bemol-2026-CinthiaCristinaDoNascimentoPereira-Assinado.pdf?expires_on=1785445264&amp;signature=WXdh%2FiKEqZQ91mtoxGA2aR8LJcKTc%2BTNm7f%2FucVIEys%3D</t>
         </is>
       </c>
       <c r="V73">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4bb0e515-b13b-4c27-9d12-c8f2d63450e7/LAUDOCLAUDIAMARIASOUZADECASTRO.pdf?expires_on=1785445163&amp;signature=BBJLZALmJjnhyethNFp9Jk2R1nAr3Cyges5%2FEwDVIyA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4bb0e515-b13b-4c27-9d12-c8f2d63450e7/LAUDOCLAUDIAMARIASOUZADECASTRO.pdf?expires_on=1785445264&amp;signature=cFsigLC7FSNulIrFKtnkfUxThLftJbayV7Cefcq2%2BV0%3D</t>
         </is>
       </c>
       <c r="V74">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/797e54fa-75a0-4c64-88de-07c01838b7c3/Laudo18-Bemol-2026-ClaudiaMatosDaCruzCoelho-Assinado.pdf?expires_on=1785445163&amp;signature=Btp5WQYF6%2FhPNkJGaDPMBaHOSMNnEQy3wugl%2Foqf0Bc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/797e54fa-75a0-4c64-88de-07c01838b7c3/Laudo18-Bemol-2026-ClaudiaMatosDaCruzCoelho-Assinado.pdf?expires_on=1785445264&amp;signature=6h2%2Fw45q2erh0y9wj7sGBDRnm0s3fJIkC6w2Qf59tQ0%3D</t>
         </is>
       </c>
       <c r="V75">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ecc81d50-7c4a-4d1f-9347-37258e35d44b/LaudoJP10-Bemol-2026-CleideCustodioDeSouza_signed.pdf?expires_on=1785445163&amp;signature=b1wEZFBmiwJExj5iZv1HDe%2FOlSjgNjbWmNDi2VuLPzk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ecc81d50-7c4a-4d1f-9347-37258e35d44b/LaudoJP10-Bemol-2026-CleideCustodioDeSouza_signed.pdf?expires_on=1785445264&amp;signature=xm7eZLQRpiMPYUcLsU2VeX%2Bb33FLcTYwawS01zcmn4E%3D</t>
         </is>
       </c>
       <c r="V76">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a32e3ff-6194-41cf-89bc-5d6c4f86838f/LaudoPA47-Bemol-2025-CleitonDosSantosRodrigues-Assinado.pdf?expires_on=1785445163&amp;signature=PcAL07WrfZ0gVXdE6bRJnGga7BjgfDKOFlXI6xDfsME%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a32e3ff-6194-41cf-89bc-5d6c4f86838f/LaudoPA47-Bemol-2025-CleitonDosSantosRodrigues-Assinado.pdf?expires_on=1785445264&amp;signature=Khe19ETefMv5wUVCYHsm4XF4VUHx7%2BrwAPNR8K616Vs%3D</t>
         </is>
       </c>
       <c r="V77">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0aa2e8f4-6c0b-421f-b58e-33066fa09f27/BEMOL-PV087-CleitondaSilva.pdf?expires_on=1785445163&amp;signature=s02VhHW2ZIikw5OaOGTQ2XHMb5fn7b%2F7wp%2BuX4I%2F%2BH8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0aa2e8f4-6c0b-421f-b58e-33066fa09f27/BEMOL-PV087-CleitondaSilva.pdf?expires_on=1785445264&amp;signature=viaU%2BtsT8MhUf16NVqzuLQ8jkZh8DHAR5U22k5h48JA%3D</t>
         </is>
       </c>
       <c r="V78">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f072c23d-6575-42e8-9558-1681be8a79da/Laudo41-Bemol-2026-CleomardePaulaLima-Assinado.pdf?expires_on=1785445163&amp;signature=5wWFvnbQl%2FD9ht67HchLkUZ8RRP1jKqaJm%2Bae%2BJoX74%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f072c23d-6575-42e8-9558-1681be8a79da/Laudo41-Bemol-2026-CleomardePaulaLima-Assinado.pdf?expires_on=1785445264&amp;signature=bG8NhnGjjiIhM3iMCVDOz01OR%2B81muCWi8LXYl7ZjL4%3D</t>
         </is>
       </c>
       <c r="V79">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f29e6a7-765f-46a0-8fee-f160391a2f0a/Laudo_AC_22-2026_-_CLODOALDA_LEANDRO_GOMES_SOUZA_assinado.pdf?expires_on=1785445163&amp;signature=XfqG5%2BRiG%2BrVhiu0r9SmDKB6TXE6PfdGZP0CMnQ4%2FwY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f29e6a7-765f-46a0-8fee-f160391a2f0a/Laudo_AC_22-2026_-_CLODOALDA_LEANDRO_GOMES_SOUZA_assinado.pdf?expires_on=1785445264&amp;signature=nKgvtHQG3ltNmHGZeh%2Fwia1Ck%2F5phivuGOt%2FsLPWzSA%3D</t>
         </is>
       </c>
       <c r="V80">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/acd15778-bfd8-495a-aff0-21f42f8fd97b/LaudoITA01-Bemol-2026-CristhianeMayaraPrestesdosAnjosdaSilva.pdf?expires_on=1785445163&amp;signature=1xOg6vjZ6u3U9VEMK5Jjp%2FSjspg3JdxOguwHsL3h55o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/acd15778-bfd8-495a-aff0-21f42f8fd97b/LaudoITA01-Bemol-2026-CristhianeMayaraPrestesdosAnjosdaSilva.pdf?expires_on=1785445264&amp;signature=x7LPtwjbVchKolHoMMkAXVjX6QByWTpCKR7xKpd1GWk%3D</t>
         </is>
       </c>
       <c r="V81">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/805f26ff-356d-41f0-8840-d8a0018997cc/RelatriodeValordeRefernciaRVR03-Bemol-2026-DaianaMacariodaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=PTiCUdRwn%2Fkdxtfvq%2FbffjoCrDUXFa4LlTRM%2Fiu89wo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/805f26ff-356d-41f0-8840-d8a0018997cc/RelatriodeValordeRefernciaRVR03-Bemol-2026-DaianaMacariodaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=FYibfIZUEO%2Fq3TDrRjY2D6totXUy0OoqkAI5mqAhV1A%3D</t>
         </is>
       </c>
       <c r="V82">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f9d89784-edd5-48d5-8590-fd86ea5ded67/LaudoB29-2026-BEMOL-DAMASIOCARNEIROLARANJEIRA.pdf?expires_on=1785445163&amp;signature=QC3BvrEZ4VZRfiBbKboTf7Ndzh9FjAd9etiNBkLxRwo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f9d89784-edd5-48d5-8590-fd86ea5ded67/LaudoB29-2026-BEMOL-DAMASIOCARNEIROLARANJEIRA.pdf?expires_on=1785445264&amp;signature=Mn9a6lhZN9Hyb5ZobGsPer%2FDgGI4nW1vta%2BYjvPkQ0A%3D</t>
         </is>
       </c>
       <c r="V83">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e5dd5af0-5eec-4ab7-93a4-97d619a27b96/M4-2026-DANIELALVESajustado.pdf?expires_on=1785445163&amp;signature=%2BYB585h1yrp7sUo%2B6ERjpNZdwQa6HAEUsl97D0Xu1c8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e5dd5af0-5eec-4ab7-93a4-97d619a27b96/M4-2026-DANIELALVESajustado.pdf?expires_on=1785445264&amp;signature=vKAwUCrNTf9kAipoFGkfiP2yH%2FBypZXUsv9tsPpjeUk%3D</t>
         </is>
       </c>
       <c r="V84">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1e229a70-a871-4616-896f-5cff1574d528/M5-2026-DANIELALVESajustado.pdf?expires_on=1785445163&amp;signature=xUqoqfnItx83Bu9RhoTWTG%2BJyV5KrFQvNkEcygu8%2Bu0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1e229a70-a871-4616-896f-5cff1574d528/M5-2026-DANIELALVESajustado.pdf?expires_on=1785445264&amp;signature=%2BVPTKA5KOJXK%2BzpCx%2Ba49jrvgiOxDgR%2FtzUsoexiLQA%3D</t>
         </is>
       </c>
       <c r="V85">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c271d4d4-53bc-45ce-8161-5360ceb3b3ef/Laudo138-Bemol-2026-DanielaDosReisSeixasCoelho.pdf?expires_on=1785445163&amp;signature=XSef9HaR8eiIYQAualU8ERwn9LproDEM%2FvHwrKikNP8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c271d4d4-53bc-45ce-8161-5360ceb3b3ef/Laudo138-Bemol-2026-DanielaDosReisSeixasCoelho.pdf?expires_on=1785445264&amp;signature=2nIKRUusq5zF80qZVLYioSNeY3t3oyzYkOkdIsBlahI%3D</t>
         </is>
       </c>
       <c r="V86">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1ce44eb-deec-40a1-a06b-868ba469526b/LAUDODANIELE.pdf?expires_on=1785445163&amp;signature=55Ccp5nkToD3JCxWtaSP430oUJ3L4FAoI7qCN%2FZ90iw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1ce44eb-deec-40a1-a06b-868ba469526b/LAUDODANIELE.pdf?expires_on=1785445264&amp;signature=Qjcuew%2F7xJZZ00cZsdcqbI0cq1ede5PjaTBWC63Uzxg%3D</t>
         </is>
       </c>
       <c r="V87">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0fee6b3f-94fb-4183-aa3e-1d0677399840/Laudo84-Bemol-2026-DarisonDeSouzaRamos-Assinado.pdf?expires_on=1785445163&amp;signature=F24IiHdkvMjXsd9eybBgoUOHU4hd7bcPaCdHuzi8nJE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0fee6b3f-94fb-4183-aa3e-1d0677399840/Laudo84-Bemol-2026-DarisonDeSouzaRamos-Assinado.pdf?expires_on=1785445264&amp;signature=3O4masa4Wq7rGMv3VCtq3d%2FGn6UR9%2F5BWh3SV1heThE%3D</t>
         </is>
       </c>
       <c r="V88">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b2d6b3a5-51a5-45fb-b5ab-0271d4525878/BEMOL-PV088-DARLINGENUNESNASCIMENTO.pdf?expires_on=1785445163&amp;signature=%2Fs1yANgIs5mEFtU0sZ5aO98s9pS%2B6RRvZksfwONR1Cg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b2d6b3a5-51a5-45fb-b5ab-0271d4525878/BEMOL-PV088-DARLINGENUNESNASCIMENTO.pdf?expires_on=1785445264&amp;signature=qV%2Bl%2FGc2RuWykqJ3fGaW9qr1fl%2FidB1R4snGMSfuxd0%3D</t>
         </is>
       </c>
       <c r="V89">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ca9e25cf-e868-4944-a385-0c98e80dd3e4/Laudo173-Bemol-2026-DaviCastroGarcia.pdf?expires_on=1785445163&amp;signature=Mo%2FPLFzc4dCQ8Wr%2FaxbOlaq5XYIKfuAA%2BBdL8oRztCg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ca9e25cf-e868-4944-a385-0c98e80dd3e4/Laudo173-Bemol-2026-DaviCastroGarcia.pdf?expires_on=1785445264&amp;signature=ww8pVaq8NAnZNpXkIGrhtEsieDLi%2FQJZcKHM9CJkHNk%3D</t>
         </is>
       </c>
       <c r="V90">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/52d0962b-f1b4-4859-a26e-2686aebba31f/Laudo29-Bemol-2026-DavidLimaDeAraujo-Assinado.pdf?expires_on=1785445163&amp;signature=ugD3jjKvQPSv%2BlJC%2BXQrpcjwnel4MwWwBj3YQNvNAHs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/52d0962b-f1b4-4859-a26e-2686aebba31f/Laudo29-Bemol-2026-DavidLimaDeAraujo-Assinado.pdf?expires_on=1785445264&amp;signature=JlY%2FA9Xs1HXEDFpW1iY1Gp4MoHY3079Ro3o0olwKOvw%3D</t>
         </is>
       </c>
       <c r="V91">
@@ -12410,7 +12410,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fc282ab4-7de8-44dc-b0d2-8db2cf5fa4d1/LaudoB11-2026-BEMOL-DAYSENAYARAGONALVESDIAS.pdf?expires_on=1785445163&amp;signature=2oaCdoT41D4ZM3kdLmvjtYOsBUo%2FbPEk6MoBX2NYR%2FI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fc282ab4-7de8-44dc-b0d2-8db2cf5fa4d1/LaudoB11-2026-BEMOL-DAYSENAYARAGONALVESDIAS.pdf?expires_on=1785445264&amp;signature=1pO%2FvWEr5V3zQBngNjMg4EVWQOMMO0nzmg2sqz9gCyk%3D</t>
         </is>
       </c>
       <c r="V92">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/63cabcc8-ee70-49ef-807f-0c102ae8dc77/LaudoP02-Bemol-2026-DelcimarGamaDaFonseca_signed.pdf?expires_on=1785445163&amp;signature=5JOjL4NRpjyxiGFJ610WSfd9%2BY1bKmYHM3FOuxzmJ2c%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/63cabcc8-ee70-49ef-807f-0c102ae8dc77/LaudoP02-Bemol-2026-DelcimarGamaDaFonseca_signed.pdf?expires_on=1785445264&amp;signature=YwdIQdfEkRIxZURr%2FLIo%2BqgJWxGRVYvEMC8xmJITeTs%3D</t>
         </is>
       </c>
       <c r="V93">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a74a35b-62b8-4181-8173-e8b4ce482191/LAUDODENILDO.pdf?expires_on=1785445163&amp;signature=13hs3D%2BzFqbgikH8Ry9U2%2BGxmZxkT7gzMBwu08fBBP4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a74a35b-62b8-4181-8173-e8b4ce482191/LAUDODENILDO.pdf?expires_on=1785445264&amp;signature=y3fsb1hxcGKqnqEym2p0AUOjSwIXctWC3Qh%2BIgKfMIM%3D</t>
         </is>
       </c>
       <c r="V94">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/15ba2ece-19de-4196-9767-72294a7b33e6/Laudo170-Bemol-2026-DeusalinaVasconcelosLima.pdf?expires_on=1785445163&amp;signature=cbs%2BL2e9f4TWHGvvuxf2f1yBvcpyOnh7UvuNnKfQW5g%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/15ba2ece-19de-4196-9767-72294a7b33e6/Laudo170-Bemol-2026-DeusalinaVasconcelosLima.pdf?expires_on=1785445264&amp;signature=CSXmtTkrM9dgL6VYa4ClNSKVe3GTigJJDQKqq4GpE5g%3D</t>
         </is>
       </c>
       <c r="V95">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b05fb8f4-a555-4d72-8c6e-bbe7d4a9436e/LaudoRVR07-Bemol-2026-DeusdeteCastroPessoa-Assinado.pdf?expires_on=1785445163&amp;signature=AvVviX0t4UqQCUh2jQ7ZKoOr7oH6E9bMXU9HgM4zvSg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b05fb8f4-a555-4d72-8c6e-bbe7d4a9436e/LaudoRVR07-Bemol-2026-DeusdeteCastroPessoa-Assinado.pdf?expires_on=1785445264&amp;signature=jvMwpslbzDAgcwsgTWq%2Fen8257bOwqo28EKg4kYAKOo%3D</t>
         </is>
       </c>
       <c r="V96">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e697831f-2be1-4bdb-a91a-fb21547d4b26/LaudoP12-Bemol-2026-DezianeAraujodaSilva_signed.pdf?expires_on=1785445163&amp;signature=vU4xuIFmLSUxK03nQZaJd3Vfpt19J6z6flxMTRstu9g%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e697831f-2be1-4bdb-a91a-fb21547d4b26/LaudoP12-Bemol-2026-DezianeAraujodaSilva_signed.pdf?expires_on=1785445264&amp;signature=n%2FliVyhALt7WS9ag%2FdPAvtlwj5ZqvcgYamZjgfQnR7Y%3D</t>
         </is>
       </c>
       <c r="V97">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/de8f14f1-b4f9-44cb-a7f1-1a2c7ea28b17/LAUDODHIJANA2corrigido.pdf?expires_on=1785445163&amp;signature=Lk4EPB%2FI4pGl%2FOoRjOJgw91sBun6eJOKT3XolG895Co%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/de8f14f1-b4f9-44cb-a7f1-1a2c7ea28b17/LAUDODHIJANA2corrigido.pdf?expires_on=1785445264&amp;signature=zzQN6FqvoAnguOmTG5JJL3itvj1XnDud3soSvzN%2Bcb4%3D</t>
         </is>
       </c>
       <c r="V98">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5552317c-4a4d-4a89-b4f6-8cd323b9d6e5/LAUDODHIJANA1corrigido.pdf?expires_on=1785445163&amp;signature=w7CyR%2BVYJl%2FP%2FZz9SHQ675Z3tVJY9r014QhIekxmvIg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5552317c-4a4d-4a89-b4f6-8cd323b9d6e5/LAUDODHIJANA1corrigido.pdf?expires_on=1785445264&amp;signature=MKYVswmPpKvbjUM36ODlp%2B%2B3S7rXayYS3dBVftNlNkU%3D</t>
         </is>
       </c>
       <c r="V99">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2c236bc5-75ef-4ae1-8301-675053e1c06c/Laudo_AC_09-2026_-_DIANA_CAROLINE_DA_SILVA_SANTOS_assinado.pdf?expires_on=1785445163&amp;signature=Mysv9PU0S0kuFgjjMkdDxl0TIwSPYxTNlIHrSgDFEbI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2c236bc5-75ef-4ae1-8301-675053e1c06c/Laudo_AC_09-2026_-_DIANA_CAROLINE_DA_SILVA_SANTOS_assinado.pdf?expires_on=1785445264&amp;signature=OO9xiKgtg%2FbS%2BIvXjCsI1FbLYRsWHODRTY8wCYrBwXo%3D</t>
         </is>
       </c>
       <c r="V100">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/62813463-d44a-4700-8adc-561de9ba2477/LAUDODIANE.pdf?expires_on=1785445163&amp;signature=r2iyl%2FOFdhczuzdGKF6yoTAgX1F95xBdzfsOsU3Lz5U%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/62813463-d44a-4700-8adc-561de9ba2477/LAUDODIANE.pdf?expires_on=1785445264&amp;signature=TVCoaIGK2Jxl2vJaEsxfHK%2BfFgQWRYb4q7QBb6xxg8A%3D</t>
         </is>
       </c>
       <c r="V101">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/604019c1-0351-4825-93c2-d471ec3dd995/LAUDODIEGO.pdf?expires_on=1785445163&amp;signature=asgVhfso09Nzzv5Dz7aYrhMf8a5uW2ASyrZvhWhr7rg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/604019c1-0351-4825-93c2-d471ec3dd995/LAUDODIEGO.pdf?expires_on=1785445264&amp;signature=ME4aZnQVcYSko7odJOb412wwpAtLJtRUToPFCrDnkek%3D</t>
         </is>
       </c>
       <c r="V102">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ebde28be-d8fc-46a9-9ac3-20bd6763718a/LaudoA17-Bemol-2025-DinalvaLacerdaDeSouza_signed.pdf?expires_on=1785445163&amp;signature=cZOxa63uBjLKUX727TOPmm5DFmHltUUS4JK%2BgbGQq64%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ebde28be-d8fc-46a9-9ac3-20bd6763718a/LaudoA17-Bemol-2025-DinalvaLacerdaDeSouza_signed.pdf?expires_on=1785445264&amp;signature=DHhF7xZRL7NqL2PAZC4RsO5prr1hKL8GkeAEXVkEE1g%3D</t>
         </is>
       </c>
       <c r="V103">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/82ae2b33-0927-43a7-81b6-dbd12bb745b8/Laudo_AC_29-2026_-_DOUVINA_COSTA_DA_SILVA_assinadoajustado.pdf?expires_on=1785445163&amp;signature=CWdkrz5XRkM41QinnVkjgMfyJXvYhy4Y5rn9X03t7AI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/82ae2b33-0927-43a7-81b6-dbd12bb745b8/Laudo_AC_29-2026_-_DOUVINA_COSTA_DA_SILVA_assinadoajustado.pdf?expires_on=1785445264&amp;signature=5LkiPlJpbe204n9DzGAcGzrtzbDj5IdG19k2CxlMpC8%3D</t>
         </is>
       </c>
       <c r="V104">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/806e066e-4cc0-4b10-805f-af20789d5423/BEMOL-PV070-DYANAJHENIFFERRAMOSTORRES.pdf?expires_on=1785445163&amp;signature=nZWISeTulOdsHAP7DcOV3Kf8cLxsYo0cKPQW1rTisTA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/806e066e-4cc0-4b10-805f-af20789d5423/BEMOL-PV070-DYANAJHENIFFERRAMOSTORRES.pdf?expires_on=1785445264&amp;signature=C3zjfl2tCeDxvwoAqxp6lx4gONTLGO020caijnF%2Biv4%3D</t>
         </is>
       </c>
       <c r="V105">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ee8f616f-928d-41ae-91b3-649b02ced3ce/Laudo482-Bemol-2025-DyhonySiqueiraFigueiredo-Assinado1.pdf?expires_on=1785445163&amp;signature=3aPtLI6ej4517RBkDl9cNONfyTGpB4quPO56UozFEhI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ee8f616f-928d-41ae-91b3-649b02ced3ce/Laudo482-Bemol-2025-DyhonySiqueiraFigueiredo-Assinado1.pdf?expires_on=1785445264&amp;signature=J480r3GCRuDVViw4wlIp7CeiyrL3xMWaAyEvHkxN%2F5A%3D</t>
         </is>
       </c>
       <c r="V106">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6b66f5cb-54de-4cf6-bf8c-b345b4805945/LaudoP05-Bemol-2026-EderlanyaCardosoDosSantos_signed.pdf?expires_on=1785445163&amp;signature=B9qf0y6Rok72CAKqus0b762pQjs1%2Fj16GG8dYLNoIDo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6b66f5cb-54de-4cf6-bf8c-b345b4805945/LaudoP05-Bemol-2026-EderlanyaCardosoDosSantos_signed.pdf?expires_on=1785445264&amp;signature=kn4r%2BtrSmH3FcbHOEne%2By9Jm5jdaaCfNM5N5fNpHrrA%3D</t>
         </is>
       </c>
       <c r="V107">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4a88bd99-8088-4036-8302-bbba9e6cda37/LAUDOEDILENE1.pdf?expires_on=1785445163&amp;signature=UZN%2FTsOQrDGZm70Zj791eemAO8tBvvajbPktkbwmSNE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4a88bd99-8088-4036-8302-bbba9e6cda37/LAUDOEDILENE1.pdf?expires_on=1785445264&amp;signature=e3L4%2Fd2Hn%2BiXFla6kXrNJvwD0FkeIWnh1i9ydihtmHU%3D</t>
         </is>
       </c>
       <c r="V108">
@@ -14664,7 +14664,7 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c5d0dc18-bb72-415b-8237-d8f0c2100c21/Laudo156-Bemol-2026-EdileneMeloVieira.pdf?expires_on=1785445163&amp;signature=tUVDf1BVCgghhlsWuFrN9gkMTlzR3aRN47Ifq9RoQkU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c5d0dc18-bb72-415b-8237-d8f0c2100c21/Laudo156-Bemol-2026-EdileneMeloVieira.pdf?expires_on=1785445264&amp;signature=UvL1mGnzX0h%2F86L4E5yuaVu6iQJIJYNdfOdR2zedLXE%3D</t>
         </is>
       </c>
       <c r="V109">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4bc7496e-b2c6-4bbb-aa43-08a93f74b3bc/BEMOL-JP039-EDILEUZAALEXANDREDEFIGUEIREDO.pdf?expires_on=1785445163&amp;signature=tXdcCAg%2Fh6zpmL14GucTHCQ4pzFhiFiybL9iBp0zXXU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4bc7496e-b2c6-4bbb-aa43-08a93f74b3bc/BEMOL-JP039-EDILEUZAALEXANDREDEFIGUEIREDO.pdf?expires_on=1785445264&amp;signature=rjgK9XsAgBUvvXFHoABn3OiMhIQ6gTzvzkSCsUBjJAU%3D</t>
         </is>
       </c>
       <c r="V110">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e50e3f5e-ff8a-4bc2-8f96-bb87ed524c4a/Laudo419-Bemol-2025-EdinaLimaSoares-Assinado.pdf?expires_on=1785445163&amp;signature=0nsEehZC3f4XH5nNp6EJ2LzR3aJAc%2BkihFmUcz2h8q4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e50e3f5e-ff8a-4bc2-8f96-bb87ed524c4a/Laudo419-Bemol-2025-EdinaLimaSoares-Assinado.pdf?expires_on=1785445264&amp;signature=WB7hwQWxMMeU74RFVoMUu819WcdJUf8oRzuT4bkYt8M%3D</t>
         </is>
       </c>
       <c r="V111">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0781f381-a5b8-4cc0-9c64-955154cc185e/LaudoB49-2026-BEMOL-EdinaldoMoraesdaCruz.pdf?expires_on=1785445163&amp;signature=KYfsZCsssRgbNbySOnvnwqTYOSbZuICb%2FkirHc1igN4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0781f381-a5b8-4cc0-9c64-955154cc185e/LaudoB49-2026-BEMOL-EdinaldoMoraesdaCruz.pdf?expires_on=1785445264&amp;signature=ApaNLenpgNvu1Hiv%2FswqqjESOKOKGfHA0cruaCuLJYc%3D</t>
         </is>
       </c>
       <c r="V112">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4605b442-6252-4740-9bef-1c907a3122f3/Laudo_AC_15-2026_-_EDINALVA_FURTADO_DO_NASCIMENTO_assinado.pdf?expires_on=1785445163&amp;signature=y%2Fz8lDfJCDL8YtKXoW8Qf8f8hrCgUs3OJSs6rH2UYIs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4605b442-6252-4740-9bef-1c907a3122f3/Laudo_AC_15-2026_-_EDINALVA_FURTADO_DO_NASCIMENTO_assinado.pdf?expires_on=1785445264&amp;signature=CCuX1od0R%2FznU6ffkxrtV%2BY3WEQ7YmXr9OW3HKV3y0o%3D</t>
         </is>
       </c>
       <c r="V113">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fd0013a3-4c79-4eed-9ad5-011dc0531ef0/LaudoITA05-Bemol-2026-EdinelzaNogueiraMota-Assinado.pdf?expires_on=1785445163&amp;signature=1Mobjvp4hjY0gTHvFJoTCwt%2BUze1cyIvBV8vTV2sVS4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fd0013a3-4c79-4eed-9ad5-011dc0531ef0/LaudoITA05-Bemol-2026-EdinelzaNogueiraMota-Assinado.pdf?expires_on=1785445264&amp;signature=WvhSRpmXDQOKptPmu4q37kWhxu2FZO%2FloTsYY1zp5pY%3D</t>
         </is>
       </c>
       <c r="V114">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f1c9b3a-952f-438e-83dd-1e11af526203/Laudo73-Bemol-2026-EdmarDiasDeSouza-Assinado.pdf?expires_on=1785445163&amp;signature=pvBHDaGEWU1J1zZYNdpsN9FnlHW1MiRLx9pq%2F7l8vYI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f1c9b3a-952f-438e-83dd-1e11af526203/Laudo73-Bemol-2026-EdmarDiasDeSouza-Assinado.pdf?expires_on=1785445264&amp;signature=PddgVcvZgNsjHnppl2TwpG8iGZnlj9ljTSsH%2BxDFqU4%3D</t>
         </is>
       </c>
       <c r="V115">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5ee14984-2d04-41e9-a6f5-7aa939a43689/LaudoCO02-Bemol-2025-EdnaGomesMaciel-Assinado.pdf?expires_on=1785445163&amp;signature=7jt68Bh819mCPMlgkLnYv7e%2BqTWwHvczKlKda8go%2FKM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5ee14984-2d04-41e9-a6f5-7aa939a43689/LaudoCO02-Bemol-2025-EdnaGomesMaciel-Assinado.pdf?expires_on=1785445264&amp;signature=%2BN%2FrquP9MduRD%2BjF7WmHf8lCFPopSu0DJprXpR0iXEM%3D</t>
         </is>
       </c>
       <c r="V116">
@@ -15695,7 +15695,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/bc5d0a32-2beb-4f27-951e-ba01c364ae7f/LaudoR04-2026-BEMOL-EdnaJanuriadeMoraisdaSilva.pdf?expires_on=1785445163&amp;signature=uXYobH1aEr4UfQ4Lfuc9I79%2FM4m6YkVCmhYbG5HdANE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/bc5d0a32-2beb-4f27-951e-ba01c364ae7f/LaudoR04-2026-BEMOL-EdnaJanuriadeMoraisdaSilva.pdf?expires_on=1785445264&amp;signature=kq%2BsG4PR8GrnW0jIzYYgCmXIvxzEavZd8RhJ2KruPgk%3D</t>
         </is>
       </c>
       <c r="V117">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/310b284b-d250-49c4-b0d5-ac80a7ddcdcb/BEMOL-JP042-EDNEIASOARESOLIVEIRA.pdf?expires_on=1785445163&amp;signature=3qygMcWz0LvNrV5bnYEodVuepAINwP%2BtiqBmp3eqO34%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/310b284b-d250-49c4-b0d5-ac80a7ddcdcb/BEMOL-JP042-EDNEIASOARESOLIVEIRA.pdf?expires_on=1785445264&amp;signature=zHFcJS%2F%2B047fCPup8LkvK6mRoDvkCAdqYsBwExocfsw%3D</t>
         </is>
       </c>
       <c r="V118">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3c082cb5-667c-4b2e-bb35-a623d0457346/Laudo133-Bemol-2026-EduardoJorgeFerreiraBarroso-Assinado.pdf?expires_on=1785445163&amp;signature=g9IUmX65Yz0XScbuqOQPt2dJFItGNnQc0UtTBg5GYP8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3c082cb5-667c-4b2e-bb35-a623d0457346/Laudo133-Bemol-2026-EduardoJorgeFerreiraBarroso-Assinado.pdf?expires_on=1785445264&amp;signature=by4m17r78rj1pkm08TufUEDu73JnpvvH88IXqz2WMcU%3D</t>
         </is>
       </c>
       <c r="V119">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/20deaef0-ad14-478d-a46f-491eb319ea63/LaudoP03-Bemol-2026-EdvarJoseModesto_signed.pdf?expires_on=1785445163&amp;signature=HDbQpEX9OMNBS2yzYqREf98Qo9dVoYKEiXI%2FaClb3WQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/20deaef0-ad14-478d-a46f-491eb319ea63/LaudoP03-Bemol-2026-EdvarJoseModesto_signed.pdf?expires_on=1785445264&amp;signature=OAxQRxq%2FgjFZM%2BAefALTr5Bpdv%2FJsqDpmIlYM0f4obo%3D</t>
         </is>
       </c>
       <c r="V120">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf9fd50d-3718-43e5-bdab-94a4b729f59a/BEMOL-JP036-ELAINECRISTINAMARGARIDADOSSANTOS.pdf?expires_on=1785445163&amp;signature=LRJ5Xfh02llll2TKaOOKVFJDT%2B6h56gFKuMS0u4CVsE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf9fd50d-3718-43e5-bdab-94a4b729f59a/BEMOL-JP036-ELAINECRISTINAMARGARIDADOSSANTOS.pdf?expires_on=1785445264&amp;signature=%2BMUQc%2Fvwazqvgirc3KJMWymu8ZY9EFkz%2F4YOndCEz4U%3D</t>
         </is>
       </c>
       <c r="V121">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/374aef79-93b6-4bad-ab45-bc3709b69cd6/RelatriodeValordeReferncia-Bemol-2026-RVR09-ElaneCristinaFerreiradaSilva.pdf?expires_on=1785445163&amp;signature=6GdfPpZcZds0me0oxSOHEMcUG2qdI9qb3kczQ6N5Idw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/374aef79-93b6-4bad-ab45-bc3709b69cd6/RelatriodeValordeReferncia-Bemol-2026-RVR09-ElaneCristinaFerreiradaSilva.pdf?expires_on=1785445264&amp;signature=QEK2bC%2BufcDye8wd0%2FthPbWTvJI%2B8M%2BtvFdyWn50A0E%3D</t>
         </is>
       </c>
       <c r="V122">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a7e37b6-ec4a-4cee-848c-2f23939b6dc2/BEMOL-PV095-ELANEFELICIOESANTOS.pdf?expires_on=1785445163&amp;signature=EtTmEvE4FLd2Z8oqZNzhl2hmwaxdXbnmBpdbrxRmMyk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a7e37b6-ec4a-4cee-848c-2f23939b6dc2/BEMOL-PV095-ELANEFELICIOESANTOS.pdf?expires_on=1785445264&amp;signature=cZC4PcHQm43rQCpN3MaUwZk%2F%2FFQ%2Bxd1tPq%2FwruvGqbo%3D</t>
         </is>
       </c>
       <c r="V123">
@@ -16624,7 +16624,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f6ac25c-5053-42c5-8335-3b4052274121/M13-2026-ELCIELI.pdf?expires_on=1785445163&amp;signature=ylHPNZK%2BH2SRHmI0GwtpxtInQ0fYy7PsdE9pI9Pgw2I%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f6ac25c-5053-42c5-8335-3b4052274121/M13-2026-ELCIELI.pdf?expires_on=1785445264&amp;signature=l%2FxZCQIvJFNCyVlWIRO%2Bn2IJ%2FfmmiIeluFrhgbJYNq8%3D</t>
         </is>
       </c>
       <c r="V124">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/93511b28-1f72-4dfa-85b3-cb6d459ef2aa/BEMOL-PV097-ELECLISSIMABARROZOMORAES.pdf?expires_on=1785445163&amp;signature=Tqo9EaeM0B%2FvN2j4kOFbmRftg2bKm%2FBIWhNIehw7RXw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/93511b28-1f72-4dfa-85b3-cb6d459ef2aa/BEMOL-PV097-ELECLISSIMABARROZOMORAES.pdf?expires_on=1785445264&amp;signature=%2FeWs43sq5W5KUsnWKGlyzg8MMYMpP%2B0SzKwXFw5edvE%3D</t>
         </is>
       </c>
       <c r="V125">
@@ -16879,7 +16879,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/56655338-63fa-409a-ad4f-9701712f7289/LaudoA03-Bemol-2026-ElenizeLima_signed.pdf?expires_on=1785445163&amp;signature=teVxDpzsguFdLkGod1xOSywST%2FUEbZUuxyxjvKiKN%2Bk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/56655338-63fa-409a-ad4f-9701712f7289/LaudoA03-Bemol-2026-ElenizeLima_signed.pdf?expires_on=1785445264&amp;signature=XlMsvLU9%2Bz8plp1%2B6%2B6Un0F994MzButAIgRt2PqyOl4%3D</t>
         </is>
       </c>
       <c r="V126">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3a34b841-1745-4596-bc96-5707bb3090b6/LaudoPA19-Bemol-2026-EliSilvaDoCarmo.pdf?expires_on=1785445163&amp;signature=vtcK2bh9fYMGgpgQgWhxwoY%2FlZDfa6VY0dvIo2fPy2o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3a34b841-1745-4596-bc96-5707bb3090b6/LaudoPA19-Bemol-2026-EliSilvaDoCarmo.pdf?expires_on=1785445264&amp;signature=zNAXSbZIj4ctA4iwkA%2FPZI0ua2lOIuiGvUJHHt%2FfeHw%3D</t>
         </is>
       </c>
       <c r="V127">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/39bcef5c-d16c-4530-8807-f44667684a79/BEMOL-PV077-ELIANASANTOSDASILVAMACEDO.pdf?expires_on=1785445163&amp;signature=MgTCeGnhjfg5X8bHMcxGDKg6G0nsnKM0NMjZKK6hiwc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/39bcef5c-d16c-4530-8807-f44667684a79/BEMOL-PV077-ELIANASANTOSDASILVAMACEDO.pdf?expires_on=1785445264&amp;signature=1xNJS8KtF931PVMHwRpn14Q4wabZEH5qsIm4RW4ZMv8%3D</t>
         </is>
       </c>
       <c r="V128">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/369aee73-674f-4435-954e-6d24f1e0907f/Laudo49-Bemol-2026-ElianaVieiraDaSilvacorrigido.pdf?expires_on=1785445163&amp;signature=%2FlKVWaav%2B1Y6QH%2BqSay7BfMIhJat2Oe2ZTSULHXw1VI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/369aee73-674f-4435-954e-6d24f1e0907f/Laudo49-Bemol-2026-ElianaVieiraDaSilvacorrigido.pdf?expires_on=1785445264&amp;signature=zfhF3Wd152D7RiwcAOtwHkNw2HCisR%2Fp29d72CXISSg%3D</t>
         </is>
       </c>
       <c r="V129">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0c43cc50-9a5b-40e2-bc16-680923cf6563/BEMOL-PV066-ELIASBALDOINOTORRESCALVALCANTE.pdf?expires_on=1785445163&amp;signature=I2ELgAeBBaFfDi4%2FEaRGS9O74tk6SMb1edKcXhkskcQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0c43cc50-9a5b-40e2-bc16-680923cf6563/BEMOL-PV066-ELIASBALDOINOTORRESCALVALCANTE.pdf?expires_on=1785445264&amp;signature=jMIxwsm30Ghw52DygJUu0Ydj6lG7J0HDjY03ZL6e66A%3D</t>
         </is>
       </c>
       <c r="V130">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/80e69f1b-0185-4993-8a09-a32d65e2c2f7/LaudoP22-Bemol-2026-ElielChagasdeSantana_signed.pdf?expires_on=1785445163&amp;signature=0mmBx4jS5S5BoypfdEhtW1gBN8mJw33hNnXnWtHBYeA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/80e69f1b-0185-4993-8a09-a32d65e2c2f7/LaudoP22-Bemol-2026-ElielChagasdeSantana_signed.pdf?expires_on=1785445264&amp;signature=4fMper61aus3zgSksa5Ka5uNabYLDEPhNXeLzN5Aykk%3D</t>
         </is>
       </c>
       <c r="V131">
@@ -17639,7 +17639,7 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d6dc533a-da09-4dde-90c2-049ab7a07ee9/M27-2026-ELISANGELAajustado.pdf?expires_on=1785445163&amp;signature=uBwAJ8uWOe5piSYMvoHVbT7OaXwKawx6JKgI%2BMizllg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d6dc533a-da09-4dde-90c2-049ab7a07ee9/M27-2026-ELISANGELAajustado.pdf?expires_on=1785445264&amp;signature=SVkMsUNhg1xeB23EIuBliV7FnYVOy2JkdbgaKvNJ00U%3D</t>
         </is>
       </c>
       <c r="V132">
@@ -17763,7 +17763,7 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/22e5c65c-adf6-43af-b03d-c4be6d2b5f27/Laudo168-Bemol-2026-ElivelttonDaSilvaMoura-Assinado.pdf?expires_on=1785445163&amp;signature=hobqGqnYf6fG3pWdcgd6Jnmvxd6WxWmGUTqbo5%2FofO4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/22e5c65c-adf6-43af-b03d-c4be6d2b5f27/Laudo168-Bemol-2026-ElivelttonDaSilvaMoura-Assinado.pdf?expires_on=1785445264&amp;signature=lBn54bFrlse14qiB2uAVkK%2FgQ9O%2FAZTM6tBoHFOmj%2B4%3D</t>
         </is>
       </c>
       <c r="V133">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d93add82-377b-4bf6-8170-0f2fd94a7b95/PA04-2026-ELIZETEajustado.pdf?expires_on=1785445163&amp;signature=OhdZu34YCI6iaR4jEEwdAut27e54Z%2FHodqa4wpXMq2s%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d93add82-377b-4bf6-8170-0f2fd94a7b95/PA04-2026-ELIZETEajustado.pdf?expires_on=1785445264&amp;signature=8kuyRDaY%2F7nQLA5FgRTKanqbajpMwAFwxNyndqCxle4%3D</t>
         </is>
       </c>
       <c r="V134">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/071c0338-2e41-4690-96cc-b4f54cb42db6/Laudo07-Bemol-2026-EliziaDoSocorroDeSouzaCarvalho-Assinado1.pdf?expires_on=1785445163&amp;signature=QLKcx5stp2zWpGc7Y4LrxMUeQGVVMZMHqRYvTfKwEaw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/071c0338-2e41-4690-96cc-b4f54cb42db6/Laudo07-Bemol-2026-EliziaDoSocorroDeSouzaCarvalho-Assinado1.pdf?expires_on=1785445264&amp;signature=PkFl50%2FTMK2OXlLtm2OxU1xx%2Bqi43oJbztm3c9P%2FphM%3D</t>
         </is>
       </c>
       <c r="V135">
@@ -18159,7 +18159,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/bb092190-5c08-4b45-a55a-a363d3a978f6/LAUDOEMIRRUIZ.pdf?expires_on=1785445163&amp;signature=SO3ct41Nsg6diwMIMl%2BosoTSXs3xe9IVHK1d%2FBSfBBk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/bb092190-5c08-4b45-a55a-a363d3a978f6/LAUDOEMIRRUIZ.pdf?expires_on=1785445264&amp;signature=NWHRhq6tl3nskAws6AopS5nE0Y6dQgwNkySb0TgRokw%3D</t>
         </is>
       </c>
       <c r="V136">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a8cfb96f-e29c-44a8-ace1-c0b45bef5640/Laudo15-Bemol-2026-EricaMarciaBezerradeAraujoBastos-Assinadocorrigido.pdf?expires_on=1785445163&amp;signature=OImsJ4qWSQl1MUEIpuhfeQIUpLCxWRWwOeHnmY4n84c%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a8cfb96f-e29c-44a8-ace1-c0b45bef5640/Laudo15-Bemol-2026-EricaMarciaBezerradeAraujoBastos-Assinadocorrigido.pdf?expires_on=1785445264&amp;signature=DuGL00XTUsLC3nLnZIC3Bln4zres%2FKDF0VNNaJNMICk%3D</t>
         </is>
       </c>
       <c r="V137">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5518488a-e8de-410c-8b82-a36223ef2561/LaudoB41-2026-BEMOL-ERICKFABIANODEALMEIDACHAGAS.pdf?expires_on=1785445163&amp;signature=hdLnCPu87iHE5r61ZBEeuMKe2XZ4fHTDt0hnLhnzyWk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5518488a-e8de-410c-8b82-a36223ef2561/LaudoB41-2026-BEMOL-ERICKFABIANODEALMEIDACHAGAS.pdf?expires_on=1785445264&amp;signature=ByGo8lPUpnyiEgmsFDB4rTHUCcXrVYdkpxyUuqs3Bf8%3D</t>
         </is>
       </c>
       <c r="V138">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/553196f4-a964-47c8-a3e0-509a649bb7d5/Laudo_AC_30-2026_-_ERINALDA_FERREIRA_DA_SILVA_assinado.pdf?expires_on=1785445163&amp;signature=ZcLY8CN5LSA0SWr3pDJOF987R%2FOOv4jt0DwZIikrBg8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/553196f4-a964-47c8-a3e0-509a649bb7d5/Laudo_AC_30-2026_-_ERINALDA_FERREIRA_DA_SILVA_assinado.pdf?expires_on=1785445264&amp;signature=C7RsFWtEFr5zIU5nn2gr%2BHFGNcXcacCnd6hod%2BKAEH4%3D</t>
         </is>
       </c>
       <c r="V139">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d62f8ab1-5332-4111-a02b-84b41c4cd850/Laudo132-Bemol-2026-ErismarDaSilvaFeitoza.pdf?expires_on=1785445163&amp;signature=bi8hKv8ezciz16yyTmYChd9Gd3XmnxJD%2B2UdT09SJdg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d62f8ab1-5332-4111-a02b-84b41c4cd850/Laudo132-Bemol-2026-ErismarDaSilvaFeitoza.pdf?expires_on=1785445264&amp;signature=LaPIv%2Fvx9vG6SoKutPEYCo70OWwn02I%2FCAg9Mrrofnw%3D</t>
         </is>
       </c>
       <c r="V140">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6261012a-89c8-4106-add5-9a22f7e2887a/Laudo39-Bemol-2026-EritondaCruzDaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=96YmyzbtWkev3dg98CfI8BEfegS5brH793ks7iIUyPI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6261012a-89c8-4106-add5-9a22f7e2887a/Laudo39-Bemol-2026-EritondaCruzDaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=biKoOyQcA84VoM7UGbZQRsPSsAWH54foeQ7UlBmPBSE%3D</t>
         </is>
       </c>
       <c r="V141">
@@ -18933,7 +18933,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9c6d0dc3-6284-4cde-a28c-51bfe9f145eb/Laudo110-Bemol-2026-ErnaneSargesCabral-Assinado.pdf?expires_on=1785445163&amp;signature=KIpfvW9bR9AZLHNE3vnvEB7jvYjV7a9Pp1NJT7h7YRs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9c6d0dc3-6284-4cde-a28c-51bfe9f145eb/Laudo110-Bemol-2026-ErnaneSargesCabral-Assinado.pdf?expires_on=1785445264&amp;signature=TU0xtMZJV6KH5o5c0K%2Bex7l3wXWp0SZs0yctFtzpGlU%3D</t>
         </is>
       </c>
       <c r="V142">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5b350b88-dafc-489d-8c5b-0a187ec4efb1/Laudo40-Bemol-2026-EugeniaOlimpioMenezes-Assinado.pdf?expires_on=1785445163&amp;signature=gB%2FtRO5yur%2BmPqIumA9Fn7IUfsR6sX9ne1VFwIb1c%2BQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5b350b88-dafc-489d-8c5b-0a187ec4efb1/Laudo40-Bemol-2026-EugeniaOlimpioMenezes-Assinado.pdf?expires_on=1785445264&amp;signature=IcVyDDKDBXELPGYNqWW%2FdUyFVQUIU7P9vDUpiZGhazM%3D</t>
         </is>
       </c>
       <c r="V143">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/de6e3d6f-1327-44f0-b564-dde96154d9d7/MP2-2026-EVAIajustado.pdf?expires_on=1785445163&amp;signature=rtyCGAAsAIVP9houLXRvOi6v2eF04LT1dDiVaCs%2Bv%2FM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/de6e3d6f-1327-44f0-b564-dde96154d9d7/MP2-2026-EVAIajustado.pdf?expires_on=1785445264&amp;signature=TwcgXv%2Bg1luM0%2F12OdDgidJDqXAHBJnzamTux38xy9g%3D</t>
         </is>
       </c>
       <c r="V144">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2eb5ac99-11bc-4b0e-9c5f-119846bc5aa2/Laudo185-Bemol-2026-EvandoCamurcaDoNascimento.pdf?expires_on=1785445163&amp;signature=c060prNXtDGv6UI%2FPs8NXXYnVJ79qBhfXuplQW929TM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2eb5ac99-11bc-4b0e-9c5f-119846bc5aa2/Laudo185-Bemol-2026-EvandoCamurcaDoNascimento.pdf?expires_on=1785445264&amp;signature=Ce%2Fw4s4ihxpUHrB%2Bsvyi88AHN8ZNnfFaEcePSCIP1NQ%3D</t>
         </is>
       </c>
       <c r="V145">
@@ -19453,7 +19453,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b46c9cdd-afef-4d37-bd38-04b70c1aced7/Laudo158-Bemol-2026-FabianeDaCostaMatos.pdf?expires_on=1785445163&amp;signature=LNlgC6P%2FNuI20Egh3ax7sER8SqPCXMjIsYD9m37RucI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b46c9cdd-afef-4d37-bd38-04b70c1aced7/Laudo158-Bemol-2026-FabianeDaCostaMatos.pdf?expires_on=1785445264&amp;signature=lPl%2FYAw3n%2Fa%2BIIXbHaPM9AHr0If6p6T45ILJlWAQ5dw%3D</t>
         </is>
       </c>
       <c r="V146">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fded754d-f2ac-4c93-9387-04ab8656c650/Laudo33-Bemol-2026-FabioCesarPimentaGoulart-Assinado.pdf?expires_on=1785445163&amp;signature=ln8GgulzwqGZYPzqHHxLCmzyPEsFzHN%2B81ovGDr5GLM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fded754d-f2ac-4c93-9387-04ab8656c650/Laudo33-Bemol-2026-FabioCesarPimentaGoulart-Assinado.pdf?expires_on=1785445264&amp;signature=Tx%2FZEYPuOzmMwEPjbDuwnzW9nsuKrwIv3i3dE3h9LYo%3D</t>
         </is>
       </c>
       <c r="V147">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c58213ad-7761-4ae6-9870-546591f93a06/LAUDOFABIOLAcorrigido.pdf?expires_on=1785445163&amp;signature=3R%2FGU1GfRdgcJXYbtAMRa7L2tVGBMPOn2CvQuQbuFfM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c58213ad-7761-4ae6-9870-546591f93a06/LAUDOFABIOLAcorrigido.pdf?expires_on=1785445264&amp;signature=cLowpHXUWf06DgZLcEVRYSJJfm6a78l0sPqLSOupCHs%3D</t>
         </is>
       </c>
       <c r="V148">
@@ -19859,7 +19859,7 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2a3a19e0-19b0-4095-bf3f-8a7be5a4c3ab/LaudoB129-2025-BEMOL-FABRICIAFELIXBEZERRA.pdf?expires_on=1785445163&amp;signature=FGRjJOHXOCJ2lZXOstduCsabf3vyvBg6IDCLXdGU5Fs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2a3a19e0-19b0-4095-bf3f-8a7be5a4c3ab/LaudoB129-2025-BEMOL-FABRICIAFELIXBEZERRA.pdf?expires_on=1785445264&amp;signature=hgWmnGlKQpOTU6oJlfUYoOowAU911dsFnTkhAuK7fic%3D</t>
         </is>
       </c>
       <c r="V149">
@@ -20009,7 +20009,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fbd53a6d-2555-48b3-a7eb-db3130ed48eb/LaudoA07-Bemol-2026-FabricioBrazDeOliveira_signed.pdf?expires_on=1785445163&amp;signature=nAzVQusiHcKtz%2BmhX4x4Hm6hoQhpv3PXFTOC3fN00aA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fbd53a6d-2555-48b3-a7eb-db3130ed48eb/LaudoA07-Bemol-2026-FabricioBrazDeOliveira_signed.pdf?expires_on=1785445264&amp;signature=j6nqDN0iaQn8fcISEtDmCAkFkgBGx%2F3CjeW20S9MHxc%3D</t>
         </is>
       </c>
       <c r="V150">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/17b79224-a2d0-4ed1-bccd-8be40d372c0c/LaudoPA02-Bemol-2026-FatimaBentesDeSouza-Assinado.pdf?expires_on=1785445163&amp;signature=HJ0DpxvzxeR9BNcO%2BT5gKLfNQpiBwsrZWl6%2FXmglyEA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/17b79224-a2d0-4ed1-bccd-8be40d372c0c/LaudoPA02-Bemol-2026-FatimaBentesDeSouza-Assinado.pdf?expires_on=1785445264&amp;signature=2SxwmpAfUj2XZ%2BdeFFbzT95cdtujCHIzmCY71C8Oq1Q%3D</t>
         </is>
       </c>
       <c r="V151">
@@ -20265,7 +20265,7 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e38cf222-5503-4e97-bbef-238ef7056e68/LaudoB10-2026-BEMOL-FAUEZFLAVIOPAIOLA_2.pdf?expires_on=1785445163&amp;signature=h4NJu%2FQSSPDNvT6z7GzoALonvW0mv7m%2FqHQzP02mE7o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e38cf222-5503-4e97-bbef-238ef7056e68/LaudoB10-2026-BEMOL-FAUEZFLAVIOPAIOLA_2.pdf?expires_on=1785445264&amp;signature=WB18T%2Bj4fm37k8Qr88Jx7WE%2BRrtXHBOOmeO6HKd2C78%3D</t>
         </is>
       </c>
       <c r="V152">
@@ -20402,7 +20402,7 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cc113fdd-7aca-4e34-82ce-e8009e845604/Laudo46-Bemol-2026-FernandaPrestesDeLima-Assinado.pdf?expires_on=1785445163&amp;signature=UllhqkYGRnKMpGGircdnhphoejXj4aNPtBwph7bLjMM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cc113fdd-7aca-4e34-82ce-e8009e845604/Laudo46-Bemol-2026-FernandaPrestesDeLima-Assinado.pdf?expires_on=1785445264&amp;signature=zPc0kYxQ5xMF1hIiHEZJXmsEBT8Shsugi5OLb1fVSXg%3D</t>
         </is>
       </c>
       <c r="V153">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e0f0ad2f-9e01-417c-a8f9-c1ca243eb234/LaudoJP05-Bemol-2026-ClaudiaBatistaDaCosta_signed.pdf?expires_on=1785445163&amp;signature=p0v2ZxGlgj%2BZ4TCd3p9M0S0ZpAOL6VJBdXT3%2FivUgLg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e0f0ad2f-9e01-417c-a8f9-c1ca243eb234/LaudoJP05-Bemol-2026-ClaudiaBatistaDaCosta_signed.pdf?expires_on=1785445264&amp;signature=1xwtVLWm8hxxU%2BXFDymc9AnuiWroBS7wPkpKfzkzfiM%3D</t>
         </is>
       </c>
       <c r="V154">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/76f476fd-df6d-46b3-b38f-f6dd09998f3f/LAUDOFILEMON.pdf?expires_on=1785445163&amp;signature=gerISPGaNbpGX%2FDuMsPyI2Yr53uG5YmurirXOYBgZwA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/76f476fd-df6d-46b3-b38f-f6dd09998f3f/LAUDOFILEMON.pdf?expires_on=1785445264&amp;signature=G8ecT0ZAW2FopypaeFmNiJ1rj6J%2FespfhaQpx1x197s%3D</t>
         </is>
       </c>
       <c r="V155">
@@ -20773,7 +20773,7 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/91d22aa8-c9b2-4d21-b3bd-d33060fc5321/Laudo116-Bemol-2026-FelipeCelaMoraesFilho-Assinado.pdf?expires_on=1785445163&amp;signature=79pIEV69AQBnzJXcbjsFI9DSPJ19dfWmVEN28avqGgw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/91d22aa8-c9b2-4d21-b3bd-d33060fc5321/Laudo116-Bemol-2026-FelipeCelaMoraesFilho-Assinado.pdf?expires_on=1785445264&amp;signature=qL%2FN74Pa4T35IWagaGYhorzdO23pJn7fWcIwezyJ4q8%3D</t>
         </is>
       </c>
       <c r="V156">
@@ -20898,7 +20898,7 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7b14bcf2-d078-42ca-9a36-bc05ae8b7690/Laudo61-Bemol-2026-FlaviaQueirozdaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=VM%2BPM3D%2BDQzU5xwnZtuX0hn44QAn5qE0cCEXlpmOwZY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7b14bcf2-d078-42ca-9a36-bc05ae8b7690/Laudo61-Bemol-2026-FlaviaQueirozdaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=RcND7XDnGLRQtMtfgKahvuQOvHC%2Bcai%2BtKOejjhXqLc%3D</t>
         </is>
       </c>
       <c r="V157">
@@ -21035,7 +21035,7 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/30219338-9c6b-4770-b8ea-27a5cbf60368/M18-2026-FLAVIO.pdf?expires_on=1785445163&amp;signature=JO7qTNZ07f%2FfHsO%2FukFdOVxoBc4nZp8r7x0QE5%2FDgWQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/30219338-9c6b-4770-b8ea-27a5cbf60368/M18-2026-FLAVIO.pdf?expires_on=1785445264&amp;signature=QlS7qxjkSGeKMIofLlTAYR3f2SDT%2FK4YjXziu0DXwqQ%3D</t>
         </is>
       </c>
       <c r="V158">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c10fe8dc-e55f-465e-b1ea-81d40b9e1233/Laudo89-Bemol-2026-FrancibertoBandeiraDaCosta-Assinado.pdf?expires_on=1785445163&amp;signature=%2BYw9rFQPzValEjNoVJFfSNY1FUUAYDRs18Omh2dGNdo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c10fe8dc-e55f-465e-b1ea-81d40b9e1233/Laudo89-Bemol-2026-FrancibertoBandeiraDaCosta-Assinado.pdf?expires_on=1785445264&amp;signature=2Bx%2BTW6JnmleFRFvJS5Dc1HkbRVlprxHnCVpdjjDfcw%3D</t>
         </is>
       </c>
       <c r="V159">
@@ -21295,7 +21295,7 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/aadac529-7fed-4e2d-bd52-b67b4f7726f3/BEMOL-JP035-FRANCIELYBATISTADEALMEIDA.pdf?expires_on=1785445163&amp;signature=yXt9Y9PU7MWtdoi1GTidHsCz8t60Xu1VhuaR%2F%2FNHXDU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/aadac529-7fed-4e2d-bd52-b67b4f7726f3/BEMOL-JP035-FRANCIELYBATISTADEALMEIDA.pdf?expires_on=1785445264&amp;signature=CiJeASGtp3H%2B8BvgBCq%2BAras7cMgrPmutHdcRnP1m%2FQ%3D</t>
         </is>
       </c>
       <c r="V160">
@@ -21427,7 +21427,7 @@
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/696900ba-642e-4a87-ac33-a5a2122e6553/Laudo177-Bemol-2026-FrancimaraCordeiroCelada.pdf?expires_on=1785445163&amp;signature=MY2DtyIuJ9oBRLK7RG3Xs3f343R4x9F1VuL0f0sZpyg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/696900ba-642e-4a87-ac33-a5a2122e6553/Laudo177-Bemol-2026-FrancimaraCordeiroCelada.pdf?expires_on=1785445264&amp;signature=1OLtFMR0TfSKrCqbah%2F4S9ChttUbFXT9qFMwiEqYLdk%3D</t>
         </is>
       </c>
       <c r="V161">
@@ -21550,7 +21550,7 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a285153-7890-4129-bd45-e2b8b03d378a/Laudo24-Bemol-2026-FranciscaCostaDoAmaral-Assinado.pdf?expires_on=1785445163&amp;signature=U5RlvBxG%2BH3%2B1bKp2neP2wbXxdwOR8gkwz3V8yZHLu8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a285153-7890-4129-bd45-e2b8b03d378a/Laudo24-Bemol-2026-FranciscaCostaDoAmaral-Assinado.pdf?expires_on=1785445264&amp;signature=H1g5AfvBuTPa6UJa%2F2LucN3TE0PBaqJ0%2FGirzmQw%2B4s%3D</t>
         </is>
       </c>
       <c r="V162">
@@ -21689,7 +21689,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/59088886-f0ae-4236-8b1a-e1ffe17e49fd/LaudoB38-2026-BEMOL-FRANCISCADASCHAGASSILVADOSSANTOS.pdf?expires_on=1785445163&amp;signature=83d7rHnmoKmK13tyYsUCV%2BPg8fhzHWW10P98IaOkhbI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/59088886-f0ae-4236-8b1a-e1ffe17e49fd/LaudoB38-2026-BEMOL-FRANCISCADASCHAGASSILVADOSSANTOS.pdf?expires_on=1785445264&amp;signature=klob2s%2F7fvck0LQmyyX8ezgKcqUDbRAthAmO8Q8hMW4%3D</t>
         </is>
       </c>
       <c r="V163">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7f9fefc9-e1ae-43f6-9d90-569732f82957/LaudoB56-2026-BEMOL-FranciscaVianaCabral.pdf?expires_on=1785445163&amp;signature=q7JWVjTdQIkjf%2BD88JcMnSwcBR5m9n6REfwNFFVqJcM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7f9fefc9-e1ae-43f6-9d90-569732f82957/LaudoB56-2026-BEMOL-FranciscaVianaCabral.pdf?expires_on=1785445264&amp;signature=4cBpMiU%2FFEAIIwhbYbZHmManiAUPv7%2FP%2FLbAl0RFbM0%3D</t>
         </is>
       </c>
       <c r="V164">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/46015ed7-e8ee-4fcf-81c2-dce488b66f97/LaudoB37-2026-BEMOL-FRANCISCOALVESDECARVALHOFILHO.pdf?expires_on=1785445163&amp;signature=Nou4Ne%2FaRR%2BAWzEkg0xjaaJd730S4K9eHMygatQNlvI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/46015ed7-e8ee-4fcf-81c2-dce488b66f97/LaudoB37-2026-BEMOL-FRANCISCOALVESDECARVALHOFILHO.pdf?expires_on=1785445264&amp;signature=zgj3MGT6nlA0oBHvypraht%2B%2BfVI5Y5jdowPaKHdRxdE%3D</t>
         </is>
       </c>
       <c r="V165">
@@ -22083,7 +22083,7 @@
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e6d71bf1-06a5-438c-88d3-a62e47e95a34/Laudo48-Bemol-2026-FranciscoBandeiraPrestes-Assinado.pdf?expires_on=1785445163&amp;signature=LdSBQhTvIwrP2yfptoI5R%2Bs5skrJpJx3hWBDqgKFn8A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e6d71bf1-06a5-438c-88d3-a62e47e95a34/Laudo48-Bemol-2026-FranciscoBandeiraPrestes-Assinado.pdf?expires_on=1785445264&amp;signature=Z8V2G5MEsHLsIIeD7SijZn6qFlvTCx5qUi%2Frezk6Ac0%3D</t>
         </is>
       </c>
       <c r="V166">
@@ -22206,7 +22206,7 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/404a2496-5d75-47a3-8332-0a14a23dd08a/LaudoP21-Bemol-2026-FranciscoDasChagasRodrigues_signed.pdf?expires_on=1785445163&amp;signature=We3mNwmMWZ3MMBdVc4pFfKZ2ODS4U66kgpeE4YJusdg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/404a2496-5d75-47a3-8332-0a14a23dd08a/LaudoP21-Bemol-2026-FranciscoDasChagasRodrigues_signed.pdf?expires_on=1785445264&amp;signature=RLWBpE1Xft7QOwp02CaqFpTNrcunNGjSRHuMT1GF2V0%3D</t>
         </is>
       </c>
       <c r="V167">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/25200ae2-be9b-48e6-b520-802786df80dc/B135-2024-BEMOL-FRANCISCODEASSISDACONCEIO.pdf?expires_on=1785445163&amp;signature=IswX4RmODsOOglk0d%2FdW6uV0WHUDmj4vbCVK4ZtfCOc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/25200ae2-be9b-48e6-b520-802786df80dc/B135-2024-BEMOL-FRANCISCODEASSISDACONCEIO.pdf?expires_on=1785445264&amp;signature=Fp%2B5od2rYJY7Z33VAO08Pqp0HJgoN0qz5ubySZ2ixe0%3D</t>
         </is>
       </c>
       <c r="V168">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/344fb1c8-16f0-4427-94fa-0961e47993c5/BEMOL-PV075-FRANCISCOMAIABATISTA.pdf?expires_on=1785445163&amp;signature=Z2FNEr%2BeZlQFgt2JAiGItqlW26tX0UtBOLcpBlvCv00%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/344fb1c8-16f0-4427-94fa-0961e47993c5/BEMOL-PV075-FRANCISCOMAIABATISTA.pdf?expires_on=1785445264&amp;signature=6M0lWuyTetosIA08q08Hi85neW%2FLZ6MFKAb9UYu6Uck%3D</t>
         </is>
       </c>
       <c r="V169">
@@ -22573,7 +22573,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/388ec1b4-83f3-441c-967f-ceb7668fb045/LAUDOFRANCISCODONASCIMENTODASILVA.pdf?expires_on=1785445163&amp;signature=GrGzr%2FHklEDw2R%2Bh3fGR8y7UgWxAmPSY5VBFDB70L1U%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/388ec1b4-83f3-441c-967f-ceb7668fb045/LAUDOFRANCISCODONASCIMENTODASILVA.pdf?expires_on=1785445264&amp;signature=CAxkSmyGiklG4vKWsGEpBCX4j28eqo6Aspp0meSkbAE%3D</t>
         </is>
       </c>
       <c r="V170">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9fcbba4c-0bc2-4661-acce-3c1f7cf014e4/Laudo112-Bemol-2026-FranciscoPereiraChaul-Assinado.pdf?expires_on=1785445163&amp;signature=MHuB9WmwzA1so%2F7eOWfSqq7uso6yLAU8lrc9xe0Lft0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9fcbba4c-0bc2-4661-acce-3c1f7cf014e4/Laudo112-Bemol-2026-FranciscoPereiraChaul-Assinado.pdf?expires_on=1785445264&amp;signature=dbWZq2EEBHfutbToLU%2Ffa43FZhkcxZtos0Wf%2Baf1vt4%3D</t>
         </is>
       </c>
       <c r="V171">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f5ec4f52-4ff3-4961-a180-72f6941834e9/franciscoregilsoncorrigido.pdf?expires_on=1785445163&amp;signature=PiJca%2Bync5jQb4ifRw%2Fv3apDA%2B%2BmkSZXWDt6KWLY2tQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f5ec4f52-4ff3-4961-a180-72f6941834e9/franciscoregilsoncorrigido.pdf?expires_on=1785445264&amp;signature=E6xhj0%2ByOktY1uCn%2Bye47WN1uH%2BLgXU2oXMjEOIIcrE%3D</t>
         </is>
       </c>
       <c r="V172">
@@ -22983,7 +22983,7 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9e0c7418-7661-4dd8-91d2-8a739caee94f/Laudo25-Bemol-2026-FrankChavesDeAraujo-Assinado.pdf?expires_on=1785445163&amp;signature=O%2FJSG80Zvtw8hZUp2xcWshVj9X%2BD6rPbI1JC601e7rg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9e0c7418-7661-4dd8-91d2-8a739caee94f/Laudo25-Bemol-2026-FrankChavesDeAraujo-Assinado.pdf?expires_on=1785445264&amp;signature=xe6usH08HpUD1mvbocdJm9QHPbkpTdf3J%2B%2Fh2UKFJc4%3D</t>
         </is>
       </c>
       <c r="V173">
@@ -23115,7 +23115,7 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7d625810-a63c-4e31-b581-22989af9a8c9/LAUDOFRANKLINcorrigido.pdf?expires_on=1785445163&amp;signature=5Dcj%2BkehT%2FwRJVMMCsa%2FrQNG3SNvrYIfsL5P8S32tag%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7d625810-a63c-4e31-b581-22989af9a8c9/LAUDOFRANKLINcorrigido.pdf?expires_on=1785445264&amp;signature=kIXkhfryLqffj9kdgfkCN2imFor58vT5%2Bfl3bMQbSNA%3D</t>
         </is>
       </c>
       <c r="V174">
@@ -23243,7 +23243,7 @@
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0c8e504e-71a8-4d99-a84c-820633f6f537/Laudo149-Bemol-2026-GabrielaOliveiraDeSouza.pdf?expires_on=1785445163&amp;signature=msQf0kehVY4m7WgvzVclnI1vsSSrp24URn0JG5C4ZhA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0c8e504e-71a8-4d99-a84c-820633f6f537/Laudo149-Bemol-2026-GabrielaOliveiraDeSouza.pdf?expires_on=1785445264&amp;signature=xvAYXYNXlWn%2B3OPrhE6oZsfwmbFvul23BhoXaCb%2Fxyg%3D</t>
         </is>
       </c>
       <c r="V175">
@@ -23361,7 +23361,7 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4853fdf8-b4c6-47a8-a2c6-a376e864c263/Laudo212-Bemol-2026-GebsAmorimDaDilva-Assinado.pdf?expires_on=1785445163&amp;signature=bgbacoejymYhcmc2mmNpv08vTQkTd%2ByJRW3KDdFsp%2B0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4853fdf8-b4c6-47a8-a2c6-a376e864c263/Laudo212-Bemol-2026-GebsAmorimDaDilva-Assinado.pdf?expires_on=1785445264&amp;signature=S3%2B8HIl5m%2BSWxYPoZ6cT4Q9RejNssY8khqJVH4gdOl8%3D</t>
         </is>
       </c>
       <c r="V176">
@@ -23482,7 +23482,7 @@
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/45997a27-288e-4063-a9cb-2c25e998c9ea/LAUDOGERSON.pdf?expires_on=1785445163&amp;signature=Pufo37APuHlcBmIMNvPqCdIpqjPgA3kxXjbUTA4%2FmLI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/45997a27-288e-4063-a9cb-2c25e998c9ea/LAUDOGERSON.pdf?expires_on=1785445264&amp;signature=y7vr5sNOGeGZrl2JJzsiRR5RqZqONABMe%2BfLz5%2F%2BVb0%3D</t>
         </is>
       </c>
       <c r="V177">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a3800c1e-5776-499b-aa65-72bc5d5c7e84/LaudoB55-2026-BEMOL-GERVANIADOSREISRIBEIROFRANCA.pdf?expires_on=1785445163&amp;signature=oqY3Q%2F8vuHb2KbjcUOVW%2F6xvhJ17yry5PNJgbIixp5A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a3800c1e-5776-499b-aa65-72bc5d5c7e84/LaudoB55-2026-BEMOL-GERVANIADOSREISRIBEIROFRANCA.pdf?expires_on=1785445264&amp;signature=uzJPhHWrpf9CmV4KeDbhwrz6TXNADkB02jBRP7MuB3I%3D</t>
         </is>
       </c>
       <c r="V178">
@@ -23756,7 +23756,7 @@
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/acacdca6-3cbd-4beb-8e6a-550a96cd4457/Laudo06-Bemol-2026-GilbersonFigueiraBarbosa-Assinado.pdf?expires_on=1785445163&amp;signature=4Wge6AekCQVbJaX5HwlhuEFdTzHJALF464dEkVIknGE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/acacdca6-3cbd-4beb-8e6a-550a96cd4457/Laudo06-Bemol-2026-GilbersonFigueiraBarbosa-Assinado.pdf?expires_on=1785445264&amp;signature=V05H68S8AfWBLYdfAdirCCMyESVh7tohN%2F08S4tTNQw%3D</t>
         </is>
       </c>
       <c r="V179">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/985f7116-d23f-4aee-8607-12f7ae4f306e/BEMOL-PV064-GilbsonPereiradeMorais.pdf?expires_on=1785445163&amp;signature=K0e9mHxnRYK77QIGZ3KY00sHdXgIIryd7Dq%2BZRp9iWE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/985f7116-d23f-4aee-8607-12f7ae4f306e/BEMOL-PV064-GilbsonPereiradeMorais.pdf?expires_on=1785445264&amp;signature=yjaWA5xmshH8qMyV%2By1thN1WIAvLbMkg3zJu8oLuaMM%3D</t>
         </is>
       </c>
       <c r="V180">
@@ -24050,7 +24050,7 @@
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e20bd625-bdff-49a2-982c-0f83256d23d2/Laudo70-Bemol-2026-GilmaraBrasilDeSeixas-Assinado.pdf?expires_on=1785445163&amp;signature=fHO0gZBTxWlHPbHSfVHKi0RBs08vUp4T%2FmRQBLp1Ji8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e20bd625-bdff-49a2-982c-0f83256d23d2/Laudo70-Bemol-2026-GilmaraBrasilDeSeixas-Assinado.pdf?expires_on=1785445264&amp;signature=9f9YjvSjuteQn6Zj2jV0dv5bSejgFEZ0Ip6cLLAOqZQ%3D</t>
         </is>
       </c>
       <c r="V181">
@@ -24190,7 +24190,7 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1187e87b-ca2a-4edf-a915-c1e1bf6ac0a3/Laudo148-Bemol-2026-GiovannaOliveiradosSantos.pdf?expires_on=1785445163&amp;signature=bzExMkKztqrapAns64899VZFxTSEas2rGjyh2RzCnjc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1187e87b-ca2a-4edf-a915-c1e1bf6ac0a3/Laudo148-Bemol-2026-GiovannaOliveiradosSantos.pdf?expires_on=1785445264&amp;signature=MAsTg8NFvcfGdBvcVAyyFtFJ01XJhN5FUPMpIg0NbmA%3D</t>
         </is>
       </c>
       <c r="V182">
@@ -24327,7 +24327,7 @@
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7dc6bd5c-fe1c-4d6b-a0ef-77e8ad596c6e/LaudoRVR02-Bemol-2026-GiseleSilvaDeLima-Assinado.pdf?expires_on=1785445163&amp;signature=%2FGKAExWhG9%2B6UcwNbcef1WRV0IGICLSlAla6or2ZyyI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7dc6bd5c-fe1c-4d6b-a0ef-77e8ad596c6e/LaudoRVR02-Bemol-2026-GiseleSilvaDeLima-Assinado.pdf?expires_on=1785445264&amp;signature=t2aUe9YiTCOABSCQOmKlyU2%2BE7p76DHgr7wsfHCGiUA%3D</t>
         </is>
       </c>
       <c r="V183">
@@ -24451,7 +24451,7 @@
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3a55d15e-7280-429f-8bb5-14c737b4a32e/BEMOL-AR023-GLAUCIADEARRUDADOMINGUEScorrigido.pdf?expires_on=1785445163&amp;signature=wQkUn%2FFhxChG8RYIldl56CPkYxm%2FG1Df1dNDBksOQMQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3a55d15e-7280-429f-8bb5-14c737b4a32e/BEMOL-AR023-GLAUCIADEARRUDADOMINGUEScorrigido.pdf?expires_on=1785445264&amp;signature=TrAYljzM9xZQIGIBhVrGnkKmDLIBYCw5ElAUX3yHe2Y%3D</t>
         </is>
       </c>
       <c r="V184">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f884ee63-cf10-4b1e-910d-ea270de3b978/LAUDOGLAUCO.pdf?expires_on=1785445163&amp;signature=648D4flidQf%2BdhGcHJJkSDuEAm994i6ljHzcLFysCWc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f884ee63-cf10-4b1e-910d-ea270de3b978/LAUDOGLAUCO.pdf?expires_on=1785445264&amp;signature=F3MuqbqzLOXv5dLL2BfGWbwxaKDORd3mCteodpowb4k%3D</t>
         </is>
       </c>
       <c r="V185">
@@ -24727,7 +24727,7 @@
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7bc1af1f-4d89-4f54-81c4-e0a39a33e154/Laudo153-Bemol-2026-GliciaCardosoDosSantosCabral-Assinado.pdf?expires_on=1785445163&amp;signature=a2xlTCyp7xcR%2BkkVJKaNX8pyVGTEjaE5hiHKVUl7mDc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7bc1af1f-4d89-4f54-81c4-e0a39a33e154/Laudo153-Bemol-2026-GliciaCardosoDosSantosCabral-Assinado.pdf?expires_on=1785445264&amp;signature=u5xeEAAzERNGOd1HwLB2K8xOFA5ZgyvCKEcRqOODs%2Bs%3D</t>
         </is>
       </c>
       <c r="V186">
@@ -24853,7 +24853,7 @@
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/91c2a256-8df1-47ab-9b2c-21e2da22aa03/LaudoITA07-Bemol-2026-GustavoDosSantosCorreaDeAzevedo-Assinado.pdf?expires_on=1785445163&amp;signature=oC2xKFOcDXtf%2FSMMiM8KgdwLavV13MUrVlVrx%2FPNsA4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/91c2a256-8df1-47ab-9b2c-21e2da22aa03/LaudoITA07-Bemol-2026-GustavoDosSantosCorreaDeAzevedo-Assinado.pdf?expires_on=1785445264&amp;signature=RICHWoUFmEfUAJBDmNlIMdbIk5X9cJ%2FyUGdhuozr3C4%3D</t>
         </is>
       </c>
       <c r="V187">
@@ -24985,7 +24985,7 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/84e417bf-6e94-401d-a747-8df0b5a6545d/Laudo_AC_10-2026_-_DEUSIMAR_MENEZES_DA_SILVA_assinado.pdf?expires_on=1785445163&amp;signature=HJMDEiFiyUW7OIdbVio1OO%2F4jj4ROivDR7MLDVuo34c%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/84e417bf-6e94-401d-a747-8df0b5a6545d/Laudo_AC_10-2026_-_DEUSIMAR_MENEZES_DA_SILVA_assinado.pdf?expires_on=1785445264&amp;signature=w9xZdp1XXL%2FN%2BrzqALMraIWIsr4oWGO1mox%2Fqpqx%2B6E%3D</t>
         </is>
       </c>
       <c r="V188">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f56afaf9-298b-4a77-a9f2-8187b2f0360a/LaudoP07-Bemol-2026-GustavoVianaDaSilva_signed.pdf?expires_on=1785445163&amp;signature=WYb9%2Fg1Nm0nV7Kxh5r05hiGW9vNRqaP4pPOH0KRZZV4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f56afaf9-298b-4a77-a9f2-8187b2f0360a/LaudoP07-Bemol-2026-GustavoVianaDaSilva_signed.pdf?expires_on=1785445264&amp;signature=nU5nuI69hzd9aiqnCqOrfJjrlgG7z6JT%2FcqSvKaC7r0%3D</t>
         </is>
       </c>
       <c r="V189">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7c23a673-4290-4995-9960-a4b6a6384bcf/Laudo350-Bemol-2025-HelanieCascaesAbreu-Assinado.pdf?expires_on=1785445163&amp;signature=bnUTMe4w2u2Ewlrodb%2Fnwz9c2Km3BpuZA87KiUP38QU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7c23a673-4290-4995-9960-a4b6a6384bcf/Laudo350-Bemol-2025-HelanieCascaesAbreu-Assinado.pdf?expires_on=1785445264&amp;signature=AhC44XbB2SSYEraepMwIq463WY9%2FKQPgKSQblOuVefs%3D</t>
         </is>
       </c>
       <c r="V190">
@@ -25403,7 +25403,7 @@
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a91aa31e-d799-4e5a-bcf3-891b838e0803/Laudo160-Bemol-2026-HeliodoroFonsecaGuerreiroFilho-Assinado.pdf?expires_on=1785445163&amp;signature=Uxn1aRKGheqPUtsKzNfS8%2FSAeWcRr0sSVlXw7xcwZwA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a91aa31e-d799-4e5a-bcf3-891b838e0803/Laudo160-Bemol-2026-HeliodoroFonsecaGuerreiroFilho-Assinado.pdf?expires_on=1785445264&amp;signature=%2BTnYtdnHdgrbLDUCqOb%2FO6VMxBjPguVqPEmKC24qnL4%3D</t>
         </is>
       </c>
       <c r="V191">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8844ac9a-59bb-4f2c-aff8-72fb3f9c9eeb/LaudoPA21-Bemol-2026-HernandesJesusdosSantos-Assinado.pdf?expires_on=1785445163&amp;signature=DJVoswYBv4MjQ9cjhcJtgr7FCQWGDSj1oHR5VbZJRjY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8844ac9a-59bb-4f2c-aff8-72fb3f9c9eeb/LaudoPA21-Bemol-2026-HernandesJesusdosSantos-Assinado.pdf?expires_on=1785445264&amp;signature=UTPHdmnf1q7h1Ag2a3Id8%2FIwIdrHFT3Rday2%2BBrO7xI%3D</t>
         </is>
       </c>
       <c r="V192">
@@ -25655,7 +25655,7 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ea1b9e95-887a-4691-a5b4-6bc283ebade6/Laudo140-Bemol-2026-IagoDaSilvaRodrigues.pdf?expires_on=1785445163&amp;signature=wOyq0%2FytRlleXRYND0Ym%2F9D1Ff4%2FZZGazzQDJsqurxo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ea1b9e95-887a-4691-a5b4-6bc283ebade6/Laudo140-Bemol-2026-IagoDaSilvaRodrigues.pdf?expires_on=1785445264&amp;signature=dOvNIhi%2B%2FCp5UFvdqZKEorAiVL3EMnBEs9y94cDhwz4%3D</t>
         </is>
       </c>
       <c r="V193">
@@ -25787,7 +25787,7 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a3957666-2105-4c3c-8ef9-39e77bc1dc39/LaudoA02-Bemol-2026-IaraDosSantosSchimanech_signed.pdf?expires_on=1785445163&amp;signature=ExdE%2BHKQFXsrzHCAlzFJa%2FRj7rdv3BBLtYVdo6RDIpw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a3957666-2105-4c3c-8ef9-39e77bc1dc39/LaudoA02-Bemol-2026-IaraDosSantosSchimanech_signed.pdf?expires_on=1785445264&amp;signature=QtIoVpkQT3GggcckRwjieI%2BBLiGB4zHr14lK3i9R1RY%3D</t>
         </is>
       </c>
       <c r="V194">
@@ -25910,7 +25910,7 @@
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/34f61018-bea2-4b9b-b81c-3f276e3c94f2/LaudoITA13-Bemol-2026-IdelfonsoMonteiroRibeiro.pdf?expires_on=1785445163&amp;signature=u8uc%2Bfatgyvvgjwvhj6Nq%2BMv%2F7jemOhK%2BcB3xAusVEk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/34f61018-bea2-4b9b-b81c-3f276e3c94f2/LaudoITA13-Bemol-2026-IdelfonsoMonteiroRibeiro.pdf?expires_on=1785445264&amp;signature=W%2FoYSLkZ3%2FvPrPwhXHoRScaIa2fNN3lNxYsxaO%2FTz3I%3D</t>
         </is>
       </c>
       <c r="V195">
@@ -26036,7 +26036,7 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c3f2997b-58e6-441e-bad9-6dd576d60062/LAUDOINEZ.pdf?expires_on=1785445163&amp;signature=sGFE%2Fs4rexkk97pPflQesZAHUSCFWjB%2BkCsa%2FSgcNIU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c3f2997b-58e6-441e-bad9-6dd576d60062/LAUDOINEZ.pdf?expires_on=1785445264&amp;signature=K1Cs8hszwXTQTeN2r6abFBtRWxs2KwOxuXmg8M4uqBE%3D</t>
         </is>
       </c>
       <c r="V196">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/adb8967f-721a-44b2-b57c-06dba882887a/Laudo67-Bemol-2026-IolandaBasilioBenevides-Assinado.pdf?expires_on=1785445163&amp;signature=dT6JZLXsxSGkVQ4sOtXrnH5qUZ%2FW8IhO6oJgoyIHwII%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/adb8967f-721a-44b2-b57c-06dba882887a/Laudo67-Bemol-2026-IolandaBasilioBenevides-Assinado.pdf?expires_on=1785445264&amp;signature=oGeVf3DmtUmRat6dk3fg7jg8EtUvLFsFsdk9AI2AZUo%3D</t>
         </is>
       </c>
       <c r="V197">
@@ -26299,7 +26299,7 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f283e60d-0fe6-4679-9509-fe8f620eac06/LaudoB6-2026-BEMOL-IRANCARNEIRODEMACEDO.pdf?expires_on=1785445163&amp;signature=yqwHOMe4do4eXL4Mf33beAG2Y%2B%2F7jX0r3uRZEcDrNbI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f283e60d-0fe6-4679-9509-fe8f620eac06/LaudoB6-2026-BEMOL-IRANCARNEIRODEMACEDO.pdf?expires_on=1785445264&amp;signature=v9m4FkNlkA8WQi%2F4wcSv7vTLPfADTZj4xw3%2Fo6bv6%2BE%3D</t>
         </is>
       </c>
       <c r="V198">
@@ -26436,7 +26436,7 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/057596ee-eb69-4dab-9a70-4c6bc66742b2/Laudo113-Bemol-2026-IraunaMaiconaBarrosdeCarvalho-Assinado.pdf?expires_on=1785445163&amp;signature=CvJVebeKnWUWECvUfYOZmlB8Twx69izgE2cZ0ub8sEw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/057596ee-eb69-4dab-9a70-4c6bc66742b2/Laudo113-Bemol-2026-IraunaMaiconaBarrosdeCarvalho-Assinado.pdf?expires_on=1785445264&amp;signature=viYXxstITsYICoR0mAZ5oY8hJujnLdAV9dHaI0MGidg%3D</t>
         </is>
       </c>
       <c r="V199">
@@ -26573,7 +26573,7 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/021e50b4-e24d-4ebb-8d0b-11127fb4eb05/RelatriodeValordeRefernciaRVR01-Bemol-2026-IrisFrotaDaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=lrzLXrn7vis7o9UX8GNX7w%2FiYbBDlgyhLXY7Qp388Xw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/021e50b4-e24d-4ebb-8d0b-11127fb4eb05/RelatriodeValordeRefernciaRVR01-Bemol-2026-IrisFrotaDaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=cd%2F0als4XTlEkzsrJR9plgj10taM2uF7SonhVzXemPg%3D</t>
         </is>
       </c>
       <c r="V200">
@@ -26712,7 +26712,7 @@
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/974e6369-461f-4ecf-960e-99a4e3c5062d/LaudoR01-2026-BEMOL-ISAIASARAUJOCRUZ_2corrigido.pdf?expires_on=1785445163&amp;signature=RIKMCH1m18qCFD3g6lwW0qcXBVGHFG6dEcY3fLpvrKw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/974e6369-461f-4ecf-960e-99a4e3c5062d/LaudoR01-2026-BEMOL-ISAIASARAUJOCRUZ_2corrigido.pdf?expires_on=1785445264&amp;signature=Ph3rEPXBoLGM6opB2wTwfrQg6ZGWv6MeVk2K0RKcNRs%3D</t>
         </is>
       </c>
       <c r="V201">
@@ -26865,7 +26865,7 @@
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/26f94ea3-7ef7-4db4-b5be-72429fc6b275/Laudo11-Bemol-2026-IsaiasBritoDaRochaFilho-Assinado.pdf?expires_on=1785445163&amp;signature=HI9HGBwV1S4r0rPfZaRhtFWUknFXVDBuPLjzcmBcMiw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/26f94ea3-7ef7-4db4-b5be-72429fc6b275/Laudo11-Bemol-2026-IsaiasBritoDaRochaFilho-Assinado.pdf?expires_on=1785445264&amp;signature=7VfWfh60fHnmlplR9CHdVxx%2FnVlFtWx0HEC0i2RjODI%3D</t>
         </is>
       </c>
       <c r="V202">
@@ -26995,7 +26995,7 @@
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1501f5db-4f26-4c17-b525-cc5d06d5bae0/Laudo187-Bemol-2026-IvaMarcelinoDeSouza-Assinado.pdf?expires_on=1785445163&amp;signature=T0Yqws4ntTNHHdQA2bybMLXsN2U0SFaf6lyw3ipknlk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1501f5db-4f26-4c17-b525-cc5d06d5bae0/Laudo187-Bemol-2026-IvaMarcelinoDeSouza-Assinado.pdf?expires_on=1785445264&amp;signature=r1lp%2Bk5vzCBVAZnzUENyQRbRZuJrQPmq2MD3kxr%2BprY%3D</t>
         </is>
       </c>
       <c r="V203">
@@ -27124,7 +27124,7 @@
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/80c26842-a8a3-4839-ae2a-fec3d1ab4e70/LAUDOIVANETE.pdf?expires_on=1785445163&amp;signature=cw%2FByhGqQwBptONYxEP%2BM9Gd6oZn6eFnELlOLWK6ed8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/80c26842-a8a3-4839-ae2a-fec3d1ab4e70/LAUDOIVANETE.pdf?expires_on=1785445264&amp;signature=4E6x1ysvwzLt%2Fp1QsJ2aBZwHlWkpMVVXKSFb%2Fxmlo2w%3D</t>
         </is>
       </c>
       <c r="V204">
@@ -27256,7 +27256,7 @@
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f3c44a28-580d-4073-a0dc-e1ec71bfd207/LaudoT02-Bemol-2026-IvanildodeAraujoFerreira.pdf?expires_on=1785445163&amp;signature=7SxEjuWcvw57AaQZXomu01dSNlnFI8KGoqXTJfH%2Fb9I%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f3c44a28-580d-4073-a0dc-e1ec71bfd207/LaudoT02-Bemol-2026-IvanildodeAraujoFerreira.pdf?expires_on=1785445264&amp;signature=uJAQ9flWvcWV3NUd8FBKj50k1jlJG25fdxKsAM75tjA%3D</t>
         </is>
       </c>
       <c r="V205">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c335268a-013b-427f-bc2b-e716b9abbdbb/Laudo117-Bemol-2026-IvoneteGoncalvesDosSantos-Assinado.pdf?expires_on=1785445163&amp;signature=UUoAOngDCo5%2FcFQaU0tEuRuw8XbIvkBzBdj4n8PrFB8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c335268a-013b-427f-bc2b-e716b9abbdbb/Laudo117-Bemol-2026-IvoneteGoncalvesDosSantos-Assinado.pdf?expires_on=1785445264&amp;signature=JDvX0iDTfVe%2B0IXCXyJN7amtDI1Jo7C1UYcvv7BZBmk%3D</t>
         </is>
       </c>
       <c r="V206">
@@ -27498,7 +27498,7 @@
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/59cc3c3d-f732-4d4f-859d-0187a585b480/Laudo186-Bemol-2026-IvoneteMagalhaesDaSilva-Assinadoajustado.pdf?expires_on=1785445163&amp;signature=yb3a28eL87vQI206Nns8aNSgiY9ZW5H5A9%2FO%2BDz%2B9U8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/59cc3c3d-f732-4d4f-859d-0187a585b480/Laudo186-Bemol-2026-IvoneteMagalhaesDaSilva-Assinadoajustado.pdf?expires_on=1785445264&amp;signature=tJp7tSSwaYfP53HYEtPeFvPho7uVTl%2FjVOWpBGc3els%3D</t>
         </is>
       </c>
       <c r="V207">
@@ -27622,7 +27622,7 @@
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/366567fd-fc3b-4139-9946-1127871896bb/LaudoB21-2026-BEMOL-IZABELAPARECIDAMACHADO.pdf?expires_on=1785445163&amp;signature=ba8nYNC95vsGdx07kkejf0t2vXlobLKRSdLqQhEXOaQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/366567fd-fc3b-4139-9946-1127871896bb/LaudoB21-2026-BEMOL-IZABELAPARECIDAMACHADO.pdf?expires_on=1785445264&amp;signature=KAoyOHyjDPn3o2pHnLFlLvPiXX5U6b9C3E8dj9UmWsM%3D</t>
         </is>
       </c>
       <c r="V208">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/eaf87586-e6fe-4b9a-b754-385b00a87480/LAUDOIZABELE.pdf?expires_on=1785445163&amp;signature=BCv2kr8WMJmFxaHOpiBpcLLUxVGl4hoczglEk09cuio%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/eaf87586-e6fe-4b9a-b754-385b00a87480/LAUDOIZABELE.pdf?expires_on=1785445264&amp;signature=mr8dpTz4UYz7SLchI1D5G2ry9cq3ok%2FnI21U2q3CF9c%3D</t>
         </is>
       </c>
       <c r="V209">
@@ -27859,7 +27859,7 @@
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a4cbc1de-57d1-4401-bbe3-bca8d904640d/Laudo142-Bemol-2026-IzabeleMaiadaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=LTZsk6n7j95lcZUtIyuQ63q6jTygbUzmxY20ifk9dn0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a4cbc1de-57d1-4401-bbe3-bca8d904640d/Laudo142-Bemol-2026-IzabeleMaiadaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=rhprGuGEcpyIUhbttKHFMT1919W4EdTwbeLG4fN%2Fefc%3D</t>
         </is>
       </c>
       <c r="V210">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/482720e0-da58-4939-b51d-a6a2e0af0272/RelatriodeValordeRefernciaRVR07-Bemol-2025-IzadoraSantosNascimento-Assinado.pdf?expires_on=1785445163&amp;signature=%2Ft4XEmlU4QxlOeZKAYC%2BgtRblGhgDB%2FVlowA2Xs7CJA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/482720e0-da58-4939-b51d-a6a2e0af0272/RelatriodeValordeRefernciaRVR07-Bemol-2025-IzadoraSantosNascimento-Assinado.pdf?expires_on=1785445264&amp;signature=H1mXlRh26umdnZk426IaAZoDTQt4JhxpijxDdUiY7Yg%3D</t>
         </is>
       </c>
       <c r="V211">
@@ -28138,7 +28138,7 @@
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1c8152d9-03f7-45fb-9bab-c6cfa31249d3/LaudoP11-Bemol-2026-IzamaraVieiraBraga_signed.pdf?expires_on=1785445163&amp;signature=ZC6DBTNfnlz5hJ57l5UhBBS5V5ijNKI9mwcKmoChp8o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1c8152d9-03f7-45fb-9bab-c6cfa31249d3/LaudoP11-Bemol-2026-IzamaraVieiraBraga_signed.pdf?expires_on=1785445264&amp;signature=6WyVH2BlPe%2Bs%2FMfTLXK72WuqYtH88jn7xbeDkHOH0Ro%3D</t>
         </is>
       </c>
       <c r="V212">
@@ -28269,7 +28269,7 @@
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/dded52eb-bf72-4b8b-91b5-814e5d7289a1/LaudoITA39-Bemol-2025-IzomarFariasRamos_signed.pdf?expires_on=1785445163&amp;signature=WKIFmTCMOhCPVT3euELH2eeOnbKkcCnFMsACS0uBK30%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/dded52eb-bf72-4b8b-91b5-814e5d7289a1/LaudoITA39-Bemol-2025-IzomarFariasRamos_signed.pdf?expires_on=1785445264&amp;signature=u3kgI8GOk8RiUZxyNDWoMSLt6uelcXg3pO6ylLQQBZw%3D</t>
         </is>
       </c>
       <c r="V213">
@@ -28412,7 +28412,7 @@
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1aef0609-59d2-4183-92d2-5a7eebabad95/Laudo197-Bemol-2026-JacquelineSalesSantos.pdf?expires_on=1785445163&amp;signature=hOhkccIJtNfRCWWnyBU4eCmbCBca7jSXQEbT%2FkTTteY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1aef0609-59d2-4183-92d2-5a7eebabad95/Laudo197-Bemol-2026-JacquelineSalesSantos.pdf?expires_on=1785445264&amp;signature=eq1VCPThlTLKJ9uDLxfBe19UBa1XKBWAU3n4pO7fmlk%3D</t>
         </is>
       </c>
       <c r="V214">
@@ -28538,7 +28538,7 @@
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e609c540-9083-4e3f-9019-8c5e5b127f44/Laudo172-Bemol-2026-JailsonDaSilvaPontes-Assinado.pdf?expires_on=1785445163&amp;signature=eBxU27wMqMIKhHOV26n2QJMSLKlwXRq5bIb%2BM2%2BYmFY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e609c540-9083-4e3f-9019-8c5e5b127f44/Laudo172-Bemol-2026-JailsonDaSilvaPontes-Assinado.pdf?expires_on=1785445264&amp;signature=Cl4lXva04Rw%2BA5aGxxAo%2FfH92MCDDKylBCvELs9tyiM%3D</t>
         </is>
       </c>
       <c r="V215">
@@ -28681,7 +28681,7 @@
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/eeab7072-bd88-492b-bfe5-746cd9ff8e4d/Laudo191-Bemol-2026-JamilysSantanaDeSouza-Assinado.pdf?expires_on=1785445163&amp;signature=qCUJgRrkSe%2Bwqu9B38Z53ypl7b6SWPRqlDeFHAnWq94%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/eeab7072-bd88-492b-bfe5-746cd9ff8e4d/Laudo191-Bemol-2026-JamilysSantanaDeSouza-Assinado.pdf?expires_on=1785445264&amp;signature=yaDYGdlkwJK%2Fl70y1O%2F4B%2Fh9aAmevw%2FUBpe8ojHxR00%3D</t>
         </is>
       </c>
       <c r="V216">
@@ -28812,7 +28812,7 @@
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2ff6e778-db4e-4b7e-9589-a6a856fcc77a/Laudo69-Bemol-2026-JandersonFreitasLopes-Assinado.pdf?expires_on=1785445163&amp;signature=x47C9Vi6QBo23N1RByg8i%2FrKg%2BsQQZDv9MxF9pRviMk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2ff6e778-db4e-4b7e-9589-a6a856fcc77a/Laudo69-Bemol-2026-JandersonFreitasLopes-Assinado.pdf?expires_on=1785445264&amp;signature=jihK%2FcXD3irPAzbIdB5lCaiT4ea5mqjzh2PJo5%2BfcqY%3D</t>
         </is>
       </c>
       <c r="V217">
@@ -28944,7 +28944,7 @@
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7de45570-38f1-4e03-bcab-9ba99b412379/LAUDOJANDERSON.pdf?expires_on=1785445163&amp;signature=sOFIaAKUUn%2BuUv8x%2FE5iKhEP3KYGCnogEYvCXnzEc4Y%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7de45570-38f1-4e03-bcab-9ba99b412379/LAUDOJANDERSON.pdf?expires_on=1785445264&amp;signature=qx4lYL%2FpJNQv7CSI5BtysfzwxwGEUw5ea6M0joPFcac%3D</t>
         </is>
       </c>
       <c r="V218">
@@ -29081,7 +29081,7 @@
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ae607539-6bfa-484c-b67f-61b2da93636f/LaudoJane.pdf?expires_on=1785445163&amp;signature=OExj7vYXy0swKGeQWZSsFSOaxm%2B14Kfg865VEhSjOhc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ae607539-6bfa-484c-b67f-61b2da93636f/LaudoJane.pdf?expires_on=1785445264&amp;signature=%2BVyXlB9ON0drh1O9OiylmXgi90efV37QNaQncaHtsck%3D</t>
         </is>
       </c>
       <c r="V219">
@@ -29218,7 +29218,7 @@
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/233271c5-70ab-469d-9b5f-eca2e8156db9/LaudoB131-2025-BEMOL-JANEDEOLIVEIRABORGES.pdf?expires_on=1785445163&amp;signature=3evSDZqcXl2HZycJK2Z78L%2FcweyxNBQxLBxpTFlROo4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/233271c5-70ab-469d-9b5f-eca2e8156db9/LaudoB131-2025-BEMOL-JANEDEOLIVEIRABORGES.pdf?expires_on=1785445264&amp;signature=HPfoVhP%2FjdtpMzQAArp2jeYWw9vsqv5UqC14AelAuS8%3D</t>
         </is>
       </c>
       <c r="V220">
@@ -29364,7 +29364,7 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/179e2d31-7675-4b25-9c3e-2d79ecd0038d/Laudo79-Bemol-2026-JaneteBastosFarias-Assinado.pdf?expires_on=1785445163&amp;signature=%2FhuPOWOEizNKowv2zwVYj9mJaEH%2BgYowpHhB%2BdWWT%2FE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/179e2d31-7675-4b25-9c3e-2d79ecd0038d/Laudo79-Bemol-2026-JaneteBastosFarias-Assinado.pdf?expires_on=1785445264&amp;signature=wHNQcdHYbUoASsVd5Re4fk4vlUT%2BiKgBnKeh1sjkhxM%3D</t>
         </is>
       </c>
       <c r="V221">
@@ -29493,7 +29493,7 @@
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4c6aef96-b97d-461b-8228-8b4005055ba9/LaudoB44-2026-BEMOL-JANUSAMENDESFERREIRA.pdf?expires_on=1785445163&amp;signature=719z7Czb0frz1KFz4c6J6%2BHbTpBqRA8p2f86Ojaj17c%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4c6aef96-b97d-461b-8228-8b4005055ba9/LaudoB44-2026-BEMOL-JANUSAMENDESFERREIRA.pdf?expires_on=1785445264&amp;signature=8z5KJVOwzDfVPdKTU5plTE03mawoze7cJapmsy0tfo8%3D</t>
         </is>
       </c>
       <c r="V222">
@@ -29622,7 +29622,7 @@
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4f5bb51e-ffda-4368-b86c-c7ba99f854f0/Laudo16-Bemol-2026-JaquelineSantanaSoares-Assinadocorrigido.pdf?expires_on=1785445163&amp;signature=Yo3y5WOn%2FqZGzFLWCrdDZMykqg9Bs49SOZLy987yw8M%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4f5bb51e-ffda-4368-b86c-c7ba99f854f0/Laudo16-Bemol-2026-JaquelineSantanaSoares-Assinadocorrigido.pdf?expires_on=1785445264&amp;signature=6TB49IszDwGPpg2ZneRm37U0acIoR1tMrB%2ByBAPoUhE%3D</t>
         </is>
       </c>
       <c r="V223">
@@ -29751,7 +29751,7 @@
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/484caac2-18d3-497b-9b11-2b22c8c01adf/LaudoPA12-Bemol-2026-JarbasPessoaFerreira.pdf?expires_on=1785445163&amp;signature=kc38dghginceREcpyMCbqTPmmwd5HhHdfm0810khUkc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/484caac2-18d3-497b-9b11-2b22c8c01adf/LaudoPA12-Bemol-2026-JarbasPessoaFerreira.pdf?expires_on=1785445264&amp;signature=Jy7g%2BXiZhPyWEwyD2Nj0VbhsoV9XzGLKvWqYxODJcFE%3D</t>
         </is>
       </c>
       <c r="V224">
@@ -29877,7 +29877,7 @@
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/69cd1182-bfed-4f9b-ab50-ae0cc6f03093/LaudoB18-2026-BEMOL-JEANEANALIADASILVA.pdf?expires_on=1785445163&amp;signature=FJsFcxIBafIZ0QuZBDELDFLaKU5c85agaUTrohTC0Io%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/69cd1182-bfed-4f9b-ab50-ae0cc6f03093/LaudoB18-2026-BEMOL-JEANEANALIADASILVA.pdf?expires_on=1785445264&amp;signature=Vpd6qWwq%2BI5jl4pxDL8RozEaLkcBhUjPH8aGS6Y5PAI%3D</t>
         </is>
       </c>
       <c r="V225">
@@ -30023,7 +30023,7 @@
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf7fb4bf-787b-45be-bec2-db57c086c035/Laudo_AC_21-2026_-_JEFERSON_SILVA_DE_SOUZA_assinado.pdf?expires_on=1785445163&amp;signature=V5HwAjhy9NidKXSMRz6vwn38da4R740ND4tPeGidO4U%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf7fb4bf-787b-45be-bec2-db57c086c035/Laudo_AC_21-2026_-_JEFERSON_SILVA_DE_SOUZA_assinado.pdf?expires_on=1785445264&amp;signature=OJvFP9IQavopGOPEp7PqAYUk36syaTfcHGMkO5M0mSE%3D</t>
         </is>
       </c>
       <c r="V226">
@@ -30153,7 +30153,7 @@
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3e3c27f6-ddba-4643-a52f-29ceedb48d1b/Laudo118-Bemol-2026-JessicaNogueiraDeLima-Assinado.pdf?expires_on=1785445163&amp;signature=Z7YvlQ1%2Bd4%2BnvG2a5ImZQDaUavHJuiAYQsSYi90Djro%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3e3c27f6-ddba-4643-a52f-29ceedb48d1b/Laudo118-Bemol-2026-JessicaNogueiraDeLima-Assinado.pdf?expires_on=1785445264&amp;signature=nZkRHVqllrFQ6lW7qKZZ%2BH7ff4YPYbf5k8CaYI9GCiE%3D</t>
         </is>
       </c>
       <c r="V227">
@@ -30285,7 +30285,7 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ff906fd7-08d4-4538-ad9a-80c333493ce7/LaudoCO03-Bemol-2026-JheniferCristianRaulinodeAndrade-Assinado.pdf?expires_on=1785445163&amp;signature=w3aMzZlZj%2Fv4DgGx%2Fy%2Fhk1N%2Bi8l91rAalxDoD7BRmds%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ff906fd7-08d4-4538-ad9a-80c333493ce7/LaudoCO03-Bemol-2026-JheniferCristianRaulinodeAndrade-Assinado.pdf?expires_on=1785445264&amp;signature=eeWK3fz1vvbA1Epxk8E%2Fpr%2FQRIpbsK%2FG4xV02FEgLcM%3D</t>
         </is>
       </c>
       <c r="V228">
@@ -30414,7 +30414,7 @@
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a7ef559f-9880-4bf8-a476-08bb3dc5a68f/Laudo207-Bemol-2026-JhullyFabianeRamosDaCosta.pdf?expires_on=1785445163&amp;signature=d%2FY1qCskdoFQDr36iLi%2Fo%2B5KjGDuvXyhECdFyR%2F15jI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a7ef559f-9880-4bf8-a476-08bb3dc5a68f/Laudo207-Bemol-2026-JhullyFabianeRamosDaCosta.pdf?expires_on=1785445264&amp;signature=Agj3DMNbenWBcY009Qzc2PVNuAROZoWb2PXeXj8XRlM%3D</t>
         </is>
       </c>
       <c r="V229">
@@ -30551,7 +30551,7 @@
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b509385b-b1a1-461d-91a3-8708fc90b198/LaudoPA18-Bemol-2026-JoaoAlcineiPereiraVieira.pdf?expires_on=1785445163&amp;signature=Baqi5Jz1vDV8JQTyEmHz5caiHdcwSgu6rgw86S3goTQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b509385b-b1a1-461d-91a3-8708fc90b198/LaudoPA18-Bemol-2026-JoaoAlcineiPereiraVieira.pdf?expires_on=1785445264&amp;signature=UEjeOnKuneUP0NCynlJuaVLTYz6vVC4c1bkjv%2BoIISk%3D</t>
         </is>
       </c>
       <c r="V230">
@@ -30682,7 +30682,7 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2e05645e-7aee-4df3-9f69-f22dde074690/LaudoRP01-Bemol-2026-JoaoSoaresFurtunato.pdf?expires_on=1785445163&amp;signature=8F4MMGWlfUPK0HZJOzZ5N3X30qoVWHYBdHPuWWVNmrM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2e05645e-7aee-4df3-9f69-f22dde074690/LaudoRP01-Bemol-2026-JoaoSoaresFurtunato.pdf?expires_on=1785445264&amp;signature=ymHRip0cj%2FQZpmhhcZD9erJ%2FZ5tE2Tu%2FBH3IyhoGMgQ%3D</t>
         </is>
       </c>
       <c r="V231">
@@ -30813,7 +30813,7 @@
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/02510d24-69da-4642-b9c8-8c1b61d32cab/Laudo388-Bemol-2025-JoaoMarioCarvalhoPessoa-Assinado.pdf?expires_on=1785445163&amp;signature=UGOJLZXEI8%2F60Cyd5qWoBIy3N5%2BmEkYeEkRT8nzRMtI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/02510d24-69da-4642-b9c8-8c1b61d32cab/Laudo388-Bemol-2025-JoaoMarioCarvalhoPessoa-Assinado.pdf?expires_on=1785445264&amp;signature=8ZLAqIaFy%2BmAKSW8BgypqKHT90veswvNNFoviT5nrQY%3D</t>
         </is>
       </c>
       <c r="V232">
@@ -30959,7 +30959,7 @@
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d6e52378-0b8e-4d53-af15-f4dd5edf3a6e/LaudoB54-2026-BEMOL-JOAOPAULODOSSANTOSVERAS.pdf?expires_on=1785445163&amp;signature=fQ6STQsztz77G%2FN74qScgm3dg%2FGbYSN2lHTBYeBrUWQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d6e52378-0b8e-4d53-af15-f4dd5edf3a6e/LaudoB54-2026-BEMOL-JOAOPAULODOSSANTOSVERAS.pdf?expires_on=1785445264&amp;signature=l4e9EvshjdB744NVK5QW3zUzSRC7XqUgWr7ZJCKS380%3D</t>
         </is>
       </c>
       <c r="V233">
@@ -31082,7 +31082,7 @@
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a5369123-0a4a-4b85-8efb-523b4233b305/LaudoPA03-Bemol-2026-JoaoPauloPereiraSoares-Assinado.pdf?expires_on=1785445163&amp;signature=9jthsyTTXG%2BhMjmDJGD4ZBec8w20SauPVhN52MCKRfs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a5369123-0a4a-4b85-8efb-523b4233b305/LaudoPA03-Bemol-2026-JoaoPauloPereiraSoares-Assinado.pdf?expires_on=1785445264&amp;signature=fUTreLfVXH5E2qDTaNQiAFNDc0SJN4nRfFEL4u%2F9iks%3D</t>
         </is>
       </c>
       <c r="V234">
@@ -31221,7 +31221,7 @@
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/40db7fb9-46cb-459c-a71b-b96f688cb5ab/Laudo193-Bemol-2026-JoaoSoaresDaSilva-Assinadoajustado.pdf?expires_on=1785445163&amp;signature=RjJnMabrNs7NtdDJ0ztXmxAhJym9jElU3LZ90Dc07xc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/40db7fb9-46cb-459c-a71b-b96f688cb5ab/Laudo193-Bemol-2026-JoaoSoaresDaSilva-Assinadoajustado.pdf?expires_on=1785445264&amp;signature=Gm6jtz7%2Fy9Hgc5o5rq85llz%2FFg9%2BLxEZy2em3Og8s7A%3D</t>
         </is>
       </c>
       <c r="V235">
@@ -31345,7 +31345,7 @@
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d93bf01b-08e9-4dcc-b01c-fe9aa02b02e9/Laudo125-Bemol-2026-JoaoVictorMagalhaesRamos.pdf?expires_on=1785445163&amp;signature=xEXcaFj7yhvZ2sNA0ZFhUoKe5ZbNG6ufqzX%2B1VWA7j0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d93bf01b-08e9-4dcc-b01c-fe9aa02b02e9/Laudo125-Bemol-2026-JoaoVictorMagalhaesRamos.pdf?expires_on=1785445264&amp;signature=%2FLgPjy00W8%2FPNlWm4Jco%2BlVSN0guoW8tlEpgowEJOY0%3D</t>
         </is>
       </c>
       <c r="V236">
@@ -31471,7 +31471,7 @@
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/24ffb2ee-bb9e-43e2-9918-9c6f71c5c0e8/Laudo_AC_-_02-2026_-_JOAQUIM_RODRIGUES_DE_MATOS_FILHO_assinado.pdf?expires_on=1785445163&amp;signature=0gUIjNWbY2OEUV4A%2FKEW%2F37NPjDD1sEKy30m7Eqh7lQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/24ffb2ee-bb9e-43e2-9918-9c6f71c5c0e8/Laudo_AC_-_02-2026_-_JOAQUIM_RODRIGUES_DE_MATOS_FILHO_assinado.pdf?expires_on=1785445264&amp;signature=F%2BLUZIAlwfLhcGZzhqaH9Axmt61HBJRcNP3v8POznpo%3D</t>
         </is>
       </c>
       <c r="V237">
@@ -31608,7 +31608,7 @@
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4b3c9bc8-2816-4bbc-8286-2cdf8381b780/Laudo80-Bemol-2026-JocimaraCorreaBenacon-Assinado.pdf?expires_on=1785445163&amp;signature=QTcxdyMWCgvUJ5k05LIq6VJTXjCRX1b9D%2FwnEsZRO%2F8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4b3c9bc8-2816-4bbc-8286-2cdf8381b780/Laudo80-Bemol-2026-JocimaraCorreaBenacon-Assinado.pdf?expires_on=1785445264&amp;signature=VBetZNjwVM3gnhGeFsnUf6wqex2aFhluS6OEd3CSANU%3D</t>
         </is>
       </c>
       <c r="V238">
@@ -31741,7 +31741,7 @@
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a0c0c102-66a4-4d89-9813-1801175523da/LAUDOJODENILDO1.pdf?expires_on=1785445163&amp;signature=bLS7wRq8PrnkrhOBxN6y9biRUgKGSpugqyeiHpmYMXw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a0c0c102-66a4-4d89-9813-1801175523da/LAUDOJODENILDO1.pdf?expires_on=1785445264&amp;signature=lmMmMxPztW4T11zu0iSjn3Sdh33FkJI3eEZdAWEWyeI%3D</t>
         </is>
       </c>
       <c r="V239">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e14d207f-f757-48ec-8666-936793222082/Laudo12-Bemol-2026-JoncileideVieiraFalcao-Assinado.pdf?expires_on=1785445163&amp;signature=IiRtGesWz4c5hBs6T2XaOtMoKOMPUYMTyzQRQFF%2BmBc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e14d207f-f757-48ec-8666-936793222082/Laudo12-Bemol-2026-JoncileideVieiraFalcao-Assinado.pdf?expires_on=1785445264&amp;signature=oIi93ltjG7j8UiOgWhBunilgM7YLcOcZAHwsnLhxtH0%3D</t>
         </is>
       </c>
       <c r="V240">
@@ -32015,7 +32015,7 @@
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1e27824b-03e2-4d5e-96e8-63566e7c9c41/Laudo141-Bemol-2026-JorgeManuelLoureiroDosSantos-Assinadocorrigido.pdf?expires_on=1785445163&amp;signature=BS%2BIECk1cbBmkZQwunu%2FsBgUMKarCx1nxY7VCzLSrvw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1e27824b-03e2-4d5e-96e8-63566e7c9c41/Laudo141-Bemol-2026-JorgeManuelLoureiroDosSantos-Assinadocorrigido.pdf?expires_on=1785445264&amp;signature=Nu%2BfCMXMmHTcyK4D7jJ5imsRyMUtCSybYLQfo%2BKFrxo%3D</t>
         </is>
       </c>
       <c r="V241">
@@ -32133,7 +32133,7 @@
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8e7825cd-2fcb-4c6f-a5fd-68c1dff60b8f/Laudo64-Bemol-2026-JorgeMartinsDosSantos-Assinado.pdf?expires_on=1785445163&amp;signature=spoBxGsX%2BZ0%2BDvd3sQSl5XkO1HpmpYKFpY8RTYPtcGo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8e7825cd-2fcb-4c6f-a5fd-68c1dff60b8f/Laudo64-Bemol-2026-JorgeMartinsDosSantos-Assinado.pdf?expires_on=1785445264&amp;signature=IItwYMU%2BwDX9Bx5ldiB1YDNA2%2BBgj0%2B0afsa7156tYo%3D</t>
         </is>
       </c>
       <c r="V242">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0d15c1a7-7003-41de-9e5c-23703991fa5a/Laudo203-Bemol-2026-JoseAntonioFernandesDaMota-Assinado.pdf?expires_on=1785445163&amp;signature=8eg6Z36vNudBVkkowp646j24lX1q8mRJW3a9qFc3Okk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0d15c1a7-7003-41de-9e5c-23703991fa5a/Laudo203-Bemol-2026-JoseAntonioFernandesDaMota-Assinado.pdf?expires_on=1785445264&amp;signature=Nbbjn55SbXpUe9Ihg%2BS1K3xRBC7JAY3tQbbk3DfjJa4%3D</t>
         </is>
       </c>
       <c r="V243">
@@ -32380,7 +32380,7 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/63b023ef-e3e1-432c-be42-8d0b5dc993b8/LaudoITA11-Bemol-2026-JoseAriloDeCastroRabeloFilho-Assinado.pdf?expires_on=1785445163&amp;signature=CbJzAG3k4MaIDRa70EIjoQNpPgvE0ELPqQT%2B%2BI27P08%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/63b023ef-e3e1-432c-be42-8d0b5dc993b8/LaudoITA11-Bemol-2026-JoseAriloDeCastroRabeloFilho-Assinado.pdf?expires_on=1785445264&amp;signature=W96YaBhdoGSmp4X1AffHPgwCJAQAB0XumHN8TTAhpVU%3D</t>
         </is>
       </c>
       <c r="V244">
@@ -32511,7 +32511,7 @@
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/44a581da-23a2-43d4-bec7-85d68d6c1e4b/LaudoP19-Bemol-2026-JosedenysondaSilvabarros_signed.pdf?expires_on=1785445163&amp;signature=R8yYBlOZJAsPUFO0HXt29Txh4KI8dQRvTo2bRsmLReM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/44a581da-23a2-43d4-bec7-85d68d6c1e4b/LaudoP19-Bemol-2026-JosedenysondaSilvabarros_signed.pdf?expires_on=1785445264&amp;signature=lOyj04WVoR68qtH1gkNBjnqZ7ocRbSWC63rl6yWep%2Bs%3D</t>
         </is>
       </c>
       <c r="V245">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f9ffca4f-c0f4-40e5-a3f9-cb3e0a54d3af/Laudo_AC_-_03-2026_-_JOSE_FERREIRA_DA_SILVA_assinado.pdf?expires_on=1785445163&amp;signature=ckAmkfq7OHIk3gJ5ihw6QOzV8dnEcD6vrzLR01S79QA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f9ffca4f-c0f4-40e5-a3f9-cb3e0a54d3af/Laudo_AC_-_03-2026_-_JOSE_FERREIRA_DA_SILVA_assinado.pdf?expires_on=1785445264&amp;signature=K8XPKQcz7j9HpJeR8ElpFT6puXYx0D87G2HPB%2B3CPdo%3D</t>
         </is>
       </c>
       <c r="V246">
@@ -32778,7 +32778,7 @@
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/32e67383-9a53-47a3-a8a3-f3924affe338/BEMOL-AR024-JOSEGUILHERMEDASILVA.pdf?expires_on=1785445163&amp;signature=%2BucMiqKlJ82heDbHKjvqbvee0NSLXwBED7wNif8ulEw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/32e67383-9a53-47a3-a8a3-f3924affe338/BEMOL-AR024-JOSEGUILHERMEDASILVA.pdf?expires_on=1785445264&amp;signature=uj9vYzYL77H5IrB9kaaoX5BOT996AEUyWRTJVXhmpOw%3D</t>
         </is>
       </c>
       <c r="V247">
@@ -32908,7 +32908,7 @@
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b445fa54-a64b-4377-8b13-d1a2678ff739/Laudo32-Bemol-2026-JoseHiltonDeAzevedo-Assinado.pdf?expires_on=1785445163&amp;signature=Z54xs8zcBYhoasO1VPVgOV437GeXIJFW1FWZKb%2BWYP8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b445fa54-a64b-4377-8b13-d1a2678ff739/Laudo32-Bemol-2026-JoseHiltonDeAzevedo-Assinado.pdf?expires_on=1785445264&amp;signature=ZQ6j9VofSguzRIUmiZDpgSqXEKY3LWz0Ip15YdXBHHY%3D</t>
         </is>
       </c>
       <c r="V248">
@@ -33040,7 +33040,7 @@
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a78e75e1-9bc8-41af-a915-51ff7bbc9720/LaudoJP20-Bemol-2025-JoselitoGoncalvesPonponet_signed.pdf?expires_on=1785445163&amp;signature=Dw36vl8J3AErQMpmr4jx%2Brqu6G%2Bcozs1kFlruCxJ69I%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a78e75e1-9bc8-41af-a915-51ff7bbc9720/LaudoJP20-Bemol-2025-JoselitoGoncalvesPonponet_signed.pdf?expires_on=1785445264&amp;signature=sWo7R%2Bv49Za27xbfQrwMKDjsb0Uu2K0jD%2FI%2FTuJ9zts%3D</t>
         </is>
       </c>
       <c r="V249">
@@ -33179,7 +33179,7 @@
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/59cf8cc8-d359-4624-80cc-358e01243f17/Laudo51-Bemol-2026-JosianeSouzaDaRocha.pdf?expires_on=1785445163&amp;signature=NAGduQsjSXTGFNJBO9uuYu88TGmOkGhgZMMc79u9doQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/59cf8cc8-d359-4624-80cc-358e01243f17/Laudo51-Bemol-2026-JosianeSouzaDaRocha.pdf?expires_on=1785445264&amp;signature=0Su1CDZ7xeH9euxNnpNlpRIFK4OcR5Zl0fj8NBinoLA%3D</t>
         </is>
       </c>
       <c r="V250">
@@ -33308,7 +33308,7 @@
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3083643d-bcb1-4c34-8d2b-b413a5548f3d/LaudoPA10-Bemol-2026-JosiasConceicaoSoares.pdf?expires_on=1785445163&amp;signature=QNY4Re4W6bR2LoS09Wus8U%2BfUsPfJvJUvYdFtXAXM44%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3083643d-bcb1-4c34-8d2b-b413a5548f3d/LaudoPA10-Bemol-2026-JosiasConceicaoSoares.pdf?expires_on=1785445264&amp;signature=RdyY3a2vpY3ED4AzHKjITcfl%2FXKc0NguWB8PJPE4Nlc%3D</t>
         </is>
       </c>
       <c r="V251">
@@ -33432,7 +33432,7 @@
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0a061aa3-403a-4950-9fe5-220a66442a39/Laudo105-Bemol-2026-JoyceKellyBezerraRozeno-Assinado.pdf?expires_on=1785445163&amp;signature=JWY%2BEwS1deqPj8yEV%2BWt0MPWJlVGhzbLqJcGFU67nUU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0a061aa3-403a-4950-9fe5-220a66442a39/Laudo105-Bemol-2026-JoyceKellyBezerraRozeno-Assinado.pdf?expires_on=1785445264&amp;signature=2lZgtyYmW2UpJr7HrjurnIpw%2B4t72XZpUoDIHmn7vBk%3D</t>
         </is>
       </c>
       <c r="V252">
@@ -33556,7 +33556,7 @@
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fcf9d45a-32f5-4428-a169-dbab8039b5c5/LAUDOJUCILEIDEcorrigido.pdf?expires_on=1785445163&amp;signature=QJv86fpYjAZpuvGa0zg8m8rx4MBvg%2FjA3NwxDOcTj0k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fcf9d45a-32f5-4428-a169-dbab8039b5c5/LAUDOJUCILEIDEcorrigido.pdf?expires_on=1785445264&amp;signature=T1lLx0RKc%2Bs2cLv8lEKflU8ox%2Fgom75CIn84DoCrS4g%3D</t>
         </is>
       </c>
       <c r="V253">
@@ -33674,7 +33674,7 @@
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fd5fc2e4-28eb-409f-9703-7cac56ee39c5/LaudoMAN01-Bemol-2026-JucimarDeSouzaFreitas.pdf?expires_on=1785445163&amp;signature=gBoNuMXLlNYimQNfJcvi8waTXXf1f5iWSLzBYxnurSo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fd5fc2e4-28eb-409f-9703-7cac56ee39c5/LaudoMAN01-Bemol-2026-JucimarDeSouzaFreitas.pdf?expires_on=1785445264&amp;signature=Jgw%2FQQxgTlhNrO4nWSdDTEh1DZqL6%2FWr%2Bh3dVRiBiFQ%3D</t>
         </is>
       </c>
       <c r="V254">
@@ -33806,7 +33806,7 @@
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/102a799e-a3eb-4b9f-b5b3-0ba81687c5f6/BEMOL-PV083-KALWANNEALVESDEMEDEIROS.pdf?expires_on=1785445163&amp;signature=RPPIJsa582cma%2BxCrdzacNWgvIZlEDjRi%2F8lSqMIFDI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/102a799e-a3eb-4b9f-b5b3-0ba81687c5f6/BEMOL-PV083-KALWANNEALVESDEMEDEIROS.pdf?expires_on=1785445264&amp;signature=nUaL%2FGotvxcKYYGy3S9BmrwOXPDBlSFwxx4IdLA7LRU%3D</t>
         </is>
       </c>
       <c r="V255">
@@ -33929,7 +33929,7 @@
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9bfc239f-7e6e-4054-9233-9b1d5637f829/LaudoMAN05-Bemol-2026-KarenSuzyOliveiraLimaVerde.pdf?expires_on=1785445163&amp;signature=Jv1CoDAyHFWQJQFWn8irGs1ShPDLVl%2FulA0sQNbxl2U%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9bfc239f-7e6e-4054-9233-9b1d5637f829/LaudoMAN05-Bemol-2026-KarenSuzyOliveiraLimaVerde.pdf?expires_on=1785445264&amp;signature=PrOUzhLSYrHjv3SCegPw8uMh7pGQru2cHyjf1oHEPOU%3D</t>
         </is>
       </c>
       <c r="V256">
@@ -34066,7 +34066,7 @@
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c4fe8ca8-baf2-4efc-83a7-233980c73c44/Laudo74-Bemol-2026-KarinaTaliaDaSilvaAlbuquerque-Assinado.pdf?expires_on=1785445163&amp;signature=EZ1AaN2RsdKmGTh8MiKLPI%2BqikWTZyd8VJu04ikZNA0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c4fe8ca8-baf2-4efc-83a7-233980c73c44/Laudo74-Bemol-2026-KarinaTaliaDaSilvaAlbuquerque-Assinado.pdf?expires_on=1785445264&amp;signature=Zw6Ox2ic%2BHthPtyoWGLByV9Rx0EmPlyAu%2BDmtqgTiiE%3D</t>
         </is>
       </c>
       <c r="V257">
@@ -34209,7 +34209,7 @@
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/09b4be70-22fc-4cd7-845b-ce60b34422f5/Laudo44-Bemol-2026-KathyLinneOliveiraQueiroz-Assinado.pdf?expires_on=1785445163&amp;signature=Wy96TFUqaAodrmi6mstfO0HVynplHArM9JvPVWF%2BOlU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/09b4be70-22fc-4cd7-845b-ce60b34422f5/Laudo44-Bemol-2026-KathyLinneOliveiraQueiroz-Assinado.pdf?expires_on=1785445264&amp;signature=pTmrp95S9Bu7tkpF%2FcI4qItWQho77RqniPDzkjAM49I%3D</t>
         </is>
       </c>
       <c r="V258">
@@ -34347,7 +34347,7 @@
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/eb1e71be-7dea-4067-ac02-45cc31dc2747/LaudoB74-2025-BEMOL-KATIACRISTINASOARESCORDOVIL-ajustado.pdf?expires_on=1785445163&amp;signature=TJmWcgO1Wx3XQEbpeOeqS1CRE0gCmedGl4Glq0zJcic%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/eb1e71be-7dea-4067-ac02-45cc31dc2747/LaudoB74-2025-BEMOL-KATIACRISTINASOARESCORDOVIL-ajustado.pdf?expires_on=1785445264&amp;signature=RH0K88BWqrTaVU7rU8770sXGhaW1dJxaSQCQsiSiy%2BY%3D</t>
         </is>
       </c>
       <c r="V259">
@@ -34487,7 +34487,7 @@
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/18a0acbb-231a-4adb-ad19-867d57322b0e/LAUDOKATIASILVEIRA.pdf?expires_on=1785445163&amp;signature=58nh%2BcH%2FRE%2FYxYstgeGHx3n%2BH%2BxKcTWG2%2FlaVuyJJK0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/18a0acbb-231a-4adb-ad19-867d57322b0e/LAUDOKATIASILVEIRA.pdf?expires_on=1785445264&amp;signature=gZY66xZPvPKPYFxlKTX1TN0JChZ1OvnmusNRSkGYV7A%3D</t>
         </is>
       </c>
       <c r="V260">
@@ -34619,7 +34619,7 @@
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0960719a-5454-4cf9-8daf-ba22e26bd11b/Laudo211-Bemol-2026-KatilaCorreiaDaCosta-Assinado.pdf?expires_on=1785445163&amp;signature=bL3Et6rZEswvuvsG6L1bButTi1UTL05%2Fk6vraO57Cos%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0960719a-5454-4cf9-8daf-ba22e26bd11b/Laudo211-Bemol-2026-KatilaCorreiaDaCosta-Assinado.pdf?expires_on=1785445264&amp;signature=%2FJHYSsgo23S5f3%2B%2BTqrnDgETG61HpJYm7Zsf8OwO110%3D</t>
         </is>
       </c>
       <c r="V261">
@@ -34742,7 +34742,7 @@
       </c>
       <c r="U262" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/78047af0-3a8a-47f5-96c5-2011fa327014/LaudoB5-2026-BEMOL-KAUYTABRENDAVIANAAGOSTINHO.pdf?expires_on=1785445163&amp;signature=xxFg09gcm%2F0kPgBP%2BF%2BfDK%2FFB7uweZt0tqMbTaBJMqw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/78047af0-3a8a-47f5-96c5-2011fa327014/LaudoB5-2026-BEMOL-KAUYTABRENDAVIANAAGOSTINHO.pdf?expires_on=1785445264&amp;signature=7w5o%2ByGCp388V%2BxXMqoOSG2%2BcDpIaKoZaAKiyypRDO4%3D</t>
         </is>
       </c>
       <c r="V262">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f14757f5-bf32-46e7-ba0b-2bca9310519f/LaudoP18-Bemol-2026-KeitianeSoaresMenezes_signed.pdf?expires_on=1785445163&amp;signature=mDQrck1wEu3DwKmxy8ZPFZ%2BdJLdU6%2FqJUt%2Fc%2Fbm6Goo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f14757f5-bf32-46e7-ba0b-2bca9310519f/LaudoP18-Bemol-2026-KeitianeSoaresMenezes_signed.pdf?expires_on=1785445264&amp;signature=x5RO57YwGuXfTYxyaXwfZObTRk7LBM7K6Rrm1lqLNhY%3D</t>
         </is>
       </c>
       <c r="V263">
@@ -34997,7 +34997,7 @@
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4589162a-b138-4232-9001-d6e6f23710f0/Laudo127-Bemol-2026-KelcianeSantosDeAraujo.pdf?expires_on=1785445163&amp;signature=n7Iip4OkR2nFurphS0d%2B4ojJVV44PerMu4JeRYXgGSQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4589162a-b138-4232-9001-d6e6f23710f0/Laudo127-Bemol-2026-KelcianeSantosDeAraujo.pdf?expires_on=1785445264&amp;signature=7sc2hFAbBBZeoAS5XjQ82RbCIR6r6il7rEbfLIyG5WM%3D</t>
         </is>
       </c>
       <c r="V264">
@@ -35129,7 +35129,7 @@
       </c>
       <c r="U265" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3d8c9a1f-7784-4fd4-b6ef-324016118989/BEMOL-JP040-KleitonOliveiraGonalves.pdf?expires_on=1785445163&amp;signature=%2BdzuIdmVoi%2Bj4Nnk9UAHQzEARrzWpXaZlZKa1aDngWE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3d8c9a1f-7784-4fd4-b6ef-324016118989/BEMOL-JP040-KleitonOliveiraGonalves.pdf?expires_on=1785445264&amp;signature=JlNLu0LLXrkqH8KEdXr2Jbp07nZ%2FJFGmyypi1oPfGYE%3D</t>
         </is>
       </c>
       <c r="V265">
@@ -35266,7 +35266,7 @@
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/84888d6c-08d7-4445-805f-82232e205d61/Laudo55-Bemol-2026-LacyAugustaDeOliveiraPereira-Assinadocorrigido.pdf?expires_on=1785445163&amp;signature=JGUcpMWlIq3VGjGVWkOZcGqsJ%2BYG%2FyzJQ4PVlCRezZE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/84888d6c-08d7-4445-805f-82232e205d61/Laudo55-Bemol-2026-LacyAugustaDeOliveiraPereira-Assinadocorrigido.pdf?expires_on=1785445264&amp;signature=0RJc3abBr8JiSED8bR5BYi2KF%2Bc1w%2BawYjn37iVzCLA%3D</t>
         </is>
       </c>
       <c r="V266">
@@ -35404,7 +35404,7 @@
       </c>
       <c r="U267" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c57e2482-e0ab-4ffd-8d4b-e915535f39a0/BEMOL-PV067-LAELSONDASILVALIMA.pdf?expires_on=1785445163&amp;signature=jNySOru7ogm9ke6q6djIKU9Efq5%2FXj1zYonqEAyrMAU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c57e2482-e0ab-4ffd-8d4b-e915535f39a0/BEMOL-PV067-LAELSONDASILVALIMA.pdf?expires_on=1785445264&amp;signature=psy4rHlT%2FLViV7oDDcAK63leFcpOLyyehfmMlqXyr3I%3D</t>
         </is>
       </c>
       <c r="V267">
@@ -35538,7 +35538,7 @@
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9cdd9b63-6138-421d-a7d5-59b099832833/M21-2026-LAERCIOajustado02.pdf?expires_on=1785445163&amp;signature=Rr7%2BsYe3O06wruDFaNgVcnSNHIKRNHfcrRBeEzuP7Zs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9cdd9b63-6138-421d-a7d5-59b099832833/M21-2026-LAERCIOajustado02.pdf?expires_on=1785445264&amp;signature=IbKXWXaMS153JDnvdfBR0GNYtxabREvkub8UHCvFA5Q%3D</t>
         </is>
       </c>
       <c r="V268">
@@ -35675,7 +35675,7 @@
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/51d2732a-d4f3-4ceb-93db-604dec01b804/Laudo384-Bemol-2025-LaraKarinaFreitasDaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=nil61huQX7JLx6i3rUvc7%2B0TIvBdw%2B%2FoFA9%2Bv460apc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/51d2732a-d4f3-4ceb-93db-604dec01b804/Laudo384-Bemol-2025-LaraKarinaFreitasDaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=i2qgvzdFhR8WX8C%2B6p5IjFnuXzDls8IbwOa%2FoxN3Aps%3D</t>
         </is>
       </c>
       <c r="V269">
@@ -35809,7 +35809,7 @@
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ad09fc29-0c35-49fa-903f-463ed726a278/LaudoB53-2026-BEMOL-LARISSADESOUZAPINHEIRO.pdf?expires_on=1785445163&amp;signature=jbvTUhhOjo7duSddv5QPTori%2FxAM2Tjsb0a3xlNp84E%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ad09fc29-0c35-49fa-903f-463ed726a278/LaudoB53-2026-BEMOL-LARISSADESOUZAPINHEIRO.pdf?expires_on=1785445264&amp;signature=R4vVlCINIPFjtsTYLGQMzva8eDBdQPx5SWItXepLVOI%3D</t>
         </is>
       </c>
       <c r="V270">
@@ -35941,7 +35941,7 @@
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5c263ebd-cfce-4688-a60b-2bf294c5af42/LaudoB7-2026-BEMOL-LELIANEBEZERRACOSTA.pdf?expires_on=1785445163&amp;signature=pyd3%2BAcINWhqdEnswLMAhGoF%2FlXXyFPdZ4uoliIM%2BD0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5c263ebd-cfce-4688-a60b-2bf294c5af42/LaudoB7-2026-BEMOL-LELIANEBEZERRACOSTA.pdf?expires_on=1785445264&amp;signature=rkJTLv7C0zKYEtMYle7tX84F2YhIXX4QLPvU1V2LlVU%3D</t>
         </is>
       </c>
       <c r="V271">
@@ -36077,7 +36077,7 @@
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/227d992b-9e09-49b9-aa03-055a9ef77a5c/LAUDOLENAGIANI.pdf?expires_on=1785445163&amp;signature=it8S%2BfmjRtNSvkPcHFrBnfbAT4tNPG1xdf%2FReLX0cXs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/227d992b-9e09-49b9-aa03-055a9ef77a5c/LAUDOLENAGIANI.pdf?expires_on=1785445264&amp;signature=%2F6pjHFFG939JqJenDlSpi27mpV5EnkYGCwrT%2Bz1Qu9M%3D</t>
         </is>
       </c>
       <c r="V272">
@@ -36206,7 +36206,7 @@
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e683766e-4fa9-40fd-bf56-e1e1d699e2b3/LaudoA12-Bemol-2026-LenilzadeSousaQuintino_signed.pdf?expires_on=1785445163&amp;signature=aFvDN7txytKa%2BGcOb5rq3jCaEHQyHAAqIlVZ8rtSxIs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e683766e-4fa9-40fd-bf56-e1e1d699e2b3/LaudoA12-Bemol-2026-LenilzadeSousaQuintino_signed.pdf?expires_on=1785445264&amp;signature=q0MVjqgsACJC1LtMxpM%2BYM%2FmHvg53gHxFue%2FZJowPHo%3D</t>
         </is>
       </c>
       <c r="V273">
@@ -36329,7 +36329,7 @@
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6a6c242c-a92f-4d3a-9f89-5f9a233e116a/Laudo145-Bemol-2026-LeonoraSuelmaSantosDeMatos-Assinado.pdf?expires_on=1785445163&amp;signature=SDHM%2BGzDWy%2FtC5F4BOmWOfaOa7MmhnqD58ezbYNYrsM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6a6c242c-a92f-4d3a-9f89-5f9a233e116a/Laudo145-Bemol-2026-LeonoraSuelmaSantosDeMatos-Assinado.pdf?expires_on=1785445264&amp;signature=519VBdy5iKyJiTnfs4L%2FXUIXgvKDWu2E3CjHTvGiZDU%3D</t>
         </is>
       </c>
       <c r="V274">
@@ -36466,7 +36466,7 @@
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/187a3450-7d8c-42db-9247-701e3aac79f7/Laudo151-Bemol-2026-LeuzaFeijoCardoso-Assinado.pdf?expires_on=1785445163&amp;signature=ooYY8B3RKwlYFaMU0qb%2B3W4A7Bl1GjKR%2FyT1xD60KLo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/187a3450-7d8c-42db-9247-701e3aac79f7/Laudo151-Bemol-2026-LeuzaFeijoCardoso-Assinado.pdf?expires_on=1785445264&amp;signature=%2FsdKQNLI6lnUv%2F%2FA9DPIs8fpX7eIOKs3kKZtxAcv2xY%3D</t>
         </is>
       </c>
       <c r="V275">
@@ -36603,7 +36603,7 @@
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e93d351e-ee9f-4c5b-a064-86d8d270c79c/M03-2026-LIANDRASIMOESANDRADE.pdf?expires_on=1785445163&amp;signature=3iykl5j7T%2F2Y66QAWbmji4%2FletFM86jUrmcYyIMuRGg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e93d351e-ee9f-4c5b-a064-86d8d270c79c/M03-2026-LIANDRASIMOESANDRADE.pdf?expires_on=1785445264&amp;signature=9%2BLg5ud28JOom3SOh3AoLUuDOJsUSJWL84sDF7JiH80%3D</t>
         </is>
       </c>
       <c r="V276">
@@ -36732,7 +36732,7 @@
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/78175ac0-ba4c-4491-95af-85e37ce609d6/LAUDOLILIANEOLIVEIRA.pdf?expires_on=1785445163&amp;signature=wnG%2FQ0AEQD%2FONB8AGWkD74VawSiTRjVvWuuxk0wUT0k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/78175ac0-ba4c-4491-95af-85e37ce609d6/LAUDOLILIANEOLIVEIRA.pdf?expires_on=1785445264&amp;signature=XvsIFZeI9BYoRpevCQ57NO1lBPC5P7PX3xVjM9c1nv0%3D</t>
         </is>
       </c>
       <c r="V277">
@@ -36859,7 +36859,7 @@
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c9572df0-c295-4af0-84b7-59f8390b6a33/LAUDOLIZANDRA.pdf?expires_on=1785445163&amp;signature=7lv5gddHrxcz%2BleYpcxozR1VTHDFrdHTZhbL8ud3b7U%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c9572df0-c295-4af0-84b7-59f8390b6a33/LAUDOLIZANDRA.pdf?expires_on=1785445264&amp;signature=eEHBCBvEfWmanpuMB6nx%2BDoo192QEYDoQsIDMz%2F6tzM%3D</t>
         </is>
       </c>
       <c r="V278">
@@ -36988,7 +36988,7 @@
       </c>
       <c r="U279" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0c32db42-3c2d-4e82-bcdf-ee3e1e4642dd/Laudo_AC_07-2026_-_LOURISMAR_MOTA_DE_ANDRADE_assinado.pdf?expires_on=1785445163&amp;signature=gOoAbldv68IGdzhaitkp1GQnO6rgp2%2FzxK6Z5rNyz4U%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0c32db42-3c2d-4e82-bcdf-ee3e1e4642dd/Laudo_AC_07-2026_-_LOURISMAR_MOTA_DE_ANDRADE_assinado.pdf?expires_on=1785445264&amp;signature=gFLoLfryqvX8xA0Qc2cSFcFB24NCKLvB%2FDzcNulimME%3D</t>
         </is>
       </c>
       <c r="V279">
@@ -37117,7 +37117,7 @@
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/bf42a80f-c835-46c0-9f47-03cc49f8ab5e/M25-2026-LUCAS.pdf?expires_on=1785445163&amp;signature=KUquhJ1FJLUKVEW%2BCDE%2BE%2FFhNdIxbxgLLSCIasmeP3c%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/bf42a80f-c835-46c0-9f47-03cc49f8ab5e/M25-2026-LUCAS.pdf?expires_on=1785445264&amp;signature=jIo74nvcTPL9FFj2d%2BLnPCuBdXCy%2F7shJxpcK2n7VC4%3D</t>
         </is>
       </c>
       <c r="V280">
@@ -37243,7 +37243,7 @@
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4673b4e7-a446-4d17-84eb-15204c8d504a/LaudoMAN07-Bemol-2026-LucasEmanuelMenezesDaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=jpQAZtAi%2FwwMIdMuRZbNHNJebSXIRuEmVAdMvSaGDWQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4673b4e7-a446-4d17-84eb-15204c8d504a/LaudoMAN07-Bemol-2026-LucasEmanuelMenezesDaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=%2B3EnSKPsWMtZBB7Bb6AMe6g6bqZjS3zCIivKPLVH%2Bxs%3D</t>
         </is>
       </c>
       <c r="V281">
@@ -37374,7 +37374,7 @@
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/01776b88-00aa-47b8-a354-40ea5c6624a7/Laudo_AC_20-2026_-_LUCIANO_SILVA_DE_OLIVEIRA_assinado.pdf?expires_on=1785445163&amp;signature=GbJINu4yd%2BzMbVPHZLoYit19QA%2FXYB%2FOuFsLSMS9hL8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/01776b88-00aa-47b8-a354-40ea5c6624a7/Laudo_AC_20-2026_-_LUCIANO_SILVA_DE_OLIVEIRA_assinado.pdf?expires_on=1785445264&amp;signature=DwMODCwW5tf%2Fbmgcp4iUzSpvOB%2FXlg1CMCOnLEviDz0%3D</t>
         </is>
       </c>
       <c r="V282">
@@ -37497,7 +37497,7 @@
       </c>
       <c r="U283" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/85fefdea-23eb-40e2-b07f-356afda61752/LaudoITA16-Bemol-2026-LucimaraMoraesdeMeloFerreira-Assinado.pdf?expires_on=1785445163&amp;signature=XwGmSUWVB%2BYuayOG5oCQRjXWxMKBEOYzCgfI28R%2BO2s%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/85fefdea-23eb-40e2-b07f-356afda61752/LaudoITA16-Bemol-2026-LucimaraMoraesdeMeloFerreira-Assinado.pdf?expires_on=1785445264&amp;signature=6BN%2Fpd05ZPn%2BTUWiWdXAauPcrm4QFStIFaErYyzJX3U%3D</t>
         </is>
       </c>
       <c r="V283">
@@ -37623,7 +37623,7 @@
       </c>
       <c r="U284" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e72b7a5e-51ec-4d8b-a69e-1ac05dec87a6/M01-2026-LUCYLENEPEREIRASILVAajuste02.pdf?expires_on=1785445163&amp;signature=U%2BwQdpynHXIRrzLO%2F0toOCcnOfCGd%2BcpA91n56MgM54%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e72b7a5e-51ec-4d8b-a69e-1ac05dec87a6/M01-2026-LUCYLENEPEREIRASILVAajuste02.pdf?expires_on=1785445264&amp;signature=RTxTMU14yKUdQcfEsfYJ1rG8tgvYZ2uJTQLRXaoW%2FLc%3D</t>
         </is>
       </c>
       <c r="V284">
@@ -37752,7 +37752,7 @@
       </c>
       <c r="U285" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/00beab08-f07e-438a-8591-56c5da193dab/LAUDOCORRIGIDOLUIZCLAUDIO.pdf?expires_on=1785445163&amp;signature=52bkK%2BFVH2siVDRMVScEjP8FDxLXTyy1PxfQzagkpuM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/00beab08-f07e-438a-8591-56c5da193dab/LAUDOCORRIGIDOLUIZCLAUDIO.pdf?expires_on=1785445264&amp;signature=iWbsSc27RGM3kCUHlZ3twT5yAuhQGD9uHsR8e2OT2PE%3D</t>
         </is>
       </c>
       <c r="V285">
@@ -37883,7 +37883,7 @@
       </c>
       <c r="U286" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e36cb59c-0bf9-441a-bca2-a7e482279dd7/LAUDOMAIQUE.pdf?expires_on=1785445163&amp;signature=koofKsH5oCcYENGn2LnbYNhXVLXXDOIj9t75yBw7PYA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e36cb59c-0bf9-441a-bca2-a7e482279dd7/LAUDOMAIQUE.pdf?expires_on=1785445264&amp;signature=OTa4cjU4FyE%2BSdnfa5husimVnXkwVw4uJb256MliqdM%3D</t>
         </is>
       </c>
       <c r="V286">
@@ -38010,7 +38010,7 @@
       </c>
       <c r="U287" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/702cee98-29a4-45c7-a98b-fac086e165d2/LaudoA13-Bemol-2026-ManoelBarbosadosSantosFilho_signed.pdf?expires_on=1785445163&amp;signature=%2FvgO8bjD5O29aahzWAcsiU4x29EdPU0H%2F88WHUR5Yfg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/702cee98-29a4-45c7-a98b-fac086e165d2/LaudoA13-Bemol-2026-ManoelBarbosadosSantosFilho_signed.pdf?expires_on=1785445264&amp;signature=FXUJNuKJoP8%2F6hJeRNuXjsXBI06kh%2Fo%2BzBM3705fmfQ%3D</t>
         </is>
       </c>
       <c r="V287">
@@ -38128,7 +38128,7 @@
       </c>
       <c r="U288" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9477ddfb-29ad-40ca-8f39-8dda636c6eca/Laudo106-Bemol-2026-MaraLindolfoGomes.pdf?expires_on=1785445163&amp;signature=n6UBkObSyLTVFCrX6yYlHuBF4trxIeV%2FYaTQy8MaZEU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9477ddfb-29ad-40ca-8f39-8dda636c6eca/Laudo106-Bemol-2026-MaraLindolfoGomes.pdf?expires_on=1785445264&amp;signature=Gxe7hvIeiel%2FKMwZtn9a%2BkRPLL4p54qgAjneb5L9%2BTo%3D</t>
         </is>
       </c>
       <c r="V288">
@@ -38269,7 +38269,7 @@
       </c>
       <c r="U289" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f5caf246-e228-41a7-bf46-0334613fbf28/Laudo_AC_68-2025_assinado1.pdf?expires_on=1785445163&amp;signature=adQCHg16tuuaYLw%2Bv58CqJ%2F9N%2FEiXE22xzhCREacqvs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f5caf246-e228-41a7-bf46-0334613fbf28/Laudo_AC_68-2025_assinado1.pdf?expires_on=1785445264&amp;signature=74sN3jk4Wi3kmOK9RHJ9pQhoAR3dF%2BlYP84PVk2n4LY%3D</t>
         </is>
       </c>
       <c r="V289">
@@ -38409,7 +38409,7 @@
       </c>
       <c r="U290" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c5e2cb6f-067e-45c0-9a3b-6cca00097d4e/Laudo208-Bemol-2026-MarceloBatistaMotta-Assinadoajustado.pdf?expires_on=1785445163&amp;signature=cDIUYdle4rjnM7YtncNANkR%2BwO6XWViW3uivF%2BB%2BbZI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c5e2cb6f-067e-45c0-9a3b-6cca00097d4e/Laudo208-Bemol-2026-MarceloBatistaMotta-Assinadoajustado.pdf?expires_on=1785445264&amp;signature=f9rWIPrvj8VxADLpfTNyxgqwis6mVm5FoZFINUe3WB8%3D</t>
         </is>
       </c>
       <c r="V290">
@@ -38543,7 +38543,7 @@
       </c>
       <c r="U291" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/84bd3365-968b-4a72-9c39-5864a865401b/LAUDOMARCELO.pdf?expires_on=1785445163&amp;signature=mymYC3UcRmQOHMNP1pjyWZjaMxYzXu0ewMC9f1vZIxI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/84bd3365-968b-4a72-9c39-5864a865401b/LAUDOMARCELO.pdf?expires_on=1785445264&amp;signature=yk9MbqtnebpUqNfjT8OnJGeGSjPUbFlNtZ9IcmGXFJk%3D</t>
         </is>
       </c>
       <c r="V291">
@@ -38685,7 +38685,7 @@
       </c>
       <c r="U292" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/989623be-06f7-43f9-add6-ae7f521d4740/BEMOL-PV073-MARCIASOUZADASILVA.pdf?expires_on=1785445163&amp;signature=QlZhhRJi6%2BflV4V0%2B8bXTSSow5Iw2ED5JSXUC%2BmpeaA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/989623be-06f7-43f9-add6-ae7f521d4740/BEMOL-PV073-MARCIASOUZADASILVA.pdf?expires_on=1785445264&amp;signature=7Tjs%2FXFmkqKXuQZpjCKZ146ZZu21PhMeh9viAEKDkh8%3D</t>
         </is>
       </c>
       <c r="V292">
@@ -38820,7 +38820,7 @@
       </c>
       <c r="U293" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/40cb37e9-67f2-4604-b382-8ac209843588/Laudo146-Bemol-2026-MarcioDaSilvaRocha-Assinado.pdf?expires_on=1785445163&amp;signature=HWh0gErzdzT0CmIFe5A%2FN6HrJpFcij4ocbbYLcOpobE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/40cb37e9-67f2-4604-b382-8ac209843588/Laudo146-Bemol-2026-MarcioDaSilvaRocha-Assinado.pdf?expires_on=1785445264&amp;signature=ikqZ4JxvQXY9%2BoDsG8ZGZGc38MGrWLB0wragtrPZKj4%3D</t>
         </is>
       </c>
       <c r="V293">
@@ -38938,7 +38938,7 @@
       </c>
       <c r="U294" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/abf6b4df-ae4e-4b23-84da-e0c88652c21a/Laudo195-Bemol-2026-MarcioRomuloSousaRodrigues-Assinado.pdf?expires_on=1785445163&amp;signature=A7M0gVcrMHqHC8vqAWOlUI1mP%2B%2FgplYFwBC1J4m5OKA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/abf6b4df-ae4e-4b23-84da-e0c88652c21a/Laudo195-Bemol-2026-MarcioRomuloSousaRodrigues-Assinado.pdf?expires_on=1785445264&amp;signature=LZNPucdSqwIoK0TxN0re42Tavy2Yb8n8tbKdZOiTcl8%3D</t>
         </is>
       </c>
       <c r="V294">
@@ -39056,7 +39056,7 @@
       </c>
       <c r="U295" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/488c405c-0f90-456c-82c2-4c7f48712df8/Laudo_AC_18-2026_-_MARCLEISON_JOSE_FACANHA_DA_SILVA_assinado.pdf?expires_on=1785445163&amp;signature=zzlaSop49ATA4ZUbJJXmq16zsqbVwZo8vlhaXt90PKQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/488c405c-0f90-456c-82c2-4c7f48712df8/Laudo_AC_18-2026_-_MARCLEISON_JOSE_FACANHA_DA_SILVA_assinado.pdf?expires_on=1785445264&amp;signature=NTcF2RzCbLrnxuuUrHRhItAXCfFMjXD%2FyvHuELCT8wc%3D</t>
         </is>
       </c>
       <c r="V295">
@@ -39188,7 +39188,7 @@
       </c>
       <c r="U296" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/75f87a88-1433-446c-acdc-913951147d2d/Laudo124-Bemol-2026-MarcoAurelioEspindolaLimaJunior.pdf?expires_on=1785445163&amp;signature=8zYz41H0tA11iQwY6WdxhAeCNKY4lqSky79IaKk%2BtHo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/75f87a88-1433-446c-acdc-913951147d2d/Laudo124-Bemol-2026-MarcoAurelioEspindolaLimaJunior.pdf?expires_on=1785445264&amp;signature=Eygq5M0KbcO%2FfxWMNnAnwrwoo%2Frr6qdMavzH68ernuE%3D</t>
         </is>
       </c>
       <c r="V296">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="U297" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/75b0c736-29a3-4de6-b907-a5e31a9e212a/BEMOL-AR025-MARCOSJOSEDOSSANTOS.pdf?expires_on=1785445163&amp;signature=StThiPV4BnJsLgVivEUL%2F04V%2BWuf3O54dZ1eCq6g1bw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/75b0c736-29a3-4de6-b907-a5e31a9e212a/BEMOL-AR025-MARCOSJOSEDOSSANTOS.pdf?expires_on=1785445264&amp;signature=%2Bn6OYHyvNNIvCDPDGGStB4tTjAyICFqFLNEmCRXNR38%3D</t>
         </is>
       </c>
       <c r="V297">
@@ -39439,7 +39439,7 @@
       </c>
       <c r="U298" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5dcfd913-bbca-4933-acfe-9c8a4d7c67e0/LAUDOMARCOSSENA.pdf?expires_on=1785445163&amp;signature=EdYFfIgRySTwRCAtWKm0xcJNq2teqIMoOBnQc9QkNyA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5dcfd913-bbca-4933-acfe-9c8a4d7c67e0/LAUDOMARCOSSENA.pdf?expires_on=1785445264&amp;signature=6Nc06DbpniVeGI0Fl1jLtsOJ3yUCwCEw5fewi3Ttcbc%3D</t>
         </is>
       </c>
       <c r="V298">
@@ -39575,7 +39575,7 @@
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/59501b5e-240f-4121-b2e9-d91ca2559083/Laudo87-Bemol-2026-MarcusJoseQueirozFerreira-Assinado.pdf?expires_on=1785445163&amp;signature=78WtiNSzlMKy5ZQrDPVneBWFDao6wrSDHgkgY0Hgt18%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/59501b5e-240f-4121-b2e9-d91ca2559083/Laudo87-Bemol-2026-MarcusJoseQueirozFerreira-Assinado.pdf?expires_on=1785445264&amp;signature=LCmg6R7xcFV%2FcUAv0kDXK8yInpp59ngOcRuR%2FfKg7I8%3D</t>
         </is>
       </c>
       <c r="V299">
@@ -39704,7 +39704,7 @@
       </c>
       <c r="U300" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/18f92f5b-5095-4626-9698-ea475b991094/Laudo_AC_26-2026_-_MARIA_ALZENIRA_BONIFACIO_DA_SILVA_assinado.pdf?expires_on=1785445163&amp;signature=6%2FovvaGxabXhZLfsjQHEhCOhXPQUGmqXsqtVDJnFN6E%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/18f92f5b-5095-4626-9698-ea475b991094/Laudo_AC_26-2026_-_MARIA_ALZENIRA_BONIFACIO_DA_SILVA_assinado.pdf?expires_on=1785445264&amp;signature=eApewLnA6tK8WfpQnBPYZlsDfDD5TH07XlUjPhBwM%2FQ%3D</t>
         </is>
       </c>
       <c r="V300">
@@ -39830,7 +39830,7 @@
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ebf883e2-2f7f-4aea-b252-a41bee85ae54/LaudoJP09-Bemol-2026-MariaAparecidaJoseBarbosa_signed.pdf?expires_on=1785445163&amp;signature=w3nCPIlOJCykJYS7MAVQG%2FQ35kGA3AYkEf5YOJ1BQvI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ebf883e2-2f7f-4aea-b252-a41bee85ae54/LaudoJP09-Bemol-2026-MariaAparecidaJoseBarbosa_signed.pdf?expires_on=1785445264&amp;signature=IEce1RrAneOAseWaoj8ZKuAuH5w95Vw7yq3ePyZXmfQ%3D</t>
         </is>
       </c>
       <c r="V301">
@@ -39967,7 +39967,7 @@
       </c>
       <c r="U302" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e233ac0a-899d-42ec-b244-ca470c80f0e0/LaudoP35-Bemol-2026-MariaArleneAlvesCavalcantePietrobeli_signed.pdf?expires_on=1785445163&amp;signature=Y7g%2FboSwR6zV9hlXBQLX11QmooqBGdadICtFL64E5Vo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e233ac0a-899d-42ec-b244-ca470c80f0e0/LaudoP35-Bemol-2026-MariaArleneAlvesCavalcantePietrobeli_signed.pdf?expires_on=1785445264&amp;signature=SKVTEx3hhADMvV2e%2B%2BHq8I7boXSvwbtq2J9eOexol44%3D</t>
         </is>
       </c>
       <c r="V302">
@@ -40096,7 +40096,7 @@
       </c>
       <c r="U303" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e095a2b6-f97b-421b-962a-6e32da7deddf/Laudo202-Bemol-2026-MariaAssuncaodaSilvaAlfaia-Assinado.pdf?expires_on=1785445163&amp;signature=YxlAyIGltCfXZlrglhEyCNC0Lz5UcdZjv7FLW%2B2FGV8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e095a2b6-f97b-421b-962a-6e32da7deddf/Laudo202-Bemol-2026-MariaAssuncaodaSilvaAlfaia-Assinado.pdf?expires_on=1785445264&amp;signature=uKkL18AD2HaQHyngsZy6Kr2f7bDCQ3AmOKD%2BXAVFCzU%3D</t>
         </is>
       </c>
       <c r="V303">
@@ -40222,7 +40222,7 @@
       </c>
       <c r="U304" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b6aac934-c406-4470-93f1-187fcfd0cc05/Laudo71-Bemol-2026-MariaAuxiliadoraDosSantosFreire-Assinado.pdf?expires_on=1785445163&amp;signature=wqARE3WIekA23VCE0K%2BmAnk%2BEenxRvsqKs%2BQcOu6njA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b6aac934-c406-4470-93f1-187fcfd0cc05/Laudo71-Bemol-2026-MariaAuxiliadoraDosSantosFreire-Assinado.pdf?expires_on=1785445264&amp;signature=twkhOcBwYjOq%2BmdvmgCBEYmKvwSR6ng376r%2FULvJ4BY%3D</t>
         </is>
       </c>
       <c r="V304">
@@ -40356,7 +40356,7 @@
       </c>
       <c r="U305" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1d3061c5-cecb-4711-9151-c91be3c95c96/LaudoP08-Bemol-2026-MariaDaConceicaoAguiarLeiteDeLima_signed.pdf?expires_on=1785445163&amp;signature=oUneqAVWg%2BGwEi2z%2FpbLrBV5sSJzFFOR7WTS7mY%2FsW4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1d3061c5-cecb-4711-9151-c91be3c95c96/LaudoP08-Bemol-2026-MariaDaConceicaoAguiarLeiteDeLima_signed.pdf?expires_on=1785445264&amp;signature=dve23P3qamKiP34%2FLNARsE2pw6bPiavlW3Bpri7kThM%3D</t>
         </is>
       </c>
       <c r="V305">
@@ -40479,7 +40479,7 @@
       </c>
       <c r="U306" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/dd88613a-1fcd-48ee-9de8-35f993dcfef6/B9-2026-BEMOL-MARIADASGRAASCEZARIODAVILA_2.PDF?expires_on=1785445163&amp;signature=EAH72TpPilWEcjohQSPfnvodXyIPYjyI2gf3rUdoG1s%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/dd88613a-1fcd-48ee-9de8-35f993dcfef6/B9-2026-BEMOL-MARIADASGRAASCEZARIODAVILA_2.PDF?expires_on=1785445264&amp;signature=%2BglkVUZIBhpXcNcj24RsE76nvTspfIy%2FP8eNOY4bSRs%3D</t>
         </is>
       </c>
       <c r="V306">
@@ -40610,7 +40610,7 @@
       </c>
       <c r="U307" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cab14ac9-6a56-4849-a10c-6152088d26df/LaudoP14-Bemol-2026-MariaDeFatimaVieiraFrazao_signed.pdf?expires_on=1785445163&amp;signature=bcQfmW6OHmWeLnFJ26eWKZMUKIGW9%2BD90j2DhOyt3X4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cab14ac9-6a56-4849-a10c-6152088d26df/LaudoP14-Bemol-2026-MariaDeFatimaVieiraFrazao_signed.pdf?expires_on=1785445264&amp;signature=If8HMA8XhlNqX1zpWJpzyyWR6MzVMKG%2B0z8IUUn9wos%3D</t>
         </is>
       </c>
       <c r="V307">
@@ -40734,7 +40734,7 @@
       </c>
       <c r="U308" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ff304689-adf2-4093-b0be-aecc6313af56/Laudo_AC_33-2026_-_MARIA_DE_JESUS_LIMA_FELIPE_assinado.pdf?expires_on=1785445163&amp;signature=l2tq6s9AwzgMLzu5zCTFr%2F9wpWNUyiU%2F0oejk1dTofw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ff304689-adf2-4093-b0be-aecc6313af56/Laudo_AC_33-2026_-_MARIA_DE_JESUS_LIMA_FELIPE_assinado.pdf?expires_on=1785445264&amp;signature=TQqS%2FydkmlBDAtIZE6CkKopxyuXgw7%2FNxRj7h4Ruj4s%3D</t>
         </is>
       </c>
       <c r="V308">
@@ -40860,7 +40860,7 @@
       </c>
       <c r="U309" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c55fb3c0-a15d-418a-adf5-ca601b20fd7d/Laudo483-Bemol-2025-MariaDeLourdesOliveiraDosSantos-Assinado.pdf?expires_on=1785445163&amp;signature=7lulyZp%2FBmJGBWT3ue8lsAuCoa%2B%2BtJSHrZS4AIvX%2Fpc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c55fb3c0-a15d-418a-adf5-ca601b20fd7d/Laudo483-Bemol-2025-MariaDeLourdesOliveiraDosSantos-Assinado.pdf?expires_on=1785445264&amp;signature=lSfQK%2FfL17yC1ojrGhyZm4vvQ4T3wvUGXGpfmLxVD1Q%3D</t>
         </is>
       </c>
       <c r="V309">
@@ -40995,7 +40995,7 @@
       </c>
       <c r="U310" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/82e2bfef-4c26-4ff1-a502-d802344e71e8/LAUDOMARIADENAZARcorrigido.pdf?expires_on=1785445163&amp;signature=Rrn4PW%2FqMAjl6vJwLm%2BthltuoP9fk3vEDts6Zumj29U%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/82e2bfef-4c26-4ff1-a502-d802344e71e8/LAUDOMARIADENAZARcorrigido.pdf?expires_on=1785445264&amp;signature=73Sn2vLgohfkJSPnJ4GjGnbI43ZH5qXbnKeVSrIcarg%3D</t>
         </is>
       </c>
       <c r="V310">
@@ -41127,7 +41127,7 @@
       </c>
       <c r="U311" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4ebdc764-7aae-430f-859d-fd287b74f5c4/RelatriodeRefernciaRVR06-Bemol-2025-MariaDoPerpetuoSocorroNoronhaPeixoto-Assinado.pdf?expires_on=1785445163&amp;signature=6QBNPX9Hcg0oMsi%2FJNLrmkVrjVsidoFAY5RFga6ft54%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4ebdc764-7aae-430f-859d-fd287b74f5c4/RelatriodeRefernciaRVR06-Bemol-2025-MariaDoPerpetuoSocorroNoronhaPeixoto-Assinado.pdf?expires_on=1785445264&amp;signature=PciizWFemleEWLiOCNa9yyVlG2XHEmyirE9Fl52A%2Bu4%3D</t>
         </is>
       </c>
       <c r="V311">
@@ -41256,7 +41256,7 @@
       </c>
       <c r="U312" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/742ca05a-a665-4c71-a272-4e082a6347fe/M15-2026-MARIADOSOCORROajustado.pdf?expires_on=1785445163&amp;signature=NFcGS4QzoudDO0mfXL5kdh9LKaUVr63XrGaj1V13ZWY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/742ca05a-a665-4c71-a272-4e082a6347fe/M15-2026-MARIADOSOCORROajustado.pdf?expires_on=1785445264&amp;signature=l84aeobh5PK5aCQ7K9UNgP4vcQrUEuvEpa0U0FDJcGU%3D</t>
         </is>
       </c>
       <c r="V312">
@@ -41382,7 +41382,7 @@
       </c>
       <c r="U313" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3897fd9c-1b1c-409e-a1e3-4693c1e2031b/LaudoPA01-Bemol-2026-MariaDulcileneReisdeSouza-Assinado1.pdf?expires_on=1785445163&amp;signature=weQfauLl9DiInR%2Bks58%2FbthTEYbBGYbpGUZGhTdTCCg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3897fd9c-1b1c-409e-a1e3-4693c1e2031b/LaudoPA01-Bemol-2026-MariaDulcileneReisdeSouza-Assinado1.pdf?expires_on=1785445264&amp;signature=F%2FBfVP958tc2Rdo%2BvXrcY2Wi%2B%2FxV1qN66%2B4rJ%2FnRiVs%3D</t>
         </is>
       </c>
       <c r="V313">
@@ -41526,7 +41526,7 @@
       </c>
       <c r="U314" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7ed173fa-cddd-4d05-8f4f-902f54d5ca8a/laudoB46-2026-BEMOL-MARIAFERNANDALARRANAGASEGOVIA.pdf?expires_on=1785445163&amp;signature=8%2BNwCKMTtoM%2BTHlfPrkyLFny9U7NHl76Nf9E5%2BS4KKs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7ed173fa-cddd-4d05-8f4f-902f54d5ca8a/laudoB46-2026-BEMOL-MARIAFERNANDALARRANAGASEGOVIA.pdf?expires_on=1785445264&amp;signature=lXdoW2mF3SmB8%2BZjxP%2FwItvOHBjgQmLdzofhMHDHm6o%3D</t>
         </is>
       </c>
       <c r="V314">
@@ -41657,7 +41657,7 @@
       </c>
       <c r="U315" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c7d38b5a-cbf9-4dda-aa89-7ed36b998de7/LAUDOMARIAFRANCISCA.pdf?expires_on=1785445163&amp;signature=DdYuP4SxV6yJyYL437q0kh8CWCRXyxRdTpIKugukV1A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c7d38b5a-cbf9-4dda-aa89-7ed36b998de7/LAUDOMARIAFRANCISCA.pdf?expires_on=1785445264&amp;signature=YfkUgSB%2FBfLXi6u5MNo5frjX%2F1OV45x7XQHhPs64Hgg%3D</t>
         </is>
       </c>
       <c r="V315">
@@ -41794,7 +41794,7 @@
       </c>
       <c r="U316" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2d546a2b-3b56-41e1-a9c7-8913a61d5532/Laudo_AC_08-2026_-_MARIA_HELENA_BRAGA_PINHEIRO_assinado.pdf?expires_on=1785445163&amp;signature=SoRAADErM9g7ezilrqV76OeeEikTdb%2BxIiQg%2FFpWekI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2d546a2b-3b56-41e1-a9c7-8913a61d5532/Laudo_AC_08-2026_-_MARIA_HELENA_BRAGA_PINHEIRO_assinado.pdf?expires_on=1785445264&amp;signature=A3qvPW52n1VWBxOIsvBDwJMQDkxl4D3IMH9SMlBvTQ8%3D</t>
         </is>
       </c>
       <c r="V316">
@@ -41931,7 +41931,7 @@
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e79fdb40-909f-4b3a-8481-13e641450f31/M7-2026-MARIAINESSOARESJACINTOajustado.pdf?expires_on=1785445163&amp;signature=7U32ZcUVvSyi68uteqoyZt%2BH6eSCxj9zCkPAtnk%2BdA4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e79fdb40-909f-4b3a-8481-13e641450f31/M7-2026-MARIAINESSOARESJACINTOajustado.pdf?expires_on=1785445264&amp;signature=pGp%2FCq4PudPg7jrYcDw33pN5VGVCdl0MwsY4x8CUiws%3D</t>
         </is>
       </c>
       <c r="V317">
@@ -42062,7 +42062,7 @@
       </c>
       <c r="U318" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/26d64727-9685-4583-8a1e-089c96c70bb9/LAUDOMARIAITAEMA.pdf?expires_on=1785445163&amp;signature=vfDjgvtWa1jNk4nyQ3BdDiYF11Z91KGBPQqlWmJvMYQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/26d64727-9685-4583-8a1e-089c96c70bb9/LAUDOMARIAITAEMA.pdf?expires_on=1785445264&amp;signature=3ltwsYzu5iF0CsWTpsmsZZfaEbcaO%2FX8WansiNXg%2FOI%3D</t>
         </is>
       </c>
       <c r="V318">
@@ -42199,7 +42199,7 @@
       </c>
       <c r="U319" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6dfdf02b-74f0-4e41-a6bf-33541f0becc3/LAUDOMariaIvone.pdf?expires_on=1785445163&amp;signature=hu4Uj%2Bic3%2Fvd9jj7tReCW%2Fe2%2BgwQps%2B9myacrWoFmhE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6dfdf02b-74f0-4e41-a6bf-33541f0becc3/LAUDOMariaIvone.pdf?expires_on=1785445264&amp;signature=Qlvl7ysCQ0I9iKZTIIAiLWPkGMlU6r5tRi0JvfwGN1I%3D</t>
         </is>
       </c>
       <c r="V319">
@@ -42323,7 +42323,7 @@
       </c>
       <c r="U320" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1488dcea-b0af-4f7b-90cc-43750768830d/BEMOL-PV094-MARIAIVONEDESOUZAMARTINS.pdf?expires_on=1785445163&amp;signature=MlQ7D8DrdA01qdnoMF9IkysLWq9EdCB3BULCbmj4DP8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1488dcea-b0af-4f7b-90cc-43750768830d/BEMOL-PV094-MARIAIVONEDESOUZAMARTINS.pdf?expires_on=1785445264&amp;signature=Ctaxwp2axbMmLwrE33ROfTZ8F%2BbTNZ12i5Mt6RAQP7g%3D</t>
         </is>
       </c>
       <c r="V320">
@@ -42455,7 +42455,7 @@
       </c>
       <c r="U321" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e90feef1-e03d-4eb1-9742-f968486ba251/Laudo_AC_-_04-2026_-_MARIA_JACINTA_DE_SOUZA_assinado.pdf?expires_on=1785445163&amp;signature=8DCt%2BfWSCDXtbk8vGMvEIGLE2T7Bh8Y4HL0uf%2BtTuRQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e90feef1-e03d-4eb1-9742-f968486ba251/Laudo_AC_-_04-2026_-_MARIA_JACINTA_DE_SOUZA_assinado.pdf?expires_on=1785445264&amp;signature=mVflFoz9EmSTZ8AD59DwMKt438VxqNwQHDQCt2VfDa4%3D</t>
         </is>
       </c>
       <c r="V321">
@@ -42597,7 +42597,7 @@
       </c>
       <c r="U322" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/dc51577b-2631-4975-8584-9becda3d52e2/Laudo147-Bemol-2026-MariaJosePiresCorrea.pdf?expires_on=1785445163&amp;signature=YOUqj%2BvEtVZA%2FxMKf5qps2erqZbIVXo3SEH4TTp0rvo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/dc51577b-2631-4975-8584-9becda3d52e2/Laudo147-Bemol-2026-MariaJosePiresCorrea.pdf?expires_on=1785445264&amp;signature=kHfGUnQMWYJxhq4cicfYbDw80FrvNQmAt0J25yY1mOk%3D</t>
         </is>
       </c>
       <c r="V322">
@@ -42734,7 +42734,7 @@
       </c>
       <c r="U323" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1ef0eda4-befd-4e84-92fb-074a2d65ecfc/LaudoB17-2026-BEMOL-MARIALUCIAFEITOSAFERREIRA.pdf?expires_on=1785445163&amp;signature=4%2B5zY17qOkqMDUU4cFMcrMyFFG1ygJePixCD8R5mc4s%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1ef0eda4-befd-4e84-92fb-074a2d65ecfc/LaudoB17-2026-BEMOL-MARIALUCIAFEITOSAFERREIRA.pdf?expires_on=1785445264&amp;signature=hAuaEVoVN3i8byDCZfuoNX0OLg5U33tnj1AtSf5PoRY%3D</t>
         </is>
       </c>
       <c r="V323">
@@ -42863,7 +42863,7 @@
       </c>
       <c r="U324" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0176fe84-495c-4590-a49f-aa8c95b5d25a/MARIALUZIADEARAJOGOMESLAUDO.pdf?expires_on=1785445163&amp;signature=tPlMb37E9EaMwx4rh7Lrml2MGiLfq8RsZnbHBdjyj%2FE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0176fe84-495c-4590-a49f-aa8c95b5d25a/MARIALUZIADEARAJOGOMESLAUDO.pdf?expires_on=1785445264&amp;signature=koLbZ3Ap34r5t9UBimJosHh%2BiAupsNjQk9aqk8JqtBg%3D</t>
         </is>
       </c>
       <c r="V324">
@@ -43006,7 +43006,7 @@
       </c>
       <c r="U325" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f41c57b3-2b18-4937-aea4-3f825fea861e/LaudoB34-2026-BEMOL-MARIAPONTESDEARAUJO.pdf?expires_on=1785445163&amp;signature=7oGpEsBsZz8dWmvHcVCrKX%2Fcon2PiRejnUagbTtxVyw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f41c57b3-2b18-4937-aea4-3f825fea861e/LaudoB34-2026-BEMOL-MARIAPONTESDEARAUJO.pdf?expires_on=1785445264&amp;signature=ptXA651%2Fqw3Ay%2B6NbfMFmS%2FKpcvornRNg4VHRTwPsDY%3D</t>
         </is>
       </c>
       <c r="V325">
@@ -43140,7 +43140,7 @@
       </c>
       <c r="U326" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/01fb9855-c9d4-43d1-946a-8878501765cc/LaudoPA16-Bemol-2026-MariaRaquelTravassosDeCarvalho.pdf?expires_on=1785445163&amp;signature=KiOHTKh980FaxUmr3t6IVFo8dNLdfL1AQx0tDWBukbc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/01fb9855-c9d4-43d1-946a-8878501765cc/LaudoPA16-Bemol-2026-MariaRaquelTravassosDeCarvalho.pdf?expires_on=1785445264&amp;signature=weiHJW3QyjPuSCPhxiyNRMZz6FbahuEbkAOYLl8Jq4A%3D</t>
         </is>
       </c>
       <c r="V326">
@@ -43266,7 +43266,7 @@
       </c>
       <c r="U327" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2be0b85f-6106-432d-b849-622ad4c020fd/Laudo17-Bemol-2026-MariaRobertinaDosSantosDaSilva-Assinadocorrigido.pdf?expires_on=1785445163&amp;signature=It2fm1nWNblVavyc8rXcKkA4%2BrasBOBq84WEXwLTWO4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2be0b85f-6106-432d-b849-622ad4c020fd/Laudo17-Bemol-2026-MariaRobertinaDosSantosDaSilva-Assinadocorrigido.pdf?expires_on=1785445264&amp;signature=PkX8FQrSpcTTF%2FUef4OZCKkp4v8y8XooyEAznKc%2B49M%3D</t>
         </is>
       </c>
       <c r="V327">
@@ -43404,7 +43404,7 @@
       </c>
       <c r="U328" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/25f8132e-7927-4fb6-afa7-a19ee524fab5/Laudo205-Bemol-2026-MariaSuzeirMatosdeAraujo.pdf?expires_on=1785445163&amp;signature=8jE9nwTMEmDBnIJWiekwHxeKpzD2z8GojN29yX34Em4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/25f8132e-7927-4fb6-afa7-a19ee524fab5/Laudo205-Bemol-2026-MariaSuzeirMatosdeAraujo.pdf?expires_on=1785445264&amp;signature=PSlnH14z88a6V1KxzEvOOLzI5xRunUgdFnuhPPDsmCI%3D</t>
         </is>
       </c>
       <c r="V328">
@@ -43533,7 +43533,7 @@
       </c>
       <c r="U329" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/89e4b8fb-6d1c-4b18-bc41-4769822c7418/Laudo27-Bemol-2026-MariaValcyDomingosDeOliveira-Assinado.pdf?expires_on=1785445163&amp;signature=crXzgKBYdUgkOBTwkn5gNFEcJw4Q6Mi3T91UkVydk1w%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/89e4b8fb-6d1c-4b18-bc41-4769822c7418/Laudo27-Bemol-2026-MariaValcyDomingosDeOliveira-Assinado.pdf?expires_on=1785445264&amp;signature=MgiRXxj6r%2BE4WBjoXD8PNIKwKCCGIuiSsaClmWFQKIU%3D</t>
         </is>
       </c>
       <c r="V329">
@@ -43675,7 +43675,7 @@
       </c>
       <c r="U330" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1cad3662-f03c-43ae-9d4f-684594cfd025/Laudo73-2025-Bemol-MarielzadaSilvaFerreira-Assinado11.pdf?expires_on=1785445163&amp;signature=xoB%2B4zdsKVruTOqCbjK0JrmWF%2BpyDUzAojg6hHfh7m0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1cad3662-f03c-43ae-9d4f-684594cfd025/Laudo73-2025-Bemol-MarielzadaSilvaFerreira-Assinado11.pdf?expires_on=1785445264&amp;signature=ExLrpjyNGJ5vhivx5b6gRuQC%2BlqZxo4jloHa670vmr4%3D</t>
         </is>
       </c>
       <c r="V330">
@@ -43807,7 +43807,7 @@
       </c>
       <c r="U331" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf95cf60-3c00-4a3e-a759-39ea4dd22760/LaudoPA20-Bemol-2026-MarileiaAraujodosSantos.pdf?expires_on=1785445163&amp;signature=zCezsPgCjsIsH1ypbvNa8TPf82PBgnax0boq1QbVjiU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cf95cf60-3c00-4a3e-a759-39ea4dd22760/LaudoPA20-Bemol-2026-MarileiaAraujodosSantos.pdf?expires_on=1785445264&amp;signature=Kx4nuemYs35nb5hwzn%2BQukO1WbHAwdcIjsImwIWnpPM%3D</t>
         </is>
       </c>
       <c r="V331">
@@ -43939,7 +43939,7 @@
       </c>
       <c r="U332" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/aecf4ecf-3b93-4133-970d-1739cf867dfd/LaudoB134-2025-BEMOL-MARILENAFERNANDESRIBEIRO.pdf?expires_on=1785445163&amp;signature=eD5vzS%2Fuzcr5Q3Tlve0tD9VnWmL9r%2BjxomtVONjQ8bw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/aecf4ecf-3b93-4133-970d-1739cf867dfd/LaudoB134-2025-BEMOL-MARILENAFERNANDESRIBEIRO.pdf?expires_on=1785445264&amp;signature=kZIIph4xOFdcyyy%2Fyag1PK6MwNCt5JnMDJGYfgXzBVw%3D</t>
         </is>
       </c>
       <c r="V332">
@@ -44085,7 +44085,7 @@
       </c>
       <c r="U333" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/dc55bd44-8950-4c50-baaa-6544f1d1f586/LAUDOCORRIGIDOMARILZA.pdf?expires_on=1785445163&amp;signature=3I81r%2Fs9PKrsVDvpjaQQ6vaErsvvhnvKdI9FtscYtWg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/dc55bd44-8950-4c50-baaa-6544f1d1f586/LAUDOCORRIGIDOMARILZA.pdf?expires_on=1785445264&amp;signature=eKKl1qo4Yyse7Q5oHaw94yUR2214lXJuEB4BhTe3YFg%3D</t>
         </is>
       </c>
       <c r="V333">
@@ -44222,7 +44222,7 @@
       </c>
       <c r="U334" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/815429c2-8ea7-4f05-a029-d9793ed024bd/Laudo154-Bemol-2026-MarioJorgeLouzadaCarvalhoSobrinho-Assinadoajustado.pdf?expires_on=1785445163&amp;signature=ATz%2B8TzyHodmW3tCVHEZjGtS4cW6XFZa5f3jjB7%2BZok%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/815429c2-8ea7-4f05-a029-d9793ed024bd/Laudo154-Bemol-2026-MarioJorgeLouzadaCarvalhoSobrinho-Assinadoajustado.pdf?expires_on=1785445264&amp;signature=DmdatczHZ5LThONKTUsNvHitTJ%2BIry9h8CUPdJfWhR0%3D</t>
         </is>
       </c>
       <c r="V334">
@@ -44348,7 +44348,7 @@
       </c>
       <c r="U335" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e0a77309-5262-4b3a-9110-b2e64bc37988/Laudo_AC_13-2026_-_MARIZELIA_PEREIRA_DE_SOUZA_assinado.pdf?expires_on=1785445163&amp;signature=sFV6pvrTelr3ctnEI2cLs6GXc94zkOmxkrkAbWGTkuE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e0a77309-5262-4b3a-9110-b2e64bc37988/Laudo_AC_13-2026_-_MARIZELIA_PEREIRA_DE_SOUZA_assinado.pdf?expires_on=1785445264&amp;signature=j2N82xMh%2FgttXzYlt6K9UO2FIDIvExHHkbL1wRhjIcg%3D</t>
         </is>
       </c>
       <c r="V335">
@@ -44479,7 +44479,7 @@
       </c>
       <c r="U336" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/bdbeccee-6613-48e7-a1f7-3c17a756b47b/Laudo484-Bemol-2025-MauricioAlexCastro-Assinado.pdf?expires_on=1785445163&amp;signature=FGV2AaIFoXUeZq8m1OUUCAtndB2dXpNZIORIrrY2QAc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/bdbeccee-6613-48e7-a1f7-3c17a756b47b/Laudo484-Bemol-2025-MauricioAlexCastro-Assinado.pdf?expires_on=1785445264&amp;signature=zT0seBD%2BlQQp2AgyDPYXckGQRtuc%2BdKqiMnPMPBwh08%3D</t>
         </is>
       </c>
       <c r="V336">
@@ -44619,7 +44619,7 @@
       </c>
       <c r="U337" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e3911817-dca4-4120-a786-d15a97470ae5/Laudo93-Bemol-2026-MerciaTatielleDosSantosPereira-Assinado.pdf?expires_on=1785445163&amp;signature=DLr86J3z5S%2FdPbJaVCKIMP45Rj3ZwgpvfD1kJw8PK4k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e3911817-dca4-4120-a786-d15a97470ae5/Laudo93-Bemol-2026-MerciaTatielleDosSantosPereira-Assinado.pdf?expires_on=1785445264&amp;signature=POR1t3nORek60ymMkEBrzIJkqjtFDbA%2BCu2FxQY5n0o%3D</t>
         </is>
       </c>
       <c r="V337">
@@ -44757,7 +44757,7 @@
       </c>
       <c r="U338" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b2112f19-0019-4577-a273-dc2e41acb014/LaudoITA17-Bemol-2025-MilsonDaSilvaMatos-Assinado.pdf?expires_on=1785445163&amp;signature=F05FDXq16a3m5VETyt7VRmSR4IEsdV8y2bcdVeXn%2FTY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b2112f19-0019-4577-a273-dc2e41acb014/LaudoITA17-Bemol-2025-MilsonDaSilvaMatos-Assinado.pdf?expires_on=1785445264&amp;signature=iM6eS4ZejNRzZwB6mWVY1Eabjpkeo36ByB2o8CivWc8%3D</t>
         </is>
       </c>
       <c r="V338">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="U339" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b2da76eb-c630-4d64-b529-e207ec5274d5/BEMOL-AR029-MIQUEIASPEREIRALIMA.pdf?expires_on=1785445163&amp;signature=ErHiiqPbpUJ1q5m0KGnstY7L7OF3UgQZFZh6RyOSVw4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b2da76eb-c630-4d64-b529-e207ec5274d5/BEMOL-AR029-MIQUEIASPEREIRALIMA.pdf?expires_on=1785445264&amp;signature=%2F0hYKHnoEUwGamNsmzZcM07IFTHYVhO1X8dkVzG8G9c%3D</t>
         </is>
       </c>
       <c r="V339">
@@ -45026,7 +45026,7 @@
       </c>
       <c r="U340" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/713476f3-cbfc-4874-878b-5d07d66cacc8/Laudo_AC_01-2026_-_MIRLANE_NUNES_LEITE_assinado.pdf?expires_on=1785445163&amp;signature=QHiHrf4JIGuYuq0X9EfiAbX1GIYia5CV1r7KNvAjunE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/713476f3-cbfc-4874-878b-5d07d66cacc8/Laudo_AC_01-2026_-_MIRLANE_NUNES_LEITE_assinado.pdf?expires_on=1785445264&amp;signature=ARHc%2BSVg5SWjOmQtMmmalrIrgXMkLsmLig4LoeGFnY0%3D</t>
         </is>
       </c>
       <c r="V340">
@@ -45163,7 +45163,7 @@
       </c>
       <c r="U341" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/dbecde08-ca35-444e-8b4f-8ed06a8e1c19/LaudoB132-2024-BEMOL-NAIADSONPEREIRANASCIMENTO_2.pdf?expires_on=1785445163&amp;signature=zKJcmpdnPQ2Bd0KZvEg6iTIsqbJqheG%2FO4aHzymsM9s%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/dbecde08-ca35-444e-8b4f-8ed06a8e1c19/LaudoB132-2024-BEMOL-NAIADSONPEREIRANASCIMENTO_2.pdf?expires_on=1785445264&amp;signature=VK8XjooRfJ4mo%2BX1njjXkXo1Z2kMsbCT5rGXzPrDfFY%3D</t>
         </is>
       </c>
       <c r="V341">
@@ -45312,7 +45312,7 @@
       </c>
       <c r="U342" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/406a23dd-f506-456c-af1a-be9bd4ee11c4/B19-2026-BEMOL-NARACRISTINADASILVANUNES.pdf?expires_on=1785445163&amp;signature=I0Ltzuz1LbvWKLYvPp7wpnvbckFxibOcR%2FxMEmxBF%2FY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/406a23dd-f506-456c-af1a-be9bd4ee11c4/B19-2026-BEMOL-NARACRISTINADASILVANUNES.pdf?expires_on=1785445264&amp;signature=7ZuQnollskMmNaUPV1b7oHKBtqd045Cw2N1RSnw9ll8%3D</t>
         </is>
       </c>
       <c r="V342">
@@ -45441,7 +45441,7 @@
       </c>
       <c r="U343" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/927e466a-c43d-4bcb-9aad-fd878691e392/Laudo50-Bemol-2026-NarleyAdsonPaivaGuedes-Assinado.pdf?expires_on=1785445163&amp;signature=8D9h44Ic%2BYghGFnnyOy6dVy4Jwk%2BNnAvK4X%2FGQHDP3o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/927e466a-c43d-4bcb-9aad-fd878691e392/Laudo50-Bemol-2026-NarleyAdsonPaivaGuedes-Assinado.pdf?expires_on=1785445264&amp;signature=7M2vh4aAGH%2B6xwDzNBoSa5c0POqbaLtL4I83zrGO860%3D</t>
         </is>
       </c>
       <c r="V343">
@@ -45571,7 +45571,7 @@
       </c>
       <c r="U344" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e4619ba4-b243-47e3-b1bc-53dbd3d3000c/BEMOL-PV084-NATALIAGONALVESSANTOSFARIA.pdf?expires_on=1785445163&amp;signature=RaxEenAr3%2FRfY%2FGX6oDF0lyiHpIC1kNCYCrG4nLardM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e4619ba4-b243-47e3-b1bc-53dbd3d3000c/BEMOL-PV084-NATALIAGONALVESSANTOSFARIA.pdf?expires_on=1785445264&amp;signature=ljn6guffklkLAZSSI7GBeOGRzGY4fPYzhgT%2FEh5n%2BNc%3D</t>
         </is>
       </c>
       <c r="V344">
@@ -45694,7 +45694,7 @@
       </c>
       <c r="U345" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f8dc64fc-c4ec-47ce-a46e-4bf527db31c2/Laudo152-Bemol-2026-NatanCavalcanteGama.pdf?expires_on=1785445163&amp;signature=P5k95HI%2FRgKkA%2FAjfJo2Di9%2FinZQd0BymcZSuXBMc0s%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f8dc64fc-c4ec-47ce-a46e-4bf527db31c2/Laudo152-Bemol-2026-NatanCavalcanteGama.pdf?expires_on=1785445264&amp;signature=toON%2B7RP7Izn2aWFN2E4BrhCm2gkj10mt2QjbNVDj9Q%3D</t>
         </is>
       </c>
       <c r="V345">
@@ -45823,7 +45823,7 @@
       </c>
       <c r="U346" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6e94f045-e010-4542-bebf-ff40b226f280/Laudo57-Bemol-2026-NeimarRodriguesDaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=bRMSj2MZWNt069Zj7D%2Bdg7jVUVxWvN%2B6P4oYIVbfa3A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6e94f045-e010-4542-bebf-ff40b226f280/Laudo57-Bemol-2026-NeimarRodriguesDaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=8fDOw1SPRYn%2Fb8WQ92FHyYMsU03LItg%2BYeg%2BdRnXf50%3D</t>
         </is>
       </c>
       <c r="V346">
@@ -45957,7 +45957,7 @@
       </c>
       <c r="U347" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/bd20bab3-e8b5-4ac4-b46e-e12eb8aa2f69/Laudo378-Bemol-2025-ThaisDoNascimentoSantos-Assinado.pdf?expires_on=1785445163&amp;signature=C2GJCo1VUOUCjQ%2B%2Ba63NONBY71BftO4TBpejz3M1%2FaI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/bd20bab3-e8b5-4ac4-b46e-e12eb8aa2f69/Laudo378-Bemol-2025-ThaisDoNascimentoSantos-Assinado.pdf?expires_on=1785445264&amp;signature=f2xh53c%2B%2FXyLQftUxVjeqBHLSlkJobcj5WrxAmhowI8%3D</t>
         </is>
       </c>
       <c r="V347">
@@ -46105,7 +46105,7 @@
       </c>
       <c r="U348" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9bbfd341-5438-4cf5-8a27-6f1088766197/LAUDONILTONCEZAR.pdf?expires_on=1785445163&amp;signature=wEH6ym2%2FWsmRzYLlOxDkh7Xo6%2Ff0Z0UAAga3feNv2iE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9bbfd341-5438-4cf5-8a27-6f1088766197/LAUDONILTONCEZAR.pdf?expires_on=1785445264&amp;signature=KrBEHsDaadzvGLWkc0CyQxN%2FoUWTdB4yK4M4ieVkX00%3D</t>
         </is>
       </c>
       <c r="V348">
@@ -46246,7 +46246,7 @@
       </c>
       <c r="U349" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d302a9e8-291d-42ac-aac8-8b33e1708abd/Laudo119-Bemol-2026-NiseMarinhoMacedo-Assinadoajustado.pdf?expires_on=1785445163&amp;signature=9WHyVIYjizxpchJCVOzhdcBAiolW2umEujePqv4lVWQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d302a9e8-291d-42ac-aac8-8b33e1708abd/Laudo119-Bemol-2026-NiseMarinhoMacedo-Assinadoajustado.pdf?expires_on=1785445264&amp;signature=VTMASTaIwNJLgBgR85nnfSqSR%2Fx6fOCEJNpUM%2FjH69k%3D</t>
         </is>
       </c>
       <c r="V349">
@@ -46364,7 +46364,7 @@
       </c>
       <c r="U350" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e3585691-556b-4fe7-8f1a-44e30851b443/LaudoB30-2026-BEMOL-NoelinadosSantosChavesLopescorrigido.pdf?expires_on=1785445163&amp;signature=ujfzcI8SYE336ZddYJeY2AVpwxAvxibpWhNNvagPfog%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e3585691-556b-4fe7-8f1a-44e30851b443/LaudoB30-2026-BEMOL-NoelinadosSantosChavesLopescorrigido.pdf?expires_on=1785445264&amp;signature=x%2BvrF2EEmgjwhSB659S5UPijFH%2FTcBAUGyR7LulwPfE%3D</t>
         </is>
       </c>
       <c r="V350">
@@ -46498,7 +46498,7 @@
       </c>
       <c r="U351" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a128a1e1-9341-4b9c-91d2-c85521f18cee/Laudo175-Bemol-2026-NormaCoutinhoBastos.pdf?expires_on=1785445163&amp;signature=g1sut1%2BHfRhmUiWPCxZFVwubSTdtcYTNBAkp%2F%2BKC8Tw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a128a1e1-9341-4b9c-91d2-c85521f18cee/Laudo175-Bemol-2026-NormaCoutinhoBastos.pdf?expires_on=1785445264&amp;signature=yF78LysYl27sg7dsiGtPTeoEm4qdOAa5aQmIpfQysEk%3D</t>
         </is>
       </c>
       <c r="V351">
@@ -46621,7 +46621,7 @@
       </c>
       <c r="U352" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/06a7e280-3b67-4984-9236-756331283a96/IT1-2026-NORMA.pdf?expires_on=1785445163&amp;signature=rH4FY21ozrVyEy5Q2K52KAn3Y4g%2F6P8ucy3l9Rw48O4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/06a7e280-3b67-4984-9236-756331283a96/IT1-2026-NORMA.pdf?expires_on=1785445264&amp;signature=tLLcOb9EQ%2BjNs8Dovw8uJAbC%2F9IuB%2FBsh6fnJ2%2Fl1BI%3D</t>
         </is>
       </c>
       <c r="V352">
@@ -46747,7 +46747,7 @@
       </c>
       <c r="U353" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/957c2ec2-8a18-4aa5-ab94-04809d837653/LaudoB123-2025-BEMOL-ODEIBIANANASCIMENTOSOUSA2.pdf?expires_on=1785445163&amp;signature=RT9gSw%2B%2BHR1LLfNpTLUV%2FucJ2zATdnnwiZ4WJ8fyPyA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/957c2ec2-8a18-4aa5-ab94-04809d837653/LaudoB123-2025-BEMOL-ODEIBIANANASCIMENTOSOUSA2.pdf?expires_on=1785445264&amp;signature=0MAaifZ%2Bc6Bw8Yo78ogrT9aPe5lRq4kkNW82pj5SS70%3D</t>
         </is>
       </c>
       <c r="V353">
@@ -46883,7 +46883,7 @@
       </c>
       <c r="U354" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f4c56a88-7cfd-486d-9871-ff069fccc652/Laudo02-Bemol-2026-OdelitaDosSantosAraujo-Assinado.pdf?expires_on=1785445163&amp;signature=rP0JAAamSUHgS8lQHrI%2BiaTTtBJnUU2VmyokraRghpU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f4c56a88-7cfd-486d-9871-ff069fccc652/Laudo02-Bemol-2026-OdelitaDosSantosAraujo-Assinado.pdf?expires_on=1785445264&amp;signature=JEvFolSa%2F6M4FKiy99cRtqnQ42lcOGbfMenBmgh%2B1j8%3D</t>
         </is>
       </c>
       <c r="V354">
@@ -47006,7 +47006,7 @@
       </c>
       <c r="U355" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/29b628c0-63cf-4205-9b90-717ca5d97f3f/LaudoMAN08-Bemol-2026-OrlenBarrosoDaSilva.pdf?expires_on=1785445163&amp;signature=rw2vLjfUbuugVxefNflAPzO1Ubn3o9bMe8syknEcaHQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/29b628c0-63cf-4205-9b90-717ca5d97f3f/LaudoMAN08-Bemol-2026-OrlenBarrosoDaSilva.pdf?expires_on=1785445264&amp;signature=izI6ZAP%2BqXBx9zEq5ot8vopMCjP8l%2FQoMvp%2B94vlxTU%3D</t>
         </is>
       </c>
       <c r="V355">
@@ -47135,7 +47135,7 @@
       </c>
       <c r="U356" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/049aa76b-eb15-4b22-975a-b99954f6425b/LAUDOOSMARPANTOJAcorrigido.pdf?expires_on=1785445163&amp;signature=CdtpuDEHGIfv2lPru7OLqvmt%2B3s1BrmOQSIGerwTUVs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/049aa76b-eb15-4b22-975a-b99954f6425b/LAUDOOSMARPANTOJAcorrigido.pdf?expires_on=1785445264&amp;signature=43GDLcYbqDN8MgXP43mNIgw3LINTPHLlfaBMzKgeVnM%3D</t>
         </is>
       </c>
       <c r="V356">
@@ -47253,7 +47253,7 @@
       </c>
       <c r="U357" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6e70ff3e-1f36-4a2a-ad63-edb54a074bb6/LaudoMAN02-Bemol-2026-OsvaldoFDaSilvaJunior-Assinado-Ajustado.pdf?expires_on=1785445163&amp;signature=GfRZChDs1%2BHOt1SjrDJLza2k%2FzqedgmYSayn%2BAqKO1k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6e70ff3e-1f36-4a2a-ad63-edb54a074bb6/LaudoMAN02-Bemol-2026-OsvaldoFDaSilvaJunior-Assinado-Ajustado.pdf?expires_on=1785445264&amp;signature=egzQEDYZHhdF272ou50E8vIz24lfaqM6X4JPjK0NilA%3D</t>
         </is>
       </c>
       <c r="V357">
@@ -47371,7 +47371,7 @@
       </c>
       <c r="U358" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5cd11b0a-bf3e-469a-9020-53993be3de6f/LaudoB27-2026-BEMOL-OsvaldoRodriguesMendesJunior.pdf?expires_on=1785445163&amp;signature=gCuNc%2FF8XDgYeKRIuTHQWPNLMwzZgCVrjCcZ%2Fi%2B%2FuME%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5cd11b0a-bf3e-469a-9020-53993be3de6f/LaudoB27-2026-BEMOL-OsvaldoRodriguesMendesJunior.pdf?expires_on=1785445264&amp;signature=9YYj%2B%2FnAFR3AUKRF2V%2FTytOM4vKuYZwq%2BrN%2FxZ0t5Z0%3D</t>
         </is>
       </c>
       <c r="V358">
@@ -47503,7 +47503,7 @@
       </c>
       <c r="U359" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/90e3641b-68c8-411b-85c2-af435523c2d7/LaudoB12-2026-BEMOL-OzielTavaresdeAraujoNeto.pdf?expires_on=1785445163&amp;signature=d6N90N95EIYyS5LlJwu0dSWTLhU9xY06qdrmVRJp2YE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/90e3641b-68c8-411b-85c2-af435523c2d7/LaudoB12-2026-BEMOL-OzielTavaresdeAraujoNeto.pdf?expires_on=1785445264&amp;signature=3V5lc%2Fl%2Bc9sB20s3uZTURpmHiTfPGRPhM2e2q1JFuhI%3D</t>
         </is>
       </c>
       <c r="V359">
@@ -47635,7 +47635,7 @@
       </c>
       <c r="U360" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d9d11df7-bc9d-448a-a227-13e1880ddfa0/Laudo481-Bemol-2025-PamellaProcopioDaFonsecaLuiz-Assinado.pdf?expires_on=1785445163&amp;signature=j9nlZwE5iEjKKymkSLFjAAs2Plr%2FYjAP1wO6g4f7IjY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d9d11df7-bc9d-448a-a227-13e1880ddfa0/Laudo481-Bemol-2025-PamellaProcopioDaFonsecaLuiz-Assinado.pdf?expires_on=1785445264&amp;signature=DlnbIupnxcSrpjnurI%2F9iT67HcArC5VcpYPoWrdHfhg%3D</t>
         </is>
       </c>
       <c r="V360">
@@ -47782,7 +47782,7 @@
       </c>
       <c r="U361" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0cd8693b-faeb-4b2c-a562-70e748431a36/LaudoP09-Bemol-2026-PatriciaRodriguesDeSouza_signed.pdf?expires_on=1785445163&amp;signature=MSJGfvTJtCn1bggxF691KOV2Fzo0yomBGHf36tb5tCw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0cd8693b-faeb-4b2c-a562-70e748431a36/LaudoP09-Bemol-2026-PatriciaRodriguesDeSouza_signed.pdf?expires_on=1785445264&amp;signature=reG76LjkxXPztcuf9E61XW5Ravx7e8oFBH1bCKNSa2I%3D</t>
         </is>
       </c>
       <c r="V361">
@@ -47914,7 +47914,7 @@
       </c>
       <c r="U362" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/71755bfc-5154-4ffa-aeef-6147e7e548cd/LaudoCORRIGIDOPA09-Bemol-2026-PatrickWendeelRibeiroDeLima-Assinado1.pdf?expires_on=1785445163&amp;signature=aZEcgN%2B9u3GOPBeKIAkbE%2FP3FJRCvpLyjQXCxLrhX3Y%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/71755bfc-5154-4ffa-aeef-6147e7e548cd/LaudoCORRIGIDOPA09-Bemol-2026-PatrickWendeelRibeiroDeLima-Assinado1.pdf?expires_on=1785445264&amp;signature=6cyxUXVxCBTwk8tpfdQ%2BL%2BGcfiJ71Nhn16fVhsg4NSE%3D</t>
         </is>
       </c>
       <c r="V362">
@@ -48037,7 +48037,7 @@
       </c>
       <c r="U363" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a6840bb8-6f41-491e-86da-94110360b62e/Laudo30corrigido-Bemol-2026-PaulaJussaraDosSantosPortela.pdf?expires_on=1785445163&amp;signature=AAeT9NwtOo9xmOYVY8sp8Ig0rR3oIPsrcop66ZFAZe8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a6840bb8-6f41-491e-86da-94110360b62e/Laudo30corrigido-Bemol-2026-PaulaJussaraDosSantosPortela.pdf?expires_on=1785445264&amp;signature=9H2ehGWMtKH%2BOcEfov0ua37N5qq7t3DpAyiDnrs9uW8%3D</t>
         </is>
       </c>
       <c r="V363">
@@ -48167,7 +48167,7 @@
       </c>
       <c r="U364" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/956352cb-2de4-4540-b97a-c355dd5d85ee/LaudoR02-2026-BEMOL-PAULOCEZARRAMOSDASILVA.pdf?expires_on=1785445163&amp;signature=vNg1sad7oQfWt5UsxvnW0JrDhTlYsHKO11dEJJeJdD0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/956352cb-2de4-4540-b97a-c355dd5d85ee/LaudoR02-2026-BEMOL-PAULOCEZARRAMOSDASILVA.pdf?expires_on=1785445264&amp;signature=ymfjFjnzkElOc5hSp9JldimLGNR8cgeEpUa1PeNyoF0%3D</t>
         </is>
       </c>
       <c r="V364">
@@ -48292,7 +48292,7 @@
       </c>
       <c r="U365" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d522f012-8c04-4896-92a4-214bc1194f74/M10-2026-PAULOCHRISTIAN.pdf?expires_on=1785445163&amp;signature=XqsTihu78lUcG%2FuUXw3j%2FxD2Pzf%2BS%2BUYcu1fF6%2FvuFs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d522f012-8c04-4896-92a4-214bc1194f74/M10-2026-PAULOCHRISTIAN.pdf?expires_on=1785445264&amp;signature=gmO5jadXSUDeFOCvplzMMLp5UaMRn%2Bdud1rPJLNJA7g%3D</t>
         </is>
       </c>
       <c r="V365">
@@ -48415,7 +48415,7 @@
       </c>
       <c r="U366" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4ca6194d-c4bc-485f-8b4d-68f8b3b9a216/LAUDOPAULOROBERTOcorrigido02.pdf?expires_on=1785445163&amp;signature=SBKNiQB%2BARB4TbJc%2BdF9OHCJfJbVQenku5hV%2BXVYkns%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4ca6194d-c4bc-485f-8b4d-68f8b3b9a216/LAUDOPAULOROBERTOcorrigido02.pdf?expires_on=1785445264&amp;signature=IpsW7%2FRH4xPGJ3DYQV5btMS4sJZqkPt4ngZMiv3gov8%3D</t>
         </is>
       </c>
       <c r="V366">
@@ -48551,7 +48551,7 @@
       </c>
       <c r="U367" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f4445083-ab81-47ff-802f-df65996f45c1/Laudo189-Bemol-2026-PedroAugustoRibeiroTavares-Assinado.pdf?expires_on=1785445163&amp;signature=UytLfSepB8hGZ69uAmL1xsunN0ZrSMCGFzPL05ng87c%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f4445083-ab81-47ff-802f-df65996f45c1/Laudo189-Bemol-2026-PedroAugustoRibeiroTavares-Assinado.pdf?expires_on=1785445264&amp;signature=QKzrLSFn3Fi76Z8qLdaG55XiFu6OjWXXpYDkolEE4M0%3D</t>
         </is>
       </c>
       <c r="V367">
@@ -48680,7 +48680,7 @@
       </c>
       <c r="U368" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1d60b079-24d2-4aec-9716-87170632877d/BEMOL-AR022-POLIANAVIEIRADASILVA.pdf?expires_on=1785445163&amp;signature=FQ5N4ZjQJzkV%2FAHzn63hBiHobmatuJm0%2Frkwgq1J2pM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1d60b079-24d2-4aec-9716-87170632877d/BEMOL-AR022-POLIANAVIEIRADASILVA.pdf?expires_on=1785445264&amp;signature=%2FWV40vR%2F%2FR9IkvDP8%2BDv61KskCou2M%2B1YhpE7qz0Hqw%3D</t>
         </is>
       </c>
       <c r="V368">
@@ -48812,7 +48812,7 @@
       </c>
       <c r="U369" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/63d9c535-82c6-4117-b3d6-e7f2c247e6e0/RelatriodeValordeRefernciaRVR04-Bemol-2026-RafaelaBatalhaDeCastroSantos-Assinado.pdf?expires_on=1785445163&amp;signature=qYAYlOeixG1evMavq4tLiJleIzx5cwLNe9lvGBE2T5w%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/63d9c535-82c6-4117-b3d6-e7f2c247e6e0/RelatriodeValordeRefernciaRVR04-Bemol-2026-RafaelaBatalhaDeCastroSantos-Assinado.pdf?expires_on=1785445264&amp;signature=4Wit4tRVcPSMGbNSZ4ff4QiCgOQeKV7uWIKFxmIreQg%3D</t>
         </is>
       </c>
       <c r="V369">
@@ -48941,7 +48941,7 @@
       </c>
       <c r="U370" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/494b7e69-62fb-4fc7-8195-67cc571ac962/LaudoPF01-Bemol-2026-RaimundaDaConceicaoDaMotaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=r2QVvtlCgPRvWO%2BHcnMrCOYMW8wNVIbGVP9juSbzPNE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/494b7e69-62fb-4fc7-8195-67cc571ac962/LaudoPF01-Bemol-2026-RaimundaDaConceicaoDaMotaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=7XWfjAJjeamdjVa2372nR8zX2Xi6jF%2B7s6aakruhG7M%3D</t>
         </is>
       </c>
       <c r="V370">
@@ -49072,7 +49072,7 @@
       </c>
       <c r="U371" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d81f64de-ca9a-4f04-99de-226a9b718a79/Laudo282-Bemol-2025-RaimundaEmiliaVenceslauDaCosta-Assinado.pdf?expires_on=1785445163&amp;signature=bsTXvfQFJRrRIIUPpCrZ7c0aeE4%2FRkUd%2BtxpQzT48VM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d81f64de-ca9a-4f04-99de-226a9b718a79/Laudo282-Bemol-2025-RaimundaEmiliaVenceslauDaCosta-Assinado.pdf?expires_on=1785445264&amp;signature=sZ2hxF9DvPNGjf%2BUt%2B0loJWoLJlbc0kbvDc7gC%2BVOLM%3D</t>
         </is>
       </c>
       <c r="V371">
@@ -49213,7 +49213,7 @@
       </c>
       <c r="U372" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1566149-eab3-4bd8-950f-23f13ef298c0/Laudo_AC_12-2026_-_RAIMUNDA_FRANCISCA_CONCEICAO_SOUSA_assinadocorrigido.pdf?expires_on=1785445163&amp;signature=lhrJcHZp4FJZPuJVA0S8NBuLSn49MamZRHzJioRCnbo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1566149-eab3-4bd8-950f-23f13ef298c0/Laudo_AC_12-2026_-_RAIMUNDA_FRANCISCA_CONCEICAO_SOUSA_assinadocorrigido.pdf?expires_on=1785445264&amp;signature=CbAO6z5muhN0HqipzqdhKpgHrezCVH6tgm%2BnHYa8U3Q%3D</t>
         </is>
       </c>
       <c r="V372">
@@ -49349,7 +49349,7 @@
       </c>
       <c r="U373" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e11c7382-2c26-44d3-8e01-7eb6427e9aa8/Laudo60-Bemol-2026-RaimundaLopesMacielLeao-Assinado.pdf?expires_on=1785445163&amp;signature=sVkJNxRYyXtjztI1E%2FtVHYBDzO876O%2BO9WmyAe%2FqaoE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e11c7382-2c26-44d3-8e01-7eb6427e9aa8/Laudo60-Bemol-2026-RaimundaLopesMacielLeao-Assinado.pdf?expires_on=1785445264&amp;signature=t%2Fk2gk61ewYkZ2qVYB0ynLvTin1KzV1zMEqhja%2FIIyk%3D</t>
         </is>
       </c>
       <c r="V373">
@@ -49472,7 +49472,7 @@
       </c>
       <c r="U374" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3e434f54-e252-422b-85b7-02202943d64c/LAUDOMELCINIRAcorrigido.pdf?expires_on=1785445163&amp;signature=HPEKZkKqdu1kP0tU%2F%2BIx%2BmEsRWQSnrq8rdu%2Bt5D6VY0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3e434f54-e252-422b-85b7-02202943d64c/LAUDOMELCINIRAcorrigido.pdf?expires_on=1785445264&amp;signature=b1rkJg9M8awnfNJtltu72tb3T22QerI0IABqcdT0tCY%3D</t>
         </is>
       </c>
       <c r="V374">
@@ -49590,7 +49590,7 @@
       </c>
       <c r="U375" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b101fd87-d809-47ca-90f1-ad0770d144e4/Laudo136-Bemol-2026-RaimundaNonataMonteiroDaSilva.pdf?expires_on=1785445163&amp;signature=Ly0OeaROb%2FOZGzQJS2ROT%2FXy0tO0%2BOyBpDJpTwITHv0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b101fd87-d809-47ca-90f1-ad0770d144e4/Laudo136-Bemol-2026-RaimundaNonataMonteiroDaSilva.pdf?expires_on=1785445264&amp;signature=KlTsEX430fe5ql5lFTjMt%2FbcU3li9A4mRfxCvHdZEuY%3D</t>
         </is>
       </c>
       <c r="V375">
@@ -49721,7 +49721,7 @@
       </c>
       <c r="U376" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1b4d4b9-fd6c-438e-832d-95e654f5ed7f/Laudo174-Bemol-2026-RaimundoDeSouzaCabral-Assinado.pdf?expires_on=1785445163&amp;signature=VecN%2BJaivmUfs4FHVvLX%2FZ3%2BMGJta8Rhm3%2FnKE7LVZw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a1b4d4b9-fd6c-438e-832d-95e654f5ed7f/Laudo174-Bemol-2026-RaimundoDeSouzaCabral-Assinado.pdf?expires_on=1785445264&amp;signature=UDe9TLKxWHZFeq1a7pvBDvaYrqxryN04CycgJtCwjQA%3D</t>
         </is>
       </c>
       <c r="V376">
@@ -49852,7 +49852,7 @@
       </c>
       <c r="U377" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/db7d1af0-2b30-4244-849a-2cbba8563f18/Laudo390-Bemol-2025-RaimundoErasmoDoCarmoDeSousa-Assinado.pdf?expires_on=1785445163&amp;signature=gQJp%2BrdiJal9Yhvj%2BMZXA31jlCFRS2%2BtZk6MQlouBJs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/db7d1af0-2b30-4244-849a-2cbba8563f18/Laudo390-Bemol-2025-RaimundoErasmoDoCarmoDeSousa-Assinado.pdf?expires_on=1785445264&amp;signature=VvW61kc1nYhQSBoZ%2BrkAjC4%2FaLz1B0wuWUXRt%2BBf0zI%3D</t>
         </is>
       </c>
       <c r="V377">
@@ -49988,7 +49988,7 @@
       </c>
       <c r="U378" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e66d51aa-7a0b-460b-99dd-b2d322db2292/LaudoB13-2026-BEMOL-RAIMUNDOSOARESDESOUZA.pdf?expires_on=1785445163&amp;signature=Kg9%2FMdqd6Qq58uoELnbRpdoGsmasUZmgfQb62LOfgOM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e66d51aa-7a0b-460b-99dd-b2d322db2292/LaudoB13-2026-BEMOL-RAIMUNDOSOARESDESOUZA.pdf?expires_on=1785445264&amp;signature=48qjjlDpmYDSdK1z8ZVYZF2N8FIbTXPFHRssNZEb5DE%3D</t>
         </is>
       </c>
       <c r="V378">
@@ -50126,7 +50126,7 @@
       </c>
       <c r="U379" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/fb4c65a4-ec50-4573-87b6-74205b566cad/Laudo90-Bemol-2026-RaimundoSocorroCosta.pdf?expires_on=1785445163&amp;signature=rR%2FbTg1cQqZYdUN34Y8%2BMvp%2Fqd1lVgE0ukiMC4h9lR4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/fb4c65a4-ec50-4573-87b6-74205b566cad/Laudo90-Bemol-2026-RaimundoSocorroCosta.pdf?expires_on=1785445264&amp;signature=Tw9LWIPm%2Fwvs9hO54b3WC7Kjy2Y%2BnE9N3hRsF0Rn3lE%3D</t>
         </is>
       </c>
       <c r="V379">
@@ -50258,7 +50258,7 @@
       </c>
       <c r="U380" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3cdfb747-3eb8-462c-9fa2-81808d55b5c2/LaudoPA06-Bemol-2026-RaquelDaCostaMoutinho-Assinado.pdf?expires_on=1785445163&amp;signature=HcKP%2F6BdeTIbMxrPVa1GZnLiqESq1rCsqih%2FjM8Y4%2FI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3cdfb747-3eb8-462c-9fa2-81808d55b5c2/LaudoPA06-Bemol-2026-RaquelDaCostaMoutinho-Assinado.pdf?expires_on=1785445264&amp;signature=4DU685Sy3MHwBKJjHQpFr8NHTMLrcHAHoXJugSV07U8%3D</t>
         </is>
       </c>
       <c r="V380">
@@ -50388,7 +50388,7 @@
       </c>
       <c r="U381" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/290237ff-97b8-48db-a808-e517e6c8ffa6/LaudoB40-2026-BEMOL-REBECACRISTINABRECKENFELDDEMELO.pdf?expires_on=1785445163&amp;signature=gcO15cPWzAKmPzYt9uU7HtYAdK78uDnErSzT2gjpiPw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/290237ff-97b8-48db-a808-e517e6c8ffa6/LaudoB40-2026-BEMOL-REBECACRISTINABRECKENFELDDEMELO.pdf?expires_on=1785445264&amp;signature=Uhge2ZISzs1Im3M1P59D1aDTNjoExEND4OFUtRUyteg%3D</t>
         </is>
       </c>
       <c r="V381">
@@ -50518,7 +50518,7 @@
       </c>
       <c r="U382" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5ebd6219-e5f4-4e59-bc39-c551536c695e/LaudoB25-2026-BEMOL-RELMASILVADESOUSA.pdf?expires_on=1785445163&amp;signature=9n2kbOFZENydoYkjCPIxhhwu5c6I%2FtttXDzBpuFo4VI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5ebd6219-e5f4-4e59-bc39-c551536c695e/LaudoB25-2026-BEMOL-RELMASILVADESOUSA.pdf?expires_on=1785445264&amp;signature=p%2F%2BFZ%2FxyaJkvfSyppfHXVCY2BnIqQmrpyM1DWoDaAtI%3D</t>
         </is>
       </c>
       <c r="V382">
@@ -50650,7 +50650,7 @@
       </c>
       <c r="U383" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2793b988-aff4-46a0-9b41-b4e708236aa0/Laudo56-Bemol-2026-RenatoGadelhaLima-Assinado.pdf?expires_on=1785445163&amp;signature=nGmaxKmdBltQ%2FVTvnj%2FMT0zwZ1l9CQf0LoYhFdFOYXs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2793b988-aff4-46a0-9b41-b4e708236aa0/Laudo56-Bemol-2026-RenatoGadelhaLima-Assinado.pdf?expires_on=1785445264&amp;signature=0wodo1nsINFlCDSPQMGjcKUn%2FLMKARR1OTbyLFz%2Bg%2FE%3D</t>
         </is>
       </c>
       <c r="V383">
@@ -50790,7 +50790,7 @@
       </c>
       <c r="U384" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/045c54ae-250b-41cf-8d59-a3f25ea628bd/LaudoP13-Bemol-2026-RenildoDeSouzaMoreiraretificado_signedcorrigido.pdf?expires_on=1785445163&amp;signature=w7e%2BJ0n%2FVHcJRbq2g%2FgFzqqiWjJ6caeIs9OJmD%2Bxmk4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/045c54ae-250b-41cf-8d59-a3f25ea628bd/LaudoP13-Bemol-2026-RenildoDeSouzaMoreiraretificado_signedcorrigido.pdf?expires_on=1785445264&amp;signature=D8BHHdHSuBeKYmFByRuuAGIDJkztk7nSttUuA89jc7U%3D</t>
         </is>
       </c>
       <c r="V384">
@@ -50908,7 +50908,7 @@
       </c>
       <c r="U385" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/75b50ec4-3e3c-4f16-a5b9-92acb1766ee2/Laudo99-Bemol-2026-ReulySilvaFerreira.pdf?expires_on=1785445163&amp;signature=LPL7x%2BpJEJ4%2BNeRRolsRBqqXq%2FBLDXgQTcmzHA4rqjY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/75b50ec4-3e3c-4f16-a5b9-92acb1766ee2/Laudo99-Bemol-2026-ReulySilvaFerreira.pdf?expires_on=1785445264&amp;signature=Rxq5y4hvVWnKcYC820xRx9CJ2zlmLIXR5q9TwXGeBkM%3D</t>
         </is>
       </c>
       <c r="V385">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="U386" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5aa360d1-e719-4ef1-b477-64124b1d5874/LaudoJP06-Bemol-2026-RilcelaradaSilva_signed.pdf?expires_on=1785445163&amp;signature=Zz9eUvdRJS9Ky5f%2BD6jmVU%2BktDGKTCQgOHLm6JniX5g%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5aa360d1-e719-4ef1-b477-64124b1d5874/LaudoJP06-Bemol-2026-RilcelaradaSilva_signed.pdf?expires_on=1785445264&amp;signature=fqWrmKnwDPRUgBKcgqwwrgCezdjJPVR8lihvhewZ2Og%3D</t>
         </is>
       </c>
       <c r="V386">
@@ -51170,7 +51170,7 @@
       </c>
       <c r="U387" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/11b0329b-6c83-4634-9dcf-045d3091dffb/LaudoITA10-Bemol-2026-RitaEvaniaDaMataOliveira-Assinado.pdf?expires_on=1785445163&amp;signature=WeHQk0%2Fd%2BK1fUrLDi4El3unu5oyO1RvmU0CkYs7Jzu4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/11b0329b-6c83-4634-9dcf-045d3091dffb/LaudoITA10-Bemol-2026-RitaEvaniaDaMataOliveira-Assinado.pdf?expires_on=1785445264&amp;signature=zSt6IM7JaF6uKWHARCTYBBIyNyMarQuN1qO92GzBNzE%3D</t>
         </is>
       </c>
       <c r="V387">
@@ -51299,7 +51299,7 @@
       </c>
       <c r="U388" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ee0a3d24-611f-4afb-94d5-d0714d4a7a2a/M19-2026-ROBERLANDE.pdf?expires_on=1785445163&amp;signature=WmyT1kJInkIA18G%2BmYqxlgvvW3OR6iByqLGXHh09Yvo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ee0a3d24-611f-4afb-94d5-d0714d4a7a2a/M19-2026-ROBERLANDE.pdf?expires_on=1785445264&amp;signature=g3oFE%2FkVqIZ880IHDhv%2Bag00txa%2FS7%2FOCqa%2Bqtv34u8%3D</t>
         </is>
       </c>
       <c r="V388">
@@ -51425,7 +51425,7 @@
       </c>
       <c r="U389" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/510d5bae-319e-4402-a6d6-9638e4ef01a3/Laudo463-Bemol-2025-RobervalEmersonOliveiraDePaulaFilho-Assinado.pdf?expires_on=1785445163&amp;signature=zIdaS%2Bn1z%2BaRi3D5MgvlYjvKp1wOuEHfptfL3BKx7RQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/510d5bae-319e-4402-a6d6-9638e4ef01a3/Laudo463-Bemol-2025-RobervalEmersonOliveiraDePaulaFilho-Assinado.pdf?expires_on=1785445264&amp;signature=uUUp18lr%2FDffM44c59zJ9gnP1biNz4MsW4efzs1%2F3LU%3D</t>
         </is>
       </c>
       <c r="V389">
@@ -51574,7 +51574,7 @@
       </c>
       <c r="U390" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b044c921-bcbf-4744-8fcc-d2fbbded2660/LAUDOROBSONMOTA.pdf?expires_on=1785445163&amp;signature=%2FHtrVnA7Y9sSTE9RQUfOvTq63P2btVyQfWjl2x64etk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b044c921-bcbf-4744-8fcc-d2fbbded2660/LAUDOROBSONMOTA.pdf?expires_on=1785445264&amp;signature=iwYkx9HVZ7namd3UkzUmsHr%2BJX9DnBXTVh11tJ0uWVU%3D</t>
         </is>
       </c>
       <c r="V390">
@@ -51705,7 +51705,7 @@
       </c>
       <c r="U391" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/bf51751a-e147-48b5-8613-d4b117602a99/LAUDOROBSONcorrigido.pdf?expires_on=1785445163&amp;signature=7oyx25lhmGMxw%2FMyO1hRhE31wpY0L0ks61mZRNZ2tmU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/bf51751a-e147-48b5-8613-d4b117602a99/LAUDOROBSONcorrigido.pdf?expires_on=1785445264&amp;signature=iMcJQL9axEQOi1VOjiAOAl2J%2BRoRl8xteDUtfDK%2FIu8%3D</t>
         </is>
       </c>
       <c r="V391">
@@ -51829,7 +51829,7 @@
       </c>
       <c r="U392" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b0eba187-eaf3-4f90-ae25-ba460f7d8f35/BEMOL-PV068-ROBSONSENACRUZCOMERCIAL.pdf?expires_on=1785445163&amp;signature=XLYiQ0c5XDKAo1Aai%2BKLBDzrxlMKSf%2BkmI1eNY3YATg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b0eba187-eaf3-4f90-ae25-ba460f7d8f35/BEMOL-PV068-ROBSONSENACRUZCOMERCIAL.pdf?expires_on=1785445264&amp;signature=PX4euZDV6LR9dminJxqw%2BvR7lXx3a%2BYB6oLaIQQYN7U%3D</t>
         </is>
       </c>
       <c r="V392">
@@ -51956,7 +51956,7 @@
       </c>
       <c r="U393" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a076174-2a26-43a7-9c07-df4f54c1ffb1/LAUDOCORRIGIDORODRIGOLEO1.pdf?expires_on=1785445163&amp;signature=HdUZeMTh%2FL26jXr5jP75%2Bm0DEve%2F8CouLzIwNyHuGcI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5a076174-2a26-43a7-9c07-df4f54c1ffb1/LAUDOCORRIGIDORODRIGOLEO1.pdf?expires_on=1785445264&amp;signature=yiHKw5d1myyFFFJuRY8maO6nc9qszDilzb9thAm0mAM%3D</t>
         </is>
       </c>
       <c r="V393">
@@ -52079,7 +52079,7 @@
       </c>
       <c r="U394" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/eac647e3-1371-4d6d-ab01-b54f520f6c13/LaudoB35-2026-BEMOL-ROMULOFREITASVASCONCELOS.pdf?expires_on=1785445163&amp;signature=gFUL%2FF1MShSSgj%2FTa6r5elD9zRB4RIUBr7I%2B27Xjyi4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/eac647e3-1371-4d6d-ab01-b54f520f6c13/LaudoB35-2026-BEMOL-ROMULOFREITASVASCONCELOS.pdf?expires_on=1785445264&amp;signature=OsAFyL0MbO6iJLpbZYzDjR9uH5Fz9jnLVsV9dQIlBR0%3D</t>
         </is>
       </c>
       <c r="V394">
@@ -52202,7 +52202,7 @@
       </c>
       <c r="U395" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0205a4bf-b863-461c-9aa1-51c6c2d3a48d/LAUDOCORRIGIDORONALDOLOPESDOSSANTOS.pdf?expires_on=1785445163&amp;signature=9JI9Zr%2FZsiAnmlrbyZUl3qeobgZ5aSMXF22JQ83%2FebA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0205a4bf-b863-461c-9aa1-51c6c2d3a48d/LAUDOCORRIGIDORONALDOLOPESDOSSANTOS.pdf?expires_on=1785445264&amp;signature=T6nt3HoyK2OcatDtpUrZT%2F%2F0grBw90ppCIXEFPd0ufY%3D</t>
         </is>
       </c>
       <c r="V395">
@@ -52331,7 +52331,7 @@
       </c>
       <c r="U396" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/742ef22b-947c-4b2f-b655-a049050fa04d/Laudo201-Bemol-2026-RonaldoLucioDeLimaMarquesFilho.pdf?expires_on=1785445163&amp;signature=RdKt675deGkQgJYYoN9S7IL0aSVqfU1P%2BTOkfaH7zGg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/742ef22b-947c-4b2f-b655-a049050fa04d/Laudo201-Bemol-2026-RonaldoLucioDeLimaMarquesFilho.pdf?expires_on=1785445264&amp;signature=8f8CYVFgBGzV2kdcm3mNv%2By%2Fmy7o90zlRsac2oUCLP8%3D</t>
         </is>
       </c>
       <c r="V396">
@@ -52454,7 +52454,7 @@
       </c>
       <c r="U397" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/a24cada2-42fc-4f3a-8128-e23e4566cee5/LaudoB45-2026-BEMOL-ROSAMARIABATISTADOSSANTOS.pdf?expires_on=1785445163&amp;signature=IZg9nMosTUcA4PQ%2BPZ5a0EjG%2Bjl%2FSCGNNOrz3TKxmqg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/a24cada2-42fc-4f3a-8128-e23e4566cee5/LaudoB45-2026-BEMOL-ROSAMARIABATISTADOSSANTOS.pdf?expires_on=1785445264&amp;signature=zILh4I5KGDeP1hHURoWmmh6qdhDUM5v0TgS9r86%2BN%2Fk%3D</t>
         </is>
       </c>
       <c r="V397">
@@ -52586,7 +52586,7 @@
       </c>
       <c r="U398" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/00d4329e-1be0-4ca9-80b8-14423a168202/Laudo68-Bemol-2026-RosaMariaMartinsCorreia.pdf?expires_on=1785445163&amp;signature=lZVDkpkSioHyH4r9iY2qS91zNG7XjE4PUJay5uBIzDk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/00d4329e-1be0-4ca9-80b8-14423a168202/Laudo68-Bemol-2026-RosaMariaMartinsCorreia.pdf?expires_on=1785445264&amp;signature=un31YHZ8sot0HiEvLL0ciFl0k%2BwiqMyziYAvyQsLG5w%3D</t>
         </is>
       </c>
       <c r="V398">
@@ -52729,7 +52729,7 @@
       </c>
       <c r="U399" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a5affc9-5efa-4b05-9ad8-3e6533d4f3bb/LAUDOROSARODRIGUES.pdf?expires_on=1785445163&amp;signature=mXxioKrscGpgrndTHyDz98d3q5983mSBv3c87RAkmmY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a5affc9-5efa-4b05-9ad8-3e6533d4f3bb/LAUDOROSARODRIGUES.pdf?expires_on=1785445264&amp;signature=vCw4I4oIvXOjzA8sD4BJPFBwMBHoN0Jbb8HMYKpyP5k%3D</t>
         </is>
       </c>
       <c r="V399">
@@ -52860,7 +52860,7 @@
       </c>
       <c r="U400" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f2b56fd5-9e5c-4418-9e2d-56f9dfbf06f3/Laudo_AC_31-2026_-_ROSA_VASQUES_DA_SILVA_SANTOS_assinado.pdf?expires_on=1785445163&amp;signature=%2BpVGBT7ndpeQfL1k1oaUIA18VyWeeQxvIXqFNr8j1jc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f2b56fd5-9e5c-4418-9e2d-56f9dfbf06f3/Laudo_AC_31-2026_-_ROSA_VASQUES_DA_SILVA_SANTOS_assinado.pdf?expires_on=1785445264&amp;signature=QD5CYJrbIkVp%2BpLd2B9sgi1KL9IHGMgYJtnXkF6ejcs%3D</t>
         </is>
       </c>
       <c r="V400">
@@ -52983,7 +52983,7 @@
       </c>
       <c r="U401" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3c4d8694-e4f6-4617-b493-395f3cd9d236/BEMOL-PV093-RosaneMunizBezerra.pdf?expires_on=1785445163&amp;signature=QNYmkDCGB3ZXCcwxUIPTXfQ5GAxeJTp16qlhfro78J4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3c4d8694-e4f6-4617-b493-395f3cd9d236/BEMOL-PV093-RosaneMunizBezerra.pdf?expires_on=1785445264&amp;signature=LQgj4zpByhZ9wH4Xb5TKR1wxxGQOIrLOk8FA7KL7p6s%3D</t>
         </is>
       </c>
       <c r="V401">
@@ -53109,7 +53109,7 @@
       </c>
       <c r="U402" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/1b16191a-86bc-42c1-ad81-956b778e918f/M14-2026-ROSEMBERG.pdf?expires_on=1785445163&amp;signature=FAHozhvaeu%2FVJV8%2F79jJuE6CbMhq0srSLCBD1Wf0XEQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/1b16191a-86bc-42c1-ad81-956b778e918f/M14-2026-ROSEMBERG.pdf?expires_on=1785445264&amp;signature=FSO%2B0%2Fpav42eqnrrheNcsIIkFBhkCbq4wt8idTr7OlU%3D</t>
         </is>
       </c>
       <c r="V402">
@@ -53232,7 +53232,7 @@
       </c>
       <c r="U403" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ed590550-e36b-4c89-960e-07f9f76ba9b2/LAUDOROSEMIRO.pdf?expires_on=1785445163&amp;signature=lvnhasByLYRbCuVopKgPdBbJIb%2F7XLMCTCC92YTAWlM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ed590550-e36b-4c89-960e-07f9f76ba9b2/LAUDOROSEMIRO.pdf?expires_on=1785445264&amp;signature=eaYg1GC1j9dv%2F1dWvEu79Jp7CeeA2iaXGbe1t%2BR%2FGcQ%3D</t>
         </is>
       </c>
       <c r="V403">
@@ -53350,7 +53350,7 @@
       </c>
       <c r="U404" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/52bcdd6c-c8cf-48c8-b72a-72e3b3408c04/M16-2026-ROSICLEUDE.pdf?expires_on=1785445163&amp;signature=aScOpTM5uARuT%2BnuaKTkbg5HQ0wzj7wXwPm43ZEPetg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/52bcdd6c-c8cf-48c8-b72a-72e3b3408c04/M16-2026-ROSICLEUDE.pdf?expires_on=1785445264&amp;signature=64Pz%2FrWxuc%2BoE9%2BVXBXPoP7AZc%2FAGJc%2BN4HAn4rVY88%3D</t>
         </is>
       </c>
       <c r="V404">
@@ -53481,7 +53481,7 @@
       </c>
       <c r="U405" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/17095173-da4d-4d28-ae1c-836a1fbb2eea/Laudo22-Bemol-2026-RosileneDosSantosAntunes-Assinado.pdf?expires_on=1785445163&amp;signature=z30JSHuC%2BQJfaLps8taICHilBOo8M4apDtR9vcYW8CE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/17095173-da4d-4d28-ae1c-836a1fbb2eea/Laudo22-Bemol-2026-RosileneDosSantosAntunes-Assinado.pdf?expires_on=1785445264&amp;signature=YpiFC6x3nEWGN3PpaC5lhCC%2F%2B0Hlzr%2BQ5JENBXNFzII%3D</t>
         </is>
       </c>
       <c r="V405">
@@ -53612,7 +53612,7 @@
       </c>
       <c r="U406" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f21cd10a-5e4b-48a8-a63b-6b37522a52ae/LAUDOROSINALDOcorrigido.pdf?expires_on=1785445163&amp;signature=BRpfZODLcBdhlF0NuzdCOonXbcnmNYwzf7hwlATDYyc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f21cd10a-5e4b-48a8-a63b-6b37522a52ae/LAUDOROSINALDOcorrigido.pdf?expires_on=1785445264&amp;signature=OqSylwjkDKcOiXkrFfUawx%2F0iGRE1aV4nTT0lv1uoXw%3D</t>
         </is>
       </c>
       <c r="V406">
@@ -53742,7 +53742,7 @@
       </c>
       <c r="U407" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/5c3aa0b6-4fe3-4d41-a19e-39ad454e553e/Laudo181-Bemol-2026-RosinildoFonsecaMoreiraJunior-Assinado.pdf?expires_on=1785445163&amp;signature=VyS4j373fuwCNEbvknRiRryYw7oWSSqhieyNjDPjNy8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/5c3aa0b6-4fe3-4d41-a19e-39ad454e553e/Laudo181-Bemol-2026-RosinildoFonsecaMoreiraJunior-Assinado.pdf?expires_on=1785445264&amp;signature=U2kqQdVCzQYczk%2BoY%2BjdYN%2BXUTlL4izSaJHrL5RojHc%3D</t>
         </is>
       </c>
       <c r="V407">
@@ -53873,7 +53873,7 @@
       </c>
       <c r="U408" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9b283502-2002-4b61-a7df-8bb0e28bf455/M8-2026-RUTHRODRIGUESajustado02.pdf?expires_on=1785445163&amp;signature=%2B1Vf3ekPM1gxxGkrto9NJ3s9oZHcoYPRbiGZ0fOtVmE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9b283502-2002-4b61-a7df-8bb0e28bf455/M8-2026-RUTHRODRIGUESajustado02.pdf?expires_on=1785445264&amp;signature=uWk0ob5PPqa71Fzx%2Bb0%2BHaH5so5M8rz7aPy%2FRQcnWFw%3D</t>
         </is>
       </c>
       <c r="V408">
@@ -53996,7 +53996,7 @@
       </c>
       <c r="U409" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/93c2225f-37ce-4285-b84e-62328919c829/Laudo34-Bemol-2026-SalomoRodriguesDaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=Qlq%2BxNqnWT%2FTAnd9vnUkEsMJ6DyvyRiLvl51V0hKQes%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/93c2225f-37ce-4285-b84e-62328919c829/Laudo34-Bemol-2026-SalomoRodriguesDaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=aMZPySJEf66IezLyIP0gn2yVRSlCn4KgiuEJBh7DSzQ%3D</t>
         </is>
       </c>
       <c r="V409">
@@ -54134,7 +54134,7 @@
       </c>
       <c r="U410" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/d0e21094-74a9-45e5-8ac5-eb49500d14cf/LaudoITA04-Bemol-2026-SamaraThailineDacioDeAbreu-Assinado.pdf?expires_on=1785445163&amp;signature=FWUxqU8B%2Fb7FLyk7sOKq8aLC99x5rbvJZ04qfxSY1CA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/d0e21094-74a9-45e5-8ac5-eb49500d14cf/LaudoITA04-Bemol-2026-SamaraThailineDacioDeAbreu-Assinado.pdf?expires_on=1785445264&amp;signature=aWBopD%2F5cVHQ99HTCcTnK6EcdBKlFaCJB654MYFrmQQ%3D</t>
         </is>
       </c>
       <c r="V410">
@@ -54261,7 +54261,7 @@
       </c>
       <c r="U411" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/88e11925-d856-4251-a278-0e0caf54b67c/LaudoPA15-Bemol-2026-SandroSantosSilva-Assinado.pdf?expires_on=1785445163&amp;signature=UMVPIPoJVAHYoGB%2Fcf7c5MFvpVbXOJaf%2FcJu4Onh0IY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/88e11925-d856-4251-a278-0e0caf54b67c/LaudoPA15-Bemol-2026-SandroSantosSilva-Assinado.pdf?expires_on=1785445264&amp;signature=eUm9j%2F2T8nDIdpKwrb%2FEMbI9NIy4guUuSjiAb382W2k%3D</t>
         </is>
       </c>
       <c r="V411">
@@ -54379,7 +54379,7 @@
       </c>
       <c r="U412" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f7e1802-680f-4f77-9cf1-8ffa0116a435/Laudo221-Bemol-2025-SaneyPerreiraMoreira-Assinado.pdf?expires_on=1785445163&amp;signature=X5Yhy2t7gKEA3EoeT6VGHo7zRo%2BqeZMecLckfOi7%2FEU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8f7e1802-680f-4f77-9cf1-8ffa0116a435/Laudo221-Bemol-2025-SaneyPerreiraMoreira-Assinado.pdf?expires_on=1785445264&amp;signature=jLsd4BCHTjClKdNGgzRZO8dp%2FV8Nb3GsZk3nyXmKZkQ%3D</t>
         </is>
       </c>
       <c r="V412">
@@ -54512,7 +54512,7 @@
       </c>
       <c r="U413" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b1180a14-7c3a-47a5-b612-5b52b17ccc68/BEMOL-PV078-SARACOELHODASILVA.pdf?expires_on=1785445163&amp;signature=OpjtQnY2Ty9EZxmUCMJ3fbeCPyc4F7DFBvvSvJsLz%2BM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b1180a14-7c3a-47a5-b612-5b52b17ccc68/BEMOL-PV078-SARACOELHODASILVA.pdf?expires_on=1785445264&amp;signature=TY%2FiVZZ8cq7M%2BU%2BN96khLfWi3Pc%2BerTZv8If1eg6MxI%3D</t>
         </is>
       </c>
       <c r="V413">
@@ -54647,7 +54647,7 @@
       </c>
       <c r="U414" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f4aa410b-2d99-41a0-bed4-291a2b831b82/LAUDOSEBASTIANA.pdf?expires_on=1785445163&amp;signature=gY25HRN4XQh1JBRYviI0xhgt297xChCfj0anErJe2mA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f4aa410b-2d99-41a0-bed4-291a2b831b82/LAUDOSEBASTIANA.pdf?expires_on=1785445264&amp;signature=vZGpbe%2BceLgMsZ2NzqIilk5SkKj9Tt6csSrioiTLBvk%3D</t>
         </is>
       </c>
       <c r="V414">
@@ -54788,7 +54788,7 @@
       </c>
       <c r="U415" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/295bf843-1893-44fc-be91-ae1169868e73/Laudo370-Bemol-2025-SebastianaTelesReigo-Assinado.pdf?expires_on=1785445163&amp;signature=KYYx9vg0Gk%2Fd7XockZz%2BLGy6biU0zZvnGsOmNGsEmXs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/295bf843-1893-44fc-be91-ae1169868e73/Laudo370-Bemol-2025-SebastianaTelesReigo-Assinado.pdf?expires_on=1785445264&amp;signature=8jfQtT8XLsZCLU45iFOa%2F42WoYHzX7o1t2ipFiIsnCQ%3D</t>
         </is>
       </c>
       <c r="V415">
@@ -54939,7 +54939,7 @@
       </c>
       <c r="U416" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ee251d2d-982d-4234-ad27-bf4b1f07ec1a/BEMOL-PV071-SEBASTIOLUIZBALAREZRIBEIROcorrigido.pdf?expires_on=1785445163&amp;signature=Csh%2BmZqllqm65zKnzctAQ8P%2BMbPOSZgCUziwKHiljwg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ee251d2d-982d-4234-ad27-bf4b1f07ec1a/BEMOL-PV071-SEBASTIOLUIZBALAREZRIBEIROcorrigido.pdf?expires_on=1785445264&amp;signature=qqexmTMeuItwDQBdNp8C%2F7Nbsr4DUGlzawl5LhSwUCk%3D</t>
         </is>
       </c>
       <c r="V416">
@@ -55062,7 +55062,7 @@
       </c>
       <c r="U417" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0687e1f1-9daf-4739-9397-6ba62af1e47b/Laudo75-Bemol-2026-SelbiaCastroDaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=TSUMTam9%2FpjBWC6zadeL6zvkRVDbL3kbpaHq2FTby9o%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0687e1f1-9daf-4739-9397-6ba62af1e47b/Laudo75-Bemol-2026-SelbiaCastroDaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=70qXFIZCXrx4qJ02Bi%2BWhJxsrnABalWwwRmcfKtYj4I%3D</t>
         </is>
       </c>
       <c r="V417">
@@ -55194,7 +55194,7 @@
       </c>
       <c r="U418" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9d71ba3e-6ff9-496b-87ae-85d0fada0632/LaudoITA03-Bemol-2026-SelenaGranaTorres-Assinado.pdf?expires_on=1785445163&amp;signature=glw%2FHEpcm0nj%2Baagdy75gYHPpl5qI6QCl20dIrjza50%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9d71ba3e-6ff9-496b-87ae-85d0fada0632/LaudoITA03-Bemol-2026-SelenaGranaTorres-Assinado.pdf?expires_on=1785445264&amp;signature=%2BA6GYAn2c7yJEMhvcPE0q6Mk%2FP0gPYJ8ClQmDMzbB%2FM%3D</t>
         </is>
       </c>
       <c r="V418">
@@ -55321,7 +55321,7 @@
       </c>
       <c r="U419" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/cb2f3f19-f054-4ffa-a025-85a15cf23aa0/LAUDOSERGIOPIGNATARIcorrigido.pdf?expires_on=1785445163&amp;signature=gK58GNiwWuuApAo7QSet2t4MGfjIQ59P9c3496%2BkusM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/cb2f3f19-f054-4ffa-a025-85a15cf23aa0/LAUDOSERGIOPIGNATARIcorrigido.pdf?expires_on=1785445264&amp;signature=1Tte44jbu%2BEpBsYNZPRH6Nk4Y0n2vKhfvjnF1kbz6m0%3D</t>
         </is>
       </c>
       <c r="V419">
@@ -55461,7 +55461,7 @@
       </c>
       <c r="U420" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/17b00c9d-e198-4b83-9a65-db38245d8064/LaudoJP02-Bemol-2026-SerliBerlandaMoreira_signed.pdf?expires_on=1785445163&amp;signature=BKddF8W93thkW6Wj4Ct%2BUxdiG3%2FFUjGQfmJVfLqKMnE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/17b00c9d-e198-4b83-9a65-db38245d8064/LaudoJP02-Bemol-2026-SerliBerlandaMoreira_signed.pdf?expires_on=1785445264&amp;signature=hE9uEionBMPZTlt7yqw9kQ3CxcgPxjRtvmu1mCqj7ck%3D</t>
         </is>
       </c>
       <c r="V420">
@@ -55585,7 +55585,7 @@
       </c>
       <c r="U421" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/da04e0d4-a624-4cf7-aa2e-f1983fd96999/LaudoMAN03-Bemol-2026-SevanildeBatalhaRabelo-Assinadoajustado.pdf?expires_on=1785445163&amp;signature=%2BaiFxZJatx7o1%2Bay68mUxzbNPVdq9DyFq2cnQfalJqU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/da04e0d4-a624-4cf7-aa2e-f1983fd96999/LaudoMAN03-Bemol-2026-SevanildeBatalhaRabelo-Assinadoajustado.pdf?expires_on=1785445264&amp;signature=miRLz2NKS4969T5A1x5nn6Alnf2GnyfF7t2TtT%2Bno48%3D</t>
         </is>
       </c>
       <c r="V421">
@@ -55703,7 +55703,7 @@
       </c>
       <c r="U422" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/80fb135e-1ea4-4edf-8ec7-a869af2f60d5/Laudo150-Bemol-2026-SeylaPalomaDaSilvaSantos-Assinado.pdf?expires_on=1785445163&amp;signature=arznUsK04i6HViXS7F46GAWI1GqkjocI1Y3DNXUt4zg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/80fb135e-1ea4-4edf-8ec7-a869af2f60d5/Laudo150-Bemol-2026-SeylaPalomaDaSilvaSantos-Assinado.pdf?expires_on=1785445264&amp;signature=z6LBM1uWQqhU7Z%2Bq2J5b2kYkfUOJF5ZlasA%2F79gFE9Y%3D</t>
         </is>
       </c>
       <c r="V422">
@@ -55832,7 +55832,7 @@
       </c>
       <c r="U423" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9cd57cf7-41f8-46f0-b888-22dbaf1a8535/Laudo_AC_34-2026_-_MARIA_FRANCINETE_FERREIRA_DE_ARAUJO_assinado.pdf?expires_on=1785445163&amp;signature=a7dRasWGuhSeN8nIHz3h8GpeKPBRdKVY9I2yiJrvQd8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9cd57cf7-41f8-46f0-b888-22dbaf1a8535/Laudo_AC_34-2026_-_MARIA_FRANCINETE_FERREIRA_DE_ARAUJO_assinado.pdf?expires_on=1785445264&amp;signature=wNUDky4tQoOe98G4MRj0asN7jM1GZ8n%2BsjIvSxzyfIU%3D</t>
         </is>
       </c>
       <c r="V423">
@@ -55964,7 +55964,7 @@
       </c>
       <c r="U424" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/41a84769-915b-4a55-801b-35d061f36cb2/LAUDOSHIRLEYPINTOcorrigido02.pdf?expires_on=1785445163&amp;signature=VXh%2BgZiBMFQ7%2FaCyCVBbpfP67pC09xU8JxfAjVU%2Fwq8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/41a84769-915b-4a55-801b-35d061f36cb2/LAUDOSHIRLEYPINTOcorrigido02.pdf?expires_on=1785445264&amp;signature=L%2BXTbcTGyhQj1LDXDseKbGRSa0nIQO8u2Z5mmDcaHAs%3D</t>
         </is>
       </c>
       <c r="V424">
@@ -56093,7 +56093,7 @@
       </c>
       <c r="U425" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f353c835-99b4-4441-ba6d-3aaf391e2610/Laudo76-Bemol-2026-SidnaReginaDaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=DEEt3uOsrDgNJ5%2B3NDyJ9zUqiAcYa5zZbij4PPsok%2FU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f353c835-99b4-4441-ba6d-3aaf391e2610/Laudo76-Bemol-2026-SidnaReginaDaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=uOUppCvyMiQtLIJD2YMA4d6QHJusGt63bp0aOClbNmM%3D</t>
         </is>
       </c>
       <c r="V425">
@@ -56231,7 +56231,7 @@
       </c>
       <c r="U426" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/47bee4e2-792f-40c2-95a2-f11264c736aa/Laudo_AC_79-2025_assinado.pdf?expires_on=1785445163&amp;signature=g3BnNNgpuZArVu3FsXckXJ9jgh1YWzz4BgASPMYLQQg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/47bee4e2-792f-40c2-95a2-f11264c736aa/Laudo_AC_79-2025_assinado.pdf?expires_on=1785445264&amp;signature=HnBdmQSaHcMo0Tgk2037jVsbfSyF%2FQ4eONOsJNaA0ko%3D</t>
         </is>
       </c>
       <c r="V426">
@@ -56377,7 +56377,7 @@
       </c>
       <c r="U427" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9d741fee-febe-4a5f-bfd5-95c526d57c04/BEMOL-PV072-SILVANAACACIABARBOSADESOUSA.pdf?expires_on=1785445163&amp;signature=q3odG3hodAazDn4H%2BmogGd77DEacHklc4N0RmTSxjv0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9d741fee-febe-4a5f-bfd5-95c526d57c04/BEMOL-PV072-SILVANAACACIABARBOSADESOUSA.pdf?expires_on=1785445264&amp;signature=mG4h2Nn%2FVtgE73TZSGWWkjBF%2B%2F9vs%2BL3eF8O9Nwk%2Blo%3D</t>
         </is>
       </c>
       <c r="V427">
@@ -56500,7 +56500,7 @@
       </c>
       <c r="U428" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7c631f93-1bbc-41c6-9b3c-076fe1bfc2ef/LaudoA05-Bemol-2026-SilvanydeOliveiraSilva_signed.pdf?expires_on=1785445163&amp;signature=6Q6WoqE06IYQe9oYbW8MEuUknUc0vrHSPwC1elZHFxc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7c631f93-1bbc-41c6-9b3c-076fe1bfc2ef/LaudoA05-Bemol-2026-SilvanydeOliveiraSilva_signed.pdf?expires_on=1785445264&amp;signature=FS2%2F0jRTZ%2FAa3zg6x%2F7nYf0xBB4Kdz%2B%2FOt6BSLxM1Jo%3D</t>
         </is>
       </c>
       <c r="V428">
@@ -56623,7 +56623,7 @@
       </c>
       <c r="U429" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6aac0250-33e3-4d15-81b3-af551ead0b44/LaudoA04-Bemol-2026-SimoneSasso_signed.pdf?expires_on=1785445163&amp;signature=UdfxUKTokVd97KJsH%2B1yhpEnf%2BaOSYDd4FZcv1RrHss%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6aac0250-33e3-4d15-81b3-af551ead0b44/LaudoA04-Bemol-2026-SimoneSasso_signed.pdf?expires_on=1785445264&amp;signature=OWfl9WJF3NvfwgZuMjAttVHljLO7ijjwphZKFTFNv00%3D</t>
         </is>
       </c>
       <c r="V429">
@@ -56749,7 +56749,7 @@
       </c>
       <c r="U430" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/ea3193b7-dd76-4be5-a605-36af08e595ce/LaudoP01-Bemol-2026-SionedaCunhaBezerra_signed.pdf?expires_on=1785445163&amp;signature=B349uqhQ0YKM07281BViV%2FLO2qDlSOD52wCa2peVJyI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/ea3193b7-dd76-4be5-a605-36af08e595ce/LaudoP01-Bemol-2026-SionedaCunhaBezerra_signed.pdf?expires_on=1785445264&amp;signature=Ou4yhoD5e4rclI8e4PKfVL5Gm%2BjMdtQ6q6ubqFVV%2BmA%3D</t>
         </is>
       </c>
       <c r="V430">
@@ -56892,7 +56892,7 @@
       </c>
       <c r="U431" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/c8fd31fb-c95b-4bca-997e-643d93bbe519/BEMOL-JP032-SIRLEIRUFINODESOUZA.pdf?expires_on=1785445163&amp;signature=V99O%2FynvOemEbWOraYo8a9HxT369qbRonZtYqzQTx4k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/c8fd31fb-c95b-4bca-997e-643d93bbe519/BEMOL-JP032-SIRLEIRUFINODESOUZA.pdf?expires_on=1785445264&amp;signature=E7QuQvfpTiJXXiQJ0juZfmGWCiO2DuyNEcpRkhYTN0M%3D</t>
         </is>
       </c>
       <c r="V431">
@@ -57031,7 +57031,7 @@
       </c>
       <c r="U432" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/94b84bd4-8b6a-4900-82a8-1389771a95ba/LaudoB14-2026-BEMOL-STHEFESONRONYLIMADASILVA_2.pdf?expires_on=1785445163&amp;signature=GvVjDB3PqdlUnsl133v8fKFqcfIkJW4oWZGcZS3pgAM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/94b84bd4-8b6a-4900-82a8-1389771a95ba/LaudoB14-2026-BEMOL-STHEFESONRONYLIMADASILVA_2.pdf?expires_on=1785445264&amp;signature=Wq3lDi%2BS45PE%2FnV%2FuPWBTffN5x4dHO3Z9f%2Fqq3wsMzk%3D</t>
         </is>
       </c>
       <c r="V432">
@@ -57160,7 +57160,7 @@
       </c>
       <c r="U433" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8a4da409-7bca-4787-ae06-0ba3582bcd45/Laudo45-Bemol-2026-SuelyRolimDosSantos-Assinado.pdf?expires_on=1785445163&amp;signature=bhtaAhSZW0IgZMmXUqvue8wTMREPsScnxYyAMC2RDWQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8a4da409-7bca-4787-ae06-0ba3582bcd45/Laudo45-Bemol-2026-SuelyRolimDosSantos-Assinado.pdf?expires_on=1785445264&amp;signature=A6UvO7QwnYNKKiMsDR0ovwCffMRWD7yUMu1WQWx7bjE%3D</t>
         </is>
       </c>
       <c r="V433">
@@ -57292,7 +57292,7 @@
       </c>
       <c r="U434" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e72ce383-285b-415d-b836-74950b0b511e/LaudoI01-Bemol-2026-SuzeteDaSilvaDeOliveira-Assinado.pdf?expires_on=1785445163&amp;signature=BwQTHfwhvxD%2B7WKQ0jMX0ud8zK%2ByzIUySgMrX1NKDYY%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e72ce383-285b-415d-b836-74950b0b511e/LaudoI01-Bemol-2026-SuzeteDaSilvaDeOliveira-Assinado.pdf?expires_on=1785445264&amp;signature=dgSqByINVuGfKrqOGD7pCfIGGq%2Bdd5GDKBqLna5pxVM%3D</t>
         </is>
       </c>
       <c r="V434">
@@ -57422,7 +57422,7 @@
       </c>
       <c r="U435" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0e4fa01b-528b-49ec-b4a8-5064e3866a36/BEMOL-AR028-TAMELACARVALHOMARQUESDEOLIVEIRA.pdf?expires_on=1785445163&amp;signature=xKrQ1qx%2FaIsQFfybWmi5x%2FDX4tmrexQKh6LZ1NW6xXE%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0e4fa01b-528b-49ec-b4a8-5064e3866a36/BEMOL-AR028-TAMELACARVALHOMARQUESDEOLIVEIRA.pdf?expires_on=1785445264&amp;signature=ELswdTns%2BX%2BiML3hzSFW2thgwN2JTQvZZAVgtZSpMDI%3D</t>
         </is>
       </c>
       <c r="V435">
@@ -57540,7 +57540,7 @@
       </c>
       <c r="U436" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/761162e5-7668-44b1-b13c-ffcc122d7d4a/Laudo128-Bemol-2026-TatianeSoaresDeMagalhaes.pdf?expires_on=1785445163&amp;signature=g4n7k6xY330PWMtQHmNPOj9Uuhacd3KjFSaGXHi6Ilc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/761162e5-7668-44b1-b13c-ffcc122d7d4a/Laudo128-Bemol-2026-TatianeSoaresDeMagalhaes.pdf?expires_on=1785445264&amp;signature=Y3D5Vj7S0wFrf5CA2XitDUsmhtXNRGm1TAHvAYNHS7I%3D</t>
         </is>
       </c>
       <c r="V436">
@@ -57666,7 +57666,7 @@
       </c>
       <c r="U437" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/356cc1cc-ebb3-4036-a919-346d083b5346/Laudo01-Bemol-2026-TayaneMenezesDaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=j5%2Bu8bADswCXuHhpj6dlf7DpzAiQ9XRDHbL1NnX3q%2Bw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/356cc1cc-ebb3-4036-a919-346d083b5346/Laudo01-Bemol-2026-TayaneMenezesDaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=HNlkxQdgS%2BEiY9IxLdLif00An4Ez3OP4e7kUAwZcjO0%3D</t>
         </is>
       </c>
       <c r="V437">
@@ -57792,7 +57792,7 @@
       </c>
       <c r="U438" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/3cd45676-ee86-489d-a025-f11e74827aca/Laudo114-Bemol-2026-ThaizeAlfaiaGuimaraes-Assinado-Ajustado.pdf?expires_on=1785445163&amp;signature=gaV4PSLtb3sgaias6cBhXSoDZc0alYor%2BNcb%2F4merXk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/3cd45676-ee86-489d-a025-f11e74827aca/Laudo114-Bemol-2026-ThaizeAlfaiaGuimaraes-Assinado-Ajustado.pdf?expires_on=1785445264&amp;signature=L82UXAMpitwjxuSNoIA%2FQJYjqS0PoDQO19iW9uvdWYs%3D</t>
         </is>
       </c>
       <c r="V438">
@@ -57923,7 +57923,7 @@
       </c>
       <c r="U439" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2b73c9ad-dc1a-4e85-b4bd-27ab6cea1143/Laudo179-Bemol-2026-ThiagoCruzDosSantos.pdf?expires_on=1785445163&amp;signature=uFGkiB4%2FjTXJacSUol9HtTdvF1npqsvz2%2FO2ZPYO5Yg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2b73c9ad-dc1a-4e85-b4bd-27ab6cea1143/Laudo179-Bemol-2026-ThiagoCruzDosSantos.pdf?expires_on=1785445264&amp;signature=XqXxOgJWL0Mv4UJZ0HGs8ggS3XHwsx5mbmuL0002JCY%3D</t>
         </is>
       </c>
       <c r="V439">
@@ -58046,7 +58046,7 @@
       </c>
       <c r="U440" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e65a6996-22f5-41de-ad7b-61de0a96c55a/LAUDOTHIAGOSILVAcorrigido.pdf?expires_on=1785445163&amp;signature=I587nXGEwYebE2V7IkeFXEqaAkaCnVzaT6Kl5VZ59vk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e65a6996-22f5-41de-ad7b-61de0a96c55a/LAUDOTHIAGOSILVAcorrigido.pdf?expires_on=1785445264&amp;signature=nozU5oPO8f3SLuMBnxYbs6ypLOWH3DtHAizGXjp7xh0%3D</t>
         </is>
       </c>
       <c r="V440">
@@ -58165,7 +58165,7 @@
       </c>
       <c r="U441" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/6aabf93a-1827-4934-913c-773405dad137/d6bee9f9-c4b4-4c19-a69b-8f003ad3d00b.pdf?expires_on=1785445163&amp;signature=F91h%2FZ1IMgQ5xYkxb9mmbfaHy8Z8W7oxW7MirLB7VSw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/6aabf93a-1827-4934-913c-773405dad137/d6bee9f9-c4b4-4c19-a69b-8f003ad3d00b.pdf?expires_on=1785445264&amp;signature=36sxozFY%2FnKMkyZOQ1zmcwXhQYcK1F6pc0HsN95ZyCY%3D</t>
         </is>
       </c>
       <c r="V441">
@@ -58296,7 +58296,7 @@
       </c>
       <c r="U442" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/66fe5fa5-3384-4db8-a60f-c481720be4e7/Laudo476-Bemol-2025-AcadiaMariaPereiraDeAraujo-Assinado11.pdf?expires_on=1785445163&amp;signature=FJpAtKLyyamsSJkctOs%2B1%2BBHVatyVBRHAngQ38r1pwk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/66fe5fa5-3384-4db8-a60f-c481720be4e7/Laudo476-Bemol-2025-AcadiaMariaPereiraDeAraujo-Assinado11.pdf?expires_on=1785445264&amp;signature=ct7mnoOq6GhC9o9U9Dm8z9vj4xi5alM1ihVNjtUs5Vs%3D</t>
         </is>
       </c>
       <c r="V442">
@@ -58419,7 +58419,7 @@
       </c>
       <c r="U443" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/95532b56-07a0-4139-94b3-3991d2e25f88/LAUDOTONNYFRANKCORRIGIDO.pdf?expires_on=1785445163&amp;signature=0VhEBGvTOYSi%2BWmz%2FLOQf8tMdGFWdyj3A%2BHoS8pyJtM%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/95532b56-07a0-4139-94b3-3991d2e25f88/LAUDOTONNYFRANKCORRIGIDO.pdf?expires_on=1785445264&amp;signature=KXA89jgWe8RnT%2B8W5vSj3%2FBtsUd4bFFQRDouCsqUhYo%3D</t>
         </is>
       </c>
       <c r="V443">
@@ -58550,7 +58550,7 @@
       </c>
       <c r="U444" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/34077b3d-5b77-4c70-ab45-6c00e62ef0af/LaudoB20-2026-BEMOL-URSULAERICATRAJANOCORREA.pdf?expires_on=1785445163&amp;signature=3tyMBL6GvKzFlX4Z9oL3oBeFhXicoAY3J9vYhQdv3ew%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/34077b3d-5b77-4c70-ab45-6c00e62ef0af/LaudoB20-2026-BEMOL-URSULAERICATRAJANOCORREA.pdf?expires_on=1785445264&amp;signature=mga3VdoqnBC7xsYPT0iCVWMCYbQwjieh1O%2FtEyj%2F%2Bug%3D</t>
         </is>
       </c>
       <c r="V444">
@@ -58678,7 +58678,7 @@
       </c>
       <c r="U445" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/e0f6c590-e981-43b8-9d2c-ee329972b331/M23-2026-VALCINETE.pdf?expires_on=1785445163&amp;signature=4MGDDQRSpvZqOfEafFPW38G1uFPybh7pLd7hdaZAIXI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/e0f6c590-e981-43b8-9d2c-ee329972b331/M23-2026-VALCINETE.pdf?expires_on=1785445264&amp;signature=AQPqUuqItZ5L7O8ycAnq7F2aWpvHItoygSupM6wBGV0%3D</t>
         </is>
       </c>
       <c r="V445">
@@ -58810,7 +58810,7 @@
       </c>
       <c r="U446" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9a138eb9-54c9-43d9-b935-78e4c16c8c15/Laudo167-Bemol-2026-ValdemirSilvaDeBrito.pdf?expires_on=1785445163&amp;signature=sbZjjJ4GeUOibkdWZdNKwWyXwU0J0miD8a%2FFXqb5CkI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9a138eb9-54c9-43d9-b935-78e4c16c8c15/Laudo167-Bemol-2026-ValdemirSilvaDeBrito.pdf?expires_on=1785445264&amp;signature=uE8kTl2x9OFqAVWk%2FlnmrC%2B9LXL5g0zRfov5zjRbu8Y%3D</t>
         </is>
       </c>
       <c r="V446">
@@ -58947,7 +58947,7 @@
       </c>
       <c r="U447" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f41eb99d-6cd2-41bc-9fe1-8e421b2e451e/Laudo404-Bemol-2025-ValdenoraGomesDaSilva-Assinado.pdf?expires_on=1785445163&amp;signature=pesbPIWqvarQCvHAniGpJhduwl0CGsLxnnVpK6JOUp0%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f41eb99d-6cd2-41bc-9fe1-8e421b2e451e/Laudo404-Bemol-2025-ValdenoraGomesDaSilva-Assinado.pdf?expires_on=1785445264&amp;signature=jnbZjBHAypttfQ7q4ap3f9wRF9MvVm%2F8BOFA7S8E21Y%3D</t>
         </is>
       </c>
       <c r="V447">
@@ -59101,7 +59101,7 @@
       </c>
       <c r="U448" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8aad0ece-7144-40eb-8fbf-765df6d0a86e/Laudo38-Bemol-2026-ValdeteTaveiradePaula-Assinado.pdf?expires_on=1785445163&amp;signature=uofqu1L%2BLpY56vsjVqoSlEC8Bs27FhcChltCyxS7HQU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8aad0ece-7144-40eb-8fbf-765df6d0a86e/Laudo38-Bemol-2026-ValdeteTaveiradePaula-Assinado.pdf?expires_on=1785445264&amp;signature=QAuEgkOlaj5Ulk%2B6cthX%2BVsQrO8Je1WDtGCfG90mYu8%3D</t>
         </is>
       </c>
       <c r="V448">
@@ -59231,7 +59231,7 @@
       </c>
       <c r="U449" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/8b3225ea-031c-40da-b116-331fb129e1dc/LaudoPA13-Bemol-2026-ValdirTeixeiraNascimento-Assinado.pdf?expires_on=1785445163&amp;signature=DLRSwtLa%2B5VdRdmXVnscrJUetA24SZpC%2BHwfzPgnAXg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/8b3225ea-031c-40da-b116-331fb129e1dc/LaudoPA13-Bemol-2026-ValdirTeixeiraNascimento-Assinado.pdf?expires_on=1785445264&amp;signature=EokrMM%2BBJwguvDEQQWylYXttWJxZePDxTp7H0DGjHIw%3D</t>
         </is>
       </c>
       <c r="V449">
@@ -59354,7 +59354,7 @@
       </c>
       <c r="U450" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/edbe4bef-e898-4b85-bb9f-d448777be229/LaudoP06-Bemol-2026-ValeriaPatriciaSouzaCastro_signed.pdf?expires_on=1785445163&amp;signature=Jyi%2BmLb9j5xQuD14hpyAqpZFMfgywRondVjEnZP%2FJLw%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/edbe4bef-e898-4b85-bb9f-d448777be229/LaudoP06-Bemol-2026-ValeriaPatriciaSouzaCastro_signed.pdf?expires_on=1785445264&amp;signature=XV0KsgsPZbyHa6pmUOcUp0wmxvF%2FEusLiMu0bB4i7G8%3D</t>
         </is>
       </c>
       <c r="V450">
@@ -59480,7 +59480,7 @@
       </c>
       <c r="U451" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9a0b236a-d8da-46a1-abde-d03053959c44/LAUDOVALMIR.pdf?expires_on=1785445163&amp;signature=EjXmfTXII2aa%2BhK6v%2FJGy25%2Fo9VIbacPYvvvjeS1grA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9a0b236a-d8da-46a1-abde-d03053959c44/LAUDOVALMIR.pdf?expires_on=1785445264&amp;signature=A7Kg01jJz5vPew7qga6%2FzNOEwbRq0dj5sKtJ7Fmzagw%3D</t>
         </is>
       </c>
       <c r="V451">
@@ -59614,7 +59614,7 @@
       </c>
       <c r="U452" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/9d50de8b-4362-4419-8e11-3e29a2d24ea2/BEMOL-JP037-VANDERLEIFERREIRADASILVA.pdf?expires_on=1785445163&amp;signature=P2qm%2Fts9fGbgjQ3cbaAZtj%2Fudoqtl5mddbttaX82tqU%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/9d50de8b-4362-4419-8e11-3e29a2d24ea2/BEMOL-JP037-VANDERLEIFERREIRADASILVA.pdf?expires_on=1785445264&amp;signature=NXl866BTSLBykrYBycgsvDBw9kTzXpu3lasEuGmryK0%3D</t>
         </is>
       </c>
       <c r="V452">
@@ -59751,7 +59751,7 @@
       </c>
       <c r="U453" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/edfc3c76-b3ac-4b05-85e0-4564e1830f59/LaudoB133-2025-BEMOL-VANDERNAYLATHAINADEOLIVEIRA_2.pdf?expires_on=1785445163&amp;signature=qDGw38wxfCTah8j6rw%2B2ETb7brrQssSwsKnlYk4Vh%2Fc%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/edfc3c76-b3ac-4b05-85e0-4564e1830f59/LaudoB133-2025-BEMOL-VANDERNAYLATHAINADEOLIVEIRA_2.pdf?expires_on=1785445264&amp;signature=wYgdeL4Pzo1NiL3MDoJXp4kr2Bs0PWqNIl4JDrXlWFs%3D</t>
         </is>
       </c>
       <c r="V453">
@@ -59896,7 +59896,7 @@
       </c>
       <c r="U454" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/234aaeae-ef51-42bf-b815-4234ee76a4e1/LAUDOVANDERSON.pdf?expires_on=1785445163&amp;signature=a8zFUcwmYwyH1cqcJrcEYMojkaNMpGOZWoWlCUnpvvk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/234aaeae-ef51-42bf-b815-4234ee76a4e1/LAUDOVANDERSON.pdf?expires_on=1785445264&amp;signature=Fvtd3UjbTw6mdX9m4ryDZrEMknVb91FoYe%2Bov9j3xSU%3D</t>
         </is>
       </c>
       <c r="V454">
@@ -60026,7 +60026,7 @@
       </c>
       <c r="U455" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/12219fa3-41df-4153-929d-be40314484c2/Laudo13-Bemol-2026-VanessaDeSouzaBendaham-Assinado.pdf?expires_on=1785445163&amp;signature=C%2FtA6lFAQZzBaToyIDRIMpWXwFbquYmXCVF2NxHPNXA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/12219fa3-41df-4153-929d-be40314484c2/Laudo13-Bemol-2026-VanessaDeSouzaBendaham-Assinado.pdf?expires_on=1785445264&amp;signature=H%2F8A3RBbWx5H2CEsBlaZdcr4hKMpUT5cafsycFksNls%3D</t>
         </is>
       </c>
       <c r="V455">
@@ -60166,7 +60166,7 @@
       </c>
       <c r="U456" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2aa16e66-6d0c-4794-8d98-59fd6c762a29/Laudo120-Bemol-2026-VanessaDiasAraujo.pdf?expires_on=1785445163&amp;signature=FAp0e4x%2FclwuiTf2Lqle26YTsHlCrBnsHTkqA5q%2BCrA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2aa16e66-6d0c-4794-8d98-59fd6c762a29/Laudo120-Bemol-2026-VanessaDiasAraujo.pdf?expires_on=1785445264&amp;signature=Z7n0lx%2BtQiiauN10z9K%2Bz6pIL15cRLrjJzgqCbCKNhk%3D</t>
         </is>
       </c>
       <c r="V456">
@@ -60303,7 +60303,7 @@
       </c>
       <c r="U457" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/65bd5fcb-023f-4fe5-b52b-064b23146334/Laudo_ITA49_-_Bemol_-_2025_-_Vanessa_Santana_Oda__assinado.pdf?expires_on=1785445163&amp;signature=TF2EF7PYXxkzeLDibZqkQpNF1UHCBcErH2Hl15aHVCI%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/65bd5fcb-023f-4fe5-b52b-064b23146334/Laudo_ITA49_-_Bemol_-_2025_-_Vanessa_Santana_Oda__assinado.pdf?expires_on=1785445264&amp;signature=3JegW%2B0LugCLC3KiCJ4h%2FiOCYIhi7YXFmtTuiBCfK%2B0%3D</t>
         </is>
       </c>
       <c r="V457">
@@ -60449,7 +60449,7 @@
       </c>
       <c r="U458" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a7077da-18e3-4e0a-80f3-e59be7715aaf/BEMOL-AR026-VANILDAGOMESDOSSANTOSDUTRA.pdf?expires_on=1785445163&amp;signature=SiuWFDPLXxqtM5r5%2B7tFAE094VHR%2Fb%2B76R98kD8g7UQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/7a7077da-18e3-4e0a-80f3-e59be7715aaf/BEMOL-AR026-VANILDAGOMESDOSSANTOSDUTRA.pdf?expires_on=1785445264&amp;signature=o2ELGTOgf142Rv50BBLqrPmS1Nf5tX5uTTHpt013Q%2Fo%3D</t>
         </is>
       </c>
       <c r="V458">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="U459" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/eec64e95-f6d9-4d2a-af6a-cb7a4cdc3fa0/LAUDOVENCESLAU.pdf?expires_on=1785445163&amp;signature=GOg1cd9YKo50a0qghKfzkqDueFkeYUzoiFUXZJQgkg8%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/eec64e95-f6d9-4d2a-af6a-cb7a4cdc3fa0/LAUDOVENCESLAU.pdf?expires_on=1785445264&amp;signature=tv4s4w99jYcdBHS3bwYxPx16a3z%2Fa21A8m%2F5Iy4y2yU%3D</t>
         </is>
       </c>
       <c r="V459">
@@ -60726,7 +60726,7 @@
       </c>
       <c r="U460" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/434c6c17-6df9-42c7-a677-ffa3cedd7afa/LaudoPA07-Registro2420-VictorMeloMeza.pdf?expires_on=1785445163&amp;signature=65H9UG%2F2OJftR0%2Bo7YXK1l4XaeAdd6UXSQEKEq0Rxnk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/434c6c17-6df9-42c7-a677-ffa3cedd7afa/LaudoPA07-Registro2420-VictorMeloMeza.pdf?expires_on=1785445264&amp;signature=goJNOoKXcJ%2Bb5VbuHwf13NmfSihEzAUcuM4oI5IzFJ4%3D</t>
         </is>
       </c>
       <c r="V460">
@@ -60850,7 +60850,7 @@
       </c>
       <c r="U461" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/212a6647-ada5-43a8-9109-8f6690ce7685/Laudo143-Bemol-2026-VivaldoDantasDeSouza-Assinado.pdf?expires_on=1785445163&amp;signature=dpp8nciRMYs8avoGzMu%2F%2BqQgthCQ0NT7%2FqtTPN0HYAs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/212a6647-ada5-43a8-9109-8f6690ce7685/Laudo143-Bemol-2026-VivaldoDantasDeSouza-Assinado.pdf?expires_on=1785445264&amp;signature=vqaxms%2BnbjtncPio4Szf5gu3qBLsqq4aScRxHrf3mSI%3D</t>
         </is>
       </c>
       <c r="V461">
@@ -60982,7 +60982,7 @@
       </c>
       <c r="U462" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/76fc2a4f-ddfd-4df9-a469-38010ed513c6/M12-2026-WALDSON.pdf?expires_on=1785445163&amp;signature=PhcrbtmuLcn%2B2hEUxOgIFThfT%2B1mZcRCFJCL48Tgv1k%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/76fc2a4f-ddfd-4df9-a469-38010ed513c6/M12-2026-WALDSON.pdf?expires_on=1785445264&amp;signature=szuTWjQu7xgmqCR31VsqkgdvU6jh3EB2ALWC30d%2Bsb0%3D</t>
         </is>
       </c>
       <c r="V462">
@@ -61132,7 +61132,7 @@
       </c>
       <c r="U463" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b1f1e143-9515-45b9-8724-931e0d2cd46d/Laudo135-Bemol-2026-WalterAndreJunior-Ajustado.pdf?expires_on=1785445163&amp;signature=dAFfl9GsmQwgrXuJgh1uDrOUjBwOtpJAeOsw8%2FnQp2A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b1f1e143-9515-45b9-8724-931e0d2cd46d/Laudo135-Bemol-2026-WalterAndreJunior-Ajustado.pdf?expires_on=1785445264&amp;signature=FPCFBAXNT5feGip7Sh8u7BnNw5Yhg5lHHJRuZMDHWPc%3D</t>
         </is>
       </c>
       <c r="V463">
@@ -61275,7 +61275,7 @@
       </c>
       <c r="U464" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/0483d9d7-9552-49f9-953c-cfacb8ae61e8/Laudo37-Bemol-2026-WashigtonDeOliveiraJunior-Assinadocorrigido.pdf?expires_on=1785445163&amp;signature=Om3jKEUX5SBeKpYdUikc2FWvWIbCspG4KyBD%2FUwqhf4%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/0483d9d7-9552-49f9-953c-cfacb8ae61e8/Laudo37-Bemol-2026-WashigtonDeOliveiraJunior-Assinadocorrigido.pdf?expires_on=1785445264&amp;signature=gsaqB6WcPiIATXUXXuXdE9hyVrxkKhxmuXmQ3HO%2Fiqw%3D</t>
         </is>
       </c>
       <c r="V464">
@@ -61414,7 +61414,7 @@
       </c>
       <c r="U465" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/66793f38-05d7-4092-983e-de03c4f5322a/Laudo_B8-2026-BEMOL-_WASHINGTON_LUIZ_DA_COSTA_MAIA_2_assinado.pdf?expires_on=1785445163&amp;signature=nrT7%2BnZ13uz3Pp3PlQv6d9SgzxyC34BthHC0JcfmSzo%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/66793f38-05d7-4092-983e-de03c4f5322a/Laudo_B8-2026-BEMOL-_WASHINGTON_LUIZ_DA_COSTA_MAIA_2_assinado.pdf?expires_on=1785445264&amp;signature=TygxJ2MNZcyZQ%2BZEqf2fk65Gu1oafkpkKNAD06FY%2Bzw%3D</t>
         </is>
       </c>
       <c r="V465">
@@ -61550,7 +61550,7 @@
       </c>
       <c r="U466" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/25793695-287a-42fb-8443-b3c434461848/BEMOL-AR021-WEFFERERSONGUEDESDASNEVES.pdf?expires_on=1785445163&amp;signature=el04vB6ozgHk92oE00uhyK3OAMMtzbmowssEjZWYYhs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/25793695-287a-42fb-8443-b3c434461848/BEMOL-AR021-WEFFERERSONGUEDESDASNEVES.pdf?expires_on=1785445264&amp;signature=Z%2F4emIAyWsSSGnRW6yMbwo0zU%2FnWUpLcdkLuqddI6cY%3D</t>
         </is>
       </c>
       <c r="V466">
@@ -61681,7 +61681,7 @@
       </c>
       <c r="U467" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/2377cef7-fbe5-4b92-ab2b-6e60c2734f26/Laudo169-Bemol-2026-WilcinayraAlvesFerreira-Assinado.pdf?expires_on=1785445163&amp;signature=vPP8SQwV1mM6GcFzkbI4rZIF3hemNEMJlvk%2BDLXIYgA%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/2377cef7-fbe5-4b92-ab2b-6e60c2734f26/Laudo169-Bemol-2026-WilcinayraAlvesFerreira-Assinado.pdf?expires_on=1785445264&amp;signature=cG9ci6sQcUAtuz8WN%2FYqtRMLWcnsR%2BYHTcAKAptzSUQ%3D</t>
         </is>
       </c>
       <c r="V467">
@@ -61810,7 +61810,7 @@
       </c>
       <c r="U468" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/65f4ad93-8dfd-4569-b462-b3eb04df94d4/BEMOL-JP043-WILSONCEZARPELLIZZETTI.pdf?expires_on=1785445163&amp;signature=EIvoo4JR%2BZccMqN7Z7zFNpoQkNWNfDvtnZmvOvhl6QQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/65f4ad93-8dfd-4569-b462-b3eb04df94d4/BEMOL-JP043-WILSONCEZARPELLIZZETTI.pdf?expires_on=1785445264&amp;signature=RMmTx7RB3H4xNxSPcruPVHAXf8WJL%2FxBpc3KnMYHnUA%3D</t>
         </is>
       </c>
       <c r="V468">
@@ -61936,7 +61936,7 @@
       </c>
       <c r="U469" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/b260852b-4031-40bb-acf9-66ddccb26be5/BEMOL-AR30-WilsonCludioMelodaSilva.pdf?expires_on=1785445163&amp;signature=ydNA%2FayrYlltAz0UJ%2F0W6uD91k3MrNl8n%2Bx4cBH%2BMuQ%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/b260852b-4031-40bb-acf9-66ddccb26be5/BEMOL-AR30-WilsonCludioMelodaSilva.pdf?expires_on=1785445264&amp;signature=4FN3xSq2Dq35Bo5u7PQ9zfE8cFwUNJzQC8IjRm9SdMM%3D</t>
         </is>
       </c>
       <c r="V469">
@@ -62067,7 +62067,7 @@
       </c>
       <c r="U470" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/be15b9fd-6153-4e68-83ea-86d15b3aa336/LAUDOWILSONFERREIRANOGUEIRAcorrigido.pdf?expires_on=1785445163&amp;signature=U28bod%2Fvwe%2BxvW3nGn4r8lo57NDyhj%2F10ab4yAMkHbk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/be15b9fd-6153-4e68-83ea-86d15b3aa336/LAUDOWILSONFERREIRANOGUEIRAcorrigido.pdf?expires_on=1785445264&amp;signature=O8wgMDlmPfM%2FGjn2HIkNttobUN0wiTS7zsoQTg%2BX1uY%3D</t>
         </is>
       </c>
       <c r="V470">
@@ -62209,7 +62209,7 @@
       </c>
       <c r="U471" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/4ac0d4ec-18c5-4f4c-8a4f-3f41f84ae112/Laudo_AC_75-2025_assinado.pdf?expires_on=1785445163&amp;signature=EAxNYKhReJDkEWgA9s2XpmqdzaKwRJjBC5quwERYYCg%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/4ac0d4ec-18c5-4f4c-8a4f-3f41f84ae112/Laudo_AC_75-2025_assinado.pdf?expires_on=1785445264&amp;signature=WMUnbNl1MZWEApcdOGwk3QFdXD4r0FVxG7kcEAQWfgM%3D</t>
         </is>
       </c>
       <c r="V471">
@@ -62335,7 +62335,7 @@
       </c>
       <c r="U472" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/f347b2e6-6687-4e4a-a567-9cb2929f140e/LaudoP24-Bemol-2026-YlenGrangeiroAtallah_signed.pdf?expires_on=1785445163&amp;signature=4%2B3IpRAa3mx45ClPSdQA9%2FqoNtvxGeHSBjZH4cj239A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/f347b2e6-6687-4e4a-a567-9cb2929f140e/LaudoP24-Bemol-2026-YlenGrangeiroAtallah_signed.pdf?expires_on=1785445264&amp;signature=vm8Z2EiqOUpmcf1lyuvkmJFCr%2FdhePB2HixO7w91s7I%3D</t>
         </is>
       </c>
       <c r="V472">
@@ -62461,7 +62461,7 @@
       </c>
       <c r="U473" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/767c8ba7-7ed6-43db-a195-03bc90974a81/LAUDOYVELISEPREZBRAGA.pdf?expires_on=1785445163&amp;signature=a3%2FLUTD%2FLcYImR3D5xLw%2F%2BsAAndPChwY01u0tX2qHSk%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/767c8ba7-7ed6-43db-a195-03bc90974a81/LAUDOYVELISEPREZBRAGA.pdf?expires_on=1785445264&amp;signature=XF3e9ukRIBmmSaSEeyZTXFwjRJ0BETKZLogkCG66EIo%3D</t>
         </is>
       </c>
       <c r="V473">
@@ -62604,7 +62604,7 @@
       </c>
       <c r="U474" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/770e1a99-8e08-4872-8418-9ff246a1ab84/LAUDOZIZAcorrigido03.pdf?expires_on=1785445163&amp;signature=77LsHqk%2BY27vO9UnKIXYz8TEJUJrzCBrNOIL2CUun2A%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/770e1a99-8e08-4872-8418-9ff246a1ab84/LAUDOZIZAcorrigido03.pdf?expires_on=1785445264&amp;signature=cveh4JYmgtk7PT1rpAQTcaWrOnv9Pp9kbsmEm%2Fj1ZbI%3D</t>
         </is>
       </c>
       <c r="V474">
@@ -62736,7 +62736,7 @@
       </c>
       <c r="U475" t="inlineStr">
         <is>
-          <t>https://app.pipefy.com/storage/v1/signed/uploads/47448835-9a16-4629-9847-5fda1c53be58/M9-2026-ZULEIDE.pdf?expires_on=1785445163&amp;signature=I0waGB4kzl3QaqUZJCJkpjphNJhlNMd%2FxwuUESrlgSs%3D</t>
+          <t>https://app.pipefy.com/storage/v1/signed/uploads/47448835-9a16-4629-9847-5fda1c53be58/M9-2026-ZULEIDE.pdf?expires_on=1785445264&amp;signature=Cvccr5MDI1sicRRYu04JY3FhNXTtzz0rE5nCsrCZd%2Fc%3D</t>
         </is>
       </c>
       <c r="V475">
